--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10831" uniqueCount="7990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10834" uniqueCount="7991">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -22789,6 +22789,9 @@
   </si>
   <si>
     <t xml:space="preserve">北宋开宝四年（971）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">益州</t>
   </si>
   <si>
     <t xml:space="preserve">我国首次刊刻“大藏经”。</t>
@@ -23081,6 +23084,15 @@
     <t xml:space="preserve">雍正帝亲自挂帅，担任“编委会主编”。 </t>
   </si>
   <si>
+    <t xml:space="preserve">《龙藏》的由来及其不平凡的编修背景</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公众号-中国文物报-李子裔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -23220,12 +23232,6 @@
       </rPr>
       <t xml:space="preserve">日，雍正去世）</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">公众号-中国文物报-李子裔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27</t>
   </si>
   <si>
     <r>
@@ -25523,35 +25529,6 @@
     <t xml:space="preserve">https://www.zsodl.cn/zjwh/1395.jhtml</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">新中国</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">第三次重印</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">2009年 </t>
   </si>
   <si>
@@ -25723,7 +25700,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">第三次重印后捐赠情况</t>
+      <t xml:space="preserve">第二次重印后捐赠情况</t>
     </r>
   </si>
   <si>
@@ -26534,7 +26511,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">第三次重印后雕版修复入藏</t>
+      <t xml:space="preserve">第二次重印后雕版修复入藏</t>
     </r>
   </si>
   <si>
@@ -28872,7 +28849,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -28907,6 +28884,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
   </fills>
@@ -29104,7 +29087,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29393,6 +29376,14 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29450,7 +29441,7 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF4000"/>
@@ -82420,7 +82411,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:AD163"/>
+  <dimension ref="A3:AD160"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.85"/>
@@ -82470,64 +82461,66 @@
       <c r="A7" s="28" t="s">
         <v>7465</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="28" t="s">
+        <v>7466</v>
+      </c>
       <c r="C7" s="43" t="s">
-        <v>7466</v>
+        <v>7467</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>7467</v>
+        <v>7468</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>7468</v>
+        <v>7469</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>7469</v>
+        <v>7470</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>7470</v>
+        <v>7471</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>7471</v>
+        <v>7472</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7472</v>
+        <v>7473</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>7473</v>
+        <v>7474</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>7474</v>
+        <v>7475</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>7475</v>
+        <v>7476</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>7476</v>
+        <v>7477</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>7477</v>
+        <v>7478</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>7479</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7480</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>7475</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>7481</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7477</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>7478</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7479</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>7474</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>7480</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>7476</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>7477</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -82543,56 +82536,56 @@
     </row>
     <row r="12" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>7481</v>
+        <v>7482</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="28"/>
-      <c r="G12" s="1"/>
+      <c r="F12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>7482</v>
+        <v>7483</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>7483</v>
+        <v>7484</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>7484</v>
+        <v>7485</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>7467</v>
+        <v>7468</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>7485</v>
+        <v>7486</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>7469</v>
+        <v>7470</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>7470</v>
+        <v>7471</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="43" t="s">
-        <v>7486</v>
+        <v>7487</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>7487</v>
+        <v>7488</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>7488</v>
+        <v>7489</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>7467</v>
+        <v>7468</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>7489</v>
+        <v>7490</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>7469</v>
+        <v>7470</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>7470</v>
+        <v>7471</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -82604,73 +82597,81 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>7490</v>
+        <v>7491</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>7491</v>
+        <v>7492</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>7492</v>
+        <v>7493</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>7493</v>
-      </c>
-      <c r="G18" s="1"/>
+        <v>7494</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>7495</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>7497</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>7494</v>
+        <v>7498</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>7495</v>
+        <v>7499</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>7496</v>
+        <v>7500</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>7497</v>
+        <v>7501</v>
       </c>
       <c r="F19" s="43" t="s">
-        <v>7498</v>
+        <v>7502</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>7499</v>
+        <v>7503</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>7500</v>
+        <v>7504</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>7501</v>
+        <v>7505</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>7502</v>
+        <v>7506</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
-        <v>7505</v>
+        <v>7507</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
       <c r="D21" s="1" t="s">
-        <v>7506</v>
+        <v>7508</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>7498</v>
+        <v>7502</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>7499</v>
+        <v>7503</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -82682,7 +82683,7 @@
     </row>
     <row r="23" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>7507</v>
+        <v>7509</v>
       </c>
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
@@ -82691,149 +82692,149 @@
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>7508</v>
+        <v>7510</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>7509</v>
+        <v>7511</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>7496</v>
+        <v>7500</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>7510</v>
+        <v>7512</v>
       </c>
       <c r="F24" s="43" t="s">
-        <v>7498</v>
+        <v>7502</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>7499</v>
+        <v>7503</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>7511</v>
+        <v>7513</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>7512</v>
+        <v>7514</v>
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="1" t="s">
-        <v>7513</v>
+        <v>7515</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>7514</v>
+        <v>7516</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>7515</v>
+        <v>7517</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>7516</v>
+        <v>7518</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>7517</v>
+        <v>7519</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>7518</v>
+        <v>7520</v>
       </c>
       <c r="D26" s="28"/>
       <c r="F26" s="28" t="s">
-        <v>7519</v>
+        <v>7521</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>7520</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>7521</v>
+        <v>7523</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>7522</v>
+        <v>7524</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>7523</v>
+        <v>7525</v>
       </c>
       <c r="D27" s="28"/>
       <c r="F27" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>7524</v>
+        <v>7526</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>7525</v>
+        <v>7527</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>7526</v>
+        <v>7528</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>7527</v>
+        <v>7529</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>7528</v>
+        <v>7530</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>7529</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>7530</v>
+        <v>7532</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>7531</v>
+        <v>7533</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>7532</v>
+        <v>7534</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>7533</v>
+        <v>7535</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>7534</v>
+        <v>7536</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>7535</v>
+        <v>7537</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>7536</v>
+        <v>7538</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>7537</v>
+        <v>7539</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28" t="s">
-        <v>7538</v>
+        <v>7540</v>
       </c>
       <c r="D30" s="28"/>
       <c r="F30" s="43" t="s">
-        <v>7528</v>
+        <v>7530</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>7529</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>7539</v>
+        <v>7541</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>7540</v>
+        <v>7542</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -82846,7 +82847,7 @@
     </row>
     <row r="36" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>7541</v>
+        <v>7543</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
@@ -82856,231 +82857,231 @@
     </row>
     <row r="37" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="44" t="s">
-        <v>7542</v>
+        <v>7544</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>7543</v>
+        <v>7545</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>7544</v>
+        <v>7546</v>
       </c>
       <c r="F37" s="45" t="s">
-        <v>7498</v>
+        <v>7502</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>7499</v>
+        <v>7503</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="44" t="s">
-        <v>7545</v>
+        <v>7547</v>
       </c>
       <c r="C38" s="28"/>
       <c r="D38" s="44" t="s">
-        <v>7543</v>
+        <v>7545</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>7546</v>
+        <v>7548</v>
       </c>
       <c r="F38" s="46" t="s">
-        <v>7547</v>
+        <v>7549</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>7548</v>
+        <v>7550</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>7549</v>
+        <v>7551</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>7550</v>
+        <v>7552</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>7551</v>
+        <v>7553</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>7527</v>
+        <v>7529</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>7553</v>
+        <v>7555</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>7528</v>
+        <v>7530</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>7529</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>7554</v>
+        <v>7556</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>7551</v>
+        <v>7553</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>7555</v>
+        <v>7557</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>7556</v>
+        <v>7558</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>7557</v>
+        <v>7559</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>7558</v>
+        <v>7560</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>7559</v>
+        <v>7561</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>7550</v>
+        <v>7552</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>7551</v>
+        <v>7553</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>7560</v>
+        <v>7562</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>7561</v>
+        <v>7563</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>7562</v>
+        <v>7564</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>7563</v>
+        <v>7565</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>7564</v>
+        <v>7566</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="47" t="s">
-        <v>7565</v>
+        <v>7567</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>7566</v>
+        <v>7568</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>7567</v>
+        <v>7569</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>7568</v>
+        <v>7570</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>7547</v>
+        <v>7549</v>
       </c>
       <c r="G44" s="48" t="s">
-        <v>7548</v>
+        <v>7550</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="47" t="s">
-        <v>7569</v>
+        <v>7571</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>7570</v>
+        <v>7572</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>7571</v>
+        <v>7573</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>7572</v>
+        <v>7574</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>7573</v>
+        <v>7575</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>7574</v>
+        <v>7576</v>
       </c>
       <c r="G45" s="48" t="s">
-        <v>7575</v>
+        <v>7577</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>7576</v>
+        <v>7578</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>7577</v>
+        <v>7579</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>7578</v>
+        <v>7580</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>7568</v>
+        <v>7570</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>7547</v>
+        <v>7549</v>
       </c>
       <c r="G46" s="48" t="s">
-        <v>7548</v>
+        <v>7550</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="1" t="s">
-        <v>7579</v>
+        <v>7581</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>7568</v>
+        <v>7570</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>7547</v>
+        <v>7549</v>
       </c>
       <c r="G47" s="48" t="s">
-        <v>7548</v>
+        <v>7550</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>7580</v>
+        <v>7582</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>7581</v>
+        <v>7583</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>7582</v>
+        <v>7584</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>7583</v>
+        <v>7585</v>
       </c>
       <c r="F48" s="28" t="s">
-        <v>7584</v>
+        <v>7586</v>
       </c>
       <c r="G48" s="48" t="s">
-        <v>7585</v>
+        <v>7587</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>7586</v>
+        <v>7588</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7587</v>
+        <v>7589</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>7588</v>
+        <v>7590</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>7589</v>
+        <v>7591</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>7590</v>
+        <v>7592</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>7591</v>
+        <v>7593</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>7592</v>
+        <v>7594</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83088,22 +83089,22 @@
         <v>36795</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>7593</v>
+        <v>7595</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>7594</v>
+        <v>7596</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>7595</v>
+        <v>7597</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>7596</v>
+        <v>7598</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>7597</v>
+        <v>7599</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>7598</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83111,22 +83112,22 @@
         <v>45216</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>7599</v>
+        <v>7601</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>7600</v>
+        <v>7602</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>7601</v>
+        <v>7603</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>7602</v>
+        <v>7604</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>7603</v>
+        <v>7605</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>7604</v>
+        <v>7606</v>
       </c>
     </row>
     <row r="52" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -83134,22 +83135,22 @@
         <v>45458</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>7605</v>
+        <v>7607</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>7606</v>
+        <v>7608</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>7467</v>
+        <v>7468</v>
       </c>
       <c r="E52" s="28" t="s">
-        <v>7607</v>
+        <v>7609</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>7469</v>
+        <v>7470</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>7470</v>
+        <v>7471</v>
       </c>
     </row>
     <row r="54" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -83157,7 +83158,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="28" t="s">
-        <v>7608</v>
+        <v>7610</v>
       </c>
       <c r="B55" s="28"/>
       <c r="C55" s="28"/>
@@ -83166,96 +83167,96 @@
     </row>
     <row r="56" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="28" t="s">
-        <v>7609</v>
+        <v>7611</v>
       </c>
       <c r="B56" s="28" t="s">
-        <v>7610</v>
+        <v>7612</v>
       </c>
       <c r="F56" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="28" t="s">
-        <v>7611</v>
+        <v>7613</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>7612</v>
+        <v>7614</v>
       </c>
       <c r="F57" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="28" t="s">
-        <v>7613</v>
+        <v>7615</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>7614</v>
+        <v>7616</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>7615</v>
+        <v>7617</v>
       </c>
       <c r="F58" s="43" t="s">
-        <v>7535</v>
+        <v>7537</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>7536</v>
+        <v>7538</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="28" t="s">
-        <v>7616</v>
+        <v>7618</v>
       </c>
       <c r="B59" s="28" t="s">
-        <v>7617</v>
+        <v>7619</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>7618</v>
+        <v>7620</v>
       </c>
       <c r="E59" s="28"/>
       <c r="F59" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="28" t="s">
-        <v>7619</v>
+        <v>7621</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>7620</v>
+        <v>7622</v>
       </c>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
       <c r="F60" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="28" t="s">
-        <v>7621</v>
+        <v>7623</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>7622</v>
+        <v>7624</v>
       </c>
       <c r="E61" s="28"/>
       <c r="F61" s="28" t="s">
-        <v>7623</v>
+        <v>7625</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>7624</v>
+        <v>7626</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -83265,137 +83266,137 @@
     </row>
     <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>7625</v>
+        <v>7627</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="43" t="s">
-        <v>7626</v>
+        <v>7628</v>
       </c>
       <c r="B64" s="28" t="s">
-        <v>7627</v>
+        <v>7629</v>
       </c>
       <c r="F64" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="28" t="s">
-        <v>7628</v>
+        <v>7630</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>7629</v>
+        <v>7631</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>7630</v>
+        <v>7632</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>7631</v>
+        <v>7633</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>7632</v>
+        <v>7634</v>
       </c>
       <c r="F65" s="43" t="s">
-        <v>7633</v>
+        <v>7635</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>7634</v>
+        <v>7636</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="28" t="s">
-        <v>7635</v>
+        <v>7637</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>7636</v>
+        <v>7638</v>
       </c>
       <c r="C66" s="28"/>
       <c r="D66" s="43"/>
       <c r="E66" s="28" t="s">
-        <v>7637</v>
+        <v>7639</v>
       </c>
       <c r="F66" s="28" t="s">
-        <v>7519</v>
+        <v>7521</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>7520</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="28" t="s">
-        <v>7638</v>
+        <v>7640</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>7639</v>
+        <v>7641</v>
       </c>
       <c r="C67" s="28"/>
       <c r="D67" s="43"/>
       <c r="E67" s="28"/>
       <c r="F67" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="49" t="s">
-        <v>7640</v>
+        <v>7642</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>7641</v>
+        <v>7643</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>7642</v>
+        <v>7644</v>
       </c>
       <c r="D68" s="43"/>
       <c r="E68" s="28"/>
       <c r="F68" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="49" t="s">
-        <v>7640</v>
+        <v>7642</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>7643</v>
+        <v>7645</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>7644</v>
+        <v>7646</v>
       </c>
       <c r="D69" s="43"/>
       <c r="E69" s="28"/>
       <c r="F69" s="28" t="s">
-        <v>7519</v>
+        <v>7521</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>7520</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="49" t="s">
-        <v>7645</v>
+        <v>7647</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>7646</v>
+        <v>7648</v>
       </c>
       <c r="C70" s="28"/>
       <c r="D70" s="1" t="s">
-        <v>7513</v>
+        <v>7515</v>
       </c>
       <c r="E70" s="28"/>
       <c r="F70" s="28" t="s">
-        <v>7514</v>
+        <v>7516</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>7515</v>
+        <v>7517</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -83408,7 +83409,7 @@
     </row>
     <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="28" t="s">
-        <v>7647</v>
+        <v>7649</v>
       </c>
       <c r="C72" s="28"/>
       <c r="E72" s="28"/>
@@ -83417,59 +83418,59 @@
     </row>
     <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="49" t="s">
-        <v>7648</v>
+        <v>7650</v>
       </c>
       <c r="B73" s="28" t="s">
-        <v>7649</v>
+        <v>7651</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>7650</v>
+        <v>7652</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>7651</v>
+        <v>7653</v>
       </c>
       <c r="F73" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="49" t="s">
-        <v>7652</v>
+        <v>7654</v>
       </c>
       <c r="B74" s="28" t="s">
-        <v>7653</v>
+        <v>7655</v>
       </c>
       <c r="C74" s="28"/>
       <c r="D74" s="1" t="s">
-        <v>7513</v>
+        <v>7515</v>
       </c>
       <c r="E74" s="28"/>
       <c r="F74" s="28" t="s">
-        <v>7514</v>
+        <v>7516</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>7515</v>
+        <v>7517</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="28" t="s">
-        <v>7654</v>
+        <v>7656</v>
       </c>
       <c r="B75" s="28" t="s">
-        <v>7655</v>
+        <v>7657</v>
       </c>
       <c r="C75" s="28"/>
       <c r="E75" s="43" t="s">
-        <v>7656</v>
+        <v>7658</v>
       </c>
       <c r="F75" s="28" t="s">
-        <v>7519</v>
+        <v>7521</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>7520</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -83477,65 +83478,65 @@
         <v>32140</v>
       </c>
       <c r="B76" s="43" t="s">
-        <v>7657</v>
+        <v>7659</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>7658</v>
+        <v>7660</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>7659</v>
+        <v>7661</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>7660</v>
+        <v>7662</v>
       </c>
       <c r="F76" s="43" t="s">
-        <v>7661</v>
+        <v>7663</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>7662</v>
+        <v>7664</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="47" t="s">
-        <v>7663</v>
+        <v>7665</v>
       </c>
       <c r="B77" s="28" t="s">
-        <v>7664</v>
+        <v>7666</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>7665</v>
+        <v>7667</v>
       </c>
       <c r="E77" s="50" t="s">
-        <v>7666</v>
+        <v>7668</v>
       </c>
       <c r="F77" s="43" t="s">
-        <v>7535</v>
+        <v>7537</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>7536</v>
+        <v>7538</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="47" t="s">
-        <v>7667</v>
+        <v>7669</v>
       </c>
       <c r="B78" s="28" t="s">
-        <v>7655</v>
+        <v>7657</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>7668</v>
+        <v>7670</v>
       </c>
       <c r="D78" s="43" t="s">
-        <v>7669</v>
+        <v>7671</v>
       </c>
       <c r="E78" s="28" t="s">
-        <v>7670</v>
+        <v>7672</v>
       </c>
       <c r="F78" s="28" t="s">
-        <v>7519</v>
+        <v>7521</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>7520</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -83543,20 +83544,20 @@
         <v>32471</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>7671</v>
+        <v>7673</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>7672</v>
+        <v>7674</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>7673</v>
+        <v>7675</v>
       </c>
       <c r="E79" s="50"/>
       <c r="F79" s="43" t="s">
-        <v>7633</v>
+        <v>7635</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>7634</v>
+        <v>7636</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83564,20 +83565,20 @@
         <v>32471</v>
       </c>
       <c r="B80" s="28" t="s">
-        <v>7674</v>
+        <v>7676</v>
       </c>
       <c r="C80" s="28" t="s">
-        <v>7675</v>
+        <v>7677</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>7676</v>
+        <v>7678</v>
       </c>
       <c r="E80" s="28"/>
       <c r="F80" s="1" t="s">
-        <v>7677</v>
+        <v>7679</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>7678</v>
+        <v>7680</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83585,20 +83586,20 @@
         <v>32471</v>
       </c>
       <c r="B81" s="28" t="s">
-        <v>7679</v>
+        <v>7681</v>
       </c>
       <c r="C81" s="28" t="s">
-        <v>7680</v>
+        <v>7682</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>7681</v>
+        <v>7683</v>
       </c>
       <c r="E81" s="28"/>
       <c r="F81" s="28" t="s">
-        <v>7661</v>
+        <v>7663</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>7682</v>
+        <v>7684</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83606,22 +83607,22 @@
         <v>32471</v>
       </c>
       <c r="B82" s="28" t="s">
-        <v>7679</v>
+        <v>7681</v>
       </c>
       <c r="C82" s="28" t="s">
+        <v>7685</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>7683</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>7681</v>
-      </c>
       <c r="E82" s="28" t="s">
-        <v>7684</v>
+        <v>7686</v>
       </c>
       <c r="F82" s="28" t="s">
-        <v>7519</v>
+        <v>7521</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>7520</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83629,157 +83630,157 @@
         <v>32517</v>
       </c>
       <c r="B83" s="28" t="s">
-        <v>7685</v>
+        <v>7687</v>
       </c>
       <c r="C83" s="28" t="s">
-        <v>7587</v>
+        <v>7589</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>7686</v>
+        <v>7688</v>
       </c>
       <c r="E83" s="28"/>
       <c r="F83" s="1" t="s">
-        <v>7591</v>
+        <v>7593</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>7592</v>
+        <v>7594</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="47"/>
       <c r="B84" s="28" t="s">
-        <v>7687</v>
+        <v>7689</v>
       </c>
       <c r="C84" s="28"/>
       <c r="D84" s="28"/>
       <c r="E84" s="28"/>
       <c r="F84" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="47" t="s">
-        <v>7688</v>
+        <v>7690</v>
       </c>
       <c r="B85" s="28" t="s">
-        <v>7689</v>
+        <v>7691</v>
       </c>
       <c r="C85" s="28" t="s">
-        <v>7690</v>
+        <v>7692</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>7513</v>
+        <v>7515</v>
       </c>
       <c r="E85" s="28"/>
       <c r="F85" s="28" t="s">
-        <v>7514</v>
+        <v>7516</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>7515</v>
+        <v>7517</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="47" t="s">
-        <v>7691</v>
+        <v>7693</v>
       </c>
       <c r="B86" s="28" t="s">
-        <v>7655</v>
+        <v>7657</v>
       </c>
       <c r="C86" s="28" t="s">
-        <v>7668</v>
+        <v>7670</v>
       </c>
       <c r="D86" s="43" t="s">
-        <v>7669</v>
+        <v>7671</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>7692</v>
+        <v>7694</v>
       </c>
       <c r="F86" s="28" t="s">
-        <v>7519</v>
+        <v>7521</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>7520</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="47" t="s">
-        <v>7693</v>
+        <v>7695</v>
       </c>
       <c r="B87" s="28" t="s">
-        <v>7694</v>
+        <v>7696</v>
       </c>
       <c r="C87" s="28"/>
       <c r="D87" s="43" t="s">
-        <v>7669</v>
+        <v>7671</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>7695</v>
+        <v>7697</v>
       </c>
       <c r="F87" s="28" t="s">
-        <v>7519</v>
+        <v>7521</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>7520</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="47" t="s">
-        <v>7696</v>
+        <v>7698</v>
       </c>
       <c r="B88" s="28" t="s">
-        <v>7697</v>
+        <v>7699</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>7698</v>
+        <v>7700</v>
       </c>
       <c r="D88" s="43" t="s">
-        <v>7669</v>
+        <v>7671</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>7699</v>
+        <v>7701</v>
       </c>
       <c r="F88" s="28" t="s">
-        <v>7519</v>
+        <v>7521</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>7520</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="43" t="s">
-        <v>7700</v>
+        <v>7702</v>
       </c>
       <c r="B89" s="28" t="s">
-        <v>7701</v>
+        <v>7703</v>
       </c>
       <c r="D89" s="43" t="s">
-        <v>7702</v>
+        <v>7704</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>7703</v>
+        <v>7705</v>
       </c>
       <c r="F89" s="51" t="s">
-        <v>7704</v>
+        <v>7706</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>7705</v>
+        <v>7707</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="49" t="s">
-        <v>7706</v>
+        <v>7708</v>
       </c>
       <c r="B90" s="28" t="s">
-        <v>7707</v>
+        <v>7709</v>
       </c>
       <c r="F90" s="43" t="s">
-        <v>7503</v>
+        <v>7496</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>7504</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -83787,7 +83788,7 @@
     </row>
     <row r="92" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="43" t="s">
-        <v>7708</v>
+        <v>7710</v>
       </c>
       <c r="B92" s="28"/>
       <c r="D92" s="43"/>
@@ -83800,1331 +83801,1322 @@
         <v>38164</v>
       </c>
       <c r="B93" s="43" t="s">
-        <v>7709</v>
+        <v>7711</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>7710</v>
+        <v>7712</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>7711</v>
+        <v>7713</v>
       </c>
       <c r="E93" s="28" t="s">
-        <v>7712</v>
+        <v>7714</v>
       </c>
       <c r="F93" s="28" t="s">
-        <v>7713</v>
+        <v>7715</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>7714</v>
+        <v>7716</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="47" t="s">
-        <v>7715</v>
+        <v>7717</v>
       </c>
       <c r="B94" s="52" t="s">
-        <v>7716</v>
+        <v>7718</v>
       </c>
       <c r="C94" s="52" t="s">
-        <v>7717</v>
+        <v>7719</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>7718</v>
+        <v>7720</v>
       </c>
       <c r="E94" s="49" t="s">
-        <v>7719</v>
+        <v>7721</v>
       </c>
       <c r="F94" s="28" t="s">
-        <v>7720</v>
+        <v>7722</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>7721</v>
+        <v>7723</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="47" t="s">
+        <v>7724</v>
+      </c>
+      <c r="B95" s="43" t="s">
+        <v>7725</v>
+      </c>
+      <c r="C95" s="28" t="s">
+        <v>7726</v>
+      </c>
+      <c r="D95" s="43" t="s">
+        <v>7727</v>
+      </c>
+      <c r="E95" s="43"/>
+      <c r="F95" s="43" t="s">
+        <v>7502</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>7503</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="47" t="s">
+        <v>7724</v>
+      </c>
+      <c r="B96" s="28" t="s">
+        <v>7728</v>
+      </c>
+      <c r="C96" s="28" t="s">
+        <v>7729</v>
+      </c>
+      <c r="D96" s="28" t="s">
+        <v>7730</v>
+      </c>
+      <c r="E96" s="28" t="s">
+        <v>7731</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>7732</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>7733</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="43" t="s">
-        <v>7722</v>
-      </c>
-      <c r="C97" s="28"/>
-      <c r="D97" s="43"/>
+      <c r="A97" s="47" t="s">
+        <v>7734</v>
+      </c>
+      <c r="B97" s="28" t="s">
+        <v>7728</v>
+      </c>
+      <c r="C97" s="28" t="s">
+        <v>7735</v>
+      </c>
+      <c r="D97" s="28" t="s">
+        <v>7736</v>
+      </c>
       <c r="E97" s="28"/>
-      <c r="F97" s="28"/>
-      <c r="G97" s="2"/>
-    </row>
-    <row r="98" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="47" t="s">
-        <v>7723</v>
-      </c>
-      <c r="B98" s="43" t="s">
-        <v>7724</v>
+      <c r="F97" s="1" t="s">
+        <v>7732</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>7733</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="47" t="n">
+        <v>42230</v>
+      </c>
+      <c r="B98" s="28" t="s">
+        <v>7728</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>7725</v>
-      </c>
-      <c r="D98" s="43" t="s">
-        <v>7726</v>
-      </c>
-      <c r="E98" s="43"/>
-      <c r="F98" s="43" t="s">
-        <v>7498</v>
+        <v>7737</v>
+      </c>
+      <c r="D98" s="28" t="s">
+        <v>7738</v>
+      </c>
+      <c r="E98" s="28" t="s">
+        <v>7739</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>7732</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>7499</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="47" t="s">
-        <v>7723</v>
-      </c>
-      <c r="B99" s="28" t="s">
-        <v>7727</v>
-      </c>
-      <c r="C99" s="28" t="s">
-        <v>7728</v>
-      </c>
-      <c r="D99" s="28" t="s">
-        <v>7729</v>
-      </c>
-      <c r="E99" s="28" t="s">
-        <v>7730</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>7731</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>7732</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="47" t="s">
         <v>7733</v>
       </c>
-      <c r="B100" s="28" t="s">
-        <v>7727</v>
-      </c>
-      <c r="C100" s="28" t="s">
-        <v>7734</v>
-      </c>
-      <c r="D100" s="28" t="s">
-        <v>7735</v>
-      </c>
-      <c r="E100" s="28"/>
-      <c r="F100" s="1" t="s">
-        <v>7731</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>7732</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="99" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="43" t="s">
+        <v>7740</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="47" t="n">
-        <v>42230</v>
-      </c>
-      <c r="B101" s="28" t="s">
-        <v>7727</v>
-      </c>
-      <c r="C101" s="28" t="s">
-        <v>7736</v>
-      </c>
-      <c r="D101" s="28" t="s">
-        <v>7737</v>
-      </c>
-      <c r="E101" s="28" t="s">
-        <v>7738</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>7731</v>
+        <v>42753</v>
+      </c>
+      <c r="B101" s="52" t="s">
+        <v>7741</v>
+      </c>
+      <c r="C101" s="43" t="s">
+        <v>7742</v>
+      </c>
+      <c r="D101" s="43" t="s">
+        <v>7743</v>
+      </c>
+      <c r="E101" s="43" t="s">
+        <v>7744</v>
+      </c>
+      <c r="F101" s="43" t="s">
+        <v>7502</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>7732</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="43" t="s">
-        <v>7739</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7503</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="47" t="n">
+        <v>42753</v>
+      </c>
+      <c r="B102" s="52" t="s">
+        <v>7745</v>
+      </c>
+      <c r="C102" s="28" t="s">
+        <v>7746</v>
+      </c>
+      <c r="D102" s="43" t="s">
+        <v>7743</v>
+      </c>
+      <c r="E102" s="53" t="s">
+        <v>7747</v>
+      </c>
+      <c r="F102" s="43" t="s">
+        <v>7502</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>7503</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="47" t="n">
+        <v>42753</v>
+      </c>
+      <c r="B103" s="52" t="s">
+        <v>7745</v>
+      </c>
+      <c r="C103" s="52" t="s">
+        <v>7748</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>7749</v>
+      </c>
+      <c r="E103" s="43" t="s">
+        <v>7750</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>7751</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>7752</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="47" t="n">
-        <v>42753</v>
-      </c>
-      <c r="B104" s="52" t="s">
-        <v>7740</v>
-      </c>
-      <c r="C104" s="43" t="s">
-        <v>7741</v>
-      </c>
-      <c r="D104" s="43" t="s">
-        <v>7742</v>
-      </c>
-      <c r="E104" s="43" t="s">
-        <v>7743</v>
-      </c>
-      <c r="F104" s="43" t="s">
-        <v>7498</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>7499</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>43725</v>
+      </c>
+      <c r="B104" s="28" t="s">
+        <v>7753</v>
+      </c>
+      <c r="C104" s="28" t="s">
+        <v>7754</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>7755</v>
+      </c>
+      <c r="E104" s="28" t="s">
+        <v>7756</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>7757</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>7758</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="47" t="n">
-        <v>42753</v>
-      </c>
-      <c r="B105" s="52" t="s">
-        <v>7744</v>
+        <v>44895</v>
+      </c>
+      <c r="B105" s="28" t="s">
+        <v>7759</v>
       </c>
       <c r="C105" s="28" t="s">
-        <v>7745</v>
+        <v>7760</v>
       </c>
       <c r="D105" s="43" t="s">
-        <v>7742</v>
-      </c>
-      <c r="E105" s="53" t="s">
-        <v>7746</v>
-      </c>
-      <c r="F105" s="43" t="s">
-        <v>7498</v>
+        <v>7761</v>
+      </c>
+      <c r="E105" s="28" t="s">
+        <v>7762</v>
+      </c>
+      <c r="F105" s="28" t="s">
+        <v>7763</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>7499</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7764</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="47" t="n">
-        <v>42753</v>
-      </c>
-      <c r="B106" s="52" t="s">
-        <v>7744</v>
-      </c>
-      <c r="C106" s="52" t="s">
-        <v>7747</v>
+        <v>45449</v>
+      </c>
+      <c r="B106" s="28" t="s">
+        <v>7765</v>
+      </c>
+      <c r="C106" s="28" t="s">
+        <v>7766</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>7748</v>
-      </c>
-      <c r="E106" s="43" t="s">
-        <v>7749</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>7750</v>
+        <v>7767</v>
+      </c>
+      <c r="E106" s="28" t="s">
+        <v>7768</v>
+      </c>
+      <c r="F106" s="28" t="s">
+        <v>7769</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>7751</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="47" t="n">
-        <v>43725</v>
+        <v>46017</v>
       </c>
       <c r="B107" s="28" t="s">
-        <v>7752</v>
+        <v>7771</v>
       </c>
       <c r="C107" s="28" t="s">
-        <v>7753</v>
+        <v>7772</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>7754</v>
+        <v>7773</v>
       </c>
       <c r="E107" s="28" t="s">
-        <v>7755</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>7756</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>7757</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="47" t="n">
-        <v>44895</v>
-      </c>
-      <c r="B108" s="28" t="s">
-        <v>7758</v>
-      </c>
-      <c r="C108" s="28" t="s">
-        <v>7759</v>
-      </c>
-      <c r="D108" s="43" t="s">
-        <v>7760</v>
-      </c>
-      <c r="E108" s="28" t="s">
-        <v>7761</v>
-      </c>
-      <c r="F108" s="28" t="s">
-        <v>7762</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>7763</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="47" t="n">
-        <v>45449</v>
-      </c>
-      <c r="B109" s="28" t="s">
-        <v>7764</v>
-      </c>
-      <c r="C109" s="28" t="s">
-        <v>7765</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>7766</v>
-      </c>
-      <c r="E109" s="28" t="s">
-        <v>7767</v>
-      </c>
-      <c r="F109" s="28" t="s">
-        <v>7768</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>7769</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="47" t="n">
-        <v>46017</v>
-      </c>
-      <c r="B110" s="28" t="s">
-        <v>7770</v>
-      </c>
-      <c r="C110" s="28" t="s">
-        <v>7771</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>7772</v>
-      </c>
-      <c r="E110" s="28" t="s">
-        <v>7773</v>
-      </c>
-      <c r="F110" s="28" t="s">
         <v>7774</v>
       </c>
-      <c r="G110" s="2" t="s">
+      <c r="F107" s="28" t="s">
         <v>7775</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="47"/>
+      <c r="G107" s="2" t="s">
+        <v>7776</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="47"/>
+      <c r="B108" s="28"/>
+      <c r="C108" s="28"/>
+      <c r="E108" s="28"/>
+      <c r="F108" s="28"/>
+      <c r="G108" s="2"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="47"/>
+      <c r="B110" s="28"/>
+      <c r="C110" s="28"/>
+      <c r="E110" s="28"/>
+      <c r="F110" s="28"/>
+      <c r="G110" s="2"/>
+    </row>
+    <row r="111" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="43" t="s">
+        <v>7777</v>
+      </c>
       <c r="B111" s="28"/>
       <c r="C111" s="28"/>
       <c r="E111" s="28"/>
       <c r="F111" s="28"/>
       <c r="G111" s="2"/>
     </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="47"/>
-      <c r="B113" s="28"/>
-      <c r="C113" s="28"/>
-      <c r="E113" s="28"/>
-      <c r="F113" s="28"/>
-      <c r="G113" s="2"/>
-    </row>
-    <row r="114" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="43" t="s">
-        <v>7776</v>
-      </c>
-      <c r="B114" s="28"/>
-      <c r="C114" s="28"/>
-      <c r="E114" s="28"/>
-      <c r="F114" s="28"/>
-      <c r="G114" s="2"/>
-    </row>
-    <row r="115" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="54" t="s">
+        <v>7778</v>
+      </c>
+      <c r="B112" s="43" t="s">
+        <v>7779</v>
+      </c>
+      <c r="C112" s="28" t="s">
+        <v>7780</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="E112" s="28" t="s">
+        <v>7705</v>
+      </c>
+      <c r="F112" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="54" t="s">
+        <v>7781</v>
+      </c>
+      <c r="B113" s="43" t="s">
+        <v>7782</v>
+      </c>
+      <c r="C113" s="28" t="s">
+        <v>7783</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>7784</v>
+      </c>
+      <c r="F113" s="51" t="s">
+        <v>7706</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>7707</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="49" t="s">
+        <v>7785</v>
+      </c>
+      <c r="B114" s="52" t="s">
+        <v>7786</v>
+      </c>
+      <c r="C114" s="28" t="s">
+        <v>7787</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="F114" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="54" t="s">
-        <v>7777</v>
-      </c>
-      <c r="B115" s="43" t="s">
-        <v>7778</v>
+        <v>7788</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>7789</v>
       </c>
       <c r="C115" s="28" t="s">
-        <v>7779</v>
+        <v>7790</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>7513</v>
+        <v>7515</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>7703</v>
+        <v>7791</v>
       </c>
       <c r="F115" s="28" t="s">
-        <v>7514</v>
+        <v>7516</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>7515</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="54" t="s">
-        <v>7780</v>
-      </c>
-      <c r="B116" s="43" t="s">
-        <v>7781</v>
+        <v>7792</v>
+      </c>
+      <c r="B116" s="28" t="s">
+        <v>7793</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>7782</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>7783</v>
-      </c>
-      <c r="F116" s="51" t="s">
-        <v>7704</v>
+        <v>7794</v>
+      </c>
+      <c r="E116" s="28"/>
+      <c r="F116" s="28" t="s">
+        <v>7516</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>7705</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="49" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="54" t="s">
+        <v>7795</v>
+      </c>
+      <c r="B117" s="28" t="s">
+        <v>7796</v>
+      </c>
+      <c r="C117" s="28" t="s">
+        <v>7797</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>7784</v>
       </c>
-      <c r="B117" s="52" t="s">
-        <v>7785</v>
-      </c>
-      <c r="C117" s="28" t="s">
-        <v>7786</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>7513</v>
-      </c>
-      <c r="F117" s="28" t="s">
-        <v>7514</v>
+      <c r="E117" s="1" t="s">
+        <v>7798</v>
+      </c>
+      <c r="F117" s="51" t="s">
+        <v>7706</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>7515</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="54" t="s">
-        <v>7787</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>7788</v>
-      </c>
-      <c r="C118" s="28" t="s">
-        <v>7789</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>7513</v>
+        <v>7707</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="47" t="n">
+        <v>44662</v>
+      </c>
+      <c r="B118" s="28" t="s">
+        <v>7799</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>7800</v>
+      </c>
+      <c r="D118" s="28" t="s">
+        <v>7801</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>7790</v>
-      </c>
-      <c r="F118" s="28" t="s">
-        <v>7514</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>7515</v>
+        <v>7802</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>7803</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>7804</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="54" t="s">
-        <v>7791</v>
+        <v>7805</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>7792</v>
-      </c>
-      <c r="C119" s="28" t="s">
-        <v>7793</v>
-      </c>
-      <c r="E119" s="28"/>
-      <c r="F119" s="28" t="s">
-        <v>7514</v>
+        <v>7806</v>
+      </c>
+      <c r="C119" s="28"/>
+      <c r="D119" s="1" t="s">
+        <v>7784</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>7807</v>
+      </c>
+      <c r="F119" s="51" t="s">
+        <v>7706</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>7515</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="54" t="s">
-        <v>7794</v>
+        <v>7707</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="47" t="n">
+        <v>44776</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>7795</v>
+        <v>7808</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>7796</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>7783</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>7797</v>
-      </c>
-      <c r="F120" s="51" t="s">
-        <v>7704</v>
+        <v>7809</v>
+      </c>
+      <c r="D120" s="28" t="s">
+        <v>7810</v>
+      </c>
+      <c r="E120" s="28" t="s">
+        <v>7811</v>
+      </c>
+      <c r="F120" s="28" t="s">
+        <v>7812</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>7705</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="47" t="n">
-        <v>44662</v>
-      </c>
-      <c r="B121" s="28" t="s">
-        <v>7798</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>7799</v>
-      </c>
-      <c r="D121" s="28" t="s">
-        <v>7800</v>
-      </c>
-      <c r="E121" s="28" t="s">
-        <v>7801</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>7802</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>7803</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="54" t="s">
-        <v>7804</v>
-      </c>
-      <c r="B122" s="28" t="s">
-        <v>7805</v>
-      </c>
-      <c r="C122" s="28"/>
-      <c r="D122" s="1" t="s">
-        <v>7783</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>7806</v>
-      </c>
-      <c r="F122" s="51" t="s">
-        <v>7704</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>7705</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="47" t="n">
-        <v>44776</v>
-      </c>
-      <c r="B123" s="28" t="s">
-        <v>7807</v>
-      </c>
-      <c r="C123" s="28" t="s">
-        <v>7808</v>
-      </c>
-      <c r="D123" s="28" t="s">
-        <v>7809</v>
-      </c>
-      <c r="E123" s="28" t="s">
-        <v>7810</v>
-      </c>
-      <c r="F123" s="28" t="s">
-        <v>7811</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>7812</v>
-      </c>
-    </row>
-    <row r="126" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="47" t="s">
         <v>7813</v>
       </c>
-      <c r="B126" s="28"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="28"/>
-      <c r="G126" s="2"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="1"/>
-      <c r="M126" s="1"/>
-      <c r="N126" s="1"/>
-      <c r="O126" s="1"/>
-      <c r="P126" s="1"/>
-      <c r="Q126" s="1"/>
-      <c r="R126" s="1"/>
-      <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
-      <c r="U126" s="1"/>
-      <c r="V126" s="1"/>
-      <c r="W126" s="1"/>
-      <c r="X126" s="1"/>
-      <c r="Y126" s="1"/>
-      <c r="Z126" s="1"/>
-      <c r="AA126" s="1"/>
-      <c r="AB126" s="1"/>
-      <c r="AC126" s="1"/>
-      <c r="AD126" s="1"/>
-    </row>
-    <row r="127" s="55" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="123" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="47" t="s">
+        <v>7814</v>
+      </c>
+      <c r="B123" s="28"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="28"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
+      <c r="K123" s="1"/>
+      <c r="L123" s="1"/>
+      <c r="M123" s="1"/>
+      <c r="N123" s="1"/>
+      <c r="O123" s="1"/>
+      <c r="P123" s="1"/>
+      <c r="Q123" s="1"/>
+      <c r="R123" s="1"/>
+      <c r="S123" s="1"/>
+      <c r="T123" s="1"/>
+      <c r="U123" s="1"/>
+      <c r="V123" s="1"/>
+      <c r="W123" s="1"/>
+      <c r="X123" s="1"/>
+      <c r="Y123" s="1"/>
+      <c r="Z123" s="1"/>
+      <c r="AA123" s="1"/>
+      <c r="AB123" s="1"/>
+      <c r="AC123" s="1"/>
+      <c r="AD123" s="1"/>
+    </row>
+    <row r="124" s="55" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="56" t="n">
+        <v>45004</v>
+      </c>
+      <c r="B124" s="55" t="s">
+        <v>7815</v>
+      </c>
+      <c r="C124" s="55" t="s">
+        <v>7816</v>
+      </c>
+      <c r="D124" s="55" t="s">
+        <v>7817</v>
+      </c>
+      <c r="E124" s="55" t="s">
+        <v>7818</v>
+      </c>
+      <c r="F124" s="57" t="s">
+        <v>7819</v>
+      </c>
+      <c r="G124" s="55" t="s">
+        <v>7820</v>
+      </c>
+    </row>
+    <row r="125" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="56" t="n">
+        <v>45005</v>
+      </c>
+      <c r="B125" s="57" t="s">
+        <v>7821</v>
+      </c>
+      <c r="C125" s="55" t="s">
+        <v>7822</v>
+      </c>
+      <c r="D125" s="55" t="s">
+        <v>7823</v>
+      </c>
+      <c r="E125" s="55" t="s">
+        <v>7824</v>
+      </c>
+      <c r="F125" s="57" t="s">
+        <v>7825</v>
+      </c>
+      <c r="G125" s="55" t="s">
+        <v>7826</v>
+      </c>
+    </row>
+    <row r="126" s="55" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="56" t="n">
+        <v>45006</v>
+      </c>
+      <c r="B126" s="55" t="s">
+        <v>7815</v>
+      </c>
+      <c r="C126" s="55" t="s">
+        <v>7827</v>
+      </c>
+      <c r="D126" s="55" t="s">
+        <v>7828</v>
+      </c>
+      <c r="E126" s="58" t="s">
+        <v>7829</v>
+      </c>
+      <c r="F126" s="57" t="s">
+        <v>7830</v>
+      </c>
+      <c r="G126" s="55" t="s">
+        <v>7831</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="56" t="n">
-        <v>45004</v>
+        <v>45036</v>
       </c>
       <c r="B127" s="55" t="s">
-        <v>7814</v>
-      </c>
-      <c r="C127" s="55" t="s">
+        <v>7832</v>
+      </c>
+      <c r="C127" s="55"/>
+      <c r="D127" s="55" t="s">
+        <v>7833</v>
+      </c>
+      <c r="E127" s="55" t="s">
+        <v>7834</v>
+      </c>
+      <c r="F127" s="55" t="s">
+        <v>7835</v>
+      </c>
+      <c r="G127" s="55" t="s">
+        <v>7836</v>
+      </c>
+      <c r="H127" s="55"/>
+      <c r="I127" s="55"/>
+      <c r="J127" s="55"/>
+      <c r="K127" s="55"/>
+      <c r="L127" s="55"/>
+      <c r="M127" s="55"/>
+      <c r="N127" s="55"/>
+      <c r="O127" s="55"/>
+      <c r="P127" s="55"/>
+      <c r="Q127" s="55"/>
+      <c r="R127" s="55"/>
+      <c r="S127" s="55"/>
+      <c r="T127" s="55"/>
+      <c r="U127" s="55"/>
+      <c r="V127" s="55"/>
+      <c r="W127" s="55"/>
+      <c r="X127" s="55"/>
+      <c r="Y127" s="55"/>
+      <c r="Z127" s="55"/>
+      <c r="AA127" s="55"/>
+      <c r="AB127" s="55"/>
+      <c r="AC127" s="55"/>
+      <c r="AD127" s="55"/>
+    </row>
+    <row r="128" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="59" t="n">
+        <v>45088</v>
+      </c>
+      <c r="B128" s="48" t="s">
         <v>7815</v>
       </c>
-      <c r="D127" s="55" t="s">
-        <v>7816</v>
-      </c>
-      <c r="E127" s="55" t="s">
-        <v>7817</v>
-      </c>
-      <c r="F127" s="57" t="s">
-        <v>7818</v>
-      </c>
-      <c r="G127" s="55" t="s">
-        <v>7819</v>
-      </c>
-    </row>
-    <row r="128" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="56" t="n">
-        <v>45005</v>
-      </c>
-      <c r="B128" s="57" t="s">
-        <v>7820</v>
-      </c>
-      <c r="C128" s="55" t="s">
-        <v>7821</v>
-      </c>
-      <c r="D128" s="55" t="s">
-        <v>7822</v>
-      </c>
-      <c r="E128" s="55" t="s">
-        <v>7823</v>
-      </c>
-      <c r="F128" s="57" t="s">
-        <v>7824</v>
-      </c>
-      <c r="G128" s="55" t="s">
-        <v>7825</v>
-      </c>
-    </row>
-    <row r="129" s="55" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="56" t="n">
-        <v>45006</v>
-      </c>
-      <c r="B129" s="55" t="s">
-        <v>7814</v>
-      </c>
-      <c r="C129" s="55" t="s">
-        <v>7826</v>
-      </c>
-      <c r="D129" s="55" t="s">
-        <v>7827</v>
-      </c>
-      <c r="E129" s="58" t="s">
-        <v>7828</v>
-      </c>
-      <c r="F129" s="57" t="s">
-        <v>7829</v>
-      </c>
-      <c r="G129" s="55" t="s">
-        <v>7830</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="56" t="n">
-        <v>45036</v>
-      </c>
-      <c r="B130" s="55" t="s">
-        <v>7831</v>
-      </c>
-      <c r="C130" s="55"/>
-      <c r="D130" s="55" t="s">
-        <v>7832</v>
-      </c>
-      <c r="E130" s="55" t="s">
-        <v>7833</v>
-      </c>
-      <c r="F130" s="55" t="s">
-        <v>7834</v>
-      </c>
-      <c r="G130" s="55" t="s">
-        <v>7835</v>
-      </c>
-      <c r="H130" s="55"/>
-      <c r="I130" s="55"/>
-      <c r="J130" s="55"/>
-      <c r="K130" s="55"/>
-      <c r="L130" s="55"/>
-      <c r="M130" s="55"/>
-      <c r="N130" s="55"/>
-      <c r="O130" s="55"/>
-      <c r="P130" s="55"/>
-      <c r="Q130" s="55"/>
-      <c r="R130" s="55"/>
-      <c r="S130" s="55"/>
-      <c r="T130" s="55"/>
-      <c r="U130" s="55"/>
-      <c r="V130" s="55"/>
-      <c r="W130" s="55"/>
-      <c r="X130" s="55"/>
-      <c r="Y130" s="55"/>
-      <c r="Z130" s="55"/>
-      <c r="AA130" s="55"/>
-      <c r="AB130" s="55"/>
-      <c r="AC130" s="55"/>
-      <c r="AD130" s="55"/>
-    </row>
-    <row r="131" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="59" t="n">
-        <v>45088</v>
-      </c>
-      <c r="B131" s="48" t="s">
-        <v>7814</v>
-      </c>
-      <c r="C131" s="48" t="s">
-        <v>7836</v>
-      </c>
-      <c r="D131" s="48" t="s">
+      <c r="C128" s="48" t="s">
         <v>7837</v>
       </c>
-      <c r="E131" s="60" t="s">
+      <c r="D128" s="48" t="s">
         <v>7838</v>
       </c>
-      <c r="F131" s="48" t="s">
-        <v>7547</v>
-      </c>
-      <c r="G131" s="48" t="s">
-        <v>7548</v>
-      </c>
+      <c r="E128" s="60" t="s">
+        <v>7839</v>
+      </c>
+      <c r="F128" s="48" t="s">
+        <v>7549</v>
+      </c>
+      <c r="G128" s="48" t="s">
+        <v>7550</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="59" t="n">
+        <v>45025</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>7840</v>
+      </c>
+      <c r="C129" s="28" t="s">
+        <v>7841</v>
+      </c>
+      <c r="D129" s="43" t="s">
+        <v>7842</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>7843</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>7844</v>
+      </c>
+    </row>
+    <row r="131" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
+        <v>7845</v>
+      </c>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+      <c r="K131" s="1"/>
+      <c r="L131" s="1"/>
+      <c r="M131" s="1"/>
+      <c r="N131" s="1"/>
+      <c r="O131" s="1"/>
+      <c r="P131" s="1"/>
+      <c r="Q131" s="1"/>
+      <c r="R131" s="1"/>
+      <c r="S131" s="1"/>
+      <c r="T131" s="1"/>
+      <c r="U131" s="1"/>
+      <c r="V131" s="1"/>
+      <c r="W131" s="1"/>
+      <c r="X131" s="1"/>
+      <c r="Y131" s="1"/>
+      <c r="Z131" s="1"/>
+      <c r="AA131" s="1"/>
+      <c r="AB131" s="1"/>
+      <c r="AC131" s="1"/>
+      <c r="AD131" s="1"/>
     </row>
     <row r="132" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="59" t="n">
-        <v>45025</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>7839</v>
-      </c>
-      <c r="C132" s="28" t="s">
-        <v>7840</v>
-      </c>
-      <c r="D132" s="43" t="s">
-        <v>7841</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>7842</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>7843</v>
-      </c>
-    </row>
-    <row r="134" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="s">
-        <v>7844</v>
-      </c>
-      <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
-      <c r="E134" s="1"/>
-      <c r="F134" s="1"/>
-      <c r="G134" s="1"/>
-      <c r="H134" s="1"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
-      <c r="K134" s="1"/>
-      <c r="L134" s="1"/>
-      <c r="M134" s="1"/>
-      <c r="N134" s="1"/>
-      <c r="O134" s="1"/>
-      <c r="P134" s="1"/>
-      <c r="Q134" s="1"/>
-      <c r="R134" s="1"/>
-      <c r="S134" s="1"/>
-      <c r="T134" s="1"/>
-      <c r="U134" s="1"/>
-      <c r="V134" s="1"/>
-      <c r="W134" s="1"/>
-      <c r="X134" s="1"/>
-      <c r="Y134" s="1"/>
-      <c r="Z134" s="1"/>
-      <c r="AA134" s="1"/>
-      <c r="AB134" s="1"/>
-      <c r="AC134" s="1"/>
-      <c r="AD134" s="1"/>
+      <c r="A132" s="61" t="n">
+        <v>39252</v>
+      </c>
+      <c r="B132" s="41"/>
+      <c r="C132" s="41" t="s">
+        <v>7846</v>
+      </c>
+      <c r="D132" s="62" t="s">
+        <v>7847</v>
+      </c>
+      <c r="E132" s="41" t="s">
+        <v>7848</v>
+      </c>
+      <c r="F132" s="41" t="s">
+        <v>7849</v>
+      </c>
+      <c r="G132" s="41" t="s">
+        <v>7850</v>
+      </c>
+      <c r="H132" s="41"/>
+      <c r="I132" s="41"/>
+      <c r="J132" s="41"/>
+      <c r="K132" s="41"/>
+      <c r="L132" s="41"/>
+      <c r="M132" s="41"/>
+      <c r="N132" s="41"/>
+      <c r="O132" s="41"/>
+      <c r="P132" s="41"/>
+      <c r="Q132" s="41"/>
+      <c r="R132" s="41"/>
+      <c r="S132" s="41"/>
+      <c r="T132" s="41"/>
+      <c r="U132" s="41"/>
+      <c r="V132" s="41"/>
+      <c r="W132" s="41"/>
+      <c r="X132" s="41"/>
+      <c r="Y132" s="41"/>
+      <c r="Z132" s="41"/>
+      <c r="AA132" s="41"/>
+      <c r="AB132" s="41"/>
+      <c r="AC132" s="41"/>
+      <c r="AD132" s="41"/>
+    </row>
+    <row r="133" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="47" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>7851</v>
+      </c>
+      <c r="C133" s="28" t="s">
+        <v>7852</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>7853</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>7854</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="47" t="s">
+        <v>7855</v>
+      </c>
+      <c r="B134" s="28" t="s">
+        <v>7856</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>7857</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>7858</v>
+      </c>
+      <c r="F134" s="28" t="s">
+        <v>7859</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>7860</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="61" t="n">
-        <v>39252</v>
-      </c>
-      <c r="B135" s="41"/>
-      <c r="C135" s="41" t="s">
-        <v>7845</v>
-      </c>
-      <c r="D135" s="62" t="s">
-        <v>7846</v>
-      </c>
-      <c r="E135" s="41" t="s">
-        <v>7847</v>
-      </c>
-      <c r="F135" s="41" t="s">
-        <v>7848</v>
-      </c>
-      <c r="G135" s="41" t="s">
-        <v>7849</v>
-      </c>
-      <c r="H135" s="41"/>
-      <c r="I135" s="41"/>
-      <c r="J135" s="41"/>
-      <c r="K135" s="41"/>
-      <c r="L135" s="41"/>
-      <c r="M135" s="41"/>
-      <c r="N135" s="41"/>
-      <c r="O135" s="41"/>
-      <c r="P135" s="41"/>
-      <c r="Q135" s="41"/>
-      <c r="R135" s="41"/>
-      <c r="S135" s="41"/>
-      <c r="T135" s="41"/>
-      <c r="U135" s="41"/>
-      <c r="V135" s="41"/>
-      <c r="W135" s="41"/>
-      <c r="X135" s="41"/>
-      <c r="Y135" s="41"/>
-      <c r="Z135" s="41"/>
-      <c r="AA135" s="41"/>
-      <c r="AB135" s="41"/>
-      <c r="AC135" s="41"/>
-      <c r="AD135" s="41"/>
-    </row>
-    <row r="136" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="47" t="n">
-        <v>46241</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>7850</v>
-      </c>
-      <c r="C136" s="28" t="s">
-        <v>7851</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>7852</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>7853</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="47" t="s">
-        <v>7854</v>
-      </c>
-      <c r="B137" s="28" t="s">
-        <v>7855</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>7856</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>7857</v>
-      </c>
-      <c r="F137" s="28" t="s">
-        <v>7858</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>7859</v>
-      </c>
-    </row>
+      <c r="A135" s="54" t="n">
+        <v>42866</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>7861</v>
+      </c>
+      <c r="C135" s="28" t="s">
+        <v>7862</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>7863</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>7864</v>
+      </c>
+      <c r="F135" s="28" t="s">
+        <v>7865</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>7866</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="138" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="54" t="n">
-        <v>42866</v>
+      <c r="A138" s="2" t="s">
+        <v>7497</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>7860</v>
-      </c>
-      <c r="C138" s="28" t="s">
-        <v>7861</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>7862</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>7863</v>
-      </c>
-      <c r="F138" s="28" t="s">
-        <v>7864</v>
-      </c>
-      <c r="G138" s="2" t="s">
+        <v>7867</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
+        <v>7868</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="61" t="s">
+        <v>7869</v>
+      </c>
+      <c r="B142" s="41" t="s">
+        <v>7870</v>
+      </c>
+      <c r="C142" s="41" t="s">
+        <v>7871</v>
+      </c>
+      <c r="D142" s="41"/>
+      <c r="E142" s="41" t="s">
+        <v>7872</v>
+      </c>
+      <c r="F142" s="41" t="s">
+        <v>7873</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>7874</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="s">
+        <v>7875</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>7876</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>7877</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>7878</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>7879</v>
+      </c>
+      <c r="F143" s="48" t="s">
+        <v>7880</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>7881</v>
+      </c>
+    </row>
+    <row r="144" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="61" t="s">
+        <v>7882</v>
+      </c>
+      <c r="B144" s="41" t="s">
+        <v>7883</v>
+      </c>
+      <c r="C144" s="41" t="s">
+        <v>7884</v>
+      </c>
+      <c r="D144" s="62" t="s">
+        <v>7885</v>
+      </c>
+      <c r="E144" s="41" t="s">
+        <v>7886</v>
+      </c>
+      <c r="F144" s="41" t="s">
+        <v>7873</v>
+      </c>
+      <c r="G144" s="41" t="s">
+        <v>7887</v>
+      </c>
+    </row>
+    <row r="145" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="63" t="n">
+        <v>42355</v>
+      </c>
+      <c r="B145" s="41" t="s">
+        <v>7888</v>
+      </c>
+      <c r="C145" s="41" t="s">
+        <v>7889</v>
+      </c>
+      <c r="D145" s="41" t="s">
+        <v>7890</v>
+      </c>
+      <c r="E145" s="41" t="s">
+        <v>7891</v>
+      </c>
+      <c r="F145" s="41" t="s">
+        <v>7892</v>
+      </c>
+    </row>
+    <row r="146" s="41" customFormat="true" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="61" t="n">
+        <v>43658</v>
+      </c>
+      <c r="B146" s="41" t="s">
+        <v>7893</v>
+      </c>
+      <c r="C146" s="41" t="s">
+        <v>7894</v>
+      </c>
+      <c r="D146" s="62" t="s">
+        <v>7895</v>
+      </c>
+      <c r="E146" s="41" t="s">
+        <v>7896</v>
+      </c>
+      <c r="F146" s="41" t="s">
+        <v>7893</v>
+      </c>
+      <c r="G146" s="41" t="s">
+        <v>7897</v>
+      </c>
+      <c r="AD146" s="41" t="s">
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="61" t="n">
+        <v>45581</v>
+      </c>
+      <c r="B147" s="41" t="s">
+        <v>7899</v>
+      </c>
+      <c r="C147" s="41" t="s">
+        <v>7900</v>
+      </c>
+      <c r="D147" s="41" t="s">
+        <v>7901</v>
+      </c>
+      <c r="E147" s="62" t="s">
+        <v>7902</v>
+      </c>
+      <c r="F147" s="41" t="s">
+        <v>7899</v>
+      </c>
+      <c r="G147" s="64" t="s">
+        <v>7903</v>
+      </c>
+      <c r="H147" s="41"/>
+      <c r="I147" s="41"/>
+      <c r="J147" s="41"/>
+      <c r="K147" s="41"/>
+      <c r="L147" s="41"/>
+      <c r="M147" s="41"/>
+      <c r="N147" s="41"/>
+      <c r="O147" s="41"/>
+      <c r="P147" s="41"/>
+      <c r="Q147" s="41"/>
+      <c r="R147" s="41"/>
+      <c r="S147" s="41"/>
+      <c r="T147" s="41"/>
+      <c r="U147" s="41"/>
+      <c r="V147" s="41"/>
+      <c r="W147" s="41"/>
+      <c r="X147" s="41"/>
+      <c r="Y147" s="41"/>
+      <c r="Z147" s="41"/>
+      <c r="AA147" s="41"/>
+      <c r="AB147" s="41"/>
+      <c r="AC147" s="41"/>
+      <c r="AD147" s="41"/>
+    </row>
+    <row r="148" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="63" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>7904</v>
+      </c>
+      <c r="C148" s="28" t="s">
+        <v>7905</v>
+      </c>
+      <c r="D148" s="28" t="s">
+        <v>7906</v>
+      </c>
+      <c r="E148" s="49" t="s">
+        <v>7907</v>
+      </c>
+      <c r="F148" s="28" t="s">
+        <v>7625</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>7626</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>7908</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="65" t="s">
+        <v>7909</v>
+      </c>
+      <c r="B151" s="66" t="s">
+        <v>7910</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>7911</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>7865</v>
       </c>
-    </row>
-    <row r="140" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="141" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="2" t="s">
-        <v>7504</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>7866</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1" t="s">
-        <v>7867</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="61" t="s">
-        <v>7868</v>
-      </c>
-      <c r="B145" s="41" t="s">
-        <v>7869</v>
-      </c>
-      <c r="C145" s="41" t="s">
-        <v>7870</v>
-      </c>
-      <c r="D145" s="41"/>
-      <c r="E145" s="41" t="s">
-        <v>7871</v>
-      </c>
-      <c r="F145" s="41" t="s">
-        <v>7872</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>7873</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
-        <v>7874</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>7875</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>7876</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>7877</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>7878</v>
-      </c>
-      <c r="F146" s="48" t="s">
-        <v>7879</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>7880</v>
-      </c>
-    </row>
-    <row r="147" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="61" t="s">
-        <v>7881</v>
-      </c>
-      <c r="B147" s="41" t="s">
-        <v>7882</v>
-      </c>
-      <c r="C147" s="41" t="s">
-        <v>7883</v>
-      </c>
-      <c r="D147" s="62" t="s">
-        <v>7884</v>
-      </c>
-      <c r="E147" s="41" t="s">
-        <v>7885</v>
-      </c>
-      <c r="F147" s="41" t="s">
-        <v>7872</v>
-      </c>
-      <c r="G147" s="41" t="s">
-        <v>7886</v>
-      </c>
-    </row>
-    <row r="148" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="63" t="n">
-        <v>42355</v>
-      </c>
-      <c r="B148" s="41" t="s">
-        <v>7887</v>
-      </c>
-      <c r="C148" s="41" t="s">
-        <v>7888</v>
-      </c>
-      <c r="D148" s="41" t="s">
-        <v>7889</v>
-      </c>
-      <c r="E148" s="41" t="s">
-        <v>7890</v>
-      </c>
-      <c r="F148" s="41" t="s">
-        <v>7891</v>
-      </c>
-    </row>
-    <row r="149" s="41" customFormat="true" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="61" t="n">
-        <v>43658</v>
-      </c>
-      <c r="B149" s="41" t="s">
-        <v>7892</v>
-      </c>
-      <c r="C149" s="41" t="s">
-        <v>7893</v>
-      </c>
-      <c r="D149" s="62" t="s">
-        <v>7894</v>
-      </c>
-      <c r="E149" s="41" t="s">
-        <v>7895</v>
-      </c>
-      <c r="F149" s="41" t="s">
-        <v>7892</v>
-      </c>
-      <c r="G149" s="41" t="s">
-        <v>7896</v>
-      </c>
-      <c r="AD149" s="41" t="s">
-        <v>7897</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="61" t="n">
-        <v>45581</v>
-      </c>
-      <c r="B150" s="41" t="s">
+      <c r="G151" s="2" t="s">
+        <v>7912</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="61" t="s">
+        <v>7913</v>
+      </c>
+      <c r="B152" s="66" t="s">
+        <v>7914</v>
+      </c>
+      <c r="C152" s="0"/>
+      <c r="F152" s="1" t="s">
+        <v>7865</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>7915</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="65" t="s">
+        <v>7909</v>
+      </c>
+      <c r="B153" s="67" t="s">
+        <v>7916</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>7917</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>7865</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>7918</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="68" t="s">
+        <v>7919</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>7920</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>7921</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>7922</v>
+      </c>
+      <c r="G154" s="2" t="s">
         <v>7898</v>
       </c>
-      <c r="C150" s="41" t="s">
-        <v>7899</v>
-      </c>
-      <c r="D150" s="41" t="s">
-        <v>7900</v>
-      </c>
-      <c r="E150" s="62" t="s">
-        <v>7901</v>
-      </c>
-      <c r="F150" s="41" t="s">
-        <v>7898</v>
-      </c>
-      <c r="G150" s="64" t="s">
-        <v>7902</v>
-      </c>
-      <c r="H150" s="41"/>
-      <c r="I150" s="41"/>
-      <c r="J150" s="41"/>
-      <c r="K150" s="41"/>
-      <c r="L150" s="41"/>
-      <c r="M150" s="41"/>
-      <c r="N150" s="41"/>
-      <c r="O150" s="41"/>
-      <c r="P150" s="41"/>
-      <c r="Q150" s="41"/>
-      <c r="R150" s="41"/>
-      <c r="S150" s="41"/>
-      <c r="T150" s="41"/>
-      <c r="U150" s="41"/>
-      <c r="V150" s="41"/>
-      <c r="W150" s="41"/>
-      <c r="X150" s="41"/>
-      <c r="Y150" s="41"/>
-      <c r="Z150" s="41"/>
-      <c r="AA150" s="41"/>
-      <c r="AB150" s="41"/>
-      <c r="AC150" s="41"/>
-      <c r="AD150" s="41"/>
-    </row>
-    <row r="151" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="63" t="n">
-        <v>45668</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>7903</v>
-      </c>
-      <c r="C151" s="28" t="s">
-        <v>7904</v>
-      </c>
-      <c r="D151" s="28" t="s">
-        <v>7905</v>
-      </c>
-      <c r="E151" s="49" t="s">
-        <v>7906</v>
-      </c>
-      <c r="F151" s="28" t="s">
-        <v>7623</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>7624</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
-        <v>7907</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="65" t="s">
-        <v>7908</v>
-      </c>
-      <c r="B154" s="66" t="s">
+    </row>
+    <row r="155" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="0" t="s">
+        <v>7923</v>
+      </c>
+      <c r="B155" s="67" t="s">
+        <v>7924</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>7925</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>7922</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>7926</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="69" t="s">
+        <v>7927</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>7928</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>7929</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>7930</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>7931</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="45" t="s">
+        <v>7932</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>7933</v>
+      </c>
+      <c r="C157" s="49" t="s">
+        <v>7934</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>7935</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="0" t="s">
+        <v>7923</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>7936</v>
+      </c>
+      <c r="C158" s="41" t="s">
+        <v>7937</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>7938</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>7922</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>7926</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="68" t="s">
+        <v>7939</v>
+      </c>
+      <c r="B159" s="68" t="s">
+        <v>7940</v>
+      </c>
+      <c r="C159" s="41" t="s">
+        <v>7941</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>7942</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>7922</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>7943</v>
+      </c>
+      <c r="H159" s="1"/>
+    </row>
+    <row r="160" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="65" t="s">
         <v>7909</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>7910</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>7864</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>7911</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="61" t="s">
-        <v>7912</v>
-      </c>
-      <c r="B155" s="66" t="s">
-        <v>7913</v>
-      </c>
-      <c r="C155" s="0"/>
-      <c r="F155" s="1" t="s">
-        <v>7864</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>7914</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="65" t="s">
-        <v>7908</v>
-      </c>
-      <c r="B156" s="67" t="s">
-        <v>7915</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>7916</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>7864</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>7917</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="68" t="s">
-        <v>7918</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>7919</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>7920</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>7921</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>7897</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0" t="s">
-        <v>7922</v>
-      </c>
-      <c r="B158" s="67" t="s">
-        <v>7923</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>7924</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>7921</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>7925</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="69" t="s">
-        <v>7926</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>7927</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>7928</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>7929</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>7930</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="45" t="s">
-        <v>7931</v>
-      </c>
       <c r="B160" s="1" t="s">
-        <v>7932</v>
-      </c>
-      <c r="C160" s="49" t="s">
-        <v>7933</v>
+        <v>7944</v>
+      </c>
+      <c r="D160" s="28" t="s">
+        <v>7945</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>7946</v>
+      </c>
+      <c r="F160" s="43" t="s">
+        <v>7947</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>7934</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="0" t="s">
-        <v>7922</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>7935</v>
-      </c>
-      <c r="C161" s="41" t="s">
-        <v>7936</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>7937</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>7921</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>7925</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="68" t="s">
-        <v>7938</v>
-      </c>
-      <c r="B162" s="68" t="s">
-        <v>7939</v>
-      </c>
-      <c r="C162" s="41" t="s">
-        <v>7940</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>7941</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>7921</v>
-      </c>
-      <c r="G162" s="2" t="s">
-        <v>7942</v>
-      </c>
-      <c r="H162" s="1"/>
-    </row>
-    <row r="163" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="65" t="s">
-        <v>7908</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>7943</v>
-      </c>
-      <c r="D163" s="28" t="s">
-        <v>7944</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>7945</v>
-      </c>
-      <c r="F163" s="43" t="s">
-        <v>7946</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>7947</v>
+        <v>7948</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G9" r:id="rId1" display="https://baike.baidu.com/item/%E5%BC%80%E5%AE%9D%E5%A4%A7%E8%97%8F%E7%BB%8F/5512186?fromtitle=%E5%BC%80%E5%AE%9D%E8%97%8F&amp;fromid=2006547&amp;fr=aladdin"/>
-    <hyperlink ref="G19" r:id="rId2" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G20" r:id="rId3" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G21" r:id="rId4" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G24" r:id="rId5" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G25" r:id="rId6" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G26" r:id="rId7" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G27" r:id="rId8" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G28" r:id="rId9" display="https://baijiahao.baidu.com/s?id=1853719866750900952&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G29" r:id="rId10" display="https://www.dpm.org.cn/ancient/special/148432.html"/>
-    <hyperlink ref="G30" r:id="rId11" display="https://baijiahao.baidu.com/s?id=1853719866750900952&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G31" r:id="rId12" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G37" r:id="rId13" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G38" r:id="rId14" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G43" r:id="rId15" display="https://whly.gd.gov.cn/service_newwwbwg/content/post_4738424.html"/>
-    <hyperlink ref="G44" r:id="rId16" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G46" r:id="rId17" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G47" r:id="rId18" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G50" r:id="rId19" display="https://edu.sina.com.cn/wander/2000-09-25/12790.shtml"/>
-    <hyperlink ref="G56" r:id="rId20" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G57" r:id="rId21" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G59" r:id="rId22" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G60" r:id="rId23" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G61" r:id="rId24" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="G64" r:id="rId25" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G65" r:id="rId26" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
-    <hyperlink ref="G66" r:id="rId27" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G67" r:id="rId28" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G68" r:id="rId29" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G69" r:id="rId30" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G70" r:id="rId31" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G73" r:id="rId32" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G74" r:id="rId33" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G75" r:id="rId34" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G76" r:id="rId35" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
-    <hyperlink ref="G78" r:id="rId36" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G79" r:id="rId37" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
-    <hyperlink ref="G80" r:id="rId38" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
-    <hyperlink ref="G81" r:id="rId39" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
-    <hyperlink ref="G82" r:id="rId40" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G83" r:id="rId41" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G84" r:id="rId42" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G85" r:id="rId43" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G86" r:id="rId44" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G87" r:id="rId45" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G88" r:id="rId46" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G89" r:id="rId47" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G90" r:id="rId48" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G93" r:id="rId49" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
-    <hyperlink ref="G98" r:id="rId50" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G99" r:id="rId51" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G100" r:id="rId52" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G101" r:id="rId53" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G104" r:id="rId54" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G105" r:id="rId55" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G108" r:id="rId56" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G109" r:id="rId57" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
-    <hyperlink ref="G110" r:id="rId58" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
-    <hyperlink ref="G115" r:id="rId59" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G116" r:id="rId60" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G117" r:id="rId61" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G118" r:id="rId62" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G119" r:id="rId63" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G120" r:id="rId64" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G122" r:id="rId65" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G123" r:id="rId66" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
-    <hyperlink ref="G127" r:id="rId67" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
-    <hyperlink ref="F129" r:id="rId68" display="中新网北京3月21日电 (记者 应妮) "/>
-    <hyperlink ref="G129" r:id="rId69" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
-    <hyperlink ref="G131" r:id="rId70" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G135" r:id="rId71" display="https://discovery.cctv.com/20070619/107154.shtml"/>
-    <hyperlink ref="G138" r:id="rId72" display="https://book.kongfz.com/102740/682706591"/>
-    <hyperlink ref="A141" r:id="rId73" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G145" r:id="rId74" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
-    <hyperlink ref="G146" r:id="rId75" display="https://book.kongfz.com/20791/3754198261"/>
-    <hyperlink ref="G149" r:id="rId76" display="https://www.ljstsg.cn/?p=6315"/>
-    <hyperlink ref="AD149" r:id="rId77" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="G150" r:id="rId78" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
-    <hyperlink ref="G151" r:id="rId79" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="B154" r:id="rId80" display="全国图书馆文献缩微复制中心"/>
-    <hyperlink ref="G154" r:id="rId81" display="https://book.kongfz.com/536651/7839562954"/>
-    <hyperlink ref="B155" r:id="rId82" display="全国图书馆文献缩微复制中心"/>
-    <hyperlink ref="G155" r:id="rId83" display="https://book.kongfz.com/23231/8186709240"/>
-    <hyperlink ref="B156" r:id="rId84" display="全国图书馆文献缩微复制中心"/>
-    <hyperlink ref="G156" r:id="rId85" display="https://book.kongfz.com/536651/7839554296"/>
-    <hyperlink ref="G157" r:id="rId86" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="B158" r:id="rId87" display="中国书店"/>
-    <hyperlink ref="G159" r:id="rId88" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
-    <hyperlink ref="G160" r:id="rId89" display="https://book.kongfz.com/200249/1819262449/"/>
-    <hyperlink ref="G161" r:id="rId90" display="https://product.dangdang.com/11721366316.html"/>
-    <hyperlink ref="B162" r:id="rId91" display="宗教文化出版社"/>
-    <hyperlink ref="G162" r:id="rId92" display="https://product.dangdang.com/22497432.html"/>
-    <hyperlink ref="G163" r:id="rId93" display="http://aiguji.net/3299.html"/>
+    <hyperlink ref="G18" r:id="rId2" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G19" r:id="rId3" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G20" r:id="rId4" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G21" r:id="rId5" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G24" r:id="rId6" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G25" r:id="rId7" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G26" r:id="rId8" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G27" r:id="rId9" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G28" r:id="rId10" display="https://baijiahao.baidu.com/s?id=1853719866750900952&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G29" r:id="rId11" display="https://www.dpm.org.cn/ancient/special/148432.html"/>
+    <hyperlink ref="G30" r:id="rId12" display="https://baijiahao.baidu.com/s?id=1853719866750900952&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G31" r:id="rId13" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G37" r:id="rId14" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G38" r:id="rId15" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G43" r:id="rId16" display="https://whly.gd.gov.cn/service_newwwbwg/content/post_4738424.html"/>
+    <hyperlink ref="G44" r:id="rId17" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G46" r:id="rId18" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G47" r:id="rId19" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G50" r:id="rId20" display="https://edu.sina.com.cn/wander/2000-09-25/12790.shtml"/>
+    <hyperlink ref="G56" r:id="rId21" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G57" r:id="rId22" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G59" r:id="rId23" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G60" r:id="rId24" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G61" r:id="rId25" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="G64" r:id="rId26" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G65" r:id="rId27" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
+    <hyperlink ref="G66" r:id="rId28" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G67" r:id="rId29" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G68" r:id="rId30" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G69" r:id="rId31" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G70" r:id="rId32" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G73" r:id="rId33" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G74" r:id="rId34" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G75" r:id="rId35" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G76" r:id="rId36" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
+    <hyperlink ref="G78" r:id="rId37" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G79" r:id="rId38" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
+    <hyperlink ref="G80" r:id="rId39" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
+    <hyperlink ref="G81" r:id="rId40" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
+    <hyperlink ref="G82" r:id="rId41" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G83" r:id="rId42" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G84" r:id="rId43" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G85" r:id="rId44" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G86" r:id="rId45" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G87" r:id="rId46" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G88" r:id="rId47" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G89" r:id="rId48" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G90" r:id="rId49" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G93" r:id="rId50" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
+    <hyperlink ref="G95" r:id="rId51" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G96" r:id="rId52" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G97" r:id="rId53" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G98" r:id="rId54" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G101" r:id="rId55" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G102" r:id="rId56" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G105" r:id="rId57" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G106" r:id="rId58" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
+    <hyperlink ref="G107" r:id="rId59" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
+    <hyperlink ref="G112" r:id="rId60" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G113" r:id="rId61" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G114" r:id="rId62" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G115" r:id="rId63" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G116" r:id="rId64" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G117" r:id="rId65" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G119" r:id="rId66" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G120" r:id="rId67" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
+    <hyperlink ref="G124" r:id="rId68" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
+    <hyperlink ref="F126" r:id="rId69" display="中新网北京3月21日电 (记者 应妮) "/>
+    <hyperlink ref="G126" r:id="rId70" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
+    <hyperlink ref="G128" r:id="rId71" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G132" r:id="rId72" display="https://discovery.cctv.com/20070619/107154.shtml"/>
+    <hyperlink ref="G135" r:id="rId73" display="https://book.kongfz.com/102740/682706591"/>
+    <hyperlink ref="A138" r:id="rId74" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G142" r:id="rId75" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
+    <hyperlink ref="G143" r:id="rId76" display="https://book.kongfz.com/20791/3754198261"/>
+    <hyperlink ref="G146" r:id="rId77" display="https://www.ljstsg.cn/?p=6315"/>
+    <hyperlink ref="AD146" r:id="rId78" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="G147" r:id="rId79" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
+    <hyperlink ref="G148" r:id="rId80" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="B151" r:id="rId81" display="全国图书馆文献缩微复制中心"/>
+    <hyperlink ref="G151" r:id="rId82" display="https://book.kongfz.com/536651/7839562954"/>
+    <hyperlink ref="B152" r:id="rId83" display="全国图书馆文献缩微复制中心"/>
+    <hyperlink ref="G152" r:id="rId84" display="https://book.kongfz.com/23231/8186709240"/>
+    <hyperlink ref="B153" r:id="rId85" display="全国图书馆文献缩微复制中心"/>
+    <hyperlink ref="G153" r:id="rId86" display="https://book.kongfz.com/536651/7839554296"/>
+    <hyperlink ref="G154" r:id="rId87" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="B155" r:id="rId88" display="中国书店"/>
+    <hyperlink ref="G156" r:id="rId89" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
+    <hyperlink ref="G157" r:id="rId90" display="https://book.kongfz.com/200249/1819262449/"/>
+    <hyperlink ref="G158" r:id="rId91" display="https://product.dangdang.com/11721366316.html"/>
+    <hyperlink ref="B159" r:id="rId92" display="宗教文化出版社"/>
+    <hyperlink ref="G159" r:id="rId93" display="https://product.dangdang.com/22497432.html"/>
+    <hyperlink ref="G160" r:id="rId94" display="http://aiguji.net/3299.html"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -85154,7 +85146,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7948</v>
+        <v>7949</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85165,7 +85157,7 @@
         <v>6766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7949</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85176,7 +85168,7 @@
         <v>7140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7950</v>
+        <v>7951</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85187,7 +85179,7 @@
         <v>7442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7951</v>
+        <v>7952</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85198,7 +85190,7 @@
         <v>7181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7952</v>
+        <v>7953</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85209,55 +85201,55 @@
         <v>7329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7953</v>
+        <v>7954</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>7954</v>
+        <v>7955</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7955</v>
+        <v>7956</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>7956</v>
+        <v>7957</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7957</v>
+        <v>7958</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>7958</v>
+        <v>7959</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7959</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>7960</v>
+        <v>7961</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>7961</v>
+        <v>7962</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>7962</v>
+        <v>7963</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7963</v>
+        <v>7964</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>7964</v>
+        <v>7965</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7965</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85272,45 +85264,45 @@
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>7831</v>
+        <v>7832</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>7966</v>
+        <v>7967</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>7967</v>
+        <v>7968</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>7968</v>
+        <v>7969</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>7969</v>
+        <v>7970</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>7970</v>
+        <v>7971</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>7971</v>
+        <v>7972</v>
       </c>
       <c r="E23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>7972</v>
+        <v>7973</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>7973</v>
+        <v>7974</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
-        <v>7661</v>
+        <v>7663</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>7974</v>
+        <v>7975</v>
       </c>
     </row>
   </sheetData>
@@ -85335,80 +85327,81 @@
   <dimension ref="A8:D15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="45.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="51.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="31.48"/>
   </cols>
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>7975</v>
+      <c r="A8" s="72" t="s">
+        <v>7976</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>7976</v>
+      <c r="A9" s="72" t="s">
+        <v>7977</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>7977</v>
+        <v>7978</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>7978</v>
-      </c>
-      <c r="B12" s="72" t="n">
+      <c r="A12" s="73" t="s">
+        <v>7979</v>
+      </c>
+      <c r="B12" s="74" t="n">
         <v>45735</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>7979</v>
+        <v>7980</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>7980</v>
+        <v>7981</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>7981</v>
-      </c>
-      <c r="B13" s="72" t="n">
+      <c r="A13" s="73" t="s">
+        <v>7982</v>
+      </c>
+      <c r="B13" s="74" t="n">
         <v>45970</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>7982</v>
+        <v>7983</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>7983</v>
+        <v>7984</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>7984</v>
-      </c>
-      <c r="B14" s="72" t="n">
+      <c r="A14" s="73" t="s">
+        <v>7985</v>
+      </c>
+      <c r="B14" s="74" t="n">
         <v>45995</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>7985</v>
+        <v>7986</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>7986</v>
+        <v>7987</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>7987</v>
-      </c>
-      <c r="B15" s="72" t="n">
+      <c r="A15" s="73" t="s">
+        <v>7988</v>
+      </c>
+      <c r="B15" s="74" t="n">
         <v>46036</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>7988</v>
+        <v>7989</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>7989</v>
+        <v>7990</v>
       </c>
     </row>
   </sheetData>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="乾隆大藏经1669清单核对" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10834" uniqueCount="7991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10836" uniqueCount="7993">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -28711,6 +28711,12 @@
   </si>
   <si>
     <t xml:space="preserve"> 工作区 `1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第22册缺索引图片</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第39册缺索引图片</t>
   </si>
 </sst>
 </file>
@@ -85324,7 +85330,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A8:D15"/>
+  <dimension ref="A8:D19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="45.83"/>
@@ -85344,7 +85350,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="72" t="s">
         <v>7978</v>
       </c>
     </row>
@@ -85402,6 +85408,16 @@
       </c>
       <c r="D15" s="0" t="s">
         <v>7990</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>7991</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>7992</v>
       </c>
     </row>
   </sheetData>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="乾隆大藏经1669清单核对" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10836" uniqueCount="7993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10849" uniqueCount="8004">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -26484,6 +26484,12 @@
   </si>
   <si>
     <t xml:space="preserve">https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">甘肃博物馆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">延藏法师向我馆捐赠《清敕修大藏经》 </t>
   </si>
   <si>
     <r>
@@ -28532,6 +28538,33 @@
   </si>
   <si>
     <t xml:space="preserve">http://aiguji.net/3299.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">清敕修大藏经保护项目简介 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013年10月</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://book.kongfz.com/467603/10356350239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">乾隆大藏经120册</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://item.jd.com/10127435513857.html?extension_id=eyJhZCI6IjI2OCIsImNoIjoiMiIsInNrdSI6IjEwMTI3NDM1NTEzODU3IiwidHMiOiIxNzkxMTAzMjU3IiwidW5pcWlkIjoie1wiY2xpY2tfaWRcIjpcIjljZjc4MDVjLTIwYjQtNGJiNy05YWY0LTY5NmJmY2I4ZWRjZFwiLFwibWF0ZXJpYWxfaWRcIjpcIjgwODM4NDI5MjkyMzY3NDkwNTJcIixcInBvc19pZFwiOlwiMjY4XCIsXCJzaWRcIjpcImNjMjMzZjcyLWFiY2MtNDdhMi1iYWZjLTNmY2Q3NDNlYmY5ZFwifSJ9&amp;jd_pop=9cf7805c-20b4-4bb7-9af4-696bfcb8edcd&amp;abt=0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">乾隆大藏经168册（第一册不含目录）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://item.jd.com/69174485133.html?extension_id=eyJhZCI6IjI2OCIsImNoIjoiMiIsInNrdSI6IjY5MTc0NDg1MTMzIiwidHMiOiIxNzkxMTAzMTkzIiwidW5pcWlkIjoie1wiY2xpY2tfaWRcIjpcIjdlZWRhNjAwLWE0ZTQtNGE5Ny04ODNlLTQzZTliM2NmNzZkZlwiLFwibWF0ZXJpYWxfaWRcIjpcIjgzNTQwMDc4MTcwNDI2MjM0MTBcIixcInBvc19pZFwiOlwiMjY4XCIsXCJzaWRcIjpcImNjMjMzZjcyLWFiY2MtNDdhMi1iYWZjLTNmY2Q3NDNlYmY5ZFwifSJ9&amp;jd_pop=7eeda600-a4e4-4a97-883e-43e9b3cf76df&amp;abt=0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">乾隆大藏经168册（第一册含目录）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://item.jd.com/10224400824653.html?extension_id=eyJhZCI6IjI2OCIsImNoIjoiMiIsInNrdSI6IjEwMjI0NDAwODI0NjUzIiwidHMiOiIxNzkxMTAzNDYxIiwidW5pcWlkIjoie1wiY2xpY2tfaWRcIjpcIjYyNzVjOGU5LTAzZWItNDM4ZC04YzU1LTFjOWMzYWYxNGQ3ZlwiLFwibWF0ZXJpYWxfaWRcIjpcIjgzNjM4NjM0MDk0NDE1NzM1ODJcIixcInBvc19pZFwiOlwiMjY4XCIsXCJzaWRcIjpcImNjMjMzZjcyLWFiY2MtNDdhMi1iYWZjLTNmY2Q3NDNlYmY5ZFwifSJ9&amp;jd_pop=6275c8e9-03eb-438d-8c55-1c9c3af14d7f&amp;abt=0</t>
   </si>
   <si>
     <t xml:space="preserve">此土注释</t>
@@ -29310,6 +29343,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29368,10 +29405,6 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -82417,7 +82450,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:AD160"/>
+  <dimension ref="A3:AD169"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.85"/>
@@ -84103,10 +84136,14 @@
         <v>7776</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="47"/>
-      <c r="B108" s="28"/>
-      <c r="C108" s="28"/>
+      <c r="B108" s="28" t="s">
+        <v>7777</v>
+      </c>
+      <c r="C108" s="54" t="s">
+        <v>7778</v>
+      </c>
       <c r="E108" s="28"/>
       <c r="F108" s="28"/>
       <c r="G108" s="2"/>
@@ -84121,7 +84158,7 @@
     </row>
     <row r="111" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="43" t="s">
-        <v>7777</v>
+        <v>7779</v>
       </c>
       <c r="B111" s="28"/>
       <c r="C111" s="28"/>
@@ -84130,14 +84167,14 @@
       <c r="G111" s="2"/>
     </row>
     <row r="112" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="54" t="s">
-        <v>7778</v>
+      <c r="A112" s="55" t="s">
+        <v>7780</v>
       </c>
       <c r="B112" s="43" t="s">
-        <v>7779</v>
+        <v>7781</v>
       </c>
       <c r="C112" s="28" t="s">
-        <v>7780</v>
+        <v>7782</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>7515</v>
@@ -84153,17 +84190,17 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="54" t="s">
-        <v>7781</v>
+      <c r="A113" s="55" t="s">
+        <v>7783</v>
       </c>
       <c r="B113" s="43" t="s">
-        <v>7782</v>
+        <v>7784</v>
       </c>
       <c r="C113" s="28" t="s">
-        <v>7783</v>
+        <v>7785</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>7784</v>
+        <v>7786</v>
       </c>
       <c r="F113" s="51" t="s">
         <v>7706</v>
@@ -84174,13 +84211,13 @@
     </row>
     <row r="114" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="49" t="s">
-        <v>7785</v>
+        <v>7787</v>
       </c>
       <c r="B114" s="52" t="s">
-        <v>7786</v>
+        <v>7788</v>
       </c>
       <c r="C114" s="28" t="s">
-        <v>7787</v>
+        <v>7789</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>7515</v>
@@ -84193,20 +84230,20 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="54" t="s">
-        <v>7788</v>
+      <c r="A115" s="55" t="s">
+        <v>7790</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>7789</v>
+        <v>7791</v>
       </c>
       <c r="C115" s="28" t="s">
-        <v>7790</v>
+        <v>7792</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>7515</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>7791</v>
+        <v>7793</v>
       </c>
       <c r="F115" s="28" t="s">
         <v>7516</v>
@@ -84216,14 +84253,14 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="54" t="s">
-        <v>7792</v>
+      <c r="A116" s="55" t="s">
+        <v>7794</v>
       </c>
       <c r="B116" s="28" t="s">
-        <v>7793</v>
+        <v>7795</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>7794</v>
+        <v>7796</v>
       </c>
       <c r="E116" s="28"/>
       <c r="F116" s="28" t="s">
@@ -84234,20 +84271,20 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="54" t="s">
-        <v>7795</v>
+      <c r="A117" s="55" t="s">
+        <v>7797</v>
       </c>
       <c r="B117" s="28" t="s">
-        <v>7796</v>
+        <v>7798</v>
       </c>
       <c r="C117" s="28" t="s">
-        <v>7797</v>
+        <v>7799</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>7784</v>
+        <v>7786</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>7798</v>
+        <v>7800</v>
       </c>
       <c r="F117" s="51" t="s">
         <v>7706</v>
@@ -84261,37 +84298,37 @@
         <v>44662</v>
       </c>
       <c r="B118" s="28" t="s">
-        <v>7799</v>
+        <v>7801</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>7800</v>
+        <v>7802</v>
       </c>
       <c r="D118" s="28" t="s">
-        <v>7801</v>
+        <v>7803</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>7802</v>
+        <v>7804</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>7803</v>
+        <v>7805</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>7804</v>
+        <v>7806</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="54" t="s">
-        <v>7805</v>
+      <c r="A119" s="55" t="s">
+        <v>7807</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>7806</v>
+        <v>7808</v>
       </c>
       <c r="C119" s="28"/>
       <c r="D119" s="1" t="s">
-        <v>7784</v>
+        <v>7786</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>7807</v>
+        <v>7809</v>
       </c>
       <c r="F119" s="51" t="s">
         <v>7706</v>
@@ -84305,27 +84342,27 @@
         <v>44776</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>7808</v>
+        <v>7810</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>7809</v>
+        <v>7811</v>
       </c>
       <c r="D120" s="28" t="s">
-        <v>7810</v>
+        <v>7812</v>
       </c>
       <c r="E120" s="28" t="s">
-        <v>7811</v>
+        <v>7813</v>
       </c>
       <c r="F120" s="28" t="s">
-        <v>7812</v>
+        <v>7814</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>7813</v>
-      </c>
-    </row>
-    <row r="123" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7815</v>
+      </c>
+    </row>
+    <row r="123" s="56" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="47" t="s">
-        <v>7814</v>
+        <v>7816</v>
       </c>
       <c r="B123" s="28"/>
       <c r="C123" s="1"/>
@@ -84357,134 +84394,134 @@
       <c r="AC123" s="1"/>
       <c r="AD123" s="1"/>
     </row>
-    <row r="124" s="55" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="56" t="n">
+    <row r="124" s="56" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="57" t="n">
         <v>45004</v>
       </c>
-      <c r="B124" s="55" t="s">
-        <v>7815</v>
-      </c>
-      <c r="C124" s="55" t="s">
-        <v>7816</v>
-      </c>
-      <c r="D124" s="55" t="s">
+      <c r="B124" s="56" t="s">
         <v>7817</v>
       </c>
-      <c r="E124" s="55" t="s">
+      <c r="C124" s="56" t="s">
         <v>7818</v>
       </c>
-      <c r="F124" s="57" t="s">
+      <c r="D124" s="56" t="s">
         <v>7819</v>
       </c>
-      <c r="G124" s="55" t="s">
+      <c r="E124" s="56" t="s">
         <v>7820</v>
       </c>
-    </row>
-    <row r="125" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="56" t="n">
+      <c r="F124" s="58" t="s">
+        <v>7821</v>
+      </c>
+      <c r="G124" s="56" t="s">
+        <v>7822</v>
+      </c>
+    </row>
+    <row r="125" s="56" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="57" t="n">
         <v>45005</v>
       </c>
-      <c r="B125" s="57" t="s">
-        <v>7821</v>
-      </c>
-      <c r="C125" s="55" t="s">
-        <v>7822</v>
-      </c>
-      <c r="D125" s="55" t="s">
+      <c r="B125" s="58" t="s">
         <v>7823</v>
       </c>
-      <c r="E125" s="55" t="s">
+      <c r="C125" s="56" t="s">
         <v>7824</v>
       </c>
-      <c r="F125" s="57" t="s">
+      <c r="D125" s="56" t="s">
         <v>7825</v>
       </c>
-      <c r="G125" s="55" t="s">
+      <c r="E125" s="56" t="s">
         <v>7826</v>
       </c>
-    </row>
-    <row r="126" s="55" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="56" t="n">
+      <c r="F125" s="58" t="s">
+        <v>7827</v>
+      </c>
+      <c r="G125" s="56" t="s">
+        <v>7828</v>
+      </c>
+    </row>
+    <row r="126" s="56" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="57" t="n">
         <v>45006</v>
       </c>
-      <c r="B126" s="55" t="s">
-        <v>7815</v>
-      </c>
-      <c r="C126" s="55" t="s">
-        <v>7827</v>
-      </c>
-      <c r="D126" s="55" t="s">
-        <v>7828</v>
-      </c>
-      <c r="E126" s="58" t="s">
+      <c r="B126" s="56" t="s">
+        <v>7817</v>
+      </c>
+      <c r="C126" s="56" t="s">
         <v>7829</v>
       </c>
-      <c r="F126" s="57" t="s">
+      <c r="D126" s="56" t="s">
         <v>7830</v>
       </c>
-      <c r="G126" s="55" t="s">
+      <c r="E126" s="59" t="s">
         <v>7831</v>
       </c>
+      <c r="F126" s="58" t="s">
+        <v>7832</v>
+      </c>
+      <c r="G126" s="56" t="s">
+        <v>7833</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="56" t="n">
+      <c r="A127" s="57" t="n">
         <v>45036</v>
       </c>
-      <c r="B127" s="55" t="s">
-        <v>7832</v>
-      </c>
-      <c r="C127" s="55"/>
-      <c r="D127" s="55" t="s">
-        <v>7833</v>
-      </c>
-      <c r="E127" s="55" t="s">
+      <c r="B127" s="56" t="s">
         <v>7834</v>
       </c>
-      <c r="F127" s="55" t="s">
+      <c r="C127" s="56"/>
+      <c r="D127" s="56" t="s">
         <v>7835</v>
       </c>
-      <c r="G127" s="55" t="s">
+      <c r="E127" s="56" t="s">
         <v>7836</v>
       </c>
-      <c r="H127" s="55"/>
-      <c r="I127" s="55"/>
-      <c r="J127" s="55"/>
-      <c r="K127" s="55"/>
-      <c r="L127" s="55"/>
-      <c r="M127" s="55"/>
-      <c r="N127" s="55"/>
-      <c r="O127" s="55"/>
-      <c r="P127" s="55"/>
-      <c r="Q127" s="55"/>
-      <c r="R127" s="55"/>
-      <c r="S127" s="55"/>
-      <c r="T127" s="55"/>
-      <c r="U127" s="55"/>
-      <c r="V127" s="55"/>
-      <c r="W127" s="55"/>
-      <c r="X127" s="55"/>
-      <c r="Y127" s="55"/>
-      <c r="Z127" s="55"/>
-      <c r="AA127" s="55"/>
-      <c r="AB127" s="55"/>
-      <c r="AC127" s="55"/>
-      <c r="AD127" s="55"/>
+      <c r="F127" s="56" t="s">
+        <v>7837</v>
+      </c>
+      <c r="G127" s="56" t="s">
+        <v>7838</v>
+      </c>
+      <c r="H127" s="56"/>
+      <c r="I127" s="56"/>
+      <c r="J127" s="56"/>
+      <c r="K127" s="56"/>
+      <c r="L127" s="56"/>
+      <c r="M127" s="56"/>
+      <c r="N127" s="56"/>
+      <c r="O127" s="56"/>
+      <c r="P127" s="56"/>
+      <c r="Q127" s="56"/>
+      <c r="R127" s="56"/>
+      <c r="S127" s="56"/>
+      <c r="T127" s="56"/>
+      <c r="U127" s="56"/>
+      <c r="V127" s="56"/>
+      <c r="W127" s="56"/>
+      <c r="X127" s="56"/>
+      <c r="Y127" s="56"/>
+      <c r="Z127" s="56"/>
+      <c r="AA127" s="56"/>
+      <c r="AB127" s="56"/>
+      <c r="AC127" s="56"/>
+      <c r="AD127" s="56"/>
     </row>
     <row r="128" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="59" t="n">
+      <c r="A128" s="60" t="n">
         <v>45088</v>
       </c>
       <c r="B128" s="48" t="s">
-        <v>7815</v>
+        <v>7817</v>
       </c>
       <c r="C128" s="48" t="s">
-        <v>7837</v>
+        <v>7839</v>
       </c>
       <c r="D128" s="48" t="s">
-        <v>7838</v>
-      </c>
-      <c r="E128" s="60" t="s">
-        <v>7839</v>
+        <v>7840</v>
+      </c>
+      <c r="E128" s="61" t="s">
+        <v>7841</v>
       </c>
       <c r="F128" s="48" t="s">
         <v>7549</v>
@@ -84494,28 +84531,28 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="59" t="n">
+      <c r="A129" s="60" t="n">
         <v>45025</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>7840</v>
+        <v>7842</v>
       </c>
       <c r="C129" s="28" t="s">
-        <v>7841</v>
+        <v>7843</v>
       </c>
       <c r="D129" s="43" t="s">
-        <v>7842</v>
+        <v>7844</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>7843</v>
+        <v>7845</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>7844</v>
+        <v>7846</v>
       </c>
     </row>
     <row r="131" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>7845</v>
+        <v>7847</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -84548,24 +84585,24 @@
       <c r="AD131" s="1"/>
     </row>
     <row r="132" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="61" t="n">
+      <c r="A132" s="62" t="n">
         <v>39252</v>
       </c>
       <c r="B132" s="41"/>
       <c r="C132" s="41" t="s">
-        <v>7846</v>
-      </c>
-      <c r="D132" s="62" t="s">
-        <v>7847</v>
+        <v>7848</v>
+      </c>
+      <c r="D132" s="63" t="s">
+        <v>7849</v>
       </c>
       <c r="E132" s="41" t="s">
-        <v>7848</v>
+        <v>7850</v>
       </c>
       <c r="F132" s="41" t="s">
-        <v>7849</v>
+        <v>7851</v>
       </c>
       <c r="G132" s="41" t="s">
-        <v>7850</v>
+        <v>7852</v>
       </c>
       <c r="H132" s="41"/>
       <c r="I132" s="41"/>
@@ -84596,59 +84633,59 @@
         <v>46241</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>7851</v>
+        <v>7853</v>
       </c>
       <c r="C133" s="28" t="s">
-        <v>7852</v>
+        <v>7854</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>7853</v>
+        <v>7855</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>7854</v>
+        <v>7856</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="47" t="s">
-        <v>7855</v>
+        <v>7857</v>
       </c>
       <c r="B134" s="28" t="s">
-        <v>7856</v>
+        <v>7858</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>7857</v>
+        <v>7859</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>7858</v>
+        <v>7860</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>7859</v>
+        <v>7861</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>7860</v>
+        <v>7862</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="54" t="n">
+      <c r="A135" s="55" t="n">
         <v>42866</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>7861</v>
+        <v>7863</v>
       </c>
       <c r="C135" s="28" t="s">
-        <v>7862</v>
+        <v>7864</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>7863</v>
+        <v>7865</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>7864</v>
+        <v>7866</v>
       </c>
       <c r="F135" s="28" t="s">
-        <v>7865</v>
+        <v>7867</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>7866</v>
+        <v>7868</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -84657,148 +84694,148 @@
         <v>7497</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>7867</v>
+        <v>7869</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>7868</v>
+        <v>7870</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="61" t="s">
-        <v>7869</v>
+      <c r="A142" s="62" t="s">
+        <v>7871</v>
       </c>
       <c r="B142" s="41" t="s">
-        <v>7870</v>
+        <v>7872</v>
       </c>
       <c r="C142" s="41" t="s">
-        <v>7871</v>
+        <v>7873</v>
       </c>
       <c r="D142" s="41"/>
       <c r="E142" s="41" t="s">
-        <v>7872</v>
+        <v>7874</v>
       </c>
       <c r="F142" s="41" t="s">
-        <v>7873</v>
+        <v>7875</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>7874</v>
+        <v>7876</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
+        <v>7877</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>7878</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>7879</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>7880</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>7881</v>
+      </c>
+      <c r="F143" s="48" t="s">
+        <v>7882</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>7883</v>
+      </c>
+    </row>
+    <row r="144" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="62" t="s">
+        <v>7884</v>
+      </c>
+      <c r="B144" s="41" t="s">
+        <v>7885</v>
+      </c>
+      <c r="C144" s="41" t="s">
+        <v>7886</v>
+      </c>
+      <c r="D144" s="63" t="s">
+        <v>7887</v>
+      </c>
+      <c r="E144" s="41" t="s">
+        <v>7888</v>
+      </c>
+      <c r="F144" s="41" t="s">
         <v>7875</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>7876</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>7877</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>7878</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>7879</v>
-      </c>
-      <c r="F143" s="48" t="s">
-        <v>7880</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>7881</v>
-      </c>
-    </row>
-    <row r="144" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="61" t="s">
-        <v>7882</v>
-      </c>
-      <c r="B144" s="41" t="s">
-        <v>7883</v>
-      </c>
-      <c r="C144" s="41" t="s">
-        <v>7884</v>
-      </c>
-      <c r="D144" s="62" t="s">
-        <v>7885</v>
-      </c>
-      <c r="E144" s="41" t="s">
-        <v>7886</v>
-      </c>
-      <c r="F144" s="41" t="s">
-        <v>7873</v>
-      </c>
       <c r="G144" s="41" t="s">
-        <v>7887</v>
+        <v>7889</v>
       </c>
     </row>
     <row r="145" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="63" t="n">
+      <c r="A145" s="64" t="n">
         <v>42355</v>
       </c>
       <c r="B145" s="41" t="s">
-        <v>7888</v>
+        <v>7890</v>
       </c>
       <c r="C145" s="41" t="s">
-        <v>7889</v>
+        <v>7891</v>
       </c>
       <c r="D145" s="41" t="s">
-        <v>7890</v>
+        <v>7892</v>
       </c>
       <c r="E145" s="41" t="s">
-        <v>7891</v>
+        <v>7893</v>
       </c>
       <c r="F145" s="41" t="s">
-        <v>7892</v>
+        <v>7894</v>
       </c>
     </row>
     <row r="146" s="41" customFormat="true" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="61" t="n">
+      <c r="A146" s="62" t="n">
         <v>43658</v>
       </c>
       <c r="B146" s="41" t="s">
-        <v>7893</v>
+        <v>7895</v>
       </c>
       <c r="C146" s="41" t="s">
-        <v>7894</v>
-      </c>
-      <c r="D146" s="62" t="s">
+        <v>7896</v>
+      </c>
+      <c r="D146" s="63" t="s">
+        <v>7897</v>
+      </c>
+      <c r="E146" s="41" t="s">
+        <v>7898</v>
+      </c>
+      <c r="F146" s="41" t="s">
         <v>7895</v>
       </c>
-      <c r="E146" s="41" t="s">
-        <v>7896</v>
-      </c>
-      <c r="F146" s="41" t="s">
-        <v>7893</v>
-      </c>
       <c r="G146" s="41" t="s">
-        <v>7897</v>
+        <v>7899</v>
       </c>
       <c r="AD146" s="41" t="s">
-        <v>7898</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="61" t="n">
+      <c r="A147" s="62" t="n">
         <v>45581</v>
       </c>
       <c r="B147" s="41" t="s">
-        <v>7899</v>
+        <v>7901</v>
       </c>
       <c r="C147" s="41" t="s">
-        <v>7900</v>
+        <v>7902</v>
       </c>
       <c r="D147" s="41" t="s">
+        <v>7903</v>
+      </c>
+      <c r="E147" s="63" t="s">
+        <v>7904</v>
+      </c>
+      <c r="F147" s="41" t="s">
         <v>7901</v>
       </c>
-      <c r="E147" s="62" t="s">
-        <v>7902</v>
-      </c>
-      <c r="F147" s="41" t="s">
-        <v>7899</v>
-      </c>
-      <c r="G147" s="64" t="s">
-        <v>7903</v>
+      <c r="G147" s="65" t="s">
+        <v>7905</v>
       </c>
       <c r="H147" s="41"/>
       <c r="I147" s="41"/>
@@ -84825,20 +84862,20 @@
       <c r="AD147" s="41"/>
     </row>
     <row r="148" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="63" t="n">
+      <c r="A148" s="64" t="n">
         <v>45668</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>7904</v>
+        <v>7906</v>
       </c>
       <c r="C148" s="28" t="s">
-        <v>7905</v>
+        <v>7907</v>
       </c>
       <c r="D148" s="28" t="s">
-        <v>7906</v>
+        <v>7908</v>
       </c>
       <c r="E148" s="49" t="s">
-        <v>7907</v>
+        <v>7909</v>
       </c>
       <c r="F148" s="28" t="s">
         <v>7625</v>
@@ -84849,182 +84886,225 @@
     </row>
     <row r="150" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>7908</v>
+        <v>7910</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="65" t="s">
-        <v>7909</v>
-      </c>
-      <c r="B151" s="66" t="s">
-        <v>7910</v>
+      <c r="A151" s="66" t="s">
+        <v>7911</v>
+      </c>
+      <c r="B151" s="67" t="s">
+        <v>7912</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>7911</v>
+        <v>7913</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>7865</v>
+        <v>7867</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>7912</v>
+        <v>7914</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="61" t="s">
-        <v>7913</v>
-      </c>
-      <c r="B152" s="66" t="s">
-        <v>7914</v>
+      <c r="A152" s="62" t="s">
+        <v>7915</v>
+      </c>
+      <c r="B152" s="67" t="s">
+        <v>7916</v>
       </c>
       <c r="C152" s="0"/>
       <c r="F152" s="1" t="s">
-        <v>7865</v>
+        <v>7867</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>7915</v>
+        <v>7917</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="65" t="s">
-        <v>7909</v>
-      </c>
-      <c r="B153" s="67" t="s">
-        <v>7916</v>
+      <c r="A153" s="66" t="s">
+        <v>7911</v>
+      </c>
+      <c r="B153" s="68" t="s">
+        <v>7918</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>7917</v>
+        <v>7919</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>7865</v>
+        <v>7867</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>7918</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="68" t="s">
-        <v>7919</v>
+      <c r="A154" s="69" t="s">
+        <v>7921</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>7920</v>
+        <v>7922</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>7921</v>
+        <v>7923</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>7922</v>
+        <v>7924</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>7898</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>7923</v>
-      </c>
-      <c r="B155" s="67" t="s">
+        <v>7925</v>
+      </c>
+      <c r="B155" s="68" t="s">
+        <v>7926</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>7927</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>7924</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>7925</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>7922</v>
-      </c>
       <c r="G155" s="1" t="s">
-        <v>7926</v>
+        <v>7928</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="69" t="s">
-        <v>7927</v>
+      <c r="A156" s="54" t="s">
+        <v>7929</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>7928</v>
+        <v>7930</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>7929</v>
+        <v>7931</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>7930</v>
+        <v>7932</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>7931</v>
+        <v>7933</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="45" t="s">
-        <v>7932</v>
+        <v>7934</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>7933</v>
+        <v>7935</v>
       </c>
       <c r="C157" s="49" t="s">
-        <v>7934</v>
+        <v>7936</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>7935</v>
+        <v>7937</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
-        <v>7923</v>
+        <v>7925</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>7936</v>
+        <v>7938</v>
       </c>
       <c r="C158" s="41" t="s">
-        <v>7937</v>
+        <v>7939</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>7938</v>
+        <v>7940</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>7922</v>
+        <v>7924</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>7926</v>
+        <v>7928</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="68" t="s">
-        <v>7939</v>
-      </c>
-      <c r="B159" s="68" t="s">
-        <v>7940</v>
+      <c r="A159" s="69" t="s">
+        <v>7941</v>
+      </c>
+      <c r="B159" s="69" t="s">
+        <v>7942</v>
       </c>
       <c r="C159" s="41" t="s">
-        <v>7941</v>
+        <v>7943</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>7942</v>
+        <v>7944</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>7922</v>
+        <v>7924</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>7943</v>
+        <v>7945</v>
       </c>
       <c r="H159" s="1"/>
     </row>
     <row r="160" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="65" t="s">
-        <v>7909</v>
+      <c r="A160" s="66" t="s">
+        <v>7911</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>7944</v>
+        <v>7946</v>
       </c>
       <c r="D160" s="28" t="s">
-        <v>7945</v>
+        <v>7947</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>7946</v>
+        <v>7948</v>
       </c>
       <c r="F160" s="43" t="s">
-        <v>7947</v>
+        <v>7949</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>7948</v>
+        <v>7950</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="54" t="s">
+        <v>7951</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>7952</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>7741</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>7867</v>
+      </c>
+      <c r="G164" s="67" t="s">
+        <v>7953</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
+        <v>7954</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>7955</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
+        <v>7956</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>7957</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="s">
+        <v>7958</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>7959</v>
       </c>
     </row>
   </sheetData>
@@ -85123,6 +85203,7 @@
     <hyperlink ref="B159" r:id="rId92" display="宗教文化出版社"/>
     <hyperlink ref="G159" r:id="rId93" display="https://product.dangdang.com/22497432.html"/>
     <hyperlink ref="G160" r:id="rId94" display="http://aiguji.net/3299.html"/>
+    <hyperlink ref="G164" r:id="rId95" display="https://book.kongfz.com/467603/10356350239"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -85152,7 +85233,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7949</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85163,7 +85244,7 @@
         <v>6766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7950</v>
+        <v>7961</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85174,7 +85255,7 @@
         <v>7140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7951</v>
+        <v>7962</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85185,7 +85266,7 @@
         <v>7442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7952</v>
+        <v>7963</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85196,7 +85277,7 @@
         <v>7181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7953</v>
+        <v>7964</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85207,55 +85288,55 @@
         <v>7329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7954</v>
+        <v>7965</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>7955</v>
+        <v>7966</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7956</v>
+        <v>7967</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>7957</v>
+        <v>7968</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7958</v>
+        <v>7969</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>7959</v>
+        <v>7970</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7960</v>
+        <v>7971</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>7961</v>
+        <v>7972</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>7962</v>
+        <v>7973</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>7963</v>
+        <v>7974</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7964</v>
+        <v>7975</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>7965</v>
+        <v>7976</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7966</v>
+        <v>7977</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85270,45 +85351,45 @@
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>7832</v>
+        <v>7834</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>7967</v>
+        <v>7978</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>7968</v>
+        <v>7979</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>7969</v>
+        <v>7980</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>7970</v>
+        <v>7981</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>7971</v>
+        <v>7982</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>7972</v>
+        <v>7983</v>
       </c>
       <c r="E23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>7973</v>
+        <v>7984</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>7974</v>
+        <v>7985</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
         <v>7663</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>7975</v>
+        <v>7986</v>
       </c>
     </row>
   </sheetData>
@@ -85341,83 +85422,83 @@
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="72" t="s">
-        <v>7976</v>
+        <v>7987</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="72" t="s">
-        <v>7977</v>
+        <v>7988</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="72" t="s">
-        <v>7978</v>
+        <v>7989</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="73" t="s">
-        <v>7979</v>
+        <v>7990</v>
       </c>
       <c r="B12" s="74" t="n">
         <v>45735</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>7980</v>
+        <v>7991</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>7981</v>
+        <v>7992</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="73" t="s">
-        <v>7982</v>
+        <v>7993</v>
       </c>
       <c r="B13" s="74" t="n">
         <v>45970</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>7983</v>
+        <v>7994</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>7984</v>
+        <v>7995</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="73" t="s">
-        <v>7985</v>
+        <v>7996</v>
       </c>
       <c r="B14" s="74" t="n">
         <v>45995</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>7986</v>
+        <v>7997</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>7987</v>
+        <v>7998</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="73" t="s">
-        <v>7988</v>
+        <v>7999</v>
       </c>
       <c r="B15" s="74" t="n">
         <v>46036</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>7989</v>
+        <v>8000</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>7990</v>
+        <v>8001</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>7991</v>
+        <v>8002</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>7992</v>
+        <v>8003</v>
       </c>
     </row>
   </sheetData>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10849" uniqueCount="8004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10852" uniqueCount="8006">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -26492,6 +26492,12 @@
     <t xml:space="preserve">延藏法师向我馆捐赠《清敕修大藏经》 </t>
   </si>
   <si>
+    <t xml:space="preserve">少林寺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -27294,9 +27300,6 @@
   <si>
     <t xml:space="preserve">采用简体横排的方式，所收佛经进行详细分段、加现代标点，采用现代排印、书册本与电子版配套的方式出版，使之更加符合现代人的阅读习惯 
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">少林寺</t>
   </si>
   <si>
     <t xml:space="preserve">少林寺方丈释永信大和尚，广西人文社会科学发展研究中心汉文大藏经研究院院长韩欣先生，善品堂创始人兼董事长何德益先生，少林文化研究资深学者、出版家李阳泉先生，作曲家张鹤女士等，共同见证了此次全本《乾隆大藏经》线装版、精装版入藏少林寺仪式。 </t>
@@ -28567,6 +28570,9 @@
     <t xml:space="preserve">https://item.jd.com/10224400824653.html?extension_id=eyJhZCI6IjI2OCIsImNoIjoiMiIsInNrdSI6IjEwMjI0NDAwODI0NjUzIiwidHMiOiIxNzkxMTAzNDYxIiwidW5pcWlkIjoie1wiY2xpY2tfaWRcIjpcIjYyNzVjOGU5LTAzZWItNDM4ZC04YzU1LTFjOWMzYWYxNGQ3ZlwiLFwibWF0ZXJpYWxfaWRcIjpcIjgzNjM4NjM0MDk0NDE1NzM1ODJcIixcInBvc19pZFwiOlwiMjY4XCIsXCJzaWRcIjpcImNjMjMzZjcyLWFiY2MtNDdhMi1iYWZjLTNmY2Q3NDNlYmY5ZFwifSJ9&amp;jd_pop=6275c8e9-03eb-438d-8c55-1c9c3af14d7f&amp;abt=0</t>
   </si>
   <si>
+    <t xml:space="preserve">《至元辨伪录》 </t>
+  </si>
+  <si>
     <t xml:space="preserve">此土注释</t>
   </si>
   <si>
@@ -28847,6 +28853,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF2A6099"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -28870,13 +28883,6 @@
       <sz val="10"/>
       <color rgb="FFFF4000"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -29126,7 +29132,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29347,6 +29353,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29363,7 +29373,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -29383,11 +29393,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -29395,7 +29405,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -82450,7 +82460,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:AD169"/>
+  <dimension ref="A3:AD176"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.85"/>
@@ -84146,104 +84156,54 @@
       </c>
       <c r="E108" s="28"/>
       <c r="F108" s="28"/>
-      <c r="G108" s="2"/>
-    </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="47"/>
-      <c r="B110" s="28"/>
-      <c r="C110" s="28"/>
-      <c r="E110" s="28"/>
-      <c r="F110" s="28"/>
-      <c r="G110" s="2"/>
-    </row>
-    <row r="111" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="43" t="s">
+    </row>
+    <row r="109" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="47" t="n">
+        <v>41741</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>7779</v>
       </c>
-      <c r="B111" s="28"/>
-      <c r="C111" s="28"/>
-      <c r="E111" s="28"/>
-      <c r="F111" s="28"/>
-      <c r="G111" s="2"/>
-    </row>
-    <row r="112" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="55" t="s">
+      <c r="G109" s="55" t="s">
         <v>7780</v>
       </c>
-      <c r="B112" s="43" t="s">
+    </row>
+    <row r="110" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="47"/>
+      <c r="B113" s="28"/>
+      <c r="C113" s="28"/>
+      <c r="E113" s="28"/>
+      <c r="F113" s="28"/>
+      <c r="G113" s="2"/>
+    </row>
+    <row r="114" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="43" t="s">
         <v>7781</v>
       </c>
-      <c r="C112" s="28" t="s">
+      <c r="B114" s="28"/>
+      <c r="C114" s="28"/>
+      <c r="E114" s="28"/>
+      <c r="F114" s="28"/>
+      <c r="G114" s="2"/>
+    </row>
+    <row r="115" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="56" t="s">
         <v>7782</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E112" s="28" t="s">
-        <v>7705</v>
-      </c>
-      <c r="F112" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="55" t="s">
+      <c r="B115" s="43" t="s">
         <v>7783</v>
       </c>
-      <c r="B113" s="43" t="s">
+      <c r="C115" s="28" t="s">
         <v>7784</v>
-      </c>
-      <c r="C113" s="28" t="s">
-        <v>7785</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>7786</v>
-      </c>
-      <c r="F113" s="51" t="s">
-        <v>7706</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>7707</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="49" t="s">
-        <v>7787</v>
-      </c>
-      <c r="B114" s="52" t="s">
-        <v>7788</v>
-      </c>
-      <c r="C114" s="28" t="s">
-        <v>7789</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="F114" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="55" t="s">
-        <v>7790</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>7791</v>
-      </c>
-      <c r="C115" s="28" t="s">
-        <v>7792</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>7515</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>7793</v>
+        <v>7705</v>
       </c>
       <c r="F115" s="28" t="s">
         <v>7516</v>
@@ -84252,859 +84212,1054 @@
         <v>7517</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="55" t="s">
+    <row r="116" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="56" t="s">
+        <v>7785</v>
+      </c>
+      <c r="B116" s="43" t="s">
+        <v>7786</v>
+      </c>
+      <c r="C116" s="28" t="s">
+        <v>7787</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>7788</v>
+      </c>
+      <c r="F116" s="51" t="s">
+        <v>7706</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>7707</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="49" t="s">
+        <v>7789</v>
+      </c>
+      <c r="B117" s="52" t="s">
+        <v>7790</v>
+      </c>
+      <c r="C117" s="28" t="s">
+        <v>7791</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="F117" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="56" t="s">
+        <v>7792</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>7793</v>
+      </c>
+      <c r="C118" s="28" t="s">
         <v>7794</v>
       </c>
-      <c r="B116" s="28" t="s">
+      <c r="D118" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="E118" s="28" t="s">
         <v>7795</v>
       </c>
-      <c r="C116" s="28" t="s">
+      <c r="F118" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="56" t="s">
         <v>7796</v>
       </c>
-      <c r="E116" s="28"/>
-      <c r="F116" s="28" t="s">
+      <c r="B119" s="28" t="s">
+        <v>7797</v>
+      </c>
+      <c r="C119" s="28" t="s">
+        <v>7798</v>
+      </c>
+      <c r="E119" s="28"/>
+      <c r="F119" s="28" t="s">
         <v>7516</v>
       </c>
-      <c r="G116" s="2" t="s">
+      <c r="G119" s="2" t="s">
         <v>7517</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="55" t="s">
-        <v>7797</v>
-      </c>
-      <c r="B117" s="28" t="s">
-        <v>7798</v>
-      </c>
-      <c r="C117" s="28" t="s">
+    <row r="120" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="56" t="s">
         <v>7799</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>7786</v>
-      </c>
-      <c r="E117" s="1" t="s">
+      <c r="B120" s="28" t="s">
         <v>7800</v>
       </c>
-      <c r="F117" s="51" t="s">
+      <c r="C120" s="28" t="s">
+        <v>7801</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>7788</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>7802</v>
+      </c>
+      <c r="F120" s="51" t="s">
         <v>7706</v>
       </c>
-      <c r="G117" s="2" t="s">
+      <c r="G120" s="2" t="s">
         <v>7707</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="47" t="n">
+    <row r="121" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="47" t="n">
         <v>44662</v>
       </c>
-      <c r="B118" s="28" t="s">
-        <v>7801</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>7802</v>
-      </c>
-      <c r="D118" s="28" t="s">
+      <c r="B121" s="28" t="s">
         <v>7803</v>
       </c>
-      <c r="E118" s="28" t="s">
+      <c r="C121" s="1" t="s">
         <v>7804</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="D121" s="28" t="s">
         <v>7805</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="E121" s="28" t="s">
         <v>7806</v>
       </c>
-    </row>
-    <row r="119" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="55" t="s">
+      <c r="F121" s="1" t="s">
         <v>7807</v>
       </c>
-      <c r="B119" s="28" t="s">
+      <c r="G121" s="1" t="s">
         <v>7808</v>
       </c>
-      <c r="C119" s="28"/>
-      <c r="D119" s="1" t="s">
-        <v>7786</v>
-      </c>
-      <c r="E119" s="1" t="s">
+    </row>
+    <row r="122" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="56" t="s">
         <v>7809</v>
       </c>
-      <c r="F119" s="51" t="s">
+      <c r="B122" s="28" t="s">
+        <v>7810</v>
+      </c>
+      <c r="C122" s="28"/>
+      <c r="D122" s="1" t="s">
+        <v>7788</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>7811</v>
+      </c>
+      <c r="F122" s="51" t="s">
         <v>7706</v>
       </c>
-      <c r="G119" s="2" t="s">
+      <c r="G122" s="2" t="s">
         <v>7707</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="47" t="n">
+    <row r="123" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="47" t="n">
         <v>44776</v>
       </c>
-      <c r="B120" s="28" t="s">
-        <v>7810</v>
-      </c>
-      <c r="C120" s="28" t="s">
-        <v>7811</v>
-      </c>
-      <c r="D120" s="28" t="s">
+      <c r="B123" s="28" t="s">
         <v>7812</v>
       </c>
-      <c r="E120" s="28" t="s">
+      <c r="C123" s="28" t="s">
         <v>7813</v>
       </c>
-      <c r="F120" s="28" t="s">
+      <c r="D123" s="28" t="s">
         <v>7814</v>
       </c>
-      <c r="G120" s="2" t="s">
+      <c r="E123" s="28" t="s">
         <v>7815</v>
       </c>
-    </row>
-    <row r="123" s="56" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="47" t="s">
+      <c r="F123" s="28" t="s">
         <v>7816</v>
       </c>
-      <c r="B123" s="28"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="28"/>
-      <c r="G123" s="2"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-      <c r="K123" s="1"/>
-      <c r="L123" s="1"/>
-      <c r="M123" s="1"/>
-      <c r="N123" s="1"/>
-      <c r="O123" s="1"/>
-      <c r="P123" s="1"/>
-      <c r="Q123" s="1"/>
-      <c r="R123" s="1"/>
-      <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
-      <c r="U123" s="1"/>
-      <c r="V123" s="1"/>
-      <c r="W123" s="1"/>
-      <c r="X123" s="1"/>
-      <c r="Y123" s="1"/>
-      <c r="Z123" s="1"/>
-      <c r="AA123" s="1"/>
-      <c r="AB123" s="1"/>
-      <c r="AC123" s="1"/>
-      <c r="AD123" s="1"/>
-    </row>
-    <row r="124" s="56" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="57" t="n">
+      <c r="G123" s="2" t="s">
+        <v>7817</v>
+      </c>
+    </row>
+    <row r="125" s="57" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="0"/>
+      <c r="H125" s="0"/>
+      <c r="I125" s="0"/>
+      <c r="J125" s="0"/>
+      <c r="K125" s="0"/>
+      <c r="L125" s="0"/>
+      <c r="M125" s="0"/>
+      <c r="N125" s="0"/>
+      <c r="O125" s="0"/>
+      <c r="P125" s="0"/>
+      <c r="Q125" s="0"/>
+      <c r="R125" s="0"/>
+      <c r="S125" s="0"/>
+      <c r="T125" s="0"/>
+      <c r="U125" s="0"/>
+      <c r="V125" s="0"/>
+      <c r="W125" s="0"/>
+      <c r="X125" s="0"/>
+      <c r="Y125" s="0"/>
+      <c r="Z125" s="0"/>
+      <c r="AA125" s="0"/>
+      <c r="AB125" s="0"/>
+      <c r="AC125" s="0"/>
+      <c r="AD125" s="0"/>
+    </row>
+    <row r="126" s="57" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="47" t="s">
+        <v>7818</v>
+      </c>
+      <c r="B126" s="28"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="28"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+      <c r="K126" s="1"/>
+      <c r="L126" s="1"/>
+      <c r="M126" s="1"/>
+      <c r="N126" s="1"/>
+      <c r="O126" s="1"/>
+      <c r="P126" s="1"/>
+      <c r="Q126" s="1"/>
+      <c r="R126" s="1"/>
+      <c r="S126" s="1"/>
+      <c r="T126" s="1"/>
+      <c r="U126" s="1"/>
+      <c r="V126" s="1"/>
+      <c r="W126" s="1"/>
+      <c r="X126" s="1"/>
+      <c r="Y126" s="1"/>
+      <c r="Z126" s="1"/>
+      <c r="AA126" s="1"/>
+      <c r="AB126" s="1"/>
+      <c r="AC126" s="1"/>
+      <c r="AD126" s="1"/>
+    </row>
+    <row r="127" s="57" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="58" t="n">
         <v>45004</v>
       </c>
-      <c r="B124" s="56" t="s">
-        <v>7817</v>
-      </c>
-      <c r="C124" s="56" t="s">
-        <v>7818</v>
-      </c>
-      <c r="D124" s="56" t="s">
+      <c r="B127" s="57" t="s">
         <v>7819</v>
       </c>
-      <c r="E124" s="56" t="s">
+      <c r="C127" s="57" t="s">
         <v>7820</v>
       </c>
-      <c r="F124" s="58" t="s">
+      <c r="D127" s="57" t="s">
         <v>7821</v>
       </c>
-      <c r="G124" s="56" t="s">
+      <c r="E127" s="57" t="s">
         <v>7822</v>
       </c>
-    </row>
-    <row r="125" s="56" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="57" t="n">
+      <c r="F127" s="59" t="s">
+        <v>7823</v>
+      </c>
+      <c r="G127" s="57" t="s">
+        <v>7824</v>
+      </c>
+    </row>
+    <row r="128" s="57" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="58" t="n">
         <v>45005</v>
       </c>
-      <c r="B125" s="58" t="s">
-        <v>7823</v>
-      </c>
-      <c r="C125" s="56" t="s">
-        <v>7824</v>
-      </c>
-      <c r="D125" s="56" t="s">
+      <c r="B128" s="59" t="s">
         <v>7825</v>
       </c>
-      <c r="E125" s="56" t="s">
+      <c r="C128" s="57" t="s">
         <v>7826</v>
       </c>
-      <c r="F125" s="58" t="s">
+      <c r="D128" s="57" t="s">
         <v>7827</v>
       </c>
-      <c r="G125" s="56" t="s">
+      <c r="E128" s="57" t="s">
         <v>7828</v>
       </c>
-    </row>
-    <row r="126" s="56" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="57" t="n">
+      <c r="F128" s="59" t="s">
+        <v>7829</v>
+      </c>
+      <c r="G128" s="57" t="s">
+        <v>7830</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="58" t="n">
         <v>45006</v>
       </c>
-      <c r="B126" s="56" t="s">
-        <v>7817</v>
-      </c>
-      <c r="C126" s="56" t="s">
-        <v>7829</v>
-      </c>
-      <c r="D126" s="56" t="s">
-        <v>7830</v>
-      </c>
-      <c r="E126" s="59" t="s">
+      <c r="B129" s="57" t="s">
+        <v>7819</v>
+      </c>
+      <c r="C129" s="57" t="s">
         <v>7831</v>
       </c>
-      <c r="F126" s="58" t="s">
+      <c r="D129" s="57" t="s">
         <v>7832</v>
       </c>
-      <c r="G126" s="56" t="s">
+      <c r="E129" s="60" t="s">
         <v>7833</v>
       </c>
-    </row>
-    <row r="127" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="57" t="n">
+      <c r="F129" s="59" t="s">
+        <v>7834</v>
+      </c>
+      <c r="G129" s="57" t="s">
+        <v>7835</v>
+      </c>
+      <c r="H129" s="57"/>
+      <c r="I129" s="57"/>
+      <c r="J129" s="57"/>
+      <c r="K129" s="57"/>
+      <c r="L129" s="57"/>
+      <c r="M129" s="57"/>
+      <c r="N129" s="57"/>
+      <c r="O129" s="57"/>
+      <c r="P129" s="57"/>
+      <c r="Q129" s="57"/>
+      <c r="R129" s="57"/>
+      <c r="S129" s="57"/>
+      <c r="T129" s="57"/>
+      <c r="U129" s="57"/>
+      <c r="V129" s="57"/>
+      <c r="W129" s="57"/>
+      <c r="X129" s="57"/>
+      <c r="Y129" s="57"/>
+      <c r="Z129" s="57"/>
+      <c r="AA129" s="57"/>
+      <c r="AB129" s="57"/>
+      <c r="AC129" s="57"/>
+      <c r="AD129" s="57"/>
+    </row>
+    <row r="130" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="58" t="n">
         <v>45036</v>
       </c>
-      <c r="B127" s="56" t="s">
-        <v>7834</v>
-      </c>
-      <c r="C127" s="56"/>
-      <c r="D127" s="56" t="s">
-        <v>7835</v>
-      </c>
-      <c r="E127" s="56" t="s">
+      <c r="B130" s="57" t="s">
         <v>7836</v>
       </c>
-      <c r="F127" s="56" t="s">
+      <c r="C130" s="57"/>
+      <c r="D130" s="57" t="s">
         <v>7837</v>
       </c>
-      <c r="G127" s="56" t="s">
+      <c r="E130" s="57" t="s">
         <v>7838</v>
       </c>
-      <c r="H127" s="56"/>
-      <c r="I127" s="56"/>
-      <c r="J127" s="56"/>
-      <c r="K127" s="56"/>
-      <c r="L127" s="56"/>
-      <c r="M127" s="56"/>
-      <c r="N127" s="56"/>
-      <c r="O127" s="56"/>
-      <c r="P127" s="56"/>
-      <c r="Q127" s="56"/>
-      <c r="R127" s="56"/>
-      <c r="S127" s="56"/>
-      <c r="T127" s="56"/>
-      <c r="U127" s="56"/>
-      <c r="V127" s="56"/>
-      <c r="W127" s="56"/>
-      <c r="X127" s="56"/>
-      <c r="Y127" s="56"/>
-      <c r="Z127" s="56"/>
-      <c r="AA127" s="56"/>
-      <c r="AB127" s="56"/>
-      <c r="AC127" s="56"/>
-      <c r="AD127" s="56"/>
-    </row>
-    <row r="128" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="60" t="n">
+      <c r="F130" s="57" t="s">
+        <v>7839</v>
+      </c>
+      <c r="G130" s="57" t="s">
+        <v>7840</v>
+      </c>
+      <c r="H130" s="57"/>
+      <c r="I130" s="57"/>
+      <c r="J130" s="57"/>
+      <c r="K130" s="57"/>
+      <c r="L130" s="57"/>
+      <c r="M130" s="57"/>
+      <c r="N130" s="57"/>
+      <c r="O130" s="57"/>
+      <c r="P130" s="57"/>
+      <c r="Q130" s="57"/>
+      <c r="R130" s="57"/>
+      <c r="S130" s="57"/>
+      <c r="T130" s="57"/>
+      <c r="U130" s="57"/>
+      <c r="V130" s="57"/>
+      <c r="W130" s="57"/>
+      <c r="X130" s="57"/>
+      <c r="Y130" s="57"/>
+      <c r="Z130" s="57"/>
+      <c r="AA130" s="57"/>
+      <c r="AB130" s="57"/>
+      <c r="AC130" s="57"/>
+      <c r="AD130" s="57"/>
+    </row>
+    <row r="131" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="61" t="n">
         <v>45088</v>
       </c>
-      <c r="B128" s="48" t="s">
-        <v>7817</v>
-      </c>
-      <c r="C128" s="48" t="s">
-        <v>7839</v>
-      </c>
-      <c r="D128" s="48" t="s">
-        <v>7840</v>
-      </c>
-      <c r="E128" s="61" t="s">
+      <c r="B131" s="48" t="s">
+        <v>7819</v>
+      </c>
+      <c r="C131" s="48" t="s">
         <v>7841</v>
       </c>
-      <c r="F128" s="48" t="s">
+      <c r="D131" s="48" t="s">
+        <v>7842</v>
+      </c>
+      <c r="E131" s="62" t="s">
+        <v>7843</v>
+      </c>
+      <c r="F131" s="48" t="s">
         <v>7549</v>
       </c>
-      <c r="G128" s="48" t="s">
+      <c r="G131" s="48" t="s">
         <v>7550</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="60" t="n">
+    <row r="132" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="61" t="n">
         <v>45025</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>7842</v>
-      </c>
-      <c r="C129" s="28" t="s">
-        <v>7843</v>
-      </c>
-      <c r="D129" s="43" t="s">
+      <c r="B132" s="1" t="s">
+        <v>7779</v>
+      </c>
+      <c r="C132" s="28" t="s">
         <v>7844</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="D132" s="43" t="s">
         <v>7845</v>
       </c>
-      <c r="G129" s="1" t="s">
+      <c r="F132" s="1" t="s">
         <v>7846</v>
       </c>
-    </row>
-    <row r="131" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1" t="s">
+      <c r="G132" s="1" t="s">
         <v>7847</v>
       </c>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
-      <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-      <c r="K131" s="1"/>
-      <c r="L131" s="1"/>
-      <c r="M131" s="1"/>
-      <c r="N131" s="1"/>
-      <c r="O131" s="1"/>
-      <c r="P131" s="1"/>
-      <c r="Q131" s="1"/>
-      <c r="R131" s="1"/>
-      <c r="S131" s="1"/>
-      <c r="T131" s="1"/>
-      <c r="U131" s="1"/>
-      <c r="V131" s="1"/>
-      <c r="W131" s="1"/>
-      <c r="X131" s="1"/>
-      <c r="Y131" s="1"/>
-      <c r="Z131" s="1"/>
-      <c r="AA131" s="1"/>
-      <c r="AB131" s="1"/>
-      <c r="AC131" s="1"/>
-      <c r="AD131" s="1"/>
-    </row>
-    <row r="132" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="62" t="n">
+    </row>
+    <row r="133" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+      <c r="F133" s="1"/>
+      <c r="G133" s="0"/>
+      <c r="H133" s="0"/>
+      <c r="I133" s="0"/>
+      <c r="J133" s="0"/>
+      <c r="K133" s="0"/>
+      <c r="L133" s="0"/>
+      <c r="M133" s="0"/>
+      <c r="N133" s="0"/>
+      <c r="O133" s="0"/>
+      <c r="P133" s="0"/>
+      <c r="Q133" s="0"/>
+      <c r="R133" s="0"/>
+      <c r="S133" s="0"/>
+      <c r="T133" s="0"/>
+      <c r="U133" s="0"/>
+      <c r="V133" s="0"/>
+      <c r="W133" s="0"/>
+      <c r="X133" s="0"/>
+      <c r="Y133" s="0"/>
+      <c r="Z133" s="0"/>
+      <c r="AA133" s="0"/>
+      <c r="AB133" s="0"/>
+      <c r="AC133" s="0"/>
+      <c r="AD133" s="0"/>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>7848</v>
+      </c>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+      <c r="L134" s="1"/>
+      <c r="M134" s="1"/>
+      <c r="N134" s="1"/>
+      <c r="O134" s="1"/>
+      <c r="P134" s="1"/>
+      <c r="Q134" s="1"/>
+      <c r="R134" s="1"/>
+      <c r="S134" s="1"/>
+      <c r="T134" s="1"/>
+      <c r="U134" s="1"/>
+      <c r="V134" s="1"/>
+      <c r="W134" s="1"/>
+      <c r="X134" s="1"/>
+      <c r="Y134" s="1"/>
+      <c r="Z134" s="1"/>
+      <c r="AA134" s="1"/>
+      <c r="AB134" s="1"/>
+      <c r="AC134" s="1"/>
+      <c r="AD134" s="1"/>
+    </row>
+    <row r="135" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="63" t="n">
         <v>39252</v>
       </c>
-      <c r="B132" s="41"/>
-      <c r="C132" s="41" t="s">
-        <v>7848</v>
-      </c>
-      <c r="D132" s="63" t="s">
+      <c r="B135" s="41"/>
+      <c r="C135" s="41" t="s">
         <v>7849</v>
       </c>
-      <c r="E132" s="41" t="s">
+      <c r="D135" s="64" t="s">
         <v>7850</v>
       </c>
-      <c r="F132" s="41" t="s">
+      <c r="E135" s="41" t="s">
         <v>7851</v>
       </c>
-      <c r="G132" s="41" t="s">
+      <c r="F135" s="41" t="s">
         <v>7852</v>
       </c>
-      <c r="H132" s="41"/>
-      <c r="I132" s="41"/>
-      <c r="J132" s="41"/>
-      <c r="K132" s="41"/>
-      <c r="L132" s="41"/>
-      <c r="M132" s="41"/>
-      <c r="N132" s="41"/>
-      <c r="O132" s="41"/>
-      <c r="P132" s="41"/>
-      <c r="Q132" s="41"/>
-      <c r="R132" s="41"/>
-      <c r="S132" s="41"/>
-      <c r="T132" s="41"/>
-      <c r="U132" s="41"/>
-      <c r="V132" s="41"/>
-      <c r="W132" s="41"/>
-      <c r="X132" s="41"/>
-      <c r="Y132" s="41"/>
-      <c r="Z132" s="41"/>
-      <c r="AA132" s="41"/>
-      <c r="AB132" s="41"/>
-      <c r="AC132" s="41"/>
-      <c r="AD132" s="41"/>
-    </row>
-    <row r="133" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="47" t="n">
+      <c r="G135" s="41" t="s">
+        <v>7853</v>
+      </c>
+      <c r="H135" s="41"/>
+      <c r="I135" s="41"/>
+      <c r="J135" s="41"/>
+      <c r="K135" s="41"/>
+      <c r="L135" s="41"/>
+      <c r="M135" s="41"/>
+      <c r="N135" s="41"/>
+      <c r="O135" s="41"/>
+      <c r="P135" s="41"/>
+      <c r="Q135" s="41"/>
+      <c r="R135" s="41"/>
+      <c r="S135" s="41"/>
+      <c r="T135" s="41"/>
+      <c r="U135" s="41"/>
+      <c r="V135" s="41"/>
+      <c r="W135" s="41"/>
+      <c r="X135" s="41"/>
+      <c r="Y135" s="41"/>
+      <c r="Z135" s="41"/>
+      <c r="AA135" s="41"/>
+      <c r="AB135" s="41"/>
+      <c r="AC135" s="41"/>
+      <c r="AD135" s="41"/>
+    </row>
+    <row r="136" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="47" t="n">
         <v>46241</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>7853</v>
-      </c>
-      <c r="C133" s="28" t="s">
+      <c r="B136" s="1" t="s">
         <v>7854</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="C136" s="28" t="s">
         <v>7855</v>
       </c>
-      <c r="G133" s="1" t="s">
+      <c r="F136" s="1" t="s">
         <v>7856</v>
       </c>
-    </row>
-    <row r="134" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="47" t="s">
+      <c r="G136" s="1" t="s">
         <v>7857</v>
       </c>
-      <c r="B134" s="28" t="s">
+    </row>
+    <row r="137" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="47" t="s">
         <v>7858</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="B137" s="28" t="s">
         <v>7859</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="C137" s="1" t="s">
         <v>7860</v>
       </c>
-      <c r="F134" s="28" t="s">
+      <c r="D137" s="1" t="s">
         <v>7861</v>
       </c>
-      <c r="G134" s="2" t="s">
+      <c r="F137" s="28" t="s">
         <v>7862</v>
       </c>
-    </row>
-    <row r="135" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="55" t="n">
+      <c r="G137" s="2" t="s">
+        <v>7863</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="56" t="n">
         <v>42866</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>7863</v>
-      </c>
-      <c r="C135" s="28" t="s">
+      <c r="B138" s="1" t="s">
         <v>7864</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="C138" s="28" t="s">
         <v>7865</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="D138" s="1" t="s">
         <v>7866</v>
       </c>
-      <c r="F135" s="28" t="s">
+      <c r="E138" s="1" t="s">
         <v>7867</v>
       </c>
-      <c r="G135" s="2" t="s">
+      <c r="F138" s="28" t="s">
         <v>7868</v>
       </c>
-    </row>
-    <row r="137" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="138" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2" t="s">
+      <c r="G138" s="2" t="s">
+        <v>7869</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="141" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
         <v>7497</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>7869</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1" t="s">
+      <c r="B141" s="1" t="s">
         <v>7870</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="62" t="s">
+    <row r="144" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
         <v>7871</v>
       </c>
-      <c r="B142" s="41" t="s">
+    </row>
+    <row r="145" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="63" t="s">
         <v>7872</v>
       </c>
-      <c r="C142" s="41" t="s">
+      <c r="B145" s="41" t="s">
         <v>7873</v>
       </c>
-      <c r="D142" s="41"/>
-      <c r="E142" s="41" t="s">
+      <c r="C145" s="41" t="s">
         <v>7874</v>
       </c>
-      <c r="F142" s="41" t="s">
+      <c r="D145" s="41"/>
+      <c r="E145" s="41" t="s">
         <v>7875</v>
       </c>
-      <c r="G142" s="2" t="s">
+      <c r="F145" s="41" t="s">
         <v>7876</v>
       </c>
-    </row>
-    <row r="143" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="1" t="s">
+      <c r="G145" s="2" t="s">
         <v>7877</v>
       </c>
-      <c r="B143" s="1" t="s">
+    </row>
+    <row r="146" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
         <v>7878</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="B146" s="1" t="s">
         <v>7879</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="C146" s="1" t="s">
         <v>7880</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="D146" s="1" t="s">
         <v>7881</v>
       </c>
-      <c r="F143" s="48" t="s">
+      <c r="E146" s="1" t="s">
         <v>7882</v>
       </c>
-      <c r="G143" s="2" t="s">
+      <c r="F146" s="48" t="s">
         <v>7883</v>
       </c>
-    </row>
-    <row r="144" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="62" t="s">
+      <c r="G146" s="2" t="s">
         <v>7884</v>
       </c>
-      <c r="B144" s="41" t="s">
+      <c r="H146" s="0"/>
+      <c r="I146" s="0"/>
+      <c r="J146" s="0"/>
+      <c r="K146" s="0"/>
+      <c r="L146" s="0"/>
+      <c r="M146" s="0"/>
+      <c r="N146" s="0"/>
+      <c r="O146" s="0"/>
+      <c r="P146" s="0"/>
+      <c r="Q146" s="0"/>
+      <c r="R146" s="0"/>
+      <c r="S146" s="0"/>
+      <c r="T146" s="0"/>
+      <c r="U146" s="0"/>
+      <c r="V146" s="0"/>
+      <c r="W146" s="0"/>
+      <c r="X146" s="0"/>
+      <c r="Y146" s="0"/>
+      <c r="Z146" s="0"/>
+      <c r="AA146" s="0"/>
+      <c r="AB146" s="0"/>
+      <c r="AC146" s="0"/>
+      <c r="AD146" s="0"/>
+    </row>
+    <row r="147" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="63" t="s">
         <v>7885</v>
       </c>
-      <c r="C144" s="41" t="s">
+      <c r="B147" s="41" t="s">
         <v>7886</v>
       </c>
-      <c r="D144" s="63" t="s">
+      <c r="C147" s="41" t="s">
         <v>7887</v>
       </c>
-      <c r="E144" s="41" t="s">
+      <c r="D147" s="64" t="s">
         <v>7888</v>
       </c>
-      <c r="F144" s="41" t="s">
-        <v>7875</v>
-      </c>
-      <c r="G144" s="41" t="s">
+      <c r="E147" s="41" t="s">
         <v>7889</v>
       </c>
-    </row>
-    <row r="145" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="64" t="n">
+      <c r="F147" s="41" t="s">
+        <v>7876</v>
+      </c>
+      <c r="G147" s="41" t="s">
+        <v>7890</v>
+      </c>
+    </row>
+    <row r="148" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="65" t="n">
         <v>42355</v>
       </c>
-      <c r="B145" s="41" t="s">
-        <v>7890</v>
-      </c>
-      <c r="C145" s="41" t="s">
+      <c r="B148" s="41" t="s">
         <v>7891</v>
       </c>
-      <c r="D145" s="41" t="s">
+      <c r="C148" s="41" t="s">
         <v>7892</v>
       </c>
-      <c r="E145" s="41" t="s">
+      <c r="D148" s="41" t="s">
         <v>7893</v>
       </c>
-      <c r="F145" s="41" t="s">
+      <c r="E148" s="41" t="s">
         <v>7894</v>
       </c>
-    </row>
-    <row r="146" s="41" customFormat="true" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="62" t="n">
+      <c r="F148" s="41" t="s">
+        <v>7895</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="63" t="n">
         <v>43658</v>
       </c>
-      <c r="B146" s="41" t="s">
-        <v>7895</v>
-      </c>
-      <c r="C146" s="41" t="s">
+      <c r="B149" s="41" t="s">
         <v>7896</v>
       </c>
-      <c r="D146" s="63" t="s">
+      <c r="C149" s="41" t="s">
         <v>7897</v>
       </c>
-      <c r="E146" s="41" t="s">
+      <c r="D149" s="64" t="s">
         <v>7898</v>
       </c>
-      <c r="F146" s="41" t="s">
-        <v>7895</v>
-      </c>
-      <c r="G146" s="41" t="s">
+      <c r="E149" s="41" t="s">
         <v>7899</v>
       </c>
-      <c r="AD146" s="41" t="s">
+      <c r="F149" s="41" t="s">
+        <v>7896</v>
+      </c>
+      <c r="G149" s="41" t="s">
         <v>7900</v>
       </c>
-    </row>
-    <row r="147" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="62" t="n">
+      <c r="H149" s="41"/>
+      <c r="I149" s="41"/>
+      <c r="J149" s="41"/>
+      <c r="K149" s="41"/>
+      <c r="L149" s="41"/>
+      <c r="M149" s="41"/>
+      <c r="N149" s="41"/>
+      <c r="O149" s="41"/>
+      <c r="P149" s="41"/>
+      <c r="Q149" s="41"/>
+      <c r="R149" s="41"/>
+      <c r="S149" s="41"/>
+      <c r="T149" s="41"/>
+      <c r="U149" s="41"/>
+      <c r="V149" s="41"/>
+      <c r="W149" s="41"/>
+      <c r="X149" s="41"/>
+      <c r="Y149" s="41"/>
+      <c r="Z149" s="41"/>
+      <c r="AA149" s="41"/>
+      <c r="AB149" s="41"/>
+      <c r="AC149" s="41"/>
+      <c r="AD149" s="41" t="s">
+        <v>7901</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="63" t="n">
         <v>45581</v>
       </c>
-      <c r="B147" s="41" t="s">
+      <c r="B150" s="41" t="s">
+        <v>7902</v>
+      </c>
+      <c r="C150" s="41" t="s">
+        <v>7903</v>
+      </c>
+      <c r="D150" s="41" t="s">
+        <v>7904</v>
+      </c>
+      <c r="E150" s="64" t="s">
+        <v>7905</v>
+      </c>
+      <c r="F150" s="41" t="s">
+        <v>7902</v>
+      </c>
+      <c r="G150" s="66" t="s">
+        <v>7906</v>
+      </c>
+      <c r="H150" s="41"/>
+      <c r="I150" s="41"/>
+      <c r="J150" s="41"/>
+      <c r="K150" s="41"/>
+      <c r="L150" s="41"/>
+      <c r="M150" s="41"/>
+      <c r="N150" s="41"/>
+      <c r="O150" s="41"/>
+      <c r="P150" s="41"/>
+      <c r="Q150" s="41"/>
+      <c r="R150" s="41"/>
+      <c r="S150" s="41"/>
+      <c r="T150" s="41"/>
+      <c r="U150" s="41"/>
+      <c r="V150" s="41"/>
+      <c r="W150" s="41"/>
+      <c r="X150" s="41"/>
+      <c r="Y150" s="41"/>
+      <c r="Z150" s="41"/>
+      <c r="AA150" s="41"/>
+      <c r="AB150" s="41"/>
+      <c r="AC150" s="41"/>
+      <c r="AD150" s="41"/>
+    </row>
+    <row r="151" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="65" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>7907</v>
+      </c>
+      <c r="C151" s="28" t="s">
+        <v>7908</v>
+      </c>
+      <c r="D151" s="28" t="s">
+        <v>7909</v>
+      </c>
+      <c r="E151" s="49" t="s">
+        <v>7910</v>
+      </c>
+      <c r="F151" s="28" t="s">
+        <v>7625</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>7626</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
+        <v>7911</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="67" t="s">
+        <v>7912</v>
+      </c>
+      <c r="B154" s="68" t="s">
+        <v>7913</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>7914</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>7868</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>7915</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="63" t="s">
+        <v>7916</v>
+      </c>
+      <c r="B155" s="68" t="s">
+        <v>7917</v>
+      </c>
+      <c r="C155" s="0"/>
+      <c r="F155" s="1" t="s">
+        <v>7868</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>7918</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="67" t="s">
+        <v>7912</v>
+      </c>
+      <c r="B156" s="69" t="s">
+        <v>7919</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>7920</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>7868</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>7921</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="70" t="s">
+        <v>7922</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>7923</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>7924</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>7925</v>
+      </c>
+      <c r="G157" s="2" t="s">
         <v>7901</v>
       </c>
-      <c r="C147" s="41" t="s">
-        <v>7902</v>
-      </c>
-      <c r="D147" s="41" t="s">
-        <v>7903</v>
-      </c>
-      <c r="E147" s="63" t="s">
-        <v>7904</v>
-      </c>
-      <c r="F147" s="41" t="s">
-        <v>7901</v>
-      </c>
-      <c r="G147" s="65" t="s">
-        <v>7905</v>
-      </c>
-      <c r="H147" s="41"/>
-      <c r="I147" s="41"/>
-      <c r="J147" s="41"/>
-      <c r="K147" s="41"/>
-      <c r="L147" s="41"/>
-      <c r="M147" s="41"/>
-      <c r="N147" s="41"/>
-      <c r="O147" s="41"/>
-      <c r="P147" s="41"/>
-      <c r="Q147" s="41"/>
-      <c r="R147" s="41"/>
-      <c r="S147" s="41"/>
-      <c r="T147" s="41"/>
-      <c r="U147" s="41"/>
-      <c r="V147" s="41"/>
-      <c r="W147" s="41"/>
-      <c r="X147" s="41"/>
-      <c r="Y147" s="41"/>
-      <c r="Z147" s="41"/>
-      <c r="AA147" s="41"/>
-      <c r="AB147" s="41"/>
-      <c r="AC147" s="41"/>
-      <c r="AD147" s="41"/>
-    </row>
-    <row r="148" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="64" t="n">
-        <v>45668</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>7906</v>
-      </c>
-      <c r="C148" s="28" t="s">
-        <v>7907</v>
-      </c>
-      <c r="D148" s="28" t="s">
-        <v>7908</v>
-      </c>
-      <c r="E148" s="49" t="s">
-        <v>7909</v>
-      </c>
-      <c r="F148" s="28" t="s">
-        <v>7625</v>
-      </c>
-      <c r="G148" s="2" t="s">
-        <v>7626</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1" t="s">
-        <v>7910</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="66" t="s">
-        <v>7911</v>
-      </c>
-      <c r="B151" s="67" t="s">
+    </row>
+    <row r="158" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="0" t="s">
+        <v>7926</v>
+      </c>
+      <c r="B158" s="69" t="s">
+        <v>7927</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>7928</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>7925</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>7929</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="54" t="s">
+        <v>7930</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>7931</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>7932</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>7933</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>7934</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="45" t="s">
+        <v>7935</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>7936</v>
+      </c>
+      <c r="C160" s="49" t="s">
+        <v>7937</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>7938</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="0" t="s">
+        <v>7926</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>7939</v>
+      </c>
+      <c r="C161" s="41" t="s">
+        <v>7940</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>7941</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>7925</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>7929</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="70" t="s">
+        <v>7942</v>
+      </c>
+      <c r="B162" s="70" t="s">
+        <v>7943</v>
+      </c>
+      <c r="C162" s="41" t="s">
+        <v>7944</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>7945</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>7925</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>7946</v>
+      </c>
+      <c r="H162" s="1"/>
+    </row>
+    <row r="163" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="67" t="s">
         <v>7912</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>7913</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>7867</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>7914</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="62" t="s">
-        <v>7915</v>
-      </c>
-      <c r="B152" s="67" t="s">
-        <v>7916</v>
-      </c>
-      <c r="C152" s="0"/>
-      <c r="F152" s="1" t="s">
-        <v>7867</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>7917</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="66" t="s">
-        <v>7911</v>
-      </c>
-      <c r="B153" s="68" t="s">
-        <v>7918</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>7919</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>7867</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>7920</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="69" t="s">
-        <v>7921</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>7922</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>7923</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>7924</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>7900</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="0" t="s">
-        <v>7925</v>
-      </c>
-      <c r="B155" s="68" t="s">
-        <v>7926</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>7927</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>7924</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>7928</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="54" t="s">
-        <v>7929</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>7930</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>7931</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>7932</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>7933</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="45" t="s">
-        <v>7934</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>7935</v>
-      </c>
-      <c r="C157" s="49" t="s">
-        <v>7936</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>7937</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0" t="s">
-        <v>7925</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>7938</v>
-      </c>
-      <c r="C158" s="41" t="s">
-        <v>7939</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>7940</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>7924</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>7928</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="69" t="s">
-        <v>7941</v>
-      </c>
-      <c r="B159" s="69" t="s">
-        <v>7942</v>
-      </c>
-      <c r="C159" s="41" t="s">
-        <v>7943</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>7944</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>7924</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>7945</v>
-      </c>
-      <c r="H159" s="1"/>
-    </row>
-    <row r="160" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="66" t="s">
-        <v>7911</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>7946</v>
-      </c>
-      <c r="D160" s="28" t="s">
+      <c r="B163" s="1" t="s">
         <v>7947</v>
       </c>
-      <c r="E160" s="1" t="s">
+      <c r="D163" s="28" t="s">
         <v>7948</v>
       </c>
-      <c r="F160" s="43" t="s">
+      <c r="E163" s="1" t="s">
         <v>7949</v>
       </c>
-      <c r="G160" s="2" t="s">
+      <c r="F163" s="43" t="s">
         <v>7950</v>
       </c>
-    </row>
-    <row r="163" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="54" t="s">
+      <c r="G163" s="2" t="s">
         <v>7951</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1" t="s">
+    <row r="166" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="54" t="s">
         <v>7952</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>7741</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>7867</v>
-      </c>
-      <c r="G164" s="67" t="s">
-        <v>7953</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
+        <v>7953</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>7741</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>7868</v>
+      </c>
+      <c r="G167" s="68" t="s">
         <v>7954</v>
       </c>
-      <c r="B167" s="1" t="s">
+    </row>
+    <row r="170" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="1" t="s">
         <v>7955</v>
       </c>
-    </row>
-    <row r="168" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="1" t="s">
+      <c r="B170" s="1" t="s">
         <v>7956</v>
       </c>
-      <c r="B168" s="1" t="s">
+    </row>
+    <row r="171" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="s">
         <v>7957</v>
       </c>
-    </row>
-    <row r="169" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="1" t="s">
+      <c r="B171" s="1" t="s">
         <v>7958</v>
       </c>
-      <c r="B169" s="1" t="s">
+    </row>
+    <row r="172" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="s">
         <v>7959</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>7960</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="54" t="s">
+        <v>7961</v>
       </c>
     </row>
   </sheetData>
@@ -85168,42 +85323,43 @@
     <hyperlink ref="G105" r:id="rId57" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
     <hyperlink ref="G106" r:id="rId58" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
     <hyperlink ref="G107" r:id="rId59" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
-    <hyperlink ref="G112" r:id="rId60" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G113" r:id="rId61" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G114" r:id="rId62" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G115" r:id="rId63" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G116" r:id="rId64" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G117" r:id="rId65" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G119" r:id="rId66" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G120" r:id="rId67" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
-    <hyperlink ref="G124" r:id="rId68" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
-    <hyperlink ref="F126" r:id="rId69" display="中新网北京3月21日电 (记者 应妮) "/>
-    <hyperlink ref="G126" r:id="rId70" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
-    <hyperlink ref="G128" r:id="rId71" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G132" r:id="rId72" display="https://discovery.cctv.com/20070619/107154.shtml"/>
-    <hyperlink ref="G135" r:id="rId73" display="https://book.kongfz.com/102740/682706591"/>
-    <hyperlink ref="A138" r:id="rId74" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G142" r:id="rId75" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
-    <hyperlink ref="G143" r:id="rId76" display="https://book.kongfz.com/20791/3754198261"/>
-    <hyperlink ref="G146" r:id="rId77" display="https://www.ljstsg.cn/?p=6315"/>
-    <hyperlink ref="AD146" r:id="rId78" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="G147" r:id="rId79" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
-    <hyperlink ref="G148" r:id="rId80" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="B151" r:id="rId81" display="全国图书馆文献缩微复制中心"/>
-    <hyperlink ref="G151" r:id="rId82" display="https://book.kongfz.com/536651/7839562954"/>
-    <hyperlink ref="B152" r:id="rId83" display="全国图书馆文献缩微复制中心"/>
-    <hyperlink ref="G152" r:id="rId84" display="https://book.kongfz.com/23231/8186709240"/>
-    <hyperlink ref="B153" r:id="rId85" display="全国图书馆文献缩微复制中心"/>
-    <hyperlink ref="G153" r:id="rId86" display="https://book.kongfz.com/536651/7839554296"/>
-    <hyperlink ref="G154" r:id="rId87" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="B155" r:id="rId88" display="中国书店"/>
-    <hyperlink ref="G156" r:id="rId89" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
-    <hyperlink ref="G157" r:id="rId90" display="https://book.kongfz.com/200249/1819262449/"/>
-    <hyperlink ref="G158" r:id="rId91" display="https://product.dangdang.com/11721366316.html"/>
-    <hyperlink ref="B159" r:id="rId92" display="宗教文化出版社"/>
-    <hyperlink ref="G159" r:id="rId93" display="https://product.dangdang.com/22497432.html"/>
-    <hyperlink ref="G160" r:id="rId94" display="http://aiguji.net/3299.html"/>
-    <hyperlink ref="G164" r:id="rId95" display="https://book.kongfz.com/467603/10356350239"/>
+    <hyperlink ref="G109" r:id="rId60" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
+    <hyperlink ref="G115" r:id="rId61" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G116" r:id="rId62" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G117" r:id="rId63" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G118" r:id="rId64" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G119" r:id="rId65" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G120" r:id="rId66" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G122" r:id="rId67" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G123" r:id="rId68" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
+    <hyperlink ref="G127" r:id="rId69" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
+    <hyperlink ref="F129" r:id="rId70" display="中新网北京3月21日电 (记者 应妮) "/>
+    <hyperlink ref="G129" r:id="rId71" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
+    <hyperlink ref="G131" r:id="rId72" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G135" r:id="rId73" display="https://discovery.cctv.com/20070619/107154.shtml"/>
+    <hyperlink ref="G138" r:id="rId74" display="https://book.kongfz.com/102740/682706591"/>
+    <hyperlink ref="A141" r:id="rId75" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G145" r:id="rId76" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
+    <hyperlink ref="G146" r:id="rId77" display="https://book.kongfz.com/20791/3754198261"/>
+    <hyperlink ref="G149" r:id="rId78" display="https://www.ljstsg.cn/?p=6315"/>
+    <hyperlink ref="AD149" r:id="rId79" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="G150" r:id="rId80" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
+    <hyperlink ref="G151" r:id="rId81" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="B154" r:id="rId82" display="全国图书馆文献缩微复制中心"/>
+    <hyperlink ref="G154" r:id="rId83" display="https://book.kongfz.com/536651/7839562954"/>
+    <hyperlink ref="B155" r:id="rId84" display="全国图书馆文献缩微复制中心"/>
+    <hyperlink ref="G155" r:id="rId85" display="https://book.kongfz.com/23231/8186709240"/>
+    <hyperlink ref="B156" r:id="rId86" display="全国图书馆文献缩微复制中心"/>
+    <hyperlink ref="G156" r:id="rId87" display="https://book.kongfz.com/536651/7839554296"/>
+    <hyperlink ref="G157" r:id="rId88" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="B158" r:id="rId89" display="中国书店"/>
+    <hyperlink ref="G159" r:id="rId90" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
+    <hyperlink ref="G160" r:id="rId91" display="https://book.kongfz.com/200249/1819262449/"/>
+    <hyperlink ref="G161" r:id="rId92" display="https://product.dangdang.com/11721366316.html"/>
+    <hyperlink ref="B162" r:id="rId93" display="宗教文化出版社"/>
+    <hyperlink ref="G162" r:id="rId94" display="https://product.dangdang.com/22497432.html"/>
+    <hyperlink ref="G163" r:id="rId95" display="http://aiguji.net/3299.html"/>
+    <hyperlink ref="G167" r:id="rId96" display="https://book.kongfz.com/467603/10356350239"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -85223,120 +85379,120 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="70" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="71" width="12.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7960</v>
+        <v>7962</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="71" t="n">
+      <c r="A2" s="72" t="n">
         <v>1539</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7961</v>
+        <v>7963</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="71" t="n">
+      <c r="A3" s="72" t="n">
         <v>1615</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7962</v>
+        <v>7964</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="71" t="n">
+      <c r="A4" s="72" t="n">
         <v>1620</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7963</v>
+        <v>7965</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71" t="n">
+      <c r="A5" s="72" t="n">
         <v>1623</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7964</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71" t="n">
+      <c r="A6" s="72" t="n">
         <v>1653</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7965</v>
+        <v>7967</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>7966</v>
+        <v>7968</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7967</v>
+        <v>7969</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>7968</v>
+        <v>7970</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7969</v>
+        <v>7971</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>7970</v>
+        <v>7972</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7971</v>
+        <v>7973</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>7972</v>
+        <v>7974</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>7973</v>
+        <v>7975</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>7974</v>
+        <v>7976</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7975</v>
+        <v>7977</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>7976</v>
+        <v>7978</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7977</v>
+        <v>7979</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85351,45 +85507,45 @@
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>7834</v>
+        <v>7836</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>7978</v>
+        <v>7980</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>7979</v>
+        <v>7981</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>7980</v>
+        <v>7982</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>7981</v>
+        <v>7983</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>7982</v>
+        <v>7984</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>7983</v>
+        <v>7985</v>
       </c>
       <c r="E23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>7984</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>7985</v>
+        <v>7987</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
         <v>7663</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>7986</v>
+        <v>7988</v>
       </c>
     </row>
   </sheetData>
@@ -85421,84 +85577,84 @@
   </cols>
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="72" t="s">
-        <v>7987</v>
+      <c r="A8" s="73" t="s">
+        <v>7989</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="72" t="s">
-        <v>7988</v>
+      <c r="A9" s="73" t="s">
+        <v>7990</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="72" t="s">
-        <v>7989</v>
+      <c r="A10" s="73" t="s">
+        <v>7991</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="73" t="s">
-        <v>7990</v>
-      </c>
-      <c r="B12" s="74" t="n">
+      <c r="A12" s="74" t="s">
+        <v>7992</v>
+      </c>
+      <c r="B12" s="75" t="n">
         <v>45735</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>7991</v>
+        <v>7993</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>7992</v>
+        <v>7994</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="73" t="s">
-        <v>7993</v>
-      </c>
-      <c r="B13" s="74" t="n">
+      <c r="A13" s="74" t="s">
+        <v>7995</v>
+      </c>
+      <c r="B13" s="75" t="n">
         <v>45970</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>7994</v>
+        <v>7996</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>7995</v>
+        <v>7997</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="73" t="s">
-        <v>7996</v>
-      </c>
-      <c r="B14" s="74" t="n">
+      <c r="A14" s="74" t="s">
+        <v>7998</v>
+      </c>
+      <c r="B14" s="75" t="n">
         <v>45995</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>7997</v>
+        <v>7999</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>7998</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="73" t="s">
-        <v>7999</v>
-      </c>
-      <c r="B15" s="74" t="n">
+      <c r="A15" s="74" t="s">
+        <v>8001</v>
+      </c>
+      <c r="B15" s="75" t="n">
         <v>46036</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>8000</v>
+        <v>8002</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>8001</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>8002</v>
+        <v>8004</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>8003</v>
+        <v>8005</v>
       </c>
     </row>
   </sheetData>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -27743,145 +27743,37 @@
     <t xml:space="preserve">年代: 不详</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">全国图书馆文献缩微复制中心</t>
-    </r>
+    <t xml:space="preserve">全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） </t>
+  </si>
+  <si>
+    <t xml:space="preserve">页码是一样的。就是我的版本缺了两页—居然。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://book.kongfz.com/536651/7839562954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年代: 2010年代 (2010-2019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://book.kongfz.com/23231/8186709240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">页码一样，千字号也一样。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://book.kongfz.com/536651/7839554296</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">出版，乾隆大藏经第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">149</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">册 此土著述（三九） </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">页码是一样的。就是我的版本缺了两页—居然。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://book.kongfz.com/536651/7839562954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">年代: 2010年代 (2010-2019)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">全国图书馆文献缩微复制中心</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">出版，乾隆大藏经第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">58</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">册 </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">https://book.kongfz.com/23231/8186709240</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">全国图书馆文献缩微复制中心</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">出版，乾隆大藏经第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">142</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">册 此土著述（三二）  </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">页码一样，千字号也一样。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://book.kongfz.com/536651/7839554296</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
@@ -27899,7 +27791,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="Noto Sans SC"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
@@ -27917,7 +27809,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="Noto Sans SC"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
@@ -27937,79 +27829,7 @@
     <t xml:space="preserve">2009年11月出版</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">中国书店</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">出版，乾隆大藏经</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">共</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">168</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">册</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 </t>
-    </r>
+    <t xml:space="preserve">中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 </t>
   </si>
   <si>
     <t xml:space="preserve">第25册页码是一样的。总目录照片—很多。</t>
@@ -28418,7 +28238,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="Noto Sans SC"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
@@ -28436,7 +28256,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="Noto Sans SC"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
@@ -28454,7 +28274,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="Noto Sans SC"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
@@ -28462,43 +28282,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">出版社</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">宗教文化出版社</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+    <t xml:space="preserve">出版社:宗教文化出版社 </t>
   </si>
   <si>
     <r>
@@ -28767,7 +28551,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\年m\月d\日"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
@@ -28853,13 +28637,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Noto Sans SC"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF2A6099"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -28889,7 +28666,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
-      <name val="Segoe UI"/>
+      <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -29132,7 +28909,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="70">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29349,14 +29126,6 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29373,7 +29142,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -29393,27 +29162,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -29429,11 +29186,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -82589,7 +82342,6 @@
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="28"/>
-      <c r="F12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
@@ -82660,7 +82412,7 @@
       <c r="C18" s="28" t="s">
         <v>7494</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>7495</v>
       </c>
       <c r="F18" s="43" t="s">
@@ -84151,7 +83903,7 @@
       <c r="B108" s="28" t="s">
         <v>7777</v>
       </c>
-      <c r="C108" s="54" t="s">
+      <c r="C108" s="43" t="s">
         <v>7778</v>
       </c>
       <c r="E108" s="28"/>
@@ -84164,13 +83916,10 @@
       <c r="B109" s="1" t="s">
         <v>7779</v>
       </c>
-      <c r="G109" s="55" t="s">
+      <c r="G109" s="2" t="s">
         <v>7780</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="111" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="112" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="47"/>
       <c r="B113" s="28"/>
@@ -84190,7 +83939,7 @@
       <c r="G114" s="2"/>
     </row>
     <row r="115" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="56" t="s">
+      <c r="A115" s="54" t="s">
         <v>7782</v>
       </c>
       <c r="B115" s="43" t="s">
@@ -84213,7 +83962,7 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="56" t="s">
+      <c r="A116" s="54" t="s">
         <v>7785</v>
       </c>
       <c r="B116" s="43" t="s">
@@ -84253,7 +84002,7 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="56" t="s">
+      <c r="A118" s="54" t="s">
         <v>7792</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -84276,7 +84025,7 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="56" t="s">
+      <c r="A119" s="54" t="s">
         <v>7796</v>
       </c>
       <c r="B119" s="28" t="s">
@@ -84294,7 +84043,7 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="56" t="s">
+      <c r="A120" s="54" t="s">
         <v>7799</v>
       </c>
       <c r="B120" s="28" t="s">
@@ -84340,7 +84089,7 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="56" t="s">
+      <c r="A122" s="54" t="s">
         <v>7809</v>
       </c>
       <c r="B122" s="28" t="s">
@@ -84383,39 +84132,39 @@
         <v>7817</v>
       </c>
     </row>
-    <row r="125" s="57" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" s="55" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
-      <c r="G125" s="0"/>
-      <c r="H125" s="0"/>
-      <c r="I125" s="0"/>
-      <c r="J125" s="0"/>
-      <c r="K125" s="0"/>
-      <c r="L125" s="0"/>
-      <c r="M125" s="0"/>
-      <c r="N125" s="0"/>
-      <c r="O125" s="0"/>
-      <c r="P125" s="0"/>
-      <c r="Q125" s="0"/>
-      <c r="R125" s="0"/>
-      <c r="S125" s="0"/>
-      <c r="T125" s="0"/>
-      <c r="U125" s="0"/>
-      <c r="V125" s="0"/>
-      <c r="W125" s="0"/>
-      <c r="X125" s="0"/>
-      <c r="Y125" s="0"/>
-      <c r="Z125" s="0"/>
-      <c r="AA125" s="0"/>
-      <c r="AB125" s="0"/>
-      <c r="AC125" s="0"/>
-      <c r="AD125" s="0"/>
-    </row>
-    <row r="126" s="57" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
+      <c r="K125" s="1"/>
+      <c r="L125" s="1"/>
+      <c r="M125" s="1"/>
+      <c r="N125" s="1"/>
+      <c r="O125" s="1"/>
+      <c r="P125" s="1"/>
+      <c r="Q125" s="1"/>
+      <c r="R125" s="1"/>
+      <c r="S125" s="1"/>
+      <c r="T125" s="1"/>
+      <c r="U125" s="1"/>
+      <c r="V125" s="1"/>
+      <c r="W125" s="1"/>
+      <c r="X125" s="1"/>
+      <c r="Y125" s="1"/>
+      <c r="Z125" s="1"/>
+      <c r="AA125" s="1"/>
+      <c r="AB125" s="1"/>
+      <c r="AC125" s="1"/>
+      <c r="AD125" s="1"/>
+    </row>
+    <row r="126" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="47" t="s">
         <v>7818</v>
       </c>
@@ -84449,144 +84198,144 @@
       <c r="AC126" s="1"/>
       <c r="AD126" s="1"/>
     </row>
-    <row r="127" s="57" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="58" t="n">
+    <row r="127" s="55" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="56" t="n">
         <v>45004</v>
       </c>
-      <c r="B127" s="57" t="s">
+      <c r="B127" s="55" t="s">
         <v>7819</v>
       </c>
-      <c r="C127" s="57" t="s">
+      <c r="C127" s="55" t="s">
         <v>7820</v>
       </c>
-      <c r="D127" s="57" t="s">
+      <c r="D127" s="55" t="s">
         <v>7821</v>
       </c>
-      <c r="E127" s="57" t="s">
+      <c r="E127" s="55" t="s">
         <v>7822</v>
       </c>
-      <c r="F127" s="59" t="s">
+      <c r="F127" s="57" t="s">
         <v>7823</v>
       </c>
-      <c r="G127" s="57" t="s">
+      <c r="G127" s="55" t="s">
         <v>7824</v>
       </c>
     </row>
-    <row r="128" s="57" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="58" t="n">
+    <row r="128" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="56" t="n">
         <v>45005</v>
       </c>
-      <c r="B128" s="59" t="s">
+      <c r="B128" s="57" t="s">
         <v>7825</v>
       </c>
-      <c r="C128" s="57" t="s">
+      <c r="C128" s="55" t="s">
         <v>7826</v>
       </c>
-      <c r="D128" s="57" t="s">
+      <c r="D128" s="55" t="s">
         <v>7827</v>
       </c>
-      <c r="E128" s="57" t="s">
+      <c r="E128" s="55" t="s">
         <v>7828</v>
       </c>
-      <c r="F128" s="59" t="s">
+      <c r="F128" s="57" t="s">
         <v>7829</v>
       </c>
-      <c r="G128" s="57" t="s">
+      <c r="G128" s="55" t="s">
         <v>7830</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="58" t="n">
+      <c r="A129" s="56" t="n">
         <v>45006</v>
       </c>
-      <c r="B129" s="57" t="s">
+      <c r="B129" s="55" t="s">
         <v>7819</v>
       </c>
-      <c r="C129" s="57" t="s">
+      <c r="C129" s="55" t="s">
         <v>7831</v>
       </c>
-      <c r="D129" s="57" t="s">
+      <c r="D129" s="55" t="s">
         <v>7832</v>
       </c>
-      <c r="E129" s="60" t="s">
+      <c r="E129" s="58" t="s">
         <v>7833</v>
       </c>
-      <c r="F129" s="59" t="s">
+      <c r="F129" s="57" t="s">
         <v>7834</v>
       </c>
-      <c r="G129" s="57" t="s">
+      <c r="G129" s="55" t="s">
         <v>7835</v>
       </c>
-      <c r="H129" s="57"/>
-      <c r="I129" s="57"/>
-      <c r="J129" s="57"/>
-      <c r="K129" s="57"/>
-      <c r="L129" s="57"/>
-      <c r="M129" s="57"/>
-      <c r="N129" s="57"/>
-      <c r="O129" s="57"/>
-      <c r="P129" s="57"/>
-      <c r="Q129" s="57"/>
-      <c r="R129" s="57"/>
-      <c r="S129" s="57"/>
-      <c r="T129" s="57"/>
-      <c r="U129" s="57"/>
-      <c r="V129" s="57"/>
-      <c r="W129" s="57"/>
-      <c r="X129" s="57"/>
-      <c r="Y129" s="57"/>
-      <c r="Z129" s="57"/>
-      <c r="AA129" s="57"/>
-      <c r="AB129" s="57"/>
-      <c r="AC129" s="57"/>
-      <c r="AD129" s="57"/>
+      <c r="H129" s="55"/>
+      <c r="I129" s="55"/>
+      <c r="J129" s="55"/>
+      <c r="K129" s="55"/>
+      <c r="L129" s="55"/>
+      <c r="M129" s="55"/>
+      <c r="N129" s="55"/>
+      <c r="O129" s="55"/>
+      <c r="P129" s="55"/>
+      <c r="Q129" s="55"/>
+      <c r="R129" s="55"/>
+      <c r="S129" s="55"/>
+      <c r="T129" s="55"/>
+      <c r="U129" s="55"/>
+      <c r="V129" s="55"/>
+      <c r="W129" s="55"/>
+      <c r="X129" s="55"/>
+      <c r="Y129" s="55"/>
+      <c r="Z129" s="55"/>
+      <c r="AA129" s="55"/>
+      <c r="AB129" s="55"/>
+      <c r="AC129" s="55"/>
+      <c r="AD129" s="55"/>
     </row>
     <row r="130" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="58" t="n">
+      <c r="A130" s="56" t="n">
         <v>45036</v>
       </c>
-      <c r="B130" s="57" t="s">
+      <c r="B130" s="55" t="s">
         <v>7836</v>
       </c>
-      <c r="C130" s="57"/>
-      <c r="D130" s="57" t="s">
+      <c r="C130" s="55"/>
+      <c r="D130" s="55" t="s">
         <v>7837</v>
       </c>
-      <c r="E130" s="57" t="s">
+      <c r="E130" s="55" t="s">
         <v>7838</v>
       </c>
-      <c r="F130" s="57" t="s">
+      <c r="F130" s="55" t="s">
         <v>7839</v>
       </c>
-      <c r="G130" s="57" t="s">
+      <c r="G130" s="55" t="s">
         <v>7840</v>
       </c>
-      <c r="H130" s="57"/>
-      <c r="I130" s="57"/>
-      <c r="J130" s="57"/>
-      <c r="K130" s="57"/>
-      <c r="L130" s="57"/>
-      <c r="M130" s="57"/>
-      <c r="N130" s="57"/>
-      <c r="O130" s="57"/>
-      <c r="P130" s="57"/>
-      <c r="Q130" s="57"/>
-      <c r="R130" s="57"/>
-      <c r="S130" s="57"/>
-      <c r="T130" s="57"/>
-      <c r="U130" s="57"/>
-      <c r="V130" s="57"/>
-      <c r="W130" s="57"/>
-      <c r="X130" s="57"/>
-      <c r="Y130" s="57"/>
-      <c r="Z130" s="57"/>
-      <c r="AA130" s="57"/>
-      <c r="AB130" s="57"/>
-      <c r="AC130" s="57"/>
-      <c r="AD130" s="57"/>
+      <c r="H130" s="55"/>
+      <c r="I130" s="55"/>
+      <c r="J130" s="55"/>
+      <c r="K130" s="55"/>
+      <c r="L130" s="55"/>
+      <c r="M130" s="55"/>
+      <c r="N130" s="55"/>
+      <c r="O130" s="55"/>
+      <c r="P130" s="55"/>
+      <c r="Q130" s="55"/>
+      <c r="R130" s="55"/>
+      <c r="S130" s="55"/>
+      <c r="T130" s="55"/>
+      <c r="U130" s="55"/>
+      <c r="V130" s="55"/>
+      <c r="W130" s="55"/>
+      <c r="X130" s="55"/>
+      <c r="Y130" s="55"/>
+      <c r="Z130" s="55"/>
+      <c r="AA130" s="55"/>
+      <c r="AB130" s="55"/>
+      <c r="AC130" s="55"/>
+      <c r="AD130" s="55"/>
     </row>
     <row r="131" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="61" t="n">
+      <c r="A131" s="59" t="n">
         <v>45088</v>
       </c>
       <c r="B131" s="48" t="s">
@@ -84598,7 +84347,7 @@
       <c r="D131" s="48" t="s">
         <v>7842</v>
       </c>
-      <c r="E131" s="62" t="s">
+      <c r="E131" s="60" t="s">
         <v>7843</v>
       </c>
       <c r="F131" s="48" t="s">
@@ -84609,7 +84358,7 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="61" t="n">
+      <c r="A132" s="59" t="n">
         <v>45025</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -84635,30 +84384,30 @@
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
-      <c r="G133" s="0"/>
-      <c r="H133" s="0"/>
-      <c r="I133" s="0"/>
-      <c r="J133" s="0"/>
-      <c r="K133" s="0"/>
-      <c r="L133" s="0"/>
-      <c r="M133" s="0"/>
-      <c r="N133" s="0"/>
-      <c r="O133" s="0"/>
-      <c r="P133" s="0"/>
-      <c r="Q133" s="0"/>
-      <c r="R133" s="0"/>
-      <c r="S133" s="0"/>
-      <c r="T133" s="0"/>
-      <c r="U133" s="0"/>
-      <c r="V133" s="0"/>
-      <c r="W133" s="0"/>
-      <c r="X133" s="0"/>
-      <c r="Y133" s="0"/>
-      <c r="Z133" s="0"/>
-      <c r="AA133" s="0"/>
-      <c r="AB133" s="0"/>
-      <c r="AC133" s="0"/>
-      <c r="AD133" s="0"/>
+      <c r="G133" s="1"/>
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="1"/>
+      <c r="K133" s="1"/>
+      <c r="L133" s="1"/>
+      <c r="M133" s="1"/>
+      <c r="N133" s="1"/>
+      <c r="O133" s="1"/>
+      <c r="P133" s="1"/>
+      <c r="Q133" s="1"/>
+      <c r="R133" s="1"/>
+      <c r="S133" s="1"/>
+      <c r="T133" s="1"/>
+      <c r="U133" s="1"/>
+      <c r="V133" s="1"/>
+      <c r="W133" s="1"/>
+      <c r="X133" s="1"/>
+      <c r="Y133" s="1"/>
+      <c r="Z133" s="1"/>
+      <c r="AA133" s="1"/>
+      <c r="AB133" s="1"/>
+      <c r="AC133" s="1"/>
+      <c r="AD133" s="1"/>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
@@ -84690,14 +84439,14 @@
       <c r="AD134" s="1"/>
     </row>
     <row r="135" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="63" t="n">
+      <c r="A135" s="61" t="n">
         <v>39252</v>
       </c>
       <c r="B135" s="41"/>
       <c r="C135" s="41" t="s">
         <v>7849</v>
       </c>
-      <c r="D135" s="64" t="s">
+      <c r="D135" s="62" t="s">
         <v>7850</v>
       </c>
       <c r="E135" s="41" t="s">
@@ -84771,7 +84520,7 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="56" t="n">
+      <c r="A138" s="54" t="n">
         <v>42866</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -84808,7 +84557,7 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="63" t="s">
+      <c r="A145" s="61" t="s">
         <v>7872</v>
       </c>
       <c r="B145" s="41" t="s">
@@ -84850,32 +84599,32 @@
       <c r="G146" s="2" t="s">
         <v>7884</v>
       </c>
-      <c r="H146" s="0"/>
-      <c r="I146" s="0"/>
-      <c r="J146" s="0"/>
-      <c r="K146" s="0"/>
-      <c r="L146" s="0"/>
-      <c r="M146" s="0"/>
-      <c r="N146" s="0"/>
-      <c r="O146" s="0"/>
-      <c r="P146" s="0"/>
-      <c r="Q146" s="0"/>
-      <c r="R146" s="0"/>
-      <c r="S146" s="0"/>
-      <c r="T146" s="0"/>
-      <c r="U146" s="0"/>
-      <c r="V146" s="0"/>
-      <c r="W146" s="0"/>
-      <c r="X146" s="0"/>
-      <c r="Y146" s="0"/>
-      <c r="Z146" s="0"/>
-      <c r="AA146" s="0"/>
-      <c r="AB146" s="0"/>
-      <c r="AC146" s="0"/>
-      <c r="AD146" s="0"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1"/>
+      <c r="K146" s="1"/>
+      <c r="L146" s="1"/>
+      <c r="M146" s="1"/>
+      <c r="N146" s="1"/>
+      <c r="O146" s="1"/>
+      <c r="P146" s="1"/>
+      <c r="Q146" s="1"/>
+      <c r="R146" s="1"/>
+      <c r="S146" s="1"/>
+      <c r="T146" s="1"/>
+      <c r="U146" s="1"/>
+      <c r="V146" s="1"/>
+      <c r="W146" s="1"/>
+      <c r="X146" s="1"/>
+      <c r="Y146" s="1"/>
+      <c r="Z146" s="1"/>
+      <c r="AA146" s="1"/>
+      <c r="AB146" s="1"/>
+      <c r="AC146" s="1"/>
+      <c r="AD146" s="1"/>
     </row>
     <row r="147" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="63" t="s">
+      <c r="A147" s="61" t="s">
         <v>7885</v>
       </c>
       <c r="B147" s="41" t="s">
@@ -84884,7 +84633,7 @@
       <c r="C147" s="41" t="s">
         <v>7887</v>
       </c>
-      <c r="D147" s="64" t="s">
+      <c r="D147" s="62" t="s">
         <v>7888</v>
       </c>
       <c r="E147" s="41" t="s">
@@ -84898,7 +84647,7 @@
       </c>
     </row>
     <row r="148" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="65" t="n">
+      <c r="A148" s="63" t="n">
         <v>42355</v>
       </c>
       <c r="B148" s="41" t="s">
@@ -84918,7 +84667,7 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="63" t="n">
+      <c r="A149" s="61" t="n">
         <v>43658</v>
       </c>
       <c r="B149" s="41" t="s">
@@ -84927,7 +84676,7 @@
       <c r="C149" s="41" t="s">
         <v>7897</v>
       </c>
-      <c r="D149" s="64" t="s">
+      <c r="D149" s="62" t="s">
         <v>7898</v>
       </c>
       <c r="E149" s="41" t="s">
@@ -84966,7 +84715,7 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="63" t="n">
+      <c r="A150" s="61" t="n">
         <v>45581</v>
       </c>
       <c r="B150" s="41" t="s">
@@ -84978,13 +84727,13 @@
       <c r="D150" s="41" t="s">
         <v>7904</v>
       </c>
-      <c r="E150" s="64" t="s">
+      <c r="E150" s="62" t="s">
         <v>7905</v>
       </c>
       <c r="F150" s="41" t="s">
         <v>7902</v>
       </c>
-      <c r="G150" s="66" t="s">
+      <c r="G150" s="64" t="s">
         <v>7906</v>
       </c>
       <c r="H150" s="41"/>
@@ -85012,7 +84761,7 @@
       <c r="AD150" s="41"/>
     </row>
     <row r="151" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="65" t="n">
+      <c r="A151" s="63" t="n">
         <v>45668</v>
       </c>
       <c r="B151" s="1" t="s">
@@ -85040,10 +84789,10 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="67" t="s">
+      <c r="A154" s="62" t="s">
         <v>7912</v>
       </c>
-      <c r="B154" s="68" t="s">
+      <c r="B154" s="2" t="s">
         <v>7913</v>
       </c>
       <c r="C154" s="1" t="s">
@@ -85057,13 +84806,12 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="63" t="s">
+      <c r="A155" s="61" t="s">
         <v>7916</v>
       </c>
-      <c r="B155" s="68" t="s">
+      <c r="B155" s="2" t="s">
         <v>7917</v>
       </c>
-      <c r="C155" s="0"/>
       <c r="F155" s="1" t="s">
         <v>7868</v>
       </c>
@@ -85071,11 +84819,11 @@
         <v>7918</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="67" t="s">
+    <row r="156" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="62" t="s">
         <v>7912</v>
       </c>
-      <c r="B156" s="69" t="s">
+      <c r="B156" s="2" t="s">
         <v>7919</v>
       </c>
       <c r="C156" s="1" t="s">
@@ -85088,8 +84836,8 @@
         <v>7921</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="70" t="s">
+    <row r="157" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="28" t="s">
         <v>7922</v>
       </c>
       <c r="B157" s="1" t="s">
@@ -85105,11 +84853,11 @@
         <v>7901</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0" t="s">
+    <row r="158" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
         <v>7926</v>
       </c>
-      <c r="B158" s="69" t="s">
+      <c r="B158" s="2" t="s">
         <v>7927</v>
       </c>
       <c r="C158" s="1" t="s">
@@ -85123,7 +84871,7 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="54" t="s">
+      <c r="A159" s="43" t="s">
         <v>7930</v>
       </c>
       <c r="B159" s="1" t="s">
@@ -85154,7 +84902,7 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="0" t="s">
+      <c r="A161" s="1" t="s">
         <v>7926</v>
       </c>
       <c r="B161" s="1" t="s">
@@ -85173,11 +84921,11 @@
         <v>7929</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="70" t="s">
+    <row r="162" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="28" t="s">
         <v>7942</v>
       </c>
-      <c r="B162" s="70" t="s">
+      <c r="B162" s="65" t="s">
         <v>7943</v>
       </c>
       <c r="C162" s="41" t="s">
@@ -85195,7 +84943,7 @@
       <c r="H162" s="1"/>
     </row>
     <row r="163" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="67" t="s">
+      <c r="A163" s="62" t="s">
         <v>7912</v>
       </c>
       <c r="B163" s="1" t="s">
@@ -85215,7 +84963,7 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="54" t="s">
+      <c r="A166" s="43" t="s">
         <v>7952</v>
       </c>
     </row>
@@ -85229,7 +84977,7 @@
       <c r="F167" s="1" t="s">
         <v>7868</v>
       </c>
-      <c r="G167" s="68" t="s">
+      <c r="G167" s="2" t="s">
         <v>7954</v>
       </c>
     </row>
@@ -85258,7 +85006,7 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="54" t="s">
+      <c r="A176" s="43" t="s">
         <v>7961</v>
       </c>
     </row>
@@ -85345,18 +85093,18 @@
     <hyperlink ref="AD149" r:id="rId79" display="https://product.dangdang.com/11084474556.html"/>
     <hyperlink ref="G150" r:id="rId80" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
     <hyperlink ref="G151" r:id="rId81" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="B154" r:id="rId82" display="全国图书馆文献缩微复制中心"/>
+    <hyperlink ref="B154" r:id="rId82" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
     <hyperlink ref="G154" r:id="rId83" display="https://book.kongfz.com/536651/7839562954"/>
-    <hyperlink ref="B155" r:id="rId84" display="全国图书馆文献缩微复制中心"/>
+    <hyperlink ref="B155" r:id="rId84" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
     <hyperlink ref="G155" r:id="rId85" display="https://book.kongfz.com/23231/8186709240"/>
-    <hyperlink ref="B156" r:id="rId86" display="全国图书馆文献缩微复制中心"/>
+    <hyperlink ref="B156" r:id="rId86" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
     <hyperlink ref="G156" r:id="rId87" display="https://book.kongfz.com/536651/7839554296"/>
     <hyperlink ref="G157" r:id="rId88" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="B158" r:id="rId89" display="中国书店"/>
+    <hyperlink ref="B158" r:id="rId89" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
     <hyperlink ref="G159" r:id="rId90" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
     <hyperlink ref="G160" r:id="rId91" display="https://book.kongfz.com/200249/1819262449/"/>
     <hyperlink ref="G161" r:id="rId92" display="https://product.dangdang.com/11721366316.html"/>
-    <hyperlink ref="B162" r:id="rId93" display="宗教文化出版社"/>
+    <hyperlink ref="B162" r:id="rId93" display="出版社:宗教文化出版社 "/>
     <hyperlink ref="G162" r:id="rId94" display="https://product.dangdang.com/22497432.html"/>
     <hyperlink ref="G163" r:id="rId95" display="http://aiguji.net/3299.html"/>
     <hyperlink ref="G167" r:id="rId96" display="https://book.kongfz.com/467603/10356350239"/>
@@ -85379,13 +85127,13 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="71" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="66" width="12.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -85393,7 +85141,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="72" t="n">
+      <c r="A2" s="67" t="n">
         <v>1539</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -85404,7 +85152,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="72" t="n">
+      <c r="A3" s="67" t="n">
         <v>1615</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -85415,7 +85163,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="72" t="n">
+      <c r="A4" s="67" t="n">
         <v>1620</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -85426,7 +85174,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="72" t="n">
+      <c r="A5" s="67" t="n">
         <v>1623</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -85437,7 +85185,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="72" t="n">
+      <c r="A6" s="67" t="n">
         <v>1653</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -85571,89 +85319,89 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="45.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="51.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="31.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="51.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="31.48"/>
   </cols>
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="68" t="s">
         <v>7989</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="68" t="s">
         <v>7990</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="68" t="s">
         <v>7991</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="68" t="s">
         <v>7992</v>
       </c>
-      <c r="B12" s="75" t="n">
+      <c r="B12" s="69" t="n">
         <v>45735</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>7993</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>7994</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="68" t="s">
         <v>7995</v>
       </c>
-      <c r="B13" s="75" t="n">
+      <c r="B13" s="69" t="n">
         <v>45970</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>7996</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>7997</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="74" t="s">
+      <c r="A14" s="68" t="s">
         <v>7998</v>
       </c>
-      <c r="B14" s="75" t="n">
+      <c r="B14" s="69" t="n">
         <v>45995</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>7999</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>8000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="74" t="s">
+      <c r="A15" s="68" t="s">
         <v>8001</v>
       </c>
-      <c r="B15" s="75" t="n">
+      <c r="B15" s="69" t="n">
         <v>46036</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>8002</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>8003</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>8004</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>8005</v>
       </c>
     </row>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10852" uniqueCount="8006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10854" uniqueCount="8009">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -25116,6 +25116,27 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">种。 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">https://www.dpm.org.cn/ancient</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">/special/148432.html</t>
     </r>
   </si>
   <si>
@@ -28327,6 +28348,12 @@
     <t xml:space="preserve">http://aiguji.net/3299.html</t>
   </si>
   <si>
+    <t xml:space="preserve">https://lib.dha.ac.cn/opac/book/41063?view=simple&amp;flag=printer https://vstudy.ruc.edu.cn/mystudy/search/detail/m20f248f0d88421bcaf7317dbb708eb82 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">人民大学和敦煌研究所，两个地方的馆藏版本</t>
+  </si>
+  <si>
     <t xml:space="preserve">清敕修大藏经保护项目简介 </t>
   </si>
   <si>
@@ -28624,6 +28651,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
@@ -28660,13 +28694,6 @@
       <sz val="10"/>
       <color rgb="FFFF4000"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -28909,7 +28936,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29118,6 +29145,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29142,7 +29173,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -29162,16 +29193,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -82213,7 +82244,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:AD176"/>
+  <dimension ref="A3:AD179"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.85"/>
@@ -83313,25 +83344,25 @@
       <c r="F77" s="43" t="s">
         <v>7537</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>7538</v>
+      <c r="G77" s="51" t="s">
+        <v>7669</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="47" t="s">
-        <v>7669</v>
+        <v>7670</v>
       </c>
       <c r="B78" s="28" t="s">
         <v>7657</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>7670</v>
+        <v>7671</v>
       </c>
       <c r="D78" s="43" t="s">
-        <v>7671</v>
+        <v>7672</v>
       </c>
       <c r="E78" s="28" t="s">
-        <v>7672</v>
+        <v>7673</v>
       </c>
       <c r="F78" s="28" t="s">
         <v>7521</v>
@@ -83345,13 +83376,13 @@
         <v>32471</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>7673</v>
+        <v>7674</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>7674</v>
+        <v>7675</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>7675</v>
+        <v>7676</v>
       </c>
       <c r="E79" s="50"/>
       <c r="F79" s="43" t="s">
@@ -83366,20 +83397,20 @@
         <v>32471</v>
       </c>
       <c r="B80" s="28" t="s">
-        <v>7676</v>
+        <v>7677</v>
       </c>
       <c r="C80" s="28" t="s">
-        <v>7677</v>
+        <v>7678</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>7678</v>
+        <v>7679</v>
       </c>
       <c r="E80" s="28"/>
       <c r="F80" s="1" t="s">
-        <v>7679</v>
+        <v>7680</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>7680</v>
+        <v>7681</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83387,20 +83418,20 @@
         <v>32471</v>
       </c>
       <c r="B81" s="28" t="s">
-        <v>7681</v>
+        <v>7682</v>
       </c>
       <c r="C81" s="28" t="s">
-        <v>7682</v>
+        <v>7683</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>7683</v>
+        <v>7684</v>
       </c>
       <c r="E81" s="28"/>
       <c r="F81" s="28" t="s">
         <v>7663</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>7684</v>
+        <v>7685</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83408,16 +83439,16 @@
         <v>32471</v>
       </c>
       <c r="B82" s="28" t="s">
-        <v>7681</v>
+        <v>7682</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>7685</v>
+        <v>7686</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>7683</v>
+        <v>7684</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>7686</v>
+        <v>7687</v>
       </c>
       <c r="F82" s="28" t="s">
         <v>7521</v>
@@ -83431,13 +83462,13 @@
         <v>32517</v>
       </c>
       <c r="B83" s="28" t="s">
-        <v>7687</v>
+        <v>7688</v>
       </c>
       <c r="C83" s="28" t="s">
         <v>7589</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>7688</v>
+        <v>7689</v>
       </c>
       <c r="E83" s="28"/>
       <c r="F83" s="1" t="s">
@@ -83450,7 +83481,7 @@
     <row r="84" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="47"/>
       <c r="B84" s="28" t="s">
-        <v>7689</v>
+        <v>7690</v>
       </c>
       <c r="C84" s="28"/>
       <c r="D84" s="28"/>
@@ -83464,13 +83495,13 @@
     </row>
     <row r="85" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="47" t="s">
-        <v>7690</v>
+        <v>7691</v>
       </c>
       <c r="B85" s="28" t="s">
-        <v>7691</v>
+        <v>7692</v>
       </c>
       <c r="C85" s="28" t="s">
-        <v>7692</v>
+        <v>7693</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>7515</v>
@@ -83485,19 +83516,19 @@
     </row>
     <row r="86" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="47" t="s">
-        <v>7693</v>
+        <v>7694</v>
       </c>
       <c r="B86" s="28" t="s">
         <v>7657</v>
       </c>
       <c r="C86" s="28" t="s">
-        <v>7670</v>
+        <v>7671</v>
       </c>
       <c r="D86" s="43" t="s">
-        <v>7671</v>
+        <v>7672</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>7694</v>
+        <v>7695</v>
       </c>
       <c r="F86" s="28" t="s">
         <v>7521</v>
@@ -83508,17 +83539,17 @@
     </row>
     <row r="87" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="47" t="s">
-        <v>7695</v>
+        <v>7696</v>
       </c>
       <c r="B87" s="28" t="s">
-        <v>7696</v>
+        <v>7697</v>
       </c>
       <c r="C87" s="28"/>
       <c r="D87" s="43" t="s">
-        <v>7671</v>
+        <v>7672</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>7697</v>
+        <v>7698</v>
       </c>
       <c r="F87" s="28" t="s">
         <v>7521</v>
@@ -83529,19 +83560,19 @@
     </row>
     <row r="88" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="47" t="s">
-        <v>7698</v>
+        <v>7699</v>
       </c>
       <c r="B88" s="28" t="s">
-        <v>7699</v>
+        <v>7700</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>7700</v>
+        <v>7701</v>
       </c>
       <c r="D88" s="43" t="s">
-        <v>7671</v>
+        <v>7672</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>7701</v>
+        <v>7702</v>
       </c>
       <c r="F88" s="28" t="s">
         <v>7521</v>
@@ -83552,30 +83583,30 @@
     </row>
     <row r="89" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="43" t="s">
-        <v>7702</v>
+        <v>7703</v>
       </c>
       <c r="B89" s="28" t="s">
-        <v>7703</v>
+        <v>7704</v>
       </c>
       <c r="D89" s="43" t="s">
-        <v>7704</v>
+        <v>7705</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>7705</v>
-      </c>
-      <c r="F89" s="51" t="s">
         <v>7706</v>
       </c>
+      <c r="F89" s="52" t="s">
+        <v>7707</v>
+      </c>
       <c r="G89" s="2" t="s">
-        <v>7707</v>
+        <v>7708</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="49" t="s">
-        <v>7708</v>
+        <v>7709</v>
       </c>
       <c r="B90" s="28" t="s">
-        <v>7709</v>
+        <v>7710</v>
       </c>
       <c r="F90" s="43" t="s">
         <v>7496</v>
@@ -83589,12 +83620,12 @@
     </row>
     <row r="92" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="43" t="s">
-        <v>7710</v>
+        <v>7711</v>
       </c>
       <c r="B92" s="28"/>
       <c r="D92" s="43"/>
       <c r="E92" s="28"/>
-      <c r="F92" s="51"/>
+      <c r="F92" s="52"/>
       <c r="G92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83602,59 +83633,59 @@
         <v>38164</v>
       </c>
       <c r="B93" s="43" t="s">
-        <v>7711</v>
+        <v>7712</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>7712</v>
+        <v>7713</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>7713</v>
+        <v>7714</v>
       </c>
       <c r="E93" s="28" t="s">
-        <v>7714</v>
+        <v>7715</v>
       </c>
       <c r="F93" s="28" t="s">
-        <v>7715</v>
+        <v>7716</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>7716</v>
+        <v>7717</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="47" t="s">
-        <v>7717</v>
-      </c>
-      <c r="B94" s="52" t="s">
         <v>7718</v>
       </c>
-      <c r="C94" s="52" t="s">
+      <c r="B94" s="53" t="s">
         <v>7719</v>
       </c>
+      <c r="C94" s="53" t="s">
+        <v>7720</v>
+      </c>
       <c r="D94" s="1" t="s">
-        <v>7720</v>
+        <v>7721</v>
       </c>
       <c r="E94" s="49" t="s">
-        <v>7721</v>
+        <v>7722</v>
       </c>
       <c r="F94" s="28" t="s">
-        <v>7722</v>
+        <v>7723</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>7723</v>
+        <v>7724</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="47" t="s">
-        <v>7724</v>
+        <v>7725</v>
       </c>
       <c r="B95" s="43" t="s">
-        <v>7725</v>
+        <v>7726</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>7726</v>
+        <v>7727</v>
       </c>
       <c r="D95" s="43" t="s">
-        <v>7727</v>
+        <v>7728</v>
       </c>
       <c r="E95" s="43"/>
       <c r="F95" s="43" t="s">
@@ -83666,46 +83697,46 @@
     </row>
     <row r="96" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="47" t="s">
-        <v>7724</v>
+        <v>7725</v>
       </c>
       <c r="B96" s="28" t="s">
-        <v>7728</v>
+        <v>7729</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>7729</v>
+        <v>7730</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>7730</v>
+        <v>7731</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>7731</v>
+        <v>7732</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>7732</v>
+        <v>7733</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>7733</v>
+        <v>7734</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="47" t="s">
-        <v>7734</v>
+        <v>7735</v>
       </c>
       <c r="B97" s="28" t="s">
-        <v>7728</v>
+        <v>7729</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>7735</v>
+        <v>7736</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>7736</v>
+        <v>7737</v>
       </c>
       <c r="E97" s="28"/>
       <c r="F97" s="1" t="s">
-        <v>7732</v>
+        <v>7733</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>7733</v>
+        <v>7734</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -83713,45 +83744,45 @@
         <v>42230</v>
       </c>
       <c r="B98" s="28" t="s">
-        <v>7728</v>
+        <v>7729</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>7737</v>
+        <v>7738</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>7738</v>
+        <v>7739</v>
       </c>
       <c r="E98" s="28" t="s">
-        <v>7739</v>
+        <v>7740</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>7732</v>
+        <v>7733</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>7733</v>
+        <v>7734</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="100" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="43" t="s">
-        <v>7740</v>
+        <v>7741</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="47" t="n">
         <v>42753</v>
       </c>
-      <c r="B101" s="52" t="s">
-        <v>7741</v>
+      <c r="B101" s="53" t="s">
+        <v>7742</v>
       </c>
       <c r="C101" s="43" t="s">
-        <v>7742</v>
+        <v>7743</v>
       </c>
       <c r="D101" s="43" t="s">
-        <v>7743</v>
+        <v>7744</v>
       </c>
       <c r="E101" s="43" t="s">
-        <v>7744</v>
+        <v>7745</v>
       </c>
       <c r="F101" s="43" t="s">
         <v>7502</v>
@@ -83764,17 +83795,17 @@
       <c r="A102" s="47" t="n">
         <v>42753</v>
       </c>
-      <c r="B102" s="52" t="s">
-        <v>7745</v>
+      <c r="B102" s="53" t="s">
+        <v>7746</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>7746</v>
+        <v>7747</v>
       </c>
       <c r="D102" s="43" t="s">
-        <v>7743</v>
-      </c>
-      <c r="E102" s="53" t="s">
-        <v>7747</v>
+        <v>7744</v>
+      </c>
+      <c r="E102" s="54" t="s">
+        <v>7748</v>
       </c>
       <c r="F102" s="43" t="s">
         <v>7502</v>
@@ -83787,23 +83818,23 @@
       <c r="A103" s="47" t="n">
         <v>42753</v>
       </c>
-      <c r="B103" s="52" t="s">
-        <v>7745</v>
-      </c>
-      <c r="C103" s="52" t="s">
-        <v>7748</v>
+      <c r="B103" s="53" t="s">
+        <v>7746</v>
+      </c>
+      <c r="C103" s="53" t="s">
+        <v>7749</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>7749</v>
+        <v>7750</v>
       </c>
       <c r="E103" s="43" t="s">
-        <v>7750</v>
+        <v>7751</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>7751</v>
+        <v>7752</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>7752</v>
+        <v>7753</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83811,22 +83842,22 @@
         <v>43725</v>
       </c>
       <c r="B104" s="28" t="s">
-        <v>7753</v>
+        <v>7754</v>
       </c>
       <c r="C104" s="28" t="s">
-        <v>7754</v>
+        <v>7755</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>7755</v>
+        <v>7756</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>7756</v>
+        <v>7757</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>7757</v>
+        <v>7758</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>7758</v>
+        <v>7759</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83834,22 +83865,22 @@
         <v>44895</v>
       </c>
       <c r="B105" s="28" t="s">
-        <v>7759</v>
+        <v>7760</v>
       </c>
       <c r="C105" s="28" t="s">
-        <v>7760</v>
+        <v>7761</v>
       </c>
       <c r="D105" s="43" t="s">
-        <v>7761</v>
+        <v>7762</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>7762</v>
+        <v>7763</v>
       </c>
       <c r="F105" s="28" t="s">
-        <v>7763</v>
+        <v>7764</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>7764</v>
+        <v>7765</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83857,22 +83888,22 @@
         <v>45449</v>
       </c>
       <c r="B106" s="28" t="s">
-        <v>7765</v>
+        <v>7766</v>
       </c>
       <c r="C106" s="28" t="s">
-        <v>7766</v>
+        <v>7767</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>7767</v>
+        <v>7768</v>
       </c>
       <c r="E106" s="28" t="s">
-        <v>7768</v>
+        <v>7769</v>
       </c>
       <c r="F106" s="28" t="s">
-        <v>7769</v>
+        <v>7770</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>7770</v>
+        <v>7771</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83880,31 +83911,31 @@
         <v>46017</v>
       </c>
       <c r="B107" s="28" t="s">
-        <v>7771</v>
+        <v>7772</v>
       </c>
       <c r="C107" s="28" t="s">
-        <v>7772</v>
+        <v>7773</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>7773</v>
+        <v>7774</v>
       </c>
       <c r="E107" s="28" t="s">
-        <v>7774</v>
+        <v>7775</v>
       </c>
       <c r="F107" s="28" t="s">
-        <v>7775</v>
+        <v>7776</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>7776</v>
+        <v>7777</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="47"/>
       <c r="B108" s="28" t="s">
-        <v>7777</v>
+        <v>7778</v>
       </c>
       <c r="C108" s="43" t="s">
-        <v>7778</v>
+        <v>7779</v>
       </c>
       <c r="E108" s="28"/>
       <c r="F108" s="28"/>
@@ -83914,10 +83945,10 @@
         <v>41741</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>7779</v>
+        <v>7780</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>7780</v>
+        <v>7781</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83930,7 +83961,7 @@
     </row>
     <row r="114" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="43" t="s">
-        <v>7781</v>
+        <v>7782</v>
       </c>
       <c r="B114" s="28"/>
       <c r="C114" s="28"/>
@@ -83939,20 +83970,20 @@
       <c r="G114" s="2"/>
     </row>
     <row r="115" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="54" t="s">
-        <v>7782</v>
+      <c r="A115" s="55" t="s">
+        <v>7783</v>
       </c>
       <c r="B115" s="43" t="s">
-        <v>7783</v>
+        <v>7784</v>
       </c>
       <c r="C115" s="28" t="s">
-        <v>7784</v>
+        <v>7785</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>7515</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>7705</v>
+        <v>7706</v>
       </c>
       <c r="F115" s="28" t="s">
         <v>7516</v>
@@ -83962,34 +83993,34 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="54" t="s">
-        <v>7785</v>
+      <c r="A116" s="55" t="s">
+        <v>7786</v>
       </c>
       <c r="B116" s="43" t="s">
-        <v>7786</v>
+        <v>7787</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>7787</v>
+        <v>7788</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>7788</v>
-      </c>
-      <c r="F116" s="51" t="s">
-        <v>7706</v>
+        <v>7789</v>
+      </c>
+      <c r="F116" s="52" t="s">
+        <v>7707</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>7707</v>
+        <v>7708</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="49" t="s">
-        <v>7789</v>
-      </c>
-      <c r="B117" s="52" t="s">
         <v>7790</v>
       </c>
+      <c r="B117" s="53" t="s">
+        <v>7791</v>
+      </c>
       <c r="C117" s="28" t="s">
-        <v>7791</v>
+        <v>7792</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>7515</v>
@@ -84002,20 +84033,20 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="54" t="s">
-        <v>7792</v>
+      <c r="A118" s="55" t="s">
+        <v>7793</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>7793</v>
+        <v>7794</v>
       </c>
       <c r="C118" s="28" t="s">
-        <v>7794</v>
+        <v>7795</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>7515</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>7795</v>
+        <v>7796</v>
       </c>
       <c r="F118" s="28" t="s">
         <v>7516</v>
@@ -84025,14 +84056,14 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="54" t="s">
-        <v>7796</v>
+      <c r="A119" s="55" t="s">
+        <v>7797</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>7797</v>
+        <v>7798</v>
       </c>
       <c r="C119" s="28" t="s">
-        <v>7798</v>
+        <v>7799</v>
       </c>
       <c r="E119" s="28"/>
       <c r="F119" s="28" t="s">
@@ -84043,26 +84074,26 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="54" t="s">
-        <v>7799</v>
+      <c r="A120" s="55" t="s">
+        <v>7800</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>7800</v>
+        <v>7801</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>7801</v>
+        <v>7802</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>7788</v>
+        <v>7789</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>7802</v>
-      </c>
-      <c r="F120" s="51" t="s">
-        <v>7706</v>
+        <v>7803</v>
+      </c>
+      <c r="F120" s="52" t="s">
+        <v>7707</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>7707</v>
+        <v>7708</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -84070,43 +84101,43 @@
         <v>44662</v>
       </c>
       <c r="B121" s="28" t="s">
-        <v>7803</v>
+        <v>7804</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>7804</v>
+        <v>7805</v>
       </c>
       <c r="D121" s="28" t="s">
-        <v>7805</v>
+        <v>7806</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>7806</v>
+        <v>7807</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>7807</v>
+        <v>7808</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>7808</v>
+        <v>7809</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="54" t="s">
-        <v>7809</v>
+      <c r="A122" s="55" t="s">
+        <v>7810</v>
       </c>
       <c r="B122" s="28" t="s">
-        <v>7810</v>
+        <v>7811</v>
       </c>
       <c r="C122" s="28"/>
       <c r="D122" s="1" t="s">
-        <v>7788</v>
+        <v>7789</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>7811</v>
-      </c>
-      <c r="F122" s="51" t="s">
-        <v>7706</v>
+        <v>7812</v>
+      </c>
+      <c r="F122" s="52" t="s">
+        <v>7707</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>7707</v>
+        <v>7708</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -84114,25 +84145,25 @@
         <v>44776</v>
       </c>
       <c r="B123" s="28" t="s">
-        <v>7812</v>
+        <v>7813</v>
       </c>
       <c r="C123" s="28" t="s">
-        <v>7813</v>
+        <v>7814</v>
       </c>
       <c r="D123" s="28" t="s">
-        <v>7814</v>
+        <v>7815</v>
       </c>
       <c r="E123" s="28" t="s">
-        <v>7815</v>
+        <v>7816</v>
       </c>
       <c r="F123" s="28" t="s">
-        <v>7816</v>
+        <v>7817</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>7817</v>
-      </c>
-    </row>
-    <row r="125" s="55" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7818</v>
+      </c>
+    </row>
+    <row r="125" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -84164,9 +84195,9 @@
       <c r="AC125" s="1"/>
       <c r="AD125" s="1"/>
     </row>
-    <row r="126" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" s="56" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="47" t="s">
-        <v>7818</v>
+        <v>7819</v>
       </c>
       <c r="B126" s="28"/>
       <c r="C126" s="1"/>
@@ -84198,157 +84229,157 @@
       <c r="AC126" s="1"/>
       <c r="AD126" s="1"/>
     </row>
-    <row r="127" s="55" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="56" t="n">
+    <row r="127" s="56" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="57" t="n">
         <v>45004</v>
       </c>
-      <c r="B127" s="55" t="s">
-        <v>7819</v>
-      </c>
-      <c r="C127" s="55" t="s">
+      <c r="B127" s="56" t="s">
         <v>7820</v>
       </c>
-      <c r="D127" s="55" t="s">
+      <c r="C127" s="56" t="s">
         <v>7821</v>
       </c>
-      <c r="E127" s="55" t="s">
+      <c r="D127" s="56" t="s">
         <v>7822</v>
       </c>
-      <c r="F127" s="57" t="s">
+      <c r="E127" s="56" t="s">
         <v>7823</v>
       </c>
-      <c r="G127" s="55" t="s">
+      <c r="F127" s="58" t="s">
         <v>7824</v>
       </c>
-    </row>
-    <row r="128" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="56" t="n">
+      <c r="G127" s="56" t="s">
+        <v>7825</v>
+      </c>
+    </row>
+    <row r="128" s="56" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="57" t="n">
         <v>45005</v>
       </c>
-      <c r="B128" s="57" t="s">
-        <v>7825</v>
-      </c>
-      <c r="C128" s="55" t="s">
+      <c r="B128" s="58" t="s">
         <v>7826</v>
       </c>
-      <c r="D128" s="55" t="s">
+      <c r="C128" s="56" t="s">
         <v>7827</v>
       </c>
-      <c r="E128" s="55" t="s">
+      <c r="D128" s="56" t="s">
         <v>7828</v>
       </c>
-      <c r="F128" s="57" t="s">
+      <c r="E128" s="56" t="s">
         <v>7829</v>
       </c>
-      <c r="G128" s="55" t="s">
+      <c r="F128" s="58" t="s">
         <v>7830</v>
       </c>
+      <c r="G128" s="56" t="s">
+        <v>7831</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="56" t="n">
+      <c r="A129" s="57" t="n">
         <v>45006</v>
       </c>
-      <c r="B129" s="55" t="s">
-        <v>7819</v>
-      </c>
-      <c r="C129" s="55" t="s">
-        <v>7831</v>
-      </c>
-      <c r="D129" s="55" t="s">
+      <c r="B129" s="56" t="s">
+        <v>7820</v>
+      </c>
+      <c r="C129" s="56" t="s">
         <v>7832</v>
       </c>
-      <c r="E129" s="58" t="s">
+      <c r="D129" s="56" t="s">
         <v>7833</v>
       </c>
-      <c r="F129" s="57" t="s">
+      <c r="E129" s="59" t="s">
         <v>7834</v>
       </c>
-      <c r="G129" s="55" t="s">
+      <c r="F129" s="58" t="s">
         <v>7835</v>
       </c>
-      <c r="H129" s="55"/>
-      <c r="I129" s="55"/>
-      <c r="J129" s="55"/>
-      <c r="K129" s="55"/>
-      <c r="L129" s="55"/>
-      <c r="M129" s="55"/>
-      <c r="N129" s="55"/>
-      <c r="O129" s="55"/>
-      <c r="P129" s="55"/>
-      <c r="Q129" s="55"/>
-      <c r="R129" s="55"/>
-      <c r="S129" s="55"/>
-      <c r="T129" s="55"/>
-      <c r="U129" s="55"/>
-      <c r="V129" s="55"/>
-      <c r="W129" s="55"/>
-      <c r="X129" s="55"/>
-      <c r="Y129" s="55"/>
-      <c r="Z129" s="55"/>
-      <c r="AA129" s="55"/>
-      <c r="AB129" s="55"/>
-      <c r="AC129" s="55"/>
-      <c r="AD129" s="55"/>
+      <c r="G129" s="56" t="s">
+        <v>7836</v>
+      </c>
+      <c r="H129" s="56"/>
+      <c r="I129" s="56"/>
+      <c r="J129" s="56"/>
+      <c r="K129" s="56"/>
+      <c r="L129" s="56"/>
+      <c r="M129" s="56"/>
+      <c r="N129" s="56"/>
+      <c r="O129" s="56"/>
+      <c r="P129" s="56"/>
+      <c r="Q129" s="56"/>
+      <c r="R129" s="56"/>
+      <c r="S129" s="56"/>
+      <c r="T129" s="56"/>
+      <c r="U129" s="56"/>
+      <c r="V129" s="56"/>
+      <c r="W129" s="56"/>
+      <c r="X129" s="56"/>
+      <c r="Y129" s="56"/>
+      <c r="Z129" s="56"/>
+      <c r="AA129" s="56"/>
+      <c r="AB129" s="56"/>
+      <c r="AC129" s="56"/>
+      <c r="AD129" s="56"/>
     </row>
     <row r="130" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="56" t="n">
+      <c r="A130" s="57" t="n">
         <v>45036</v>
       </c>
-      <c r="B130" s="55" t="s">
-        <v>7836</v>
-      </c>
-      <c r="C130" s="55"/>
-      <c r="D130" s="55" t="s">
+      <c r="B130" s="56" t="s">
         <v>7837</v>
       </c>
-      <c r="E130" s="55" t="s">
+      <c r="C130" s="56"/>
+      <c r="D130" s="56" t="s">
         <v>7838</v>
       </c>
-      <c r="F130" s="55" t="s">
+      <c r="E130" s="56" t="s">
         <v>7839</v>
       </c>
-      <c r="G130" s="55" t="s">
+      <c r="F130" s="56" t="s">
         <v>7840</v>
       </c>
-      <c r="H130" s="55"/>
-      <c r="I130" s="55"/>
-      <c r="J130" s="55"/>
-      <c r="K130" s="55"/>
-      <c r="L130" s="55"/>
-      <c r="M130" s="55"/>
-      <c r="N130" s="55"/>
-      <c r="O130" s="55"/>
-      <c r="P130" s="55"/>
-      <c r="Q130" s="55"/>
-      <c r="R130" s="55"/>
-      <c r="S130" s="55"/>
-      <c r="T130" s="55"/>
-      <c r="U130" s="55"/>
-      <c r="V130" s="55"/>
-      <c r="W130" s="55"/>
-      <c r="X130" s="55"/>
-      <c r="Y130" s="55"/>
-      <c r="Z130" s="55"/>
-      <c r="AA130" s="55"/>
-      <c r="AB130" s="55"/>
-      <c r="AC130" s="55"/>
-      <c r="AD130" s="55"/>
+      <c r="G130" s="56" t="s">
+        <v>7841</v>
+      </c>
+      <c r="H130" s="56"/>
+      <c r="I130" s="56"/>
+      <c r="J130" s="56"/>
+      <c r="K130" s="56"/>
+      <c r="L130" s="56"/>
+      <c r="M130" s="56"/>
+      <c r="N130" s="56"/>
+      <c r="O130" s="56"/>
+      <c r="P130" s="56"/>
+      <c r="Q130" s="56"/>
+      <c r="R130" s="56"/>
+      <c r="S130" s="56"/>
+      <c r="T130" s="56"/>
+      <c r="U130" s="56"/>
+      <c r="V130" s="56"/>
+      <c r="W130" s="56"/>
+      <c r="X130" s="56"/>
+      <c r="Y130" s="56"/>
+      <c r="Z130" s="56"/>
+      <c r="AA130" s="56"/>
+      <c r="AB130" s="56"/>
+      <c r="AC130" s="56"/>
+      <c r="AD130" s="56"/>
     </row>
     <row r="131" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="59" t="n">
+      <c r="A131" s="60" t="n">
         <v>45088</v>
       </c>
       <c r="B131" s="48" t="s">
-        <v>7819</v>
+        <v>7820</v>
       </c>
       <c r="C131" s="48" t="s">
-        <v>7841</v>
+        <v>7842</v>
       </c>
       <c r="D131" s="48" t="s">
-        <v>7842</v>
-      </c>
-      <c r="E131" s="60" t="s">
         <v>7843</v>
+      </c>
+      <c r="E131" s="61" t="s">
+        <v>7844</v>
       </c>
       <c r="F131" s="48" t="s">
         <v>7549</v>
@@ -84358,23 +84389,23 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="59" t="n">
+      <c r="A132" s="60" t="n">
         <v>45025</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>7779</v>
+        <v>7780</v>
       </c>
       <c r="C132" s="28" t="s">
-        <v>7844</v>
+        <v>7845</v>
       </c>
       <c r="D132" s="43" t="s">
-        <v>7845</v>
+        <v>7846</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>7846</v>
+        <v>7847</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>7847</v>
+        <v>7848</v>
       </c>
     </row>
     <row r="133" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -84411,7 +84442,7 @@
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>7848</v>
+        <v>7849</v>
       </c>
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
@@ -84439,24 +84470,24 @@
       <c r="AD134" s="1"/>
     </row>
     <row r="135" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="61" t="n">
+      <c r="A135" s="62" t="n">
         <v>39252</v>
       </c>
       <c r="B135" s="41"/>
       <c r="C135" s="41" t="s">
-        <v>7849</v>
-      </c>
-      <c r="D135" s="62" t="s">
         <v>7850</v>
       </c>
+      <c r="D135" s="63" t="s">
+        <v>7851</v>
+      </c>
       <c r="E135" s="41" t="s">
-        <v>7851</v>
+        <v>7852</v>
       </c>
       <c r="F135" s="41" t="s">
-        <v>7852</v>
+        <v>7853</v>
       </c>
       <c r="G135" s="41" t="s">
-        <v>7853</v>
+        <v>7854</v>
       </c>
       <c r="H135" s="41"/>
       <c r="I135" s="41"/>
@@ -84487,59 +84518,59 @@
         <v>46241</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>7854</v>
+        <v>7855</v>
       </c>
       <c r="C136" s="28" t="s">
-        <v>7855</v>
+        <v>7856</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>7856</v>
+        <v>7857</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>7857</v>
+        <v>7858</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="47" t="s">
-        <v>7858</v>
+        <v>7859</v>
       </c>
       <c r="B137" s="28" t="s">
-        <v>7859</v>
+        <v>7860</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>7860</v>
+        <v>7861</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>7861</v>
+        <v>7862</v>
       </c>
       <c r="F137" s="28" t="s">
-        <v>7862</v>
+        <v>7863</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>7863</v>
+        <v>7864</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="54" t="n">
+      <c r="A138" s="55" t="n">
         <v>42866</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>7864</v>
+        <v>7865</v>
       </c>
       <c r="C138" s="28" t="s">
-        <v>7865</v>
+        <v>7866</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>7866</v>
+        <v>7867</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>7867</v>
+        <v>7868</v>
       </c>
       <c r="F138" s="28" t="s">
-        <v>7868</v>
+        <v>7869</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>7869</v>
+        <v>7870</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -84548,56 +84579,56 @@
         <v>7497</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>7870</v>
+        <v>7871</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>7871</v>
+        <v>7872</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="61" t="s">
-        <v>7872</v>
+      <c r="A145" s="62" t="s">
+        <v>7873</v>
       </c>
       <c r="B145" s="41" t="s">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="C145" s="41" t="s">
-        <v>7874</v>
+        <v>7875</v>
       </c>
       <c r="D145" s="41"/>
       <c r="E145" s="41" t="s">
-        <v>7875</v>
+        <v>7876</v>
       </c>
       <c r="F145" s="41" t="s">
-        <v>7876</v>
+        <v>7877</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>7877</v>
+        <v>7878</v>
       </c>
     </row>
     <row r="146" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>7878</v>
+        <v>7879</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>7879</v>
+        <v>7880</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>7880</v>
+        <v>7881</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>7881</v>
+        <v>7882</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>7882</v>
+        <v>7883</v>
       </c>
       <c r="F146" s="48" t="s">
-        <v>7883</v>
+        <v>7884</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>7884</v>
+        <v>7885</v>
       </c>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
@@ -84624,69 +84655,69 @@
       <c r="AD146" s="1"/>
     </row>
     <row r="147" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="61" t="s">
-        <v>7885</v>
+      <c r="A147" s="62" t="s">
+        <v>7886</v>
       </c>
       <c r="B147" s="41" t="s">
-        <v>7886</v>
+        <v>7887</v>
       </c>
       <c r="C147" s="41" t="s">
-        <v>7887</v>
-      </c>
-      <c r="D147" s="62" t="s">
         <v>7888</v>
       </c>
+      <c r="D147" s="63" t="s">
+        <v>7889</v>
+      </c>
       <c r="E147" s="41" t="s">
-        <v>7889</v>
+        <v>7890</v>
       </c>
       <c r="F147" s="41" t="s">
-        <v>7876</v>
+        <v>7877</v>
       </c>
       <c r="G147" s="41" t="s">
-        <v>7890</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="148" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="63" t="n">
+      <c r="A148" s="64" t="n">
         <v>42355</v>
       </c>
       <c r="B148" s="41" t="s">
-        <v>7891</v>
+        <v>7892</v>
       </c>
       <c r="C148" s="41" t="s">
-        <v>7892</v>
+        <v>7893</v>
       </c>
       <c r="D148" s="41" t="s">
-        <v>7893</v>
+        <v>7894</v>
       </c>
       <c r="E148" s="41" t="s">
-        <v>7894</v>
+        <v>7895</v>
       </c>
       <c r="F148" s="41" t="s">
-        <v>7895</v>
+        <v>7896</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="61" t="n">
+      <c r="A149" s="62" t="n">
         <v>43658</v>
       </c>
       <c r="B149" s="41" t="s">
-        <v>7896</v>
+        <v>7897</v>
       </c>
       <c r="C149" s="41" t="s">
+        <v>7898</v>
+      </c>
+      <c r="D149" s="63" t="s">
+        <v>7899</v>
+      </c>
+      <c r="E149" s="41" t="s">
+        <v>7900</v>
+      </c>
+      <c r="F149" s="41" t="s">
         <v>7897</v>
       </c>
-      <c r="D149" s="62" t="s">
-        <v>7898</v>
-      </c>
-      <c r="E149" s="41" t="s">
-        <v>7899</v>
-      </c>
-      <c r="F149" s="41" t="s">
-        <v>7896</v>
-      </c>
       <c r="G149" s="41" t="s">
-        <v>7900</v>
+        <v>7901</v>
       </c>
       <c r="H149" s="41"/>
       <c r="I149" s="41"/>
@@ -84711,30 +84742,30 @@
       <c r="AB149" s="41"/>
       <c r="AC149" s="41"/>
       <c r="AD149" s="41" t="s">
-        <v>7901</v>
+        <v>7902</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="61" t="n">
+      <c r="A150" s="62" t="n">
         <v>45581</v>
       </c>
       <c r="B150" s="41" t="s">
-        <v>7902</v>
+        <v>7903</v>
       </c>
       <c r="C150" s="41" t="s">
+        <v>7904</v>
+      </c>
+      <c r="D150" s="41" t="s">
+        <v>7905</v>
+      </c>
+      <c r="E150" s="63" t="s">
+        <v>7906</v>
+      </c>
+      <c r="F150" s="41" t="s">
         <v>7903</v>
       </c>
-      <c r="D150" s="41" t="s">
-        <v>7904</v>
-      </c>
-      <c r="E150" s="62" t="s">
-        <v>7905</v>
-      </c>
-      <c r="F150" s="41" t="s">
-        <v>7902</v>
-      </c>
-      <c r="G150" s="64" t="s">
-        <v>7906</v>
+      <c r="G150" s="65" t="s">
+        <v>7907</v>
       </c>
       <c r="H150" s="41"/>
       <c r="I150" s="41"/>
@@ -84761,20 +84792,20 @@
       <c r="AD150" s="41"/>
     </row>
     <row r="151" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="63" t="n">
+      <c r="A151" s="64" t="n">
         <v>45668</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>7907</v>
+        <v>7908</v>
       </c>
       <c r="C151" s="28" t="s">
-        <v>7908</v>
+        <v>7909</v>
       </c>
       <c r="D151" s="28" t="s">
-        <v>7909</v>
+        <v>7910</v>
       </c>
       <c r="E151" s="49" t="s">
-        <v>7910</v>
+        <v>7911</v>
       </c>
       <c r="F151" s="28" t="s">
         <v>7625</v>
@@ -84785,229 +84816,237 @@
     </row>
     <row r="153" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>7911</v>
+        <v>7912</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="62" t="s">
-        <v>7912</v>
+      <c r="A154" s="63" t="s">
+        <v>7913</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>7914</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>7915</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>7869</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>7916</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="62" t="s">
+        <v>7917</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>7918</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>7869</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>7919</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="63" t="s">
         <v>7913</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>7914</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>7868</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>7915</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="61" t="s">
-        <v>7916</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>7917</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>7868</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>7918</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="62" t="s">
-        <v>7912</v>
-      </c>
       <c r="B156" s="2" t="s">
-        <v>7919</v>
+        <v>7920</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>7920</v>
+        <v>7921</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>7868</v>
+        <v>7869</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>7921</v>
+        <v>7922</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="28" t="s">
-        <v>7922</v>
+        <v>7923</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>7923</v>
+        <v>7924</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>7924</v>
+        <v>7925</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>7925</v>
+        <v>7926</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>7901</v>
+        <v>7902</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
+        <v>7927</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>7928</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>7929</v>
+      </c>
+      <c r="F158" s="1" t="s">
         <v>7926</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>7927</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>7928</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>7925</v>
-      </c>
       <c r="G158" s="1" t="s">
-        <v>7929</v>
+        <v>7930</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="43" t="s">
-        <v>7930</v>
+        <v>7931</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>7931</v>
+        <v>7932</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>7932</v>
+        <v>7933</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>7933</v>
+        <v>7934</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>7934</v>
+        <v>7935</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="45" t="s">
-        <v>7935</v>
+        <v>7936</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>7936</v>
+        <v>7937</v>
       </c>
       <c r="C160" s="49" t="s">
-        <v>7937</v>
+        <v>7938</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>7938</v>
+        <v>7939</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
+        <v>7927</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>7940</v>
+      </c>
+      <c r="C161" s="41" t="s">
+        <v>7941</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>7942</v>
+      </c>
+      <c r="F161" s="1" t="s">
         <v>7926</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>7939</v>
-      </c>
-      <c r="C161" s="41" t="s">
-        <v>7940</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>7941</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>7925</v>
-      </c>
       <c r="G161" s="2" t="s">
-        <v>7929</v>
+        <v>7930</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="28" t="s">
-        <v>7942</v>
-      </c>
-      <c r="B162" s="65" t="s">
         <v>7943</v>
       </c>
+      <c r="B162" s="2" t="s">
+        <v>7944</v>
+      </c>
       <c r="C162" s="41" t="s">
-        <v>7944</v>
+        <v>7945</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>7945</v>
+        <v>7946</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>7925</v>
+        <v>7926</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>7946</v>
+        <v>7947</v>
       </c>
       <c r="H162" s="1"/>
     </row>
     <row r="163" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="62" t="s">
-        <v>7912</v>
+      <c r="A163" s="63" t="s">
+        <v>7913</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>7947</v>
+        <v>7948</v>
       </c>
       <c r="D163" s="28" t="s">
-        <v>7948</v>
+        <v>7949</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>7949</v>
+        <v>7950</v>
       </c>
       <c r="F163" s="43" t="s">
-        <v>7950</v>
+        <v>7951</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>7951</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="43" t="s">
         <v>7952</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="1" t="s">
+    <row r="165" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="66" t="s">
         <v>7953</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>7741</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>7868</v>
-      </c>
-      <c r="G167" s="2" t="s">
+      <c r="B165" s="1" t="s">
         <v>7954</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="43" t="s">
+        <v>7955</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>7955</v>
+        <v>7956</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>7956</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="1" t="s">
+        <v>7742</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>7869</v>
+      </c>
+      <c r="G170" s="2" t="s">
         <v>7957</v>
       </c>
-      <c r="B171" s="1" t="s">
+    </row>
+    <row r="173" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="1" t="s">
         <v>7958</v>
       </c>
-    </row>
-    <row r="172" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="1" t="s">
+      <c r="B173" s="1" t="s">
         <v>7959</v>
       </c>
-      <c r="B172" s="1" t="s">
+    </row>
+    <row r="174" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="1" t="s">
         <v>7960</v>
       </c>
-    </row>
-    <row r="176" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="43" t="s">
+      <c r="B174" s="1" t="s">
         <v>7961</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="1" t="s">
+        <v>7962</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>7963</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="43" t="s">
+        <v>7964</v>
       </c>
     </row>
   </sheetData>
@@ -85048,66 +85087,67 @@
     <hyperlink ref="G74" r:id="rId34" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
     <hyperlink ref="G75" r:id="rId35" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
     <hyperlink ref="G76" r:id="rId36" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
-    <hyperlink ref="G78" r:id="rId37" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G79" r:id="rId38" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
-    <hyperlink ref="G80" r:id="rId39" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
-    <hyperlink ref="G81" r:id="rId40" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
-    <hyperlink ref="G82" r:id="rId41" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G83" r:id="rId42" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G84" r:id="rId43" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G85" r:id="rId44" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G86" r:id="rId45" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G87" r:id="rId46" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G88" r:id="rId47" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G89" r:id="rId48" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G90" r:id="rId49" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G93" r:id="rId50" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
-    <hyperlink ref="G95" r:id="rId51" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G96" r:id="rId52" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G97" r:id="rId53" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G98" r:id="rId54" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G101" r:id="rId55" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G102" r:id="rId56" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G105" r:id="rId57" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G106" r:id="rId58" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
-    <hyperlink ref="G107" r:id="rId59" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
-    <hyperlink ref="G109" r:id="rId60" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
-    <hyperlink ref="G115" r:id="rId61" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G116" r:id="rId62" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G117" r:id="rId63" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G118" r:id="rId64" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G119" r:id="rId65" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G120" r:id="rId66" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G122" r:id="rId67" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G123" r:id="rId68" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
-    <hyperlink ref="G127" r:id="rId69" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
-    <hyperlink ref="F129" r:id="rId70" display="中新网北京3月21日电 (记者 应妮) "/>
-    <hyperlink ref="G129" r:id="rId71" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
-    <hyperlink ref="G131" r:id="rId72" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G135" r:id="rId73" display="https://discovery.cctv.com/20070619/107154.shtml"/>
-    <hyperlink ref="G138" r:id="rId74" display="https://book.kongfz.com/102740/682706591"/>
-    <hyperlink ref="A141" r:id="rId75" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G145" r:id="rId76" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
-    <hyperlink ref="G146" r:id="rId77" display="https://book.kongfz.com/20791/3754198261"/>
-    <hyperlink ref="G149" r:id="rId78" display="https://www.ljstsg.cn/?p=6315"/>
-    <hyperlink ref="AD149" r:id="rId79" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="G150" r:id="rId80" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
-    <hyperlink ref="G151" r:id="rId81" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="B154" r:id="rId82" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
-    <hyperlink ref="G154" r:id="rId83" display="https://book.kongfz.com/536651/7839562954"/>
-    <hyperlink ref="B155" r:id="rId84" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
-    <hyperlink ref="G155" r:id="rId85" display="https://book.kongfz.com/23231/8186709240"/>
-    <hyperlink ref="B156" r:id="rId86" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
-    <hyperlink ref="G156" r:id="rId87" display="https://book.kongfz.com/536651/7839554296"/>
-    <hyperlink ref="G157" r:id="rId88" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="B158" r:id="rId89" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
-    <hyperlink ref="G159" r:id="rId90" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
-    <hyperlink ref="G160" r:id="rId91" display="https://book.kongfz.com/200249/1819262449/"/>
-    <hyperlink ref="G161" r:id="rId92" display="https://product.dangdang.com/11721366316.html"/>
-    <hyperlink ref="B162" r:id="rId93" display="出版社:宗教文化出版社 "/>
-    <hyperlink ref="G162" r:id="rId94" display="https://product.dangdang.com/22497432.html"/>
-    <hyperlink ref="G163" r:id="rId95" display="http://aiguji.net/3299.html"/>
-    <hyperlink ref="G167" r:id="rId96" display="https://book.kongfz.com/467603/10356350239"/>
+    <hyperlink ref="G77" r:id="rId37" display="https://www.dpm.org.cn/ancient"/>
+    <hyperlink ref="G78" r:id="rId38" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G79" r:id="rId39" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
+    <hyperlink ref="G80" r:id="rId40" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
+    <hyperlink ref="G81" r:id="rId41" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
+    <hyperlink ref="G82" r:id="rId42" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G83" r:id="rId43" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G84" r:id="rId44" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G85" r:id="rId45" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G86" r:id="rId46" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G87" r:id="rId47" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G88" r:id="rId48" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G89" r:id="rId49" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G90" r:id="rId50" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G93" r:id="rId51" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
+    <hyperlink ref="G95" r:id="rId52" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G96" r:id="rId53" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G97" r:id="rId54" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G98" r:id="rId55" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G101" r:id="rId56" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G102" r:id="rId57" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G105" r:id="rId58" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G106" r:id="rId59" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
+    <hyperlink ref="G107" r:id="rId60" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
+    <hyperlink ref="G109" r:id="rId61" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
+    <hyperlink ref="G115" r:id="rId62" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G116" r:id="rId63" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G117" r:id="rId64" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G118" r:id="rId65" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G119" r:id="rId66" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G120" r:id="rId67" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G122" r:id="rId68" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G123" r:id="rId69" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
+    <hyperlink ref="G127" r:id="rId70" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
+    <hyperlink ref="F129" r:id="rId71" display="中新网北京3月21日电 (记者 应妮) "/>
+    <hyperlink ref="G129" r:id="rId72" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
+    <hyperlink ref="G131" r:id="rId73" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G135" r:id="rId74" display="https://discovery.cctv.com/20070619/107154.shtml"/>
+    <hyperlink ref="G138" r:id="rId75" display="https://book.kongfz.com/102740/682706591"/>
+    <hyperlink ref="A141" r:id="rId76" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G145" r:id="rId77" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
+    <hyperlink ref="G146" r:id="rId78" display="https://book.kongfz.com/20791/3754198261"/>
+    <hyperlink ref="G149" r:id="rId79" display="https://www.ljstsg.cn/?p=6315"/>
+    <hyperlink ref="AD149" r:id="rId80" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="G150" r:id="rId81" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
+    <hyperlink ref="G151" r:id="rId82" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="B154" r:id="rId83" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
+    <hyperlink ref="G154" r:id="rId84" display="https://book.kongfz.com/536651/7839562954"/>
+    <hyperlink ref="B155" r:id="rId85" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
+    <hyperlink ref="G155" r:id="rId86" display="https://book.kongfz.com/23231/8186709240"/>
+    <hyperlink ref="B156" r:id="rId87" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
+    <hyperlink ref="G156" r:id="rId88" display="https://book.kongfz.com/536651/7839554296"/>
+    <hyperlink ref="G157" r:id="rId89" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="B158" r:id="rId90" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
+    <hyperlink ref="G159" r:id="rId91" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
+    <hyperlink ref="G160" r:id="rId92" display="https://book.kongfz.com/200249/1819262449/"/>
+    <hyperlink ref="G161" r:id="rId93" display="https://product.dangdang.com/11721366316.html"/>
+    <hyperlink ref="B162" r:id="rId94" display="出版社:宗教文化出版社 "/>
+    <hyperlink ref="G162" r:id="rId95" display="https://product.dangdang.com/22497432.html"/>
+    <hyperlink ref="G163" r:id="rId96" display="http://aiguji.net/3299.html"/>
+    <hyperlink ref="G170" r:id="rId97" display="https://book.kongfz.com/467603/10356350239"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -85127,120 +85167,120 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="66" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="67" width="12.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7962</v>
+        <v>7965</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="67" t="n">
+      <c r="A2" s="68" t="n">
         <v>1539</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7963</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="67" t="n">
+      <c r="A3" s="68" t="n">
         <v>1615</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7964</v>
+        <v>7967</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="67" t="n">
+      <c r="A4" s="68" t="n">
         <v>1620</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7965</v>
+        <v>7968</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="67" t="n">
+      <c r="A5" s="68" t="n">
         <v>1623</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7966</v>
+        <v>7969</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="67" t="n">
+      <c r="A6" s="68" t="n">
         <v>1653</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7967</v>
+        <v>7970</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>7968</v>
+        <v>7971</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7969</v>
+        <v>7972</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>7970</v>
+        <v>7973</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7971</v>
+        <v>7974</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>7972</v>
+        <v>7975</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7973</v>
+        <v>7976</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>7974</v>
+        <v>7977</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>7975</v>
+        <v>7978</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>7976</v>
+        <v>7979</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7977</v>
+        <v>7980</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>7978</v>
+        <v>7981</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7979</v>
+        <v>7982</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85255,45 +85295,45 @@
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>7836</v>
+        <v>7837</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>7980</v>
+        <v>7983</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>7981</v>
+        <v>7984</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>7982</v>
+        <v>7985</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>7983</v>
+        <v>7986</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>7984</v>
+        <v>7987</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>7985</v>
+        <v>7988</v>
       </c>
       <c r="E23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>7986</v>
+        <v>7989</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>7987</v>
+        <v>7990</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
         <v>7663</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>7988</v>
+        <v>7991</v>
       </c>
     </row>
   </sheetData>
@@ -85325,84 +85365,84 @@
   </cols>
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="68" t="s">
-        <v>7989</v>
+      <c r="A8" s="69" t="s">
+        <v>7992</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="68" t="s">
-        <v>7990</v>
+      <c r="A9" s="69" t="s">
+        <v>7993</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="68" t="s">
-        <v>7991</v>
+      <c r="A10" s="69" t="s">
+        <v>7994</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="68" t="s">
-        <v>7992</v>
-      </c>
-      <c r="B12" s="69" t="n">
+      <c r="A12" s="69" t="s">
+        <v>7995</v>
+      </c>
+      <c r="B12" s="70" t="n">
         <v>45735</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7993</v>
+        <v>7996</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>7994</v>
+        <v>7997</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="68" t="s">
-        <v>7995</v>
-      </c>
-      <c r="B13" s="69" t="n">
+      <c r="A13" s="69" t="s">
+        <v>7998</v>
+      </c>
+      <c r="B13" s="70" t="n">
         <v>45970</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7996</v>
+        <v>7999</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>7997</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="68" t="s">
-        <v>7998</v>
-      </c>
-      <c r="B14" s="69" t="n">
+      <c r="A14" s="69" t="s">
+        <v>8001</v>
+      </c>
+      <c r="B14" s="70" t="n">
         <v>45995</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>7999</v>
+        <v>8002</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8000</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="68" t="s">
-        <v>8001</v>
-      </c>
-      <c r="B15" s="69" t="n">
+      <c r="A15" s="69" t="s">
+        <v>8004</v>
+      </c>
+      <c r="B15" s="70" t="n">
         <v>46036</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8002</v>
+        <v>8005</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8003</v>
+        <v>8006</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>8004</v>
+        <v>8007</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>8005</v>
+        <v>8008</v>
       </c>
     </row>
   </sheetData>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10854" uniqueCount="8009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10856" uniqueCount="8012">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -25359,7 +25359,7 @@
     <t xml:space="preserve">重印工程圆满结束 </t>
   </si>
   <si>
-    <t xml:space="preserve">1991年 </t>
+    <t xml:space="preserve">1991年 6月</t>
   </si>
   <si>
     <t xml:space="preserve">出访泰国 </t>
@@ -28352,6 +28352,15 @@
   </si>
   <si>
     <t xml:space="preserve">人民大学和敦煌研究所，两个地方的馆藏版本</t>
+  </si>
+  <si>
+    <t xml:space="preserve">清刻藏经</t>
+  </si>
+  <si>
+    <t xml:space="preserve">吕澄 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.fjdh.cn/wumin/2009/04/22484866694.html</t>
   </si>
   <si>
     <t xml:space="preserve">清敕修大藏经保护项目简介 </t>
@@ -28936,7 +28945,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29205,6 +29214,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -83521,9 +83534,7 @@
       <c r="B86" s="28" t="s">
         <v>7657</v>
       </c>
-      <c r="C86" s="28" t="s">
-        <v>7671</v>
-      </c>
+      <c r="C86" s="28"/>
       <c r="D86" s="43" t="s">
         <v>7672</v>
       </c>
@@ -85001,14 +85012,25 @@
         <v>7954</v>
       </c>
     </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="0" t="s">
+        <v>7955</v>
+      </c>
+      <c r="B166" s="67" t="s">
+        <v>7956</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>7957</v>
+      </c>
+    </row>
     <row r="169" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="43" t="s">
-        <v>7955</v>
+        <v>7958</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>7956</v>
+        <v>7959</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>7742</v>
@@ -85017,36 +85039,36 @@
         <v>7869</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>7957</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>7958</v>
+        <v>7961</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>7959</v>
+        <v>7962</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>7960</v>
+        <v>7963</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>7961</v>
+        <v>7964</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>7962</v>
+        <v>7965</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>7963</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="43" t="s">
-        <v>7964</v>
+        <v>7967</v>
       </c>
     </row>
   </sheetData>
@@ -85167,120 +85189,120 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="67" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="68" width="12.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7965</v>
+        <v>7968</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="68" t="n">
+      <c r="A2" s="69" t="n">
         <v>1539</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7966</v>
+        <v>7969</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="68" t="n">
+      <c r="A3" s="69" t="n">
         <v>1615</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7967</v>
+        <v>7970</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="68" t="n">
+      <c r="A4" s="69" t="n">
         <v>1620</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7968</v>
+        <v>7971</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="68" t="n">
+      <c r="A5" s="69" t="n">
         <v>1623</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7969</v>
+        <v>7972</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="68" t="n">
+      <c r="A6" s="69" t="n">
         <v>1653</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7970</v>
+        <v>7973</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>7971</v>
+        <v>7974</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7972</v>
+        <v>7975</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>7973</v>
+        <v>7976</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7974</v>
+        <v>7977</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>7975</v>
+        <v>7978</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7976</v>
+        <v>7979</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>7977</v>
+        <v>7980</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>7978</v>
+        <v>7981</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>7979</v>
+        <v>7982</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7980</v>
+        <v>7983</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>7981</v>
+        <v>7984</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7982</v>
+        <v>7985</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85298,42 +85320,42 @@
         <v>7837</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>7983</v>
+        <v>7986</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>7984</v>
+        <v>7987</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>7985</v>
+        <v>7988</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>7986</v>
+        <v>7989</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>7987</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>7988</v>
+        <v>7991</v>
       </c>
       <c r="E23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>7989</v>
+        <v>7992</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>7990</v>
+        <v>7993</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
         <v>7663</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>7991</v>
+        <v>7994</v>
       </c>
     </row>
   </sheetData>
@@ -85365,84 +85387,84 @@
   </cols>
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="69" t="s">
-        <v>7992</v>
+      <c r="A8" s="70" t="s">
+        <v>7995</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="69" t="s">
-        <v>7993</v>
+      <c r="A9" s="70" t="s">
+        <v>7996</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="69" t="s">
-        <v>7994</v>
+      <c r="A10" s="70" t="s">
+        <v>7997</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="69" t="s">
-        <v>7995</v>
-      </c>
-      <c r="B12" s="70" t="n">
+      <c r="A12" s="70" t="s">
+        <v>7998</v>
+      </c>
+      <c r="B12" s="71" t="n">
         <v>45735</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7996</v>
+        <v>7999</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>7997</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="69" t="s">
-        <v>7998</v>
-      </c>
-      <c r="B13" s="70" t="n">
+      <c r="A13" s="70" t="s">
+        <v>8001</v>
+      </c>
+      <c r="B13" s="71" t="n">
         <v>45970</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7999</v>
+        <v>8002</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8000</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="69" t="s">
-        <v>8001</v>
-      </c>
-      <c r="B14" s="70" t="n">
+      <c r="A14" s="70" t="s">
+        <v>8004</v>
+      </c>
+      <c r="B14" s="71" t="n">
         <v>45995</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8002</v>
+        <v>8005</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8003</v>
+        <v>8006</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="69" t="s">
-        <v>8004</v>
-      </c>
-      <c r="B15" s="70" t="n">
+      <c r="A15" s="70" t="s">
+        <v>8007</v>
+      </c>
+      <c r="B15" s="71" t="n">
         <v>46036</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8005</v>
+        <v>8008</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8006</v>
+        <v>8009</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>8007</v>
+        <v>8010</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>8008</v>
+        <v>8011</v>
       </c>
     </row>
   </sheetData>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10856" uniqueCount="8012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10871" uniqueCount="8025">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -24974,7 +24974,81 @@
     <t xml:space="preserve">智化寺所藏经版73024块安全运抵</t>
   </si>
   <si>
+    <t xml:space="preserve">凤凰新媒体 ( 苏士澍/文物出版社社长)</t>
+  </si>
+  <si>
     <t xml:space="preserve">北京广济寺 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">为更好地保护和整理这套珍贵文物，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1987</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">日在中国佛教协会所在地广济寺，召开重印《乾隆版大藏经》汇报会。赵朴老听了大家的汇报，非常高兴地说：“重印《乾隆版大藏经》是一项非常重要的工作，要完成如此大的工作，只有盛世才能做到。雕造、刷印《乾隆版大藏经》是在历史上‘康乾盛世’完成的。又是盛世，我们重印《乾隆版大藏经》，无论对佛教界还是文化界都是一件非常了不起的事情。” </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">中国民主促进会</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mj.org.cn/hszl/hsgc/202607/t20260707_308549.htm</t>
   </si>
   <si>
     <t xml:space="preserve">中国佛教协会、北京市文物局、文物出版社联合召开 </t>
@@ -25152,6 +25226,47 @@
     <t xml:space="preserve">正式开印</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">为这部大藏经题词的全国人大常委会副委员长、中国佛教协会名誉会长班禅额尔德尼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">确吉坚赞，撰写序文的全国政协副主席、中国佛教协会会长赵朴初参加了仪式。 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">世界最大木板典籍《乾隆版大藏经》重印 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">由文物出版社首批重印的《乾隆版大藏经》，共五十部二千卷，装二百函。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">深圳市盐田区档案馆 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yantian.gov.cn/ytdayszxxw/lsjt/content/post_11734380.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">北京</t>
   </si>
   <si>
@@ -25426,7 +25541,62 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">绝大部分运往十三陵做长期存藏</t>
+  </si>
+  <si>
     <t xml:space="preserve">经版再被搬迁，绝大部分运往十三陵做长期存藏， 有两千余块经版被保留在云居寺。 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2009</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">北京现代化专业库房</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">经北京市文物局批准，对《龙藏》经版开展保护工作。至此，《龙藏》经版自诞生以来第一次有了现代化专业库房，并补齐、修复了全部佚失及损坏的经版。自刊成至今</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">281</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年，其间沧桑变化，《龙藏》经版留存至今，至为难得。 </t>
+    </r>
   </si>
   <si>
     <r>
@@ -28661,6 +28831,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
@@ -28669,12 +28845,6 @@
     <font>
       <sz val="11"/>
       <name val="Noto Sans SC"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -28945,7 +29115,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29146,15 +29316,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -29212,10 +29390,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -82257,7 +82431,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:AD179"/>
+  <dimension ref="A3:AD183"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.85"/>
@@ -83311,8 +83485,8 @@
       <c r="E75" s="43" t="s">
         <v>7658</v>
       </c>
-      <c r="F75" s="28" t="s">
-        <v>7521</v>
+      <c r="F75" s="0" t="s">
+        <v>7659</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>7522</v>
@@ -83322,761 +83496,750 @@
       <c r="A76" s="47" t="n">
         <v>32140</v>
       </c>
-      <c r="B76" s="43" t="s">
-        <v>7659</v>
-      </c>
-      <c r="C76" s="28" t="s">
+      <c r="B76" s="28"/>
+      <c r="C76" s="28"/>
+      <c r="E76" s="0"/>
+      <c r="F76" s="0"/>
+    </row>
+    <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="47" t="n">
+        <v>32140</v>
+      </c>
+      <c r="B77" s="43" t="s">
         <v>7660</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="C77" s="50" t="s">
         <v>7661</v>
       </c>
-      <c r="E76" s="28" t="s">
+      <c r="E77" s="43"/>
+      <c r="F77" s="28" t="s">
         <v>7662</v>
       </c>
-      <c r="F76" s="43" t="s">
+      <c r="G77" s="2" t="s">
         <v>7663</v>
       </c>
-      <c r="G76" s="2" t="s">
+    </row>
+    <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="47" t="n">
+        <v>32140</v>
+      </c>
+      <c r="B78" s="43" t="s">
+        <v>7660</v>
+      </c>
+      <c r="C78" s="28" t="s">
         <v>7664</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="47" t="s">
+      <c r="D78" s="1" t="s">
         <v>7665</v>
       </c>
-      <c r="B77" s="28" t="s">
+      <c r="E78" s="28" t="s">
         <v>7666</v>
       </c>
-      <c r="D77" s="28" t="s">
+      <c r="F78" s="43" t="s">
         <v>7667</v>
       </c>
-      <c r="E77" s="50" t="s">
+      <c r="G78" s="2" t="s">
         <v>7668</v>
       </c>
-      <c r="F77" s="43" t="s">
+    </row>
+    <row r="79" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="47" t="s">
+        <v>7669</v>
+      </c>
+      <c r="B79" s="28" t="s">
+        <v>7670</v>
+      </c>
+      <c r="D79" s="28" t="s">
+        <v>7671</v>
+      </c>
+      <c r="E79" s="51" t="s">
+        <v>7672</v>
+      </c>
+      <c r="F79" s="43" t="s">
         <v>7537</v>
       </c>
-      <c r="G77" s="51" t="s">
-        <v>7669</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="47" t="s">
-        <v>7670</v>
-      </c>
-      <c r="B78" s="28" t="s">
+      <c r="G79" s="52" t="s">
+        <v>7673</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="47" t="s">
+        <v>7674</v>
+      </c>
+      <c r="B80" s="28" t="s">
         <v>7657</v>
       </c>
-      <c r="C78" s="28" t="s">
-        <v>7671</v>
-      </c>
-      <c r="D78" s="43" t="s">
-        <v>7672</v>
-      </c>
-      <c r="E78" s="28" t="s">
-        <v>7673</v>
-      </c>
-      <c r="F78" s="28" t="s">
+      <c r="C80" s="28" t="s">
+        <v>7675</v>
+      </c>
+      <c r="D80" s="43" t="s">
+        <v>7676</v>
+      </c>
+      <c r="E80" s="28" t="s">
+        <v>7677</v>
+      </c>
+      <c r="F80" s="28" t="s">
         <v>7521</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G80" s="2" t="s">
         <v>7522</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="47" t="n">
-        <v>32471</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>7674</v>
-      </c>
-      <c r="C79" s="28" t="s">
-        <v>7675</v>
-      </c>
-      <c r="D79" s="28" t="s">
-        <v>7676</v>
-      </c>
-      <c r="E79" s="50"/>
-      <c r="F79" s="43" t="s">
-        <v>7635</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>7636</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="47" t="n">
-        <v>32471</v>
-      </c>
-      <c r="B80" s="28" t="s">
-        <v>7677</v>
-      </c>
-      <c r="C80" s="28" t="s">
-        <v>7678</v>
-      </c>
-      <c r="D80" s="28" t="s">
-        <v>7679</v>
-      </c>
-      <c r="E80" s="28"/>
-      <c r="F80" s="1" t="s">
-        <v>7680</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>7681</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="47" t="n">
         <v>32471</v>
       </c>
-      <c r="B81" s="28" t="s">
+      <c r="B81" s="28"/>
+      <c r="C81" s="50" t="s">
+        <v>7678</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>7679</v>
+      </c>
+      <c r="E81" s="53" t="s">
+        <v>7680</v>
+      </c>
+      <c r="F81" s="53" t="s">
+        <v>7681</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>7682</v>
       </c>
-      <c r="C81" s="28" t="s">
-        <v>7683</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>7684</v>
-      </c>
-      <c r="E81" s="28"/>
-      <c r="F81" s="28" t="s">
-        <v>7663</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>7685</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="82" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="47" t="n">
         <v>32471</v>
       </c>
-      <c r="B82" s="28" t="s">
-        <v>7682</v>
+      <c r="B82" s="1" t="s">
+        <v>7683</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>7686</v>
-      </c>
-      <c r="D82" s="1" t="s">
         <v>7684</v>
       </c>
-      <c r="E82" s="28" t="s">
-        <v>7687</v>
-      </c>
-      <c r="F82" s="28" t="s">
-        <v>7521</v>
+      <c r="D82" s="28" t="s">
+        <v>7685</v>
+      </c>
+      <c r="E82" s="51"/>
+      <c r="F82" s="43" t="s">
+        <v>7635</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>7522</v>
+        <v>7636</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="47" t="n">
-        <v>32517</v>
+        <v>32471</v>
       </c>
       <c r="B83" s="28" t="s">
+        <v>7686</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>7687</v>
+      </c>
+      <c r="D83" s="28" t="s">
         <v>7688</v>
-      </c>
-      <c r="C83" s="28" t="s">
-        <v>7589</v>
-      </c>
-      <c r="D83" s="28" t="s">
-        <v>7689</v>
       </c>
       <c r="E83" s="28"/>
       <c r="F83" s="1" t="s">
+        <v>7689</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>7690</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B84" s="28" t="s">
+        <v>7691</v>
+      </c>
+      <c r="C84" s="28" t="s">
+        <v>7692</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>7693</v>
+      </c>
+      <c r="E84" s="28"/>
+      <c r="F84" s="28" t="s">
+        <v>7667</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>7694</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B85" s="28" t="s">
+        <v>7691</v>
+      </c>
+      <c r="C85" s="28" t="s">
+        <v>7695</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>7693</v>
+      </c>
+      <c r="E85" s="28" t="s">
+        <v>7696</v>
+      </c>
+      <c r="F85" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="47" t="n">
+        <v>32517</v>
+      </c>
+      <c r="B86" s="28" t="s">
+        <v>7697</v>
+      </c>
+      <c r="C86" s="28" t="s">
+        <v>7589</v>
+      </c>
+      <c r="D86" s="28" t="s">
+        <v>7698</v>
+      </c>
+      <c r="E86" s="28"/>
+      <c r="F86" s="1" t="s">
         <v>7593</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G86" s="2" t="s">
         <v>7594</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="47"/>
-      <c r="B84" s="28" t="s">
-        <v>7690</v>
-      </c>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="43" t="s">
+    <row r="87" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="47"/>
+      <c r="B87" s="28" t="s">
+        <v>7699</v>
+      </c>
+      <c r="C87" s="28"/>
+      <c r="D87" s="28"/>
+      <c r="E87" s="28"/>
+      <c r="F87" s="43" t="s">
         <v>7496</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G87" s="2" t="s">
         <v>7497</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="47" t="s">
-        <v>7691</v>
-      </c>
-      <c r="B85" s="28" t="s">
-        <v>7692</v>
-      </c>
-      <c r="C85" s="28" t="s">
-        <v>7693</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E85" s="28"/>
-      <c r="F85" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="47" t="s">
-        <v>7694</v>
-      </c>
-      <c r="B86" s="28" t="s">
-        <v>7657</v>
-      </c>
-      <c r="C86" s="28"/>
-      <c r="D86" s="43" t="s">
-        <v>7672</v>
-      </c>
-      <c r="E86" s="28" t="s">
-        <v>7695</v>
-      </c>
-      <c r="F86" s="28" t="s">
-        <v>7521</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="47" t="s">
-        <v>7696</v>
-      </c>
-      <c r="B87" s="28" t="s">
-        <v>7697</v>
-      </c>
-      <c r="C87" s="28"/>
-      <c r="D87" s="43" t="s">
-        <v>7672</v>
-      </c>
-      <c r="E87" s="28" t="s">
-        <v>7698</v>
-      </c>
-      <c r="F87" s="28" t="s">
-        <v>7521</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>7522</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="47" t="s">
-        <v>7699</v>
+        <v>7700</v>
       </c>
       <c r="B88" s="28" t="s">
-        <v>7700</v>
+        <v>7701</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>7701</v>
-      </c>
-      <c r="D88" s="43" t="s">
-        <v>7672</v>
-      </c>
-      <c r="E88" s="28" t="s">
         <v>7702</v>
       </c>
+      <c r="D88" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="E88" s="28"/>
       <c r="F88" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="47" t="s">
+        <v>7703</v>
+      </c>
+      <c r="B89" s="28" t="s">
+        <v>7657</v>
+      </c>
+      <c r="C89" s="28"/>
+      <c r="D89" s="43" t="s">
+        <v>7676</v>
+      </c>
+      <c r="E89" s="28" t="s">
+        <v>7704</v>
+      </c>
+      <c r="F89" s="28" t="s">
         <v>7521</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G89" s="2" t="s">
         <v>7522</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="43" t="s">
-        <v>7703</v>
-      </c>
-      <c r="B89" s="28" t="s">
-        <v>7704</v>
-      </c>
-      <c r="D89" s="43" t="s">
+    <row r="90" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="47" t="s">
         <v>7705</v>
       </c>
-      <c r="E89" s="28" t="s">
+      <c r="B90" s="28" t="s">
         <v>7706</v>
       </c>
-      <c r="F89" s="52" t="s">
+      <c r="C90" s="28"/>
+      <c r="D90" s="43" t="s">
+        <v>7676</v>
+      </c>
+      <c r="E90" s="28" t="s">
         <v>7707</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="F90" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="47" t="s">
         <v>7708</v>
       </c>
-    </row>
-    <row r="90" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="49" t="s">
+      <c r="B91" s="28" t="s">
         <v>7709</v>
       </c>
-      <c r="B90" s="28" t="s">
+      <c r="C91" s="28" t="s">
         <v>7710</v>
       </c>
-      <c r="F90" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="49"/>
+      <c r="D91" s="43" t="s">
+        <v>7676</v>
+      </c>
+      <c r="E91" s="28" t="s">
+        <v>7711</v>
+      </c>
+      <c r="F91" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>7522</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="43" t="s">
-        <v>7711</v>
-      </c>
-      <c r="B92" s="28"/>
-      <c r="D92" s="43"/>
-      <c r="E92" s="28"/>
-      <c r="F92" s="52"/>
-      <c r="G92" s="2"/>
-    </row>
-    <row r="93" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="47" t="n">
+        <v>7712</v>
+      </c>
+      <c r="B92" s="0"/>
+      <c r="C92" s="28" t="s">
+        <v>7713</v>
+      </c>
+      <c r="D92" s="43" t="s">
+        <v>7714</v>
+      </c>
+      <c r="E92" s="28" t="s">
+        <v>7715</v>
+      </c>
+      <c r="F92" s="54" t="s">
+        <v>7716</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>7717</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="49" t="s">
+        <v>7718</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>7719</v>
+      </c>
+      <c r="C93" s="28" t="s">
+        <v>7720</v>
+      </c>
+      <c r="F93" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="49" t="s">
+        <v>7721</v>
+      </c>
+      <c r="B94" s="53" t="s">
+        <v>7722</v>
+      </c>
+      <c r="C94" s="50" t="s">
+        <v>7723</v>
+      </c>
+      <c r="D94" s="0"/>
+      <c r="F94" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="49"/>
+    </row>
+    <row r="96" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="43" t="s">
+        <v>7724</v>
+      </c>
+      <c r="B96" s="28"/>
+      <c r="D96" s="43"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="54"/>
+      <c r="G96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="47" t="n">
         <v>38164</v>
       </c>
-      <c r="B93" s="43" t="s">
-        <v>7712</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>7713</v>
-      </c>
-      <c r="D93" s="28" t="s">
-        <v>7714</v>
-      </c>
-      <c r="E93" s="28" t="s">
-        <v>7715</v>
-      </c>
-      <c r="F93" s="28" t="s">
-        <v>7716</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>7717</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="47" t="s">
-        <v>7718</v>
-      </c>
-      <c r="B94" s="53" t="s">
-        <v>7719</v>
-      </c>
-      <c r="C94" s="53" t="s">
-        <v>7720</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>7721</v>
-      </c>
-      <c r="E94" s="49" t="s">
-        <v>7722</v>
-      </c>
-      <c r="F94" s="28" t="s">
-        <v>7723</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>7724</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="47" t="s">
+      <c r="B97" s="43" t="s">
         <v>7725</v>
       </c>
-      <c r="B95" s="43" t="s">
+      <c r="C97" s="1" t="s">
         <v>7726</v>
       </c>
-      <c r="C95" s="28" t="s">
+      <c r="D97" s="28" t="s">
         <v>7727</v>
       </c>
-      <c r="D95" s="43" t="s">
+      <c r="E97" s="28" t="s">
         <v>7728</v>
       </c>
-      <c r="E95" s="43"/>
-      <c r="F95" s="43" t="s">
+      <c r="F97" s="28" t="s">
+        <v>7729</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>7730</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="47" t="s">
+        <v>7731</v>
+      </c>
+      <c r="B98" s="55" t="s">
+        <v>7732</v>
+      </c>
+      <c r="C98" s="55" t="s">
+        <v>7733</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>7734</v>
+      </c>
+      <c r="E98" s="49" t="s">
+        <v>7735</v>
+      </c>
+      <c r="F98" s="28" t="s">
+        <v>7736</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>7737</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="47" t="s">
+        <v>7738</v>
+      </c>
+      <c r="B99" s="43" t="s">
+        <v>7739</v>
+      </c>
+      <c r="C99" s="28" t="s">
+        <v>7740</v>
+      </c>
+      <c r="D99" s="43" t="s">
+        <v>7741</v>
+      </c>
+      <c r="E99" s="43"/>
+      <c r="F99" s="43" t="s">
         <v>7502</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G99" s="2" t="s">
         <v>7503</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="47" t="s">
-        <v>7725</v>
-      </c>
-      <c r="B96" s="28" t="s">
-        <v>7729</v>
-      </c>
-      <c r="C96" s="28" t="s">
-        <v>7730</v>
-      </c>
-      <c r="D96" s="28" t="s">
-        <v>7731</v>
-      </c>
-      <c r="E96" s="28" t="s">
-        <v>7732</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>7733</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>7734</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="47" t="s">
-        <v>7735</v>
-      </c>
-      <c r="B97" s="28" t="s">
-        <v>7729</v>
-      </c>
-      <c r="C97" s="28" t="s">
-        <v>7736</v>
-      </c>
-      <c r="D97" s="28" t="s">
-        <v>7737</v>
-      </c>
-      <c r="E97" s="28"/>
-      <c r="F97" s="1" t="s">
-        <v>7733</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>7734</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="47" t="n">
+    <row r="100" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="47" t="s">
+        <v>7738</v>
+      </c>
+      <c r="B100" s="28" t="s">
+        <v>7742</v>
+      </c>
+      <c r="C100" s="28" t="s">
+        <v>7743</v>
+      </c>
+      <c r="D100" s="28" t="s">
+        <v>7744</v>
+      </c>
+      <c r="E100" s="28" t="s">
+        <v>7745</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>7746</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>7747</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="47" t="s">
+        <v>7748</v>
+      </c>
+      <c r="B101" s="28" t="s">
+        <v>7742</v>
+      </c>
+      <c r="C101" s="28" t="s">
+        <v>7749</v>
+      </c>
+      <c r="D101" s="28" t="s">
+        <v>7750</v>
+      </c>
+      <c r="E101" s="28"/>
+      <c r="F101" s="1" t="s">
+        <v>7746</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>7747</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="47" t="n">
         <v>42230</v>
       </c>
-      <c r="B98" s="28" t="s">
-        <v>7729</v>
-      </c>
-      <c r="C98" s="28" t="s">
-        <v>7738</v>
-      </c>
-      <c r="D98" s="28" t="s">
-        <v>7739</v>
-      </c>
-      <c r="E98" s="28" t="s">
-        <v>7740</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>7733</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>7734</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="43" t="s">
-        <v>7741</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="47" t="n">
+      <c r="B102" s="28" t="s">
+        <v>7742</v>
+      </c>
+      <c r="C102" s="28" t="s">
+        <v>7751</v>
+      </c>
+      <c r="D102" s="28" t="s">
+        <v>7752</v>
+      </c>
+      <c r="E102" s="28" t="s">
+        <v>7753</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>7746</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>7747</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="43" t="s">
+        <v>7754</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="47" t="n">
         <v>42753</v>
       </c>
-      <c r="B101" s="53" t="s">
-        <v>7742</v>
-      </c>
-      <c r="C101" s="43" t="s">
-        <v>7743</v>
-      </c>
-      <c r="D101" s="43" t="s">
-        <v>7744</v>
-      </c>
-      <c r="E101" s="43" t="s">
-        <v>7745</v>
-      </c>
-      <c r="F101" s="43" t="s">
+      <c r="B105" s="55" t="s">
+        <v>7755</v>
+      </c>
+      <c r="C105" s="43" t="s">
+        <v>7756</v>
+      </c>
+      <c r="D105" s="43" t="s">
+        <v>7757</v>
+      </c>
+      <c r="E105" s="43" t="s">
+        <v>7758</v>
+      </c>
+      <c r="F105" s="43" t="s">
         <v>7502</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="G105" s="2" t="s">
         <v>7503</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="47" t="n">
+    <row r="106" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="47" t="n">
         <v>42753</v>
       </c>
-      <c r="B102" s="53" t="s">
-        <v>7746</v>
-      </c>
-      <c r="C102" s="28" t="s">
-        <v>7747</v>
-      </c>
-      <c r="D102" s="43" t="s">
-        <v>7744</v>
-      </c>
-      <c r="E102" s="54" t="s">
-        <v>7748</v>
-      </c>
-      <c r="F102" s="43" t="s">
+      <c r="B106" s="55" t="s">
+        <v>7759</v>
+      </c>
+      <c r="C106" s="28" t="s">
+        <v>7760</v>
+      </c>
+      <c r="D106" s="43" t="s">
+        <v>7757</v>
+      </c>
+      <c r="E106" s="56" t="s">
+        <v>7761</v>
+      </c>
+      <c r="F106" s="43" t="s">
         <v>7502</v>
       </c>
-      <c r="G102" s="2" t="s">
+      <c r="G106" s="2" t="s">
         <v>7503</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="47" t="n">
+    <row r="107" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="47" t="n">
         <v>42753</v>
       </c>
-      <c r="B103" s="53" t="s">
-        <v>7746</v>
-      </c>
-      <c r="C103" s="53" t="s">
-        <v>7749</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>7750</v>
-      </c>
-      <c r="E103" s="43" t="s">
-        <v>7751</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>7752</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>7753</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="47" t="n">
+      <c r="B107" s="55" t="s">
+        <v>7759</v>
+      </c>
+      <c r="C107" s="55" t="s">
+        <v>7762</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>7763</v>
+      </c>
+      <c r="E107" s="43" t="s">
+        <v>7764</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>7765</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>7766</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="47" t="n">
         <v>43725</v>
       </c>
-      <c r="B104" s="28" t="s">
-        <v>7754</v>
-      </c>
-      <c r="C104" s="28" t="s">
-        <v>7755</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>7756</v>
-      </c>
-      <c r="E104" s="28" t="s">
-        <v>7757</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>7758</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>7759</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="47" t="n">
-        <v>44895</v>
-      </c>
-      <c r="B105" s="28" t="s">
-        <v>7760</v>
-      </c>
-      <c r="C105" s="28" t="s">
-        <v>7761</v>
-      </c>
-      <c r="D105" s="43" t="s">
-        <v>7762</v>
-      </c>
-      <c r="E105" s="28" t="s">
-        <v>7763</v>
-      </c>
-      <c r="F105" s="28" t="s">
-        <v>7764</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>7765</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="47" t="n">
-        <v>45449</v>
-      </c>
-      <c r="B106" s="28" t="s">
-        <v>7766</v>
-      </c>
-      <c r="C106" s="28" t="s">
+      <c r="B108" s="28" t="s">
         <v>7767</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="C108" s="28" t="s">
         <v>7768</v>
       </c>
-      <c r="E106" s="28" t="s">
+      <c r="D108" s="1" t="s">
         <v>7769</v>
       </c>
-      <c r="F106" s="28" t="s">
+      <c r="E108" s="28" t="s">
         <v>7770</v>
       </c>
-      <c r="G106" s="2" t="s">
+      <c r="F108" s="1" t="s">
         <v>7771</v>
       </c>
-    </row>
-    <row r="107" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="47" t="n">
-        <v>46017</v>
-      </c>
-      <c r="B107" s="28" t="s">
+      <c r="G108" s="1" t="s">
         <v>7772</v>
       </c>
-      <c r="C107" s="28" t="s">
-        <v>7773</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>7774</v>
-      </c>
-      <c r="E107" s="28" t="s">
-        <v>7775</v>
-      </c>
-      <c r="F107" s="28" t="s">
-        <v>7776</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>7777</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="47"/>
-      <c r="B108" s="28" t="s">
-        <v>7778</v>
-      </c>
-      <c r="C108" s="43" t="s">
-        <v>7779</v>
-      </c>
-      <c r="E108" s="28"/>
-      <c r="F108" s="28"/>
     </row>
     <row r="109" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="47" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B109" s="28" t="s">
+        <v>7773</v>
+      </c>
+      <c r="C109" s="28" t="s">
+        <v>7774</v>
+      </c>
+      <c r="D109" s="43" t="s">
+        <v>7775</v>
+      </c>
+      <c r="E109" s="28" t="s">
+        <v>7776</v>
+      </c>
+      <c r="F109" s="28" t="s">
+        <v>7777</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>7778</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="47" t="n">
+        <v>45449</v>
+      </c>
+      <c r="B110" s="28" t="s">
+        <v>7779</v>
+      </c>
+      <c r="C110" s="28" t="s">
+        <v>7780</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>7781</v>
+      </c>
+      <c r="E110" s="28" t="s">
+        <v>7782</v>
+      </c>
+      <c r="F110" s="28" t="s">
+        <v>7783</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>7784</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="47" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B111" s="28" t="s">
+        <v>7785</v>
+      </c>
+      <c r="C111" s="28" t="s">
+        <v>7786</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>7787</v>
+      </c>
+      <c r="E111" s="28" t="s">
+        <v>7788</v>
+      </c>
+      <c r="F111" s="28" t="s">
+        <v>7789</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>7790</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="47"/>
+      <c r="B112" s="28" t="s">
+        <v>7791</v>
+      </c>
+      <c r="C112" s="43" t="s">
+        <v>7792</v>
+      </c>
+      <c r="E112" s="28"/>
+      <c r="F112" s="28"/>
+    </row>
+    <row r="113" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="47" t="n">
         <v>41741</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>7780</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>7781</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="47"/>
-      <c r="B113" s="28"/>
-      <c r="C113" s="28"/>
-      <c r="E113" s="28"/>
-      <c r="F113" s="28"/>
-      <c r="G113" s="2"/>
-    </row>
-    <row r="114" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="43" t="s">
-        <v>7782</v>
-      </c>
-      <c r="B114" s="28"/>
-      <c r="C114" s="28"/>
-      <c r="E114" s="28"/>
-      <c r="F114" s="28"/>
-      <c r="G114" s="2"/>
-    </row>
-    <row r="115" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="55" t="s">
-        <v>7783</v>
-      </c>
-      <c r="B115" s="43" t="s">
-        <v>7784</v>
-      </c>
-      <c r="C115" s="28" t="s">
-        <v>7785</v>
-      </c>
-      <c r="D115" s="1" t="s">
+      <c r="B113" s="1" t="s">
+        <v>7793</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>7794</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="47"/>
+      <c r="B117" s="28"/>
+      <c r="C117" s="28"/>
+      <c r="E117" s="28"/>
+      <c r="F117" s="28"/>
+      <c r="G117" s="2"/>
+    </row>
+    <row r="118" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="43" t="s">
+        <v>7795</v>
+      </c>
+      <c r="B118" s="28"/>
+      <c r="C118" s="28"/>
+      <c r="E118" s="28"/>
+      <c r="F118" s="28"/>
+      <c r="G118" s="2"/>
+    </row>
+    <row r="119" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="57" t="s">
+        <v>7796</v>
+      </c>
+      <c r="B119" s="43" t="s">
+        <v>7797</v>
+      </c>
+      <c r="C119" s="28" t="s">
+        <v>7798</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>7515</v>
       </c>
-      <c r="E115" s="28" t="s">
-        <v>7706</v>
-      </c>
-      <c r="F115" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="55" t="s">
-        <v>7786</v>
-      </c>
-      <c r="B116" s="43" t="s">
-        <v>7787</v>
-      </c>
-      <c r="C116" s="28" t="s">
-        <v>7788</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>7789</v>
-      </c>
-      <c r="F116" s="52" t="s">
-        <v>7707</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>7708</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="49" t="s">
-        <v>7790</v>
-      </c>
-      <c r="B117" s="53" t="s">
-        <v>7791</v>
-      </c>
-      <c r="C117" s="28" t="s">
-        <v>7792</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="F117" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="55" t="s">
-        <v>7793</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>7794</v>
-      </c>
-      <c r="C118" s="28" t="s">
-        <v>7795</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E118" s="28" t="s">
-        <v>7796</v>
-      </c>
-      <c r="F118" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="55" t="s">
-        <v>7797</v>
-      </c>
-      <c r="B119" s="28" t="s">
-        <v>7798</v>
-      </c>
-      <c r="C119" s="28" t="s">
-        <v>7799</v>
-      </c>
-      <c r="E119" s="28"/>
+      <c r="E119" s="28" t="s">
+        <v>7715</v>
+      </c>
       <c r="F119" s="28" t="s">
         <v>7516</v>
       </c>
@@ -84084,991 +84247,1072 @@
         <v>7517</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="55" t="s">
+    <row r="120" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="57" t="s">
+        <v>7799</v>
+      </c>
+      <c r="B120" s="43" t="s">
         <v>7800</v>
       </c>
-      <c r="B120" s="28" t="s">
+      <c r="C120" s="28" t="s">
         <v>7801</v>
       </c>
-      <c r="C120" s="28" t="s">
+      <c r="D120" s="1" t="s">
         <v>7802</v>
       </c>
-      <c r="D120" s="1" t="s">
-        <v>7789</v>
-      </c>
-      <c r="E120" s="1" t="s">
+      <c r="F120" s="54" t="s">
+        <v>7716</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>7717</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="49" t="s">
         <v>7803</v>
       </c>
-      <c r="F120" s="52" t="s">
-        <v>7707</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>7708</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="47" t="n">
+      <c r="B121" s="55" t="s">
+        <v>7804</v>
+      </c>
+      <c r="C121" s="28" t="s">
+        <v>7805</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="F121" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="57" t="s">
+        <v>7806</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>7807</v>
+      </c>
+      <c r="C122" s="28" t="s">
+        <v>7808</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="E122" s="28" t="s">
+        <v>7809</v>
+      </c>
+      <c r="F122" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="57" t="s">
+        <v>7810</v>
+      </c>
+      <c r="B123" s="28" t="s">
+        <v>7811</v>
+      </c>
+      <c r="C123" s="28" t="s">
+        <v>7812</v>
+      </c>
+      <c r="E123" s="28"/>
+      <c r="F123" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="57" t="s">
+        <v>7813</v>
+      </c>
+      <c r="B124" s="28" t="s">
+        <v>7814</v>
+      </c>
+      <c r="C124" s="28" t="s">
+        <v>7815</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>7802</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>7816</v>
+      </c>
+      <c r="F124" s="54" t="s">
+        <v>7716</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>7717</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="47" t="n">
         <v>44662</v>
       </c>
-      <c r="B121" s="28" t="s">
-        <v>7804</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>7805</v>
-      </c>
-      <c r="D121" s="28" t="s">
-        <v>7806</v>
-      </c>
-      <c r="E121" s="28" t="s">
-        <v>7807</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>7808</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>7809</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="55" t="s">
-        <v>7810</v>
-      </c>
-      <c r="B122" s="28" t="s">
-        <v>7811</v>
-      </c>
-      <c r="C122" s="28"/>
-      <c r="D122" s="1" t="s">
-        <v>7789</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>7812</v>
-      </c>
-      <c r="F122" s="52" t="s">
-        <v>7707</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>7708</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="47" t="n">
+      <c r="B125" s="28" t="s">
+        <v>7817</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>7818</v>
+      </c>
+      <c r="D125" s="28" t="s">
+        <v>7819</v>
+      </c>
+      <c r="E125" s="28" t="s">
+        <v>7820</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>7821</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>7822</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="57" t="s">
+        <v>7823</v>
+      </c>
+      <c r="B126" s="28" t="s">
+        <v>7824</v>
+      </c>
+      <c r="C126" s="28"/>
+      <c r="D126" s="1" t="s">
+        <v>7802</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>7825</v>
+      </c>
+      <c r="F126" s="54" t="s">
+        <v>7716</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>7717</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="47" t="n">
         <v>44776</v>
       </c>
-      <c r="B123" s="28" t="s">
-        <v>7813</v>
-      </c>
-      <c r="C123" s="28" t="s">
-        <v>7814</v>
-      </c>
-      <c r="D123" s="28" t="s">
-        <v>7815</v>
-      </c>
-      <c r="E123" s="28" t="s">
-        <v>7816</v>
-      </c>
-      <c r="F123" s="28" t="s">
-        <v>7817</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>7818</v>
-      </c>
-    </row>
-    <row r="125" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
-      <c r="K125" s="1"/>
-      <c r="L125" s="1"/>
-      <c r="M125" s="1"/>
-      <c r="N125" s="1"/>
-      <c r="O125" s="1"/>
-      <c r="P125" s="1"/>
-      <c r="Q125" s="1"/>
-      <c r="R125" s="1"/>
-      <c r="S125" s="1"/>
-      <c r="T125" s="1"/>
-      <c r="U125" s="1"/>
-      <c r="V125" s="1"/>
-      <c r="W125" s="1"/>
-      <c r="X125" s="1"/>
-      <c r="Y125" s="1"/>
-      <c r="Z125" s="1"/>
-      <c r="AA125" s="1"/>
-      <c r="AB125" s="1"/>
-      <c r="AC125" s="1"/>
-      <c r="AD125" s="1"/>
-    </row>
-    <row r="126" s="56" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="47" t="s">
-        <v>7819</v>
-      </c>
-      <c r="B126" s="28"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="28"/>
-      <c r="G126" s="2"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="1"/>
-      <c r="M126" s="1"/>
-      <c r="N126" s="1"/>
-      <c r="O126" s="1"/>
-      <c r="P126" s="1"/>
-      <c r="Q126" s="1"/>
-      <c r="R126" s="1"/>
-      <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
-      <c r="U126" s="1"/>
-      <c r="V126" s="1"/>
-      <c r="W126" s="1"/>
-      <c r="X126" s="1"/>
-      <c r="Y126" s="1"/>
-      <c r="Z126" s="1"/>
-      <c r="AA126" s="1"/>
-      <c r="AB126" s="1"/>
-      <c r="AC126" s="1"/>
-      <c r="AD126" s="1"/>
-    </row>
-    <row r="127" s="56" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="57" t="n">
+      <c r="B127" s="28" t="s">
+        <v>7826</v>
+      </c>
+      <c r="C127" s="28" t="s">
+        <v>7827</v>
+      </c>
+      <c r="D127" s="28" t="s">
+        <v>7828</v>
+      </c>
+      <c r="E127" s="28" t="s">
+        <v>7829</v>
+      </c>
+      <c r="F127" s="28" t="s">
+        <v>7830</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>7831</v>
+      </c>
+    </row>
+    <row r="129" s="58" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="1"/>
+      <c r="N129" s="1"/>
+      <c r="O129" s="1"/>
+      <c r="P129" s="1"/>
+      <c r="Q129" s="1"/>
+      <c r="R129" s="1"/>
+      <c r="S129" s="1"/>
+      <c r="T129" s="1"/>
+      <c r="U129" s="1"/>
+      <c r="V129" s="1"/>
+      <c r="W129" s="1"/>
+      <c r="X129" s="1"/>
+      <c r="Y129" s="1"/>
+      <c r="Z129" s="1"/>
+      <c r="AA129" s="1"/>
+      <c r="AB129" s="1"/>
+      <c r="AC129" s="1"/>
+      <c r="AD129" s="1"/>
+    </row>
+    <row r="130" s="58" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="47" t="s">
+        <v>7832</v>
+      </c>
+      <c r="B130" s="28"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="28"/>
+      <c r="G130" s="2"/>
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1"/>
+      <c r="K130" s="1"/>
+      <c r="L130" s="1"/>
+      <c r="M130" s="1"/>
+      <c r="N130" s="1"/>
+      <c r="O130" s="1"/>
+      <c r="P130" s="1"/>
+      <c r="Q130" s="1"/>
+      <c r="R130" s="1"/>
+      <c r="S130" s="1"/>
+      <c r="T130" s="1"/>
+      <c r="U130" s="1"/>
+      <c r="V130" s="1"/>
+      <c r="W130" s="1"/>
+      <c r="X130" s="1"/>
+      <c r="Y130" s="1"/>
+      <c r="Z130" s="1"/>
+      <c r="AA130" s="1"/>
+      <c r="AB130" s="1"/>
+      <c r="AC130" s="1"/>
+      <c r="AD130" s="1"/>
+    </row>
+    <row r="131" s="58" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="59" t="n">
         <v>45004</v>
       </c>
-      <c r="B127" s="56" t="s">
-        <v>7820</v>
-      </c>
-      <c r="C127" s="56" t="s">
-        <v>7821</v>
-      </c>
-      <c r="D127" s="56" t="s">
-        <v>7822</v>
-      </c>
-      <c r="E127" s="56" t="s">
-        <v>7823</v>
-      </c>
-      <c r="F127" s="58" t="s">
-        <v>7824</v>
-      </c>
-      <c r="G127" s="56" t="s">
-        <v>7825</v>
-      </c>
-    </row>
-    <row r="128" s="56" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="57" t="n">
+      <c r="B131" s="58" t="s">
+        <v>7833</v>
+      </c>
+      <c r="C131" s="58" t="s">
+        <v>7834</v>
+      </c>
+      <c r="D131" s="58" t="s">
+        <v>7835</v>
+      </c>
+      <c r="E131" s="58" t="s">
+        <v>7836</v>
+      </c>
+      <c r="F131" s="60" t="s">
+        <v>7837</v>
+      </c>
+      <c r="G131" s="58" t="s">
+        <v>7838</v>
+      </c>
+    </row>
+    <row r="132" s="58" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="59" t="n">
         <v>45005</v>
       </c>
-      <c r="B128" s="58" t="s">
-        <v>7826</v>
-      </c>
-      <c r="C128" s="56" t="s">
-        <v>7827</v>
-      </c>
-      <c r="D128" s="56" t="s">
-        <v>7828</v>
-      </c>
-      <c r="E128" s="56" t="s">
-        <v>7829</v>
-      </c>
-      <c r="F128" s="58" t="s">
-        <v>7830</v>
-      </c>
-      <c r="G128" s="56" t="s">
-        <v>7831</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="57" t="n">
+      <c r="B132" s="60" t="s">
+        <v>7839</v>
+      </c>
+      <c r="C132" s="58" t="s">
+        <v>7840</v>
+      </c>
+      <c r="D132" s="58" t="s">
+        <v>7841</v>
+      </c>
+      <c r="E132" s="58" t="s">
+        <v>7842</v>
+      </c>
+      <c r="F132" s="60" t="s">
+        <v>7843</v>
+      </c>
+      <c r="G132" s="58" t="s">
+        <v>7844</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="59" t="n">
         <v>45006</v>
       </c>
-      <c r="B129" s="56" t="s">
-        <v>7820</v>
-      </c>
-      <c r="C129" s="56" t="s">
-        <v>7832</v>
-      </c>
-      <c r="D129" s="56" t="s">
+      <c r="B133" s="58" t="s">
         <v>7833</v>
       </c>
-      <c r="E129" s="59" t="s">
-        <v>7834</v>
-      </c>
-      <c r="F129" s="58" t="s">
-        <v>7835</v>
-      </c>
-      <c r="G129" s="56" t="s">
-        <v>7836</v>
-      </c>
-      <c r="H129" s="56"/>
-      <c r="I129" s="56"/>
-      <c r="J129" s="56"/>
-      <c r="K129" s="56"/>
-      <c r="L129" s="56"/>
-      <c r="M129" s="56"/>
-      <c r="N129" s="56"/>
-      <c r="O129" s="56"/>
-      <c r="P129" s="56"/>
-      <c r="Q129" s="56"/>
-      <c r="R129" s="56"/>
-      <c r="S129" s="56"/>
-      <c r="T129" s="56"/>
-      <c r="U129" s="56"/>
-      <c r="V129" s="56"/>
-      <c r="W129" s="56"/>
-      <c r="X129" s="56"/>
-      <c r="Y129" s="56"/>
-      <c r="Z129" s="56"/>
-      <c r="AA129" s="56"/>
-      <c r="AB129" s="56"/>
-      <c r="AC129" s="56"/>
-      <c r="AD129" s="56"/>
-    </row>
-    <row r="130" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="57" t="n">
+      <c r="C133" s="58" t="s">
+        <v>7845</v>
+      </c>
+      <c r="D133" s="58" t="s">
+        <v>7846</v>
+      </c>
+      <c r="E133" s="61" t="s">
+        <v>7847</v>
+      </c>
+      <c r="F133" s="60" t="s">
+        <v>7848</v>
+      </c>
+      <c r="G133" s="58" t="s">
+        <v>7849</v>
+      </c>
+      <c r="H133" s="58"/>
+      <c r="I133" s="58"/>
+      <c r="J133" s="58"/>
+      <c r="K133" s="58"/>
+      <c r="L133" s="58"/>
+      <c r="M133" s="58"/>
+      <c r="N133" s="58"/>
+      <c r="O133" s="58"/>
+      <c r="P133" s="58"/>
+      <c r="Q133" s="58"/>
+      <c r="R133" s="58"/>
+      <c r="S133" s="58"/>
+      <c r="T133" s="58"/>
+      <c r="U133" s="58"/>
+      <c r="V133" s="58"/>
+      <c r="W133" s="58"/>
+      <c r="X133" s="58"/>
+      <c r="Y133" s="58"/>
+      <c r="Z133" s="58"/>
+      <c r="AA133" s="58"/>
+      <c r="AB133" s="58"/>
+      <c r="AC133" s="58"/>
+      <c r="AD133" s="58"/>
+    </row>
+    <row r="134" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="59" t="n">
         <v>45036</v>
       </c>
-      <c r="B130" s="56" t="s">
-        <v>7837</v>
-      </c>
-      <c r="C130" s="56"/>
-      <c r="D130" s="56" t="s">
-        <v>7838</v>
-      </c>
-      <c r="E130" s="56" t="s">
-        <v>7839</v>
-      </c>
-      <c r="F130" s="56" t="s">
-        <v>7840</v>
-      </c>
-      <c r="G130" s="56" t="s">
-        <v>7841</v>
-      </c>
-      <c r="H130" s="56"/>
-      <c r="I130" s="56"/>
-      <c r="J130" s="56"/>
-      <c r="K130" s="56"/>
-      <c r="L130" s="56"/>
-      <c r="M130" s="56"/>
-      <c r="N130" s="56"/>
-      <c r="O130" s="56"/>
-      <c r="P130" s="56"/>
-      <c r="Q130" s="56"/>
-      <c r="R130" s="56"/>
-      <c r="S130" s="56"/>
-      <c r="T130" s="56"/>
-      <c r="U130" s="56"/>
-      <c r="V130" s="56"/>
-      <c r="W130" s="56"/>
-      <c r="X130" s="56"/>
-      <c r="Y130" s="56"/>
-      <c r="Z130" s="56"/>
-      <c r="AA130" s="56"/>
-      <c r="AB130" s="56"/>
-      <c r="AC130" s="56"/>
-      <c r="AD130" s="56"/>
-    </row>
-    <row r="131" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="60" t="n">
+      <c r="B134" s="58" t="s">
+        <v>7850</v>
+      </c>
+      <c r="C134" s="58"/>
+      <c r="D134" s="58" t="s">
+        <v>7851</v>
+      </c>
+      <c r="E134" s="58" t="s">
+        <v>7852</v>
+      </c>
+      <c r="F134" s="58" t="s">
+        <v>7853</v>
+      </c>
+      <c r="G134" s="58" t="s">
+        <v>7854</v>
+      </c>
+      <c r="H134" s="58"/>
+      <c r="I134" s="58"/>
+      <c r="J134" s="58"/>
+      <c r="K134" s="58"/>
+      <c r="L134" s="58"/>
+      <c r="M134" s="58"/>
+      <c r="N134" s="58"/>
+      <c r="O134" s="58"/>
+      <c r="P134" s="58"/>
+      <c r="Q134" s="58"/>
+      <c r="R134" s="58"/>
+      <c r="S134" s="58"/>
+      <c r="T134" s="58"/>
+      <c r="U134" s="58"/>
+      <c r="V134" s="58"/>
+      <c r="W134" s="58"/>
+      <c r="X134" s="58"/>
+      <c r="Y134" s="58"/>
+      <c r="Z134" s="58"/>
+      <c r="AA134" s="58"/>
+      <c r="AB134" s="58"/>
+      <c r="AC134" s="58"/>
+      <c r="AD134" s="58"/>
+    </row>
+    <row r="135" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="62" t="n">
         <v>45088</v>
       </c>
-      <c r="B131" s="48" t="s">
-        <v>7820</v>
-      </c>
-      <c r="C131" s="48" t="s">
-        <v>7842</v>
-      </c>
-      <c r="D131" s="48" t="s">
-        <v>7843</v>
-      </c>
-      <c r="E131" s="61" t="s">
-        <v>7844</v>
-      </c>
-      <c r="F131" s="48" t="s">
+      <c r="B135" s="48" t="s">
+        <v>7833</v>
+      </c>
+      <c r="C135" s="48" t="s">
+        <v>7855</v>
+      </c>
+      <c r="D135" s="48" t="s">
+        <v>7856</v>
+      </c>
+      <c r="E135" s="63" t="s">
+        <v>7857</v>
+      </c>
+      <c r="F135" s="48" t="s">
         <v>7549</v>
       </c>
-      <c r="G131" s="48" t="s">
+      <c r="G135" s="48" t="s">
         <v>7550</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="60" t="n">
+    <row r="136" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="62" t="n">
         <v>45025</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>7780</v>
-      </c>
-      <c r="C132" s="28" t="s">
-        <v>7845</v>
-      </c>
-      <c r="D132" s="43" t="s">
-        <v>7846</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>7847</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>7848</v>
-      </c>
-    </row>
-    <row r="133" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="1"/>
-      <c r="F133" s="1"/>
-      <c r="G133" s="1"/>
-      <c r="H133" s="1"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="1"/>
-      <c r="K133" s="1"/>
-      <c r="L133" s="1"/>
-      <c r="M133" s="1"/>
-      <c r="N133" s="1"/>
-      <c r="O133" s="1"/>
-      <c r="P133" s="1"/>
-      <c r="Q133" s="1"/>
-      <c r="R133" s="1"/>
-      <c r="S133" s="1"/>
-      <c r="T133" s="1"/>
-      <c r="U133" s="1"/>
-      <c r="V133" s="1"/>
-      <c r="W133" s="1"/>
-      <c r="X133" s="1"/>
-      <c r="Y133" s="1"/>
-      <c r="Z133" s="1"/>
-      <c r="AA133" s="1"/>
-      <c r="AB133" s="1"/>
-      <c r="AC133" s="1"/>
-      <c r="AD133" s="1"/>
-    </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="s">
-        <v>7849</v>
-      </c>
-      <c r="G134" s="1"/>
-      <c r="H134" s="1"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
-      <c r="K134" s="1"/>
-      <c r="L134" s="1"/>
-      <c r="M134" s="1"/>
-      <c r="N134" s="1"/>
-      <c r="O134" s="1"/>
-      <c r="P134" s="1"/>
-      <c r="Q134" s="1"/>
-      <c r="R134" s="1"/>
-      <c r="S134" s="1"/>
-      <c r="T134" s="1"/>
-      <c r="U134" s="1"/>
-      <c r="V134" s="1"/>
-      <c r="W134" s="1"/>
-      <c r="X134" s="1"/>
-      <c r="Y134" s="1"/>
-      <c r="Z134" s="1"/>
-      <c r="AA134" s="1"/>
-      <c r="AB134" s="1"/>
-      <c r="AC134" s="1"/>
-      <c r="AD134" s="1"/>
-    </row>
-    <row r="135" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="62" t="n">
+      <c r="B136" s="1" t="s">
+        <v>7793</v>
+      </c>
+      <c r="C136" s="28" t="s">
+        <v>7858</v>
+      </c>
+      <c r="D136" s="43" t="s">
+        <v>7859</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>7860</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>7861</v>
+      </c>
+    </row>
+    <row r="137" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+      <c r="G137" s="1"/>
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
+      <c r="K137" s="1"/>
+      <c r="L137" s="1"/>
+      <c r="M137" s="1"/>
+      <c r="N137" s="1"/>
+      <c r="O137" s="1"/>
+      <c r="P137" s="1"/>
+      <c r="Q137" s="1"/>
+      <c r="R137" s="1"/>
+      <c r="S137" s="1"/>
+      <c r="T137" s="1"/>
+      <c r="U137" s="1"/>
+      <c r="V137" s="1"/>
+      <c r="W137" s="1"/>
+      <c r="X137" s="1"/>
+      <c r="Y137" s="1"/>
+      <c r="Z137" s="1"/>
+      <c r="AA137" s="1"/>
+      <c r="AB137" s="1"/>
+      <c r="AC137" s="1"/>
+      <c r="AD137" s="1"/>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="s">
+        <v>7862</v>
+      </c>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
+      <c r="K138" s="1"/>
+      <c r="L138" s="1"/>
+      <c r="M138" s="1"/>
+      <c r="N138" s="1"/>
+      <c r="O138" s="1"/>
+      <c r="P138" s="1"/>
+      <c r="Q138" s="1"/>
+      <c r="R138" s="1"/>
+      <c r="S138" s="1"/>
+      <c r="T138" s="1"/>
+      <c r="U138" s="1"/>
+      <c r="V138" s="1"/>
+      <c r="W138" s="1"/>
+      <c r="X138" s="1"/>
+      <c r="Y138" s="1"/>
+      <c r="Z138" s="1"/>
+      <c r="AA138" s="1"/>
+      <c r="AB138" s="1"/>
+      <c r="AC138" s="1"/>
+      <c r="AD138" s="1"/>
+    </row>
+    <row r="139" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="64" t="n">
         <v>39252</v>
       </c>
-      <c r="B135" s="41"/>
-      <c r="C135" s="41" t="s">
-        <v>7850</v>
-      </c>
-      <c r="D135" s="63" t="s">
-        <v>7851</v>
-      </c>
-      <c r="E135" s="41" t="s">
-        <v>7852</v>
-      </c>
-      <c r="F135" s="41" t="s">
-        <v>7853</v>
-      </c>
-      <c r="G135" s="41" t="s">
-        <v>7854</v>
-      </c>
-      <c r="H135" s="41"/>
-      <c r="I135" s="41"/>
-      <c r="J135" s="41"/>
-      <c r="K135" s="41"/>
-      <c r="L135" s="41"/>
-      <c r="M135" s="41"/>
-      <c r="N135" s="41"/>
-      <c r="O135" s="41"/>
-      <c r="P135" s="41"/>
-      <c r="Q135" s="41"/>
-      <c r="R135" s="41"/>
-      <c r="S135" s="41"/>
-      <c r="T135" s="41"/>
-      <c r="U135" s="41"/>
-      <c r="V135" s="41"/>
-      <c r="W135" s="41"/>
-      <c r="X135" s="41"/>
-      <c r="Y135" s="41"/>
-      <c r="Z135" s="41"/>
-      <c r="AA135" s="41"/>
-      <c r="AB135" s="41"/>
-      <c r="AC135" s="41"/>
-      <c r="AD135" s="41"/>
-    </row>
-    <row r="136" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="47" t="n">
+      <c r="B139" s="41"/>
+      <c r="C139" s="41" t="s">
+        <v>7863</v>
+      </c>
+      <c r="D139" s="65" t="s">
+        <v>7864</v>
+      </c>
+      <c r="E139" s="41" t="s">
+        <v>7865</v>
+      </c>
+      <c r="F139" s="41" t="s">
+        <v>7866</v>
+      </c>
+      <c r="G139" s="41" t="s">
+        <v>7867</v>
+      </c>
+      <c r="H139" s="41"/>
+      <c r="I139" s="41"/>
+      <c r="J139" s="41"/>
+      <c r="K139" s="41"/>
+      <c r="L139" s="41"/>
+      <c r="M139" s="41"/>
+      <c r="N139" s="41"/>
+      <c r="O139" s="41"/>
+      <c r="P139" s="41"/>
+      <c r="Q139" s="41"/>
+      <c r="R139" s="41"/>
+      <c r="S139" s="41"/>
+      <c r="T139" s="41"/>
+      <c r="U139" s="41"/>
+      <c r="V139" s="41"/>
+      <c r="W139" s="41"/>
+      <c r="X139" s="41"/>
+      <c r="Y139" s="41"/>
+      <c r="Z139" s="41"/>
+      <c r="AA139" s="41"/>
+      <c r="AB139" s="41"/>
+      <c r="AC139" s="41"/>
+      <c r="AD139" s="41"/>
+    </row>
+    <row r="140" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="47" t="n">
         <v>46241</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>7855</v>
-      </c>
-      <c r="C136" s="28" t="s">
-        <v>7856</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>7857</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>7858</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="47" t="s">
-        <v>7859</v>
-      </c>
-      <c r="B137" s="28" t="s">
-        <v>7860</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>7861</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>7862</v>
-      </c>
-      <c r="F137" s="28" t="s">
-        <v>7863</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>7864</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="55" t="n">
+      <c r="B140" s="1" t="s">
+        <v>7868</v>
+      </c>
+      <c r="C140" s="28" t="s">
+        <v>7869</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>7870</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>7871</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="47" t="s">
+        <v>7872</v>
+      </c>
+      <c r="B141" s="28" t="s">
+        <v>7873</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>7874</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>7875</v>
+      </c>
+      <c r="F141" s="28" t="s">
+        <v>7876</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>7877</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="57" t="n">
         <v>42866</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>7865</v>
-      </c>
-      <c r="C138" s="28" t="s">
-        <v>7866</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>7867</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>7868</v>
-      </c>
-      <c r="F138" s="28" t="s">
-        <v>7869</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>7870</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="141" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="2" t="s">
+      <c r="B142" s="1" t="s">
+        <v>7878</v>
+      </c>
+      <c r="C142" s="28" t="s">
+        <v>7879</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>7880</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>7881</v>
+      </c>
+      <c r="F142" s="28" t="s">
+        <v>7882</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>7883</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="145" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="2" t="s">
         <v>7497</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>7871</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1" t="s">
-        <v>7872</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="62" t="s">
-        <v>7873</v>
-      </c>
-      <c r="B145" s="41" t="s">
-        <v>7874</v>
-      </c>
-      <c r="C145" s="41" t="s">
-        <v>7875</v>
-      </c>
-      <c r="D145" s="41"/>
-      <c r="E145" s="41" t="s">
-        <v>7876</v>
-      </c>
-      <c r="F145" s="41" t="s">
-        <v>7877</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>7878</v>
-      </c>
-    </row>
-    <row r="146" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
-        <v>7879</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>7880</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>7881</v>
-      </c>
-      <c r="D146" s="1" t="s">
+      <c r="B145" s="1" t="s">
+        <v>7884</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
+        <v>7885</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="64" t="s">
+        <v>7886</v>
+      </c>
+      <c r="B149" s="41" t="s">
+        <v>7887</v>
+      </c>
+      <c r="C149" s="41" t="s">
+        <v>7888</v>
+      </c>
+      <c r="D149" s="41"/>
+      <c r="E149" s="41" t="s">
+        <v>7889</v>
+      </c>
+      <c r="F149" s="41" t="s">
+        <v>7890</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>7891</v>
+      </c>
+    </row>
+    <row r="150" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>7892</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>7893</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>7894</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>7895</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>7896</v>
+      </c>
+      <c r="F150" s="48" t="s">
+        <v>7897</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>7898</v>
+      </c>
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+      <c r="J150" s="1"/>
+      <c r="K150" s="1"/>
+      <c r="L150" s="1"/>
+      <c r="M150" s="1"/>
+      <c r="N150" s="1"/>
+      <c r="O150" s="1"/>
+      <c r="P150" s="1"/>
+      <c r="Q150" s="1"/>
+      <c r="R150" s="1"/>
+      <c r="S150" s="1"/>
+      <c r="T150" s="1"/>
+      <c r="U150" s="1"/>
+      <c r="V150" s="1"/>
+      <c r="W150" s="1"/>
+      <c r="X150" s="1"/>
+      <c r="Y150" s="1"/>
+      <c r="Z150" s="1"/>
+      <c r="AA150" s="1"/>
+      <c r="AB150" s="1"/>
+      <c r="AC150" s="1"/>
+      <c r="AD150" s="1"/>
+    </row>
+    <row r="151" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="64" t="s">
+        <v>7899</v>
+      </c>
+      <c r="B151" s="41" t="s">
+        <v>7900</v>
+      </c>
+      <c r="C151" s="41" t="s">
+        <v>7901</v>
+      </c>
+      <c r="D151" s="65" t="s">
+        <v>7902</v>
+      </c>
+      <c r="E151" s="41" t="s">
+        <v>7903</v>
+      </c>
+      <c r="F151" s="41" t="s">
+        <v>7890</v>
+      </c>
+      <c r="G151" s="41" t="s">
+        <v>7904</v>
+      </c>
+    </row>
+    <row r="152" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="66" t="n">
+        <v>42355</v>
+      </c>
+      <c r="B152" s="41" t="s">
+        <v>7905</v>
+      </c>
+      <c r="C152" s="41" t="s">
+        <v>7906</v>
+      </c>
+      <c r="D152" s="41" t="s">
+        <v>7907</v>
+      </c>
+      <c r="E152" s="41" t="s">
+        <v>7908</v>
+      </c>
+      <c r="F152" s="41" t="s">
+        <v>7909</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="64" t="n">
+        <v>43658</v>
+      </c>
+      <c r="B153" s="41" t="s">
+        <v>7910</v>
+      </c>
+      <c r="C153" s="41" t="s">
+        <v>7911</v>
+      </c>
+      <c r="D153" s="65" t="s">
+        <v>7912</v>
+      </c>
+      <c r="E153" s="41" t="s">
+        <v>7913</v>
+      </c>
+      <c r="F153" s="41" t="s">
+        <v>7910</v>
+      </c>
+      <c r="G153" s="41" t="s">
+        <v>7914</v>
+      </c>
+      <c r="H153" s="41"/>
+      <c r="I153" s="41"/>
+      <c r="J153" s="41"/>
+      <c r="K153" s="41"/>
+      <c r="L153" s="41"/>
+      <c r="M153" s="41"/>
+      <c r="N153" s="41"/>
+      <c r="O153" s="41"/>
+      <c r="P153" s="41"/>
+      <c r="Q153" s="41"/>
+      <c r="R153" s="41"/>
+      <c r="S153" s="41"/>
+      <c r="T153" s="41"/>
+      <c r="U153" s="41"/>
+      <c r="V153" s="41"/>
+      <c r="W153" s="41"/>
+      <c r="X153" s="41"/>
+      <c r="Y153" s="41"/>
+      <c r="Z153" s="41"/>
+      <c r="AA153" s="41"/>
+      <c r="AB153" s="41"/>
+      <c r="AC153" s="41"/>
+      <c r="AD153" s="41" t="s">
+        <v>7915</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="64" t="n">
+        <v>45581</v>
+      </c>
+      <c r="B154" s="41" t="s">
+        <v>7916</v>
+      </c>
+      <c r="C154" s="41" t="s">
+        <v>7917</v>
+      </c>
+      <c r="D154" s="41" t="s">
+        <v>7918</v>
+      </c>
+      <c r="E154" s="65" t="s">
+        <v>7919</v>
+      </c>
+      <c r="F154" s="41" t="s">
+        <v>7916</v>
+      </c>
+      <c r="G154" s="67" t="s">
+        <v>7920</v>
+      </c>
+      <c r="H154" s="41"/>
+      <c r="I154" s="41"/>
+      <c r="J154" s="41"/>
+      <c r="K154" s="41"/>
+      <c r="L154" s="41"/>
+      <c r="M154" s="41"/>
+      <c r="N154" s="41"/>
+      <c r="O154" s="41"/>
+      <c r="P154" s="41"/>
+      <c r="Q154" s="41"/>
+      <c r="R154" s="41"/>
+      <c r="S154" s="41"/>
+      <c r="T154" s="41"/>
+      <c r="U154" s="41"/>
+      <c r="V154" s="41"/>
+      <c r="W154" s="41"/>
+      <c r="X154" s="41"/>
+      <c r="Y154" s="41"/>
+      <c r="Z154" s="41"/>
+      <c r="AA154" s="41"/>
+      <c r="AB154" s="41"/>
+      <c r="AC154" s="41"/>
+      <c r="AD154" s="41"/>
+    </row>
+    <row r="155" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="66" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>7921</v>
+      </c>
+      <c r="C155" s="28" t="s">
+        <v>7922</v>
+      </c>
+      <c r="D155" s="28" t="s">
+        <v>7923</v>
+      </c>
+      <c r="E155" s="49" t="s">
+        <v>7924</v>
+      </c>
+      <c r="F155" s="28" t="s">
+        <v>7625</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>7626</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="s">
+        <v>7925</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="65" t="s">
+        <v>7926</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>7927</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>7928</v>
+      </c>
+      <c r="F158" s="1" t="s">
         <v>7882</v>
       </c>
-      <c r="E146" s="1" t="s">
-        <v>7883</v>
-      </c>
-      <c r="F146" s="48" t="s">
-        <v>7884</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>7885</v>
-      </c>
-      <c r="H146" s="1"/>
-      <c r="I146" s="1"/>
-      <c r="J146" s="1"/>
-      <c r="K146" s="1"/>
-      <c r="L146" s="1"/>
-      <c r="M146" s="1"/>
-      <c r="N146" s="1"/>
-      <c r="O146" s="1"/>
-      <c r="P146" s="1"/>
-      <c r="Q146" s="1"/>
-      <c r="R146" s="1"/>
-      <c r="S146" s="1"/>
-      <c r="T146" s="1"/>
-      <c r="U146" s="1"/>
-      <c r="V146" s="1"/>
-      <c r="W146" s="1"/>
-      <c r="X146" s="1"/>
-      <c r="Y146" s="1"/>
-      <c r="Z146" s="1"/>
-      <c r="AA146" s="1"/>
-      <c r="AB146" s="1"/>
-      <c r="AC146" s="1"/>
-      <c r="AD146" s="1"/>
-    </row>
-    <row r="147" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="62" t="s">
-        <v>7886</v>
-      </c>
-      <c r="B147" s="41" t="s">
-        <v>7887</v>
-      </c>
-      <c r="C147" s="41" t="s">
-        <v>7888</v>
-      </c>
-      <c r="D147" s="63" t="s">
-        <v>7889</v>
-      </c>
-      <c r="E147" s="41" t="s">
-        <v>7890</v>
-      </c>
-      <c r="F147" s="41" t="s">
-        <v>7877</v>
-      </c>
-      <c r="G147" s="41" t="s">
-        <v>7891</v>
-      </c>
-    </row>
-    <row r="148" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="64" t="n">
-        <v>42355</v>
-      </c>
-      <c r="B148" s="41" t="s">
-        <v>7892</v>
-      </c>
-      <c r="C148" s="41" t="s">
-        <v>7893</v>
-      </c>
-      <c r="D148" s="41" t="s">
-        <v>7894</v>
-      </c>
-      <c r="E148" s="41" t="s">
-        <v>7895</v>
-      </c>
-      <c r="F148" s="41" t="s">
-        <v>7896</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="62" t="n">
-        <v>43658</v>
-      </c>
-      <c r="B149" s="41" t="s">
-        <v>7897</v>
-      </c>
-      <c r="C149" s="41" t="s">
-        <v>7898</v>
-      </c>
-      <c r="D149" s="63" t="s">
-        <v>7899</v>
-      </c>
-      <c r="E149" s="41" t="s">
-        <v>7900</v>
-      </c>
-      <c r="F149" s="41" t="s">
-        <v>7897</v>
-      </c>
-      <c r="G149" s="41" t="s">
-        <v>7901</v>
-      </c>
-      <c r="H149" s="41"/>
-      <c r="I149" s="41"/>
-      <c r="J149" s="41"/>
-      <c r="K149" s="41"/>
-      <c r="L149" s="41"/>
-      <c r="M149" s="41"/>
-      <c r="N149" s="41"/>
-      <c r="O149" s="41"/>
-      <c r="P149" s="41"/>
-      <c r="Q149" s="41"/>
-      <c r="R149" s="41"/>
-      <c r="S149" s="41"/>
-      <c r="T149" s="41"/>
-      <c r="U149" s="41"/>
-      <c r="V149" s="41"/>
-      <c r="W149" s="41"/>
-      <c r="X149" s="41"/>
-      <c r="Y149" s="41"/>
-      <c r="Z149" s="41"/>
-      <c r="AA149" s="41"/>
-      <c r="AB149" s="41"/>
-      <c r="AC149" s="41"/>
-      <c r="AD149" s="41" t="s">
-        <v>7902</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="62" t="n">
-        <v>45581</v>
-      </c>
-      <c r="B150" s="41" t="s">
-        <v>7903</v>
-      </c>
-      <c r="C150" s="41" t="s">
-        <v>7904</v>
-      </c>
-      <c r="D150" s="41" t="s">
-        <v>7905</v>
-      </c>
-      <c r="E150" s="63" t="s">
-        <v>7906</v>
-      </c>
-      <c r="F150" s="41" t="s">
-        <v>7903</v>
-      </c>
-      <c r="G150" s="65" t="s">
-        <v>7907</v>
-      </c>
-      <c r="H150" s="41"/>
-      <c r="I150" s="41"/>
-      <c r="J150" s="41"/>
-      <c r="K150" s="41"/>
-      <c r="L150" s="41"/>
-      <c r="M150" s="41"/>
-      <c r="N150" s="41"/>
-      <c r="O150" s="41"/>
-      <c r="P150" s="41"/>
-      <c r="Q150" s="41"/>
-      <c r="R150" s="41"/>
-      <c r="S150" s="41"/>
-      <c r="T150" s="41"/>
-      <c r="U150" s="41"/>
-      <c r="V150" s="41"/>
-      <c r="W150" s="41"/>
-      <c r="X150" s="41"/>
-      <c r="Y150" s="41"/>
-      <c r="Z150" s="41"/>
-      <c r="AA150" s="41"/>
-      <c r="AB150" s="41"/>
-      <c r="AC150" s="41"/>
-      <c r="AD150" s="41"/>
-    </row>
-    <row r="151" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="64" t="n">
-        <v>45668</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>7908</v>
-      </c>
-      <c r="C151" s="28" t="s">
-        <v>7909</v>
-      </c>
-      <c r="D151" s="28" t="s">
-        <v>7910</v>
-      </c>
-      <c r="E151" s="49" t="s">
-        <v>7911</v>
-      </c>
-      <c r="F151" s="28" t="s">
-        <v>7625</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>7626</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
-        <v>7912</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="63" t="s">
-        <v>7913</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>7914</v>
-      </c>
-      <c r="C154" s="1" t="s">
+      <c r="G158" s="2" t="s">
+        <v>7929</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="64" t="s">
+        <v>7930</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>7931</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>7882</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>7932</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="65" t="s">
+        <v>7926</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>7933</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>7934</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>7882</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>7935</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="28" t="s">
+        <v>7936</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>7937</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>7938</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>7939</v>
+      </c>
+      <c r="G161" s="2" t="s">
         <v>7915</v>
       </c>
-      <c r="F154" s="1" t="s">
-        <v>7869</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>7916</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="62" t="s">
-        <v>7917</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>7918</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>7869</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>7919</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="63" t="s">
-        <v>7913</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>7920</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>7921</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>7869</v>
-      </c>
-      <c r="G156" s="2" t="s">
-        <v>7922</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="28" t="s">
-        <v>7923</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>7924</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>7925</v>
-      </c>
-      <c r="F157" s="1" t="s">
+    </row>
+    <row r="162" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
+        <v>7940</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>7941</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>7942</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>7939</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>7943</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="43" t="s">
+        <v>7944</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>7945</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>7946</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>7947</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>7948</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="45" t="s">
+        <v>7949</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>7950</v>
+      </c>
+      <c r="C164" s="49" t="s">
+        <v>7951</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>7952</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1" t="s">
+        <v>7940</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>7953</v>
+      </c>
+      <c r="C165" s="41" t="s">
+        <v>7954</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>7955</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>7939</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>7943</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="28" t="s">
+        <v>7956</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>7957</v>
+      </c>
+      <c r="C166" s="41" t="s">
+        <v>7958</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>7959</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>7939</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>7960</v>
+      </c>
+      <c r="H166" s="1"/>
+    </row>
+    <row r="167" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="65" t="s">
         <v>7926</v>
       </c>
-      <c r="G157" s="2" t="s">
-        <v>7902</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="s">
-        <v>7927</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>7928</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>7929</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>7926</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>7930</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="43" t="s">
-        <v>7931</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>7932</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>7933</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>7934</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>7935</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="45" t="s">
-        <v>7936</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>7937</v>
-      </c>
-      <c r="C160" s="49" t="s">
-        <v>7938</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>7939</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1" t="s">
-        <v>7927</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>7940</v>
-      </c>
-      <c r="C161" s="41" t="s">
-        <v>7941</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>7942</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>7926</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>7930</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="28" t="s">
-        <v>7943</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>7944</v>
-      </c>
-      <c r="C162" s="41" t="s">
-        <v>7945</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>7946</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>7926</v>
-      </c>
-      <c r="G162" s="2" t="s">
-        <v>7947</v>
-      </c>
-      <c r="H162" s="1"/>
-    </row>
-    <row r="163" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="63" t="s">
-        <v>7913</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>7948</v>
-      </c>
-      <c r="D163" s="28" t="s">
-        <v>7949</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>7950</v>
-      </c>
-      <c r="F163" s="43" t="s">
-        <v>7951</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>7952</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="66" t="s">
-        <v>7953</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>7954</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="0" t="s">
-        <v>7955</v>
-      </c>
-      <c r="B166" s="67" t="s">
-        <v>7956</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>7957</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="43" t="s">
-        <v>7958</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="1" t="s">
-        <v>7959</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>7742</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>7869</v>
-      </c>
-      <c r="G170" s="2" t="s">
-        <v>7960</v>
+      <c r="B167" s="1" t="s">
+        <v>7961</v>
+      </c>
+      <c r="D167" s="28" t="s">
+        <v>7962</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>7963</v>
+      </c>
+      <c r="F167" s="43" t="s">
+        <v>7964</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>7965</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="68" t="s">
+        <v>7966</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>7967</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="0" t="s">
+        <v>7968</v>
+      </c>
+      <c r="B170" s="50" t="s">
+        <v>7969</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>7970</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="1" t="s">
-        <v>7961</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>7962</v>
+      <c r="A173" s="43" t="s">
+        <v>7971</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>7963</v>
+        <v>7972</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>7964</v>
-      </c>
-    </row>
-    <row r="175" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="1" t="s">
-        <v>7965</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>7966</v>
+        <v>7755</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>7882</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>7973</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="1" t="s">
+        <v>7974</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>7975</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="1" t="s">
+        <v>7976</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>7977</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="43" t="s">
-        <v>7967</v>
+      <c r="A179" s="1" t="s">
+        <v>7978</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>7979</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="43" t="s">
+        <v>7980</v>
       </c>
     </row>
   </sheetData>
@@ -85108,68 +85352,69 @@
     <hyperlink ref="G73" r:id="rId33" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
     <hyperlink ref="G74" r:id="rId34" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
     <hyperlink ref="G75" r:id="rId35" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G76" r:id="rId36" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
-    <hyperlink ref="G77" r:id="rId37" display="https://www.dpm.org.cn/ancient"/>
-    <hyperlink ref="G78" r:id="rId38" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G79" r:id="rId39" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
-    <hyperlink ref="G80" r:id="rId40" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
-    <hyperlink ref="G81" r:id="rId41" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
-    <hyperlink ref="G82" r:id="rId42" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G83" r:id="rId43" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G84" r:id="rId44" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G85" r:id="rId45" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G86" r:id="rId46" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G87" r:id="rId47" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G88" r:id="rId48" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G89" r:id="rId49" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G90" r:id="rId50" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G93" r:id="rId51" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
-    <hyperlink ref="G95" r:id="rId52" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G96" r:id="rId53" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G97" r:id="rId54" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G98" r:id="rId55" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G101" r:id="rId56" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G102" r:id="rId57" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G105" r:id="rId58" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G106" r:id="rId59" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
-    <hyperlink ref="G107" r:id="rId60" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
-    <hyperlink ref="G109" r:id="rId61" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
-    <hyperlink ref="G115" r:id="rId62" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G116" r:id="rId63" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G117" r:id="rId64" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G118" r:id="rId65" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G119" r:id="rId66" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G120" r:id="rId67" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G122" r:id="rId68" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G123" r:id="rId69" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
-    <hyperlink ref="G127" r:id="rId70" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
-    <hyperlink ref="F129" r:id="rId71" display="中新网北京3月21日电 (记者 应妮) "/>
-    <hyperlink ref="G129" r:id="rId72" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
-    <hyperlink ref="G131" r:id="rId73" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G135" r:id="rId74" display="https://discovery.cctv.com/20070619/107154.shtml"/>
-    <hyperlink ref="G138" r:id="rId75" display="https://book.kongfz.com/102740/682706591"/>
-    <hyperlink ref="A141" r:id="rId76" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G145" r:id="rId77" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
-    <hyperlink ref="G146" r:id="rId78" display="https://book.kongfz.com/20791/3754198261"/>
-    <hyperlink ref="G149" r:id="rId79" display="https://www.ljstsg.cn/?p=6315"/>
-    <hyperlink ref="AD149" r:id="rId80" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="G150" r:id="rId81" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
-    <hyperlink ref="G151" r:id="rId82" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="B154" r:id="rId83" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
-    <hyperlink ref="G154" r:id="rId84" display="https://book.kongfz.com/536651/7839562954"/>
-    <hyperlink ref="B155" r:id="rId85" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
-    <hyperlink ref="G155" r:id="rId86" display="https://book.kongfz.com/23231/8186709240"/>
-    <hyperlink ref="B156" r:id="rId87" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
-    <hyperlink ref="G156" r:id="rId88" display="https://book.kongfz.com/536651/7839554296"/>
-    <hyperlink ref="G157" r:id="rId89" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="B158" r:id="rId90" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
-    <hyperlink ref="G159" r:id="rId91" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
-    <hyperlink ref="G160" r:id="rId92" display="https://book.kongfz.com/200249/1819262449/"/>
-    <hyperlink ref="G161" r:id="rId93" display="https://product.dangdang.com/11721366316.html"/>
-    <hyperlink ref="B162" r:id="rId94" display="出版社:宗教文化出版社 "/>
-    <hyperlink ref="G162" r:id="rId95" display="https://product.dangdang.com/22497432.html"/>
-    <hyperlink ref="G163" r:id="rId96" display="http://aiguji.net/3299.html"/>
-    <hyperlink ref="G170" r:id="rId97" display="https://book.kongfz.com/467603/10356350239"/>
+    <hyperlink ref="G78" r:id="rId36" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
+    <hyperlink ref="G79" r:id="rId37" display="https://www.dpm.org.cn/ancient"/>
+    <hyperlink ref="G80" r:id="rId38" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G82" r:id="rId39" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
+    <hyperlink ref="G83" r:id="rId40" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
+    <hyperlink ref="G84" r:id="rId41" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
+    <hyperlink ref="G85" r:id="rId42" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G86" r:id="rId43" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G87" r:id="rId44" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G88" r:id="rId45" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G89" r:id="rId46" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G90" r:id="rId47" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G91" r:id="rId48" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G92" r:id="rId49" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G93" r:id="rId50" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G94" r:id="rId51" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G97" r:id="rId52" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
+    <hyperlink ref="G99" r:id="rId53" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G100" r:id="rId54" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G101" r:id="rId55" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G102" r:id="rId56" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G105" r:id="rId57" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G106" r:id="rId58" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G109" r:id="rId59" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G110" r:id="rId60" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
+    <hyperlink ref="G111" r:id="rId61" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
+    <hyperlink ref="G113" r:id="rId62" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
+    <hyperlink ref="G119" r:id="rId63" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G120" r:id="rId64" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G121" r:id="rId65" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G122" r:id="rId66" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G123" r:id="rId67" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G124" r:id="rId68" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G126" r:id="rId69" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G127" r:id="rId70" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
+    <hyperlink ref="G131" r:id="rId71" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
+    <hyperlink ref="F133" r:id="rId72" display="中新网北京3月21日电 (记者 应妮) "/>
+    <hyperlink ref="G133" r:id="rId73" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
+    <hyperlink ref="G135" r:id="rId74" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G139" r:id="rId75" display="https://discovery.cctv.com/20070619/107154.shtml"/>
+    <hyperlink ref="G142" r:id="rId76" display="https://book.kongfz.com/102740/682706591"/>
+    <hyperlink ref="A145" r:id="rId77" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G149" r:id="rId78" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
+    <hyperlink ref="G150" r:id="rId79" display="https://book.kongfz.com/20791/3754198261"/>
+    <hyperlink ref="G153" r:id="rId80" display="https://www.ljstsg.cn/?p=6315"/>
+    <hyperlink ref="AD153" r:id="rId81" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="G154" r:id="rId82" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
+    <hyperlink ref="G155" r:id="rId83" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="B158" r:id="rId84" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
+    <hyperlink ref="G158" r:id="rId85" display="https://book.kongfz.com/536651/7839562954"/>
+    <hyperlink ref="B159" r:id="rId86" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
+    <hyperlink ref="G159" r:id="rId87" display="https://book.kongfz.com/23231/8186709240"/>
+    <hyperlink ref="B160" r:id="rId88" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
+    <hyperlink ref="G160" r:id="rId89" display="https://book.kongfz.com/536651/7839554296"/>
+    <hyperlink ref="G161" r:id="rId90" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="B162" r:id="rId91" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
+    <hyperlink ref="G163" r:id="rId92" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
+    <hyperlink ref="G164" r:id="rId93" display="https://book.kongfz.com/200249/1819262449/"/>
+    <hyperlink ref="G165" r:id="rId94" display="https://product.dangdang.com/11721366316.html"/>
+    <hyperlink ref="B166" r:id="rId95" display="出版社:宗教文化出版社 "/>
+    <hyperlink ref="G166" r:id="rId96" display="https://product.dangdang.com/22497432.html"/>
+    <hyperlink ref="G167" r:id="rId97" display="http://aiguji.net/3299.html"/>
+    <hyperlink ref="G174" r:id="rId98" display="https://book.kongfz.com/467603/10356350239"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -85189,120 +85434,120 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="68" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="69" width="12.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7968</v>
+        <v>7981</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="69" t="n">
+      <c r="A2" s="70" t="n">
         <v>1539</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7969</v>
+        <v>7982</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="69" t="n">
+      <c r="A3" s="70" t="n">
         <v>1615</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7970</v>
+        <v>7983</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="69" t="n">
+      <c r="A4" s="70" t="n">
         <v>1620</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7971</v>
+        <v>7984</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="69" t="n">
+      <c r="A5" s="70" t="n">
         <v>1623</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7972</v>
+        <v>7985</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="69" t="n">
+      <c r="A6" s="70" t="n">
         <v>1653</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7973</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>7974</v>
+        <v>7987</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7975</v>
+        <v>7988</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>7976</v>
+        <v>7989</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7977</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>7978</v>
+        <v>7991</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7979</v>
+        <v>7992</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>7980</v>
+        <v>7993</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>7981</v>
+        <v>7994</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>7982</v>
+        <v>7995</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7983</v>
+        <v>7996</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>7984</v>
+        <v>7997</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7985</v>
+        <v>7998</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85317,45 +85562,45 @@
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>7837</v>
+        <v>7850</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>7986</v>
+        <v>7999</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>7987</v>
+        <v>8000</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>7988</v>
+        <v>8001</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>7989</v>
+        <v>8002</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>7990</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>7991</v>
+        <v>8004</v>
       </c>
       <c r="E23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>7992</v>
+        <v>8005</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>7993</v>
+        <v>8006</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
-        <v>7663</v>
+        <v>7667</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>7994</v>
+        <v>8007</v>
       </c>
     </row>
   </sheetData>
@@ -85387,84 +85632,84 @@
   </cols>
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="70" t="s">
-        <v>7995</v>
+      <c r="A8" s="71" t="s">
+        <v>8008</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="70" t="s">
-        <v>7996</v>
+      <c r="A9" s="71" t="s">
+        <v>8009</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="70" t="s">
-        <v>7997</v>
+      <c r="A10" s="71" t="s">
+        <v>8010</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="70" t="s">
-        <v>7998</v>
-      </c>
-      <c r="B12" s="71" t="n">
+      <c r="A12" s="71" t="s">
+        <v>8011</v>
+      </c>
+      <c r="B12" s="72" t="n">
         <v>45735</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7999</v>
+        <v>8012</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8000</v>
+        <v>8013</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="70" t="s">
-        <v>8001</v>
-      </c>
-      <c r="B13" s="71" t="n">
+      <c r="A13" s="71" t="s">
+        <v>8014</v>
+      </c>
+      <c r="B13" s="72" t="n">
         <v>45970</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8002</v>
+        <v>8015</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8003</v>
+        <v>8016</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="70" t="s">
-        <v>8004</v>
-      </c>
-      <c r="B14" s="71" t="n">
+      <c r="A14" s="71" t="s">
+        <v>8017</v>
+      </c>
+      <c r="B14" s="72" t="n">
         <v>45995</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8005</v>
+        <v>8018</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8006</v>
+        <v>8019</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="70" t="s">
-        <v>8007</v>
-      </c>
-      <c r="B15" s="71" t="n">
+      <c r="A15" s="71" t="s">
+        <v>8020</v>
+      </c>
+      <c r="B15" s="72" t="n">
         <v>46036</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8008</v>
+        <v>8021</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8009</v>
+        <v>8022</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>8010</v>
+        <v>8023</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>8011</v>
+        <v>8024</v>
       </c>
     </row>
   </sheetData>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10871" uniqueCount="8025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10894" uniqueCount="8041">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -24736,6 +24736,21 @@
     <t xml:space="preserve">拨归北平古物陈列所管理 </t>
   </si>
   <si>
+    <t xml:space="preserve">1932年</t>
+  </si>
+  <si>
+    <t xml:space="preserve">《龙藏》的第二次大规模刷印是1932年，南京中山陵筹建藏经楼，发起请印《龙藏》。全国各名山大刹亦随之陆续请印了22部。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">云居寺展出《龙藏》木经版 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">凤凰佛教</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fo.ifeng.com/news/200801/0116_14_48272.shtml</t>
+  </si>
+  <si>
     <t xml:space="preserve">1935年</t>
   </si>
   <si>
@@ -24912,6 +24927,29 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">年 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">《龙藏》经版运抵位于大兴的古籍印刷厂</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1987</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年，《龙藏》经版运抵位于大兴的古籍印刷厂，按照传统方式印制佛经。市文物局和房山区政府商定，经版刷印后不再运回智化寺，移至云居寺存放。 </t>
     </r>
   </si>
   <si>
@@ -27588,7 +27626,43 @@
     <t xml:space="preserve">https://book.kongfz.com/102740/682706591</t>
   </si>
   <si>
-    <t xml:space="preserve">煌煌《龙藏》——《乾隆版大藏经》的前世和新生  </t>
+    <t xml:space="preserve">民族文化宫图书馆 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">尊婆须蜜菩萨所集论十五卷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 的图片，可惜明显不一样，不知道哪个是正版。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">道中华丨追寻《龙藏》的前世今生 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">现在民族文化宫图书馆珍藏有《龙藏》两部，一部为经折装的《龙藏》，另一部就是本文重点关注的、珍稀的、装帧形式特殊的《龙藏》。《龙藏》存世量稀少，民族文化宫图书馆藏《龙藏》为幸存的珍贵版本。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://baijiahao.baidu.com/s?id=1767494632561741658&amp;wfr=spider&amp;for=pc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">国宝明版大藏经 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.zhangye.gov.cn/szb/dzdt/gjzy/202307/t20230731_1086692.html</t>
   </si>
   <si>
     <t xml:space="preserve">168册影印版朔源</t>
@@ -28533,6 +28607,15 @@
     <t xml:space="preserve">https://www.fjdh.cn/wumin/2009/04/22484866694.html</t>
   </si>
   <si>
+    <t xml:space="preserve">「三藏」是什么？ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">总计包括经丶律丶论和语录等梵箧为一千六百七十二部，至为浩瀚。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://baijiahao.baidu.com/s?for=pc&amp;id=1667928883553168661&amp;wfr=spider</t>
+  </si>
+  <si>
     <t xml:space="preserve">清敕修大藏经保护项目简介 </t>
   </si>
   <si>
@@ -28757,7 +28840,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\年m\月d\日"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
@@ -28860,6 +28943,13 @@
       <color rgb="FF2A6099"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -29115,7 +29205,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29312,7 +29402,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -29325,10 +29423,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -29380,11 +29474,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -82431,7 +82529,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:AD183"/>
+  <dimension ref="A3:AD186"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.85"/>
@@ -83263,114 +83361,116 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="28" t="s">
         <v>7623</v>
       </c>
-      <c r="D61" s="28" t="s">
+      <c r="B61" s="49" t="s">
+        <v>7619</v>
+      </c>
+      <c r="C61" s="0" t="s">
         <v>7624</v>
       </c>
+      <c r="D61" s="1" t="s">
+        <v>7625</v>
+      </c>
       <c r="E61" s="28"/>
-      <c r="F61" s="28" t="s">
-        <v>7625</v>
+      <c r="F61" s="0" t="s">
+        <v>7626</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>7626</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D62" s="28"/>
+        <v>7627</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="28" t="s">
+        <v>7628</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>7629</v>
+      </c>
       <c r="E62" s="28"/>
-      <c r="F62" s="43"/>
+      <c r="F62" s="28" t="s">
+        <v>7630</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>7631</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
-        <v>7627</v>
-      </c>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="43"/>
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="43" t="s">
-        <v>7628</v>
-      </c>
-      <c r="B64" s="28" t="s">
-        <v>7629</v>
-      </c>
-      <c r="F64" s="43" t="s">
+      <c r="A64" s="1" t="s">
+        <v>7632</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="43" t="s">
+        <v>7633</v>
+      </c>
+      <c r="B65" s="28" t="s">
+        <v>7634</v>
+      </c>
+      <c r="F65" s="43" t="s">
         <v>7496</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="G65" s="2" t="s">
         <v>7497</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="28" t="s">
-        <v>7630</v>
-      </c>
-      <c r="B65" s="28" t="s">
-        <v>7631</v>
-      </c>
-      <c r="C65" s="28" t="s">
-        <v>7632</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>7633</v>
-      </c>
-      <c r="E65" s="28" t="s">
-        <v>7634</v>
-      </c>
-      <c r="F65" s="43" t="s">
-        <v>7635</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>7636</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="28" t="s">
+        <v>7635</v>
+      </c>
+      <c r="B66" s="28" t="s">
+        <v>7636</v>
+      </c>
+      <c r="C66" s="28" t="s">
         <v>7637</v>
       </c>
-      <c r="B66" s="28" t="s">
+      <c r="D66" s="1" t="s">
         <v>7638</v>
       </c>
-      <c r="C66" s="28"/>
-      <c r="D66" s="43"/>
       <c r="E66" s="28" t="s">
         <v>7639</v>
       </c>
-      <c r="F66" s="28" t="s">
-        <v>7521</v>
+      <c r="F66" s="43" t="s">
+        <v>7640</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>7522</v>
+        <v>7641</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="28" t="s">
-        <v>7640</v>
+        <v>7642</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>7641</v>
+        <v>7643</v>
       </c>
       <c r="C67" s="28"/>
       <c r="D67" s="43"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="43" t="s">
-        <v>7496</v>
+      <c r="E67" s="28" t="s">
+        <v>7644</v>
+      </c>
+      <c r="F67" s="28" t="s">
+        <v>7521</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>7497</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="49" t="s">
-        <v>7642</v>
+      <c r="A68" s="28" t="s">
+        <v>7645</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>7643</v>
-      </c>
-      <c r="C68" s="28" t="s">
-        <v>7644</v>
-      </c>
+        <v>7646</v>
+      </c>
+      <c r="C68" s="28"/>
       <c r="D68" s="43"/>
       <c r="E68" s="28"/>
       <c r="F68" s="43" t="s">
@@ -83381,292 +83481,296 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="49" t="s">
-        <v>7642</v>
-      </c>
-      <c r="B69" s="28" t="s">
+      <c r="A69" s="28" t="s">
         <v>7645</v>
       </c>
-      <c r="C69" s="28" t="s">
-        <v>7646</v>
-      </c>
+      <c r="B69" s="28"/>
+      <c r="C69" s="28"/>
       <c r="D69" s="43"/>
       <c r="E69" s="28"/>
-      <c r="F69" s="28" t="s">
-        <v>7521</v>
+      <c r="F69" s="0" t="s">
+        <v>7626</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>7522</v>
+        <v>7627</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="49" t="s">
+      <c r="A70" s="50" t="s">
         <v>7647</v>
       </c>
       <c r="B70" s="28" t="s">
         <v>7648</v>
       </c>
-      <c r="C70" s="28"/>
-      <c r="D70" s="1" t="s">
+      <c r="C70" s="28" t="s">
+        <v>7649</v>
+      </c>
+      <c r="D70" s="43"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="50" t="s">
+        <v>7647</v>
+      </c>
+      <c r="B71" s="28" t="s">
+        <v>7650</v>
+      </c>
+      <c r="C71" s="28" t="s">
+        <v>7651</v>
+      </c>
+      <c r="D71" s="43"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="50" t="s">
+        <v>7652</v>
+      </c>
+      <c r="B72" s="28" t="s">
+        <v>7653</v>
+      </c>
+      <c r="C72" s="28"/>
+      <c r="D72" s="1" t="s">
         <v>7515</v>
       </c>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28" t="s">
+      <c r="E72" s="28"/>
+      <c r="F72" s="28" t="s">
         <v>7516</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G72" s="2" t="s">
         <v>7517</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="49"/>
-      <c r="B71" s="28"/>
-      <c r="C71" s="28"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="2"/>
-    </row>
-    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="28" t="s">
-        <v>7649</v>
-      </c>
-      <c r="C72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="2"/>
-    </row>
     <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="49" t="s">
-        <v>7650</v>
-      </c>
-      <c r="B73" s="28" t="s">
-        <v>7651</v>
-      </c>
-      <c r="C73" s="28" t="s">
-        <v>7652</v>
-      </c>
-      <c r="E73" s="28" t="s">
-        <v>7653</v>
-      </c>
-      <c r="F73" s="43" t="s">
+      <c r="A73" s="50"/>
+      <c r="B73" s="28"/>
+      <c r="C73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="28" t="s">
+        <v>7654</v>
+      </c>
+      <c r="C74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="28"/>
+      <c r="G74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="50" t="s">
+        <v>7655</v>
+      </c>
+      <c r="B75" s="51" t="s">
+        <v>7656</v>
+      </c>
+      <c r="C75" s="50" t="s">
+        <v>7657</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>7625</v>
+      </c>
+      <c r="E75" s="28"/>
+      <c r="F75" s="0" t="s">
+        <v>7626</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>7627</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="50" t="s">
+        <v>7655</v>
+      </c>
+      <c r="B76" s="28" t="s">
+        <v>7658</v>
+      </c>
+      <c r="C76" s="28" t="s">
+        <v>7659</v>
+      </c>
+      <c r="E76" s="28" t="s">
+        <v>7660</v>
+      </c>
+      <c r="F76" s="43" t="s">
         <v>7496</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G76" s="2" t="s">
         <v>7497</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="49" t="s">
-        <v>7654</v>
-      </c>
-      <c r="B74" s="28" t="s">
-        <v>7655</v>
-      </c>
-      <c r="C74" s="28"/>
-      <c r="D74" s="1" t="s">
+    <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="50" t="s">
+        <v>7661</v>
+      </c>
+      <c r="B77" s="28" t="s">
+        <v>7662</v>
+      </c>
+      <c r="C77" s="28"/>
+      <c r="D77" s="1" t="s">
         <v>7515</v>
       </c>
-      <c r="E74" s="28"/>
-      <c r="F74" s="28" t="s">
+      <c r="E77" s="28"/>
+      <c r="F77" s="28" t="s">
         <v>7516</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G77" s="2" t="s">
         <v>7517</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="28" t="s">
-        <v>7656</v>
-      </c>
-      <c r="B75" s="28" t="s">
-        <v>7657</v>
-      </c>
-      <c r="C75" s="28"/>
-      <c r="E75" s="43" t="s">
-        <v>7658</v>
-      </c>
-      <c r="F75" s="0" t="s">
-        <v>7659</v>
-      </c>
-      <c r="G75" s="2" t="s">
+    <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="28" t="s">
+        <v>7663</v>
+      </c>
+      <c r="B78" s="28" t="s">
+        <v>7664</v>
+      </c>
+      <c r="C78" s="28"/>
+      <c r="E78" s="43" t="s">
+        <v>7665</v>
+      </c>
+      <c r="F78" s="0" t="s">
+        <v>7666</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>7522</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="47" t="n">
+    <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="47" t="n">
         <v>32140</v>
       </c>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
-      <c r="E76" s="0"/>
-      <c r="F76" s="0"/>
-    </row>
-    <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="47" t="n">
+      <c r="B79" s="43" t="s">
+        <v>7667</v>
+      </c>
+      <c r="C79" s="52" t="s">
+        <v>7668</v>
+      </c>
+      <c r="E79" s="43"/>
+      <c r="F79" s="28" t="s">
+        <v>7669</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>7670</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="47" t="n">
         <v>32140</v>
       </c>
-      <c r="B77" s="43" t="s">
-        <v>7660</v>
-      </c>
-      <c r="C77" s="50" t="s">
-        <v>7661</v>
-      </c>
-      <c r="E77" s="43"/>
-      <c r="F77" s="28" t="s">
-        <v>7662</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>7663</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="47" t="n">
-        <v>32140</v>
-      </c>
-      <c r="B78" s="43" t="s">
-        <v>7660</v>
-      </c>
-      <c r="C78" s="28" t="s">
+      <c r="B80" s="43" t="s">
+        <v>7667</v>
+      </c>
+      <c r="C80" s="28" t="s">
+        <v>7671</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>7672</v>
+      </c>
+      <c r="E80" s="28" t="s">
+        <v>7673</v>
+      </c>
+      <c r="F80" s="43" t="s">
+        <v>7674</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>7675</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="47" t="s">
+        <v>7676</v>
+      </c>
+      <c r="B81" s="28" t="s">
+        <v>7677</v>
+      </c>
+      <c r="D81" s="28" t="s">
+        <v>7678</v>
+      </c>
+      <c r="E81" s="53" t="s">
+        <v>7679</v>
+      </c>
+      <c r="F81" s="43" t="s">
+        <v>7537</v>
+      </c>
+      <c r="G81" s="54" t="s">
+        <v>7680</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="47" t="s">
+        <v>7681</v>
+      </c>
+      <c r="B82" s="28" t="s">
         <v>7664</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>7665</v>
-      </c>
-      <c r="E78" s="28" t="s">
-        <v>7666</v>
-      </c>
-      <c r="F78" s="43" t="s">
-        <v>7667</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>7668</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="47" t="s">
-        <v>7669</v>
-      </c>
-      <c r="B79" s="28" t="s">
-        <v>7670</v>
-      </c>
-      <c r="D79" s="28" t="s">
-        <v>7671</v>
-      </c>
-      <c r="E79" s="51" t="s">
-        <v>7672</v>
-      </c>
-      <c r="F79" s="43" t="s">
-        <v>7537</v>
-      </c>
-      <c r="G79" s="52" t="s">
-        <v>7673</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="47" t="s">
-        <v>7674</v>
-      </c>
-      <c r="B80" s="28" t="s">
-        <v>7657</v>
-      </c>
-      <c r="C80" s="28" t="s">
-        <v>7675</v>
-      </c>
-      <c r="D80" s="43" t="s">
-        <v>7676</v>
-      </c>
-      <c r="E80" s="28" t="s">
-        <v>7677</v>
-      </c>
-      <c r="F80" s="28" t="s">
+      <c r="C82" s="28" t="s">
+        <v>7682</v>
+      </c>
+      <c r="D82" s="43" t="s">
+        <v>7683</v>
+      </c>
+      <c r="E82" s="28" t="s">
+        <v>7684</v>
+      </c>
+      <c r="F82" s="28" t="s">
         <v>7521</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G82" s="2" t="s">
         <v>7522</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="47" t="n">
-        <v>32471</v>
-      </c>
-      <c r="B81" s="28"/>
-      <c r="C81" s="50" t="s">
-        <v>7678</v>
-      </c>
-      <c r="D81" s="0" t="s">
-        <v>7679</v>
-      </c>
-      <c r="E81" s="53" t="s">
-        <v>7680</v>
-      </c>
-      <c r="F81" s="53" t="s">
-        <v>7681</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>7682</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="47" t="n">
-        <v>32471</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>7683</v>
-      </c>
-      <c r="C82" s="28" t="s">
-        <v>7684</v>
-      </c>
-      <c r="D82" s="28" t="s">
-        <v>7685</v>
-      </c>
-      <c r="E82" s="51"/>
-      <c r="F82" s="43" t="s">
-        <v>7635</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>7636</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="47" t="n">
         <v>32471</v>
       </c>
-      <c r="B83" s="28" t="s">
+      <c r="B83" s="28"/>
+      <c r="C83" s="52" t="s">
+        <v>7685</v>
+      </c>
+      <c r="D83" s="0" t="s">
         <v>7686</v>
       </c>
-      <c r="C83" s="28" t="s">
+      <c r="E83" s="51" t="s">
         <v>7687</v>
       </c>
-      <c r="D83" s="28" t="s">
+      <c r="F83" s="51" t="s">
         <v>7688</v>
       </c>
-      <c r="E83" s="28"/>
-      <c r="F83" s="1" t="s">
+      <c r="G83" s="2" t="s">
         <v>7689</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>7690</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="84" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="47" t="n">
         <v>32471</v>
       </c>
-      <c r="B84" s="28" t="s">
+      <c r="B84" s="1" t="s">
+        <v>7690</v>
+      </c>
+      <c r="C84" s="28" t="s">
         <v>7691</v>
       </c>
-      <c r="C84" s="28" t="s">
+      <c r="D84" s="28" t="s">
         <v>7692</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>7693</v>
-      </c>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28" t="s">
-        <v>7667</v>
+      <c r="E84" s="53"/>
+      <c r="F84" s="43" t="s">
+        <v>7640</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>7694</v>
+        <v>7641</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83674,135 +83778,133 @@
         <v>32471</v>
       </c>
       <c r="B85" s="28" t="s">
-        <v>7691</v>
+        <v>7693</v>
       </c>
       <c r="C85" s="28" t="s">
+        <v>7694</v>
+      </c>
+      <c r="D85" s="28" t="s">
         <v>7695</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>7693</v>
-      </c>
-      <c r="E85" s="28" t="s">
+      <c r="E85" s="28"/>
+      <c r="F85" s="1" t="s">
         <v>7696</v>
       </c>
-      <c r="F85" s="28" t="s">
-        <v>7521</v>
-      </c>
       <c r="G85" s="2" t="s">
-        <v>7522</v>
+        <v>7697</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B86" s="28" t="s">
+        <v>7698</v>
+      </c>
+      <c r="C86" s="28" t="s">
+        <v>7699</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>7700</v>
+      </c>
+      <c r="E86" s="28"/>
+      <c r="F86" s="28" t="s">
+        <v>7674</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>7701</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B87" s="28" t="s">
+        <v>7698</v>
+      </c>
+      <c r="C87" s="28" t="s">
+        <v>7702</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>7700</v>
+      </c>
+      <c r="E87" s="28" t="s">
+        <v>7703</v>
+      </c>
+      <c r="F87" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="47" t="n">
         <v>32517</v>
       </c>
-      <c r="B86" s="28" t="s">
-        <v>7697</v>
-      </c>
-      <c r="C86" s="28" t="s">
+      <c r="B88" s="28" t="s">
+        <v>7704</v>
+      </c>
+      <c r="C88" s="28" t="s">
         <v>7589</v>
       </c>
-      <c r="D86" s="28" t="s">
-        <v>7698</v>
-      </c>
-      <c r="E86" s="28"/>
-      <c r="F86" s="1" t="s">
+      <c r="D88" s="28" t="s">
+        <v>7705</v>
+      </c>
+      <c r="E88" s="28"/>
+      <c r="F88" s="1" t="s">
         <v>7593</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>7594</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="47"/>
-      <c r="B87" s="28" t="s">
-        <v>7699</v>
-      </c>
-      <c r="C87" s="28"/>
-      <c r="D87" s="28"/>
-      <c r="E87" s="28"/>
-      <c r="F87" s="43" t="s">
+    <row r="89" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="47"/>
+      <c r="B89" s="28" t="s">
+        <v>7706</v>
+      </c>
+      <c r="C89" s="28"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="43" t="s">
         <v>7496</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G89" s="2" t="s">
         <v>7497</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="47" t="s">
-        <v>7700</v>
-      </c>
-      <c r="B88" s="28" t="s">
-        <v>7701</v>
-      </c>
-      <c r="C88" s="28" t="s">
-        <v>7702</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E88" s="28"/>
-      <c r="F88" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="47" t="s">
-        <v>7703</v>
-      </c>
-      <c r="B89" s="28" t="s">
-        <v>7657</v>
-      </c>
-      <c r="C89" s="28"/>
-      <c r="D89" s="43" t="s">
-        <v>7676</v>
-      </c>
-      <c r="E89" s="28" t="s">
-        <v>7704</v>
-      </c>
-      <c r="F89" s="28" t="s">
-        <v>7521</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>7522</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="47" t="s">
-        <v>7705</v>
+        <v>7707</v>
       </c>
       <c r="B90" s="28" t="s">
-        <v>7706</v>
-      </c>
-      <c r="C90" s="28"/>
-      <c r="D90" s="43" t="s">
-        <v>7676</v>
-      </c>
-      <c r="E90" s="28" t="s">
-        <v>7707</v>
-      </c>
+        <v>7708</v>
+      </c>
+      <c r="C90" s="28" t="s">
+        <v>7709</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="E90" s="28"/>
       <c r="F90" s="28" t="s">
-        <v>7521</v>
+        <v>7516</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>7522</v>
+        <v>7517</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="47" t="s">
-        <v>7708</v>
+        <v>7710</v>
       </c>
       <c r="B91" s="28" t="s">
-        <v>7709</v>
-      </c>
-      <c r="C91" s="28" t="s">
-        <v>7710</v>
-      </c>
+        <v>7664</v>
+      </c>
+      <c r="C91" s="28"/>
       <c r="D91" s="43" t="s">
-        <v>7676</v>
+        <v>7683</v>
       </c>
       <c r="E91" s="28" t="s">
         <v>7711</v>
@@ -83814,464 +83916,465 @@
         <v>7522</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="43" t="s">
+    <row r="92" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="47" t="s">
         <v>7712</v>
       </c>
-      <c r="B92" s="0"/>
-      <c r="C92" s="28" t="s">
+      <c r="B92" s="28" t="s">
         <v>7713</v>
       </c>
+      <c r="C92" s="28"/>
       <c r="D92" s="43" t="s">
+        <v>7683</v>
+      </c>
+      <c r="E92" s="28" t="s">
         <v>7714</v>
       </c>
-      <c r="E92" s="28" t="s">
+      <c r="F92" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="47" t="s">
         <v>7715</v>
       </c>
-      <c r="F92" s="54" t="s">
+      <c r="B93" s="28" t="s">
         <v>7716</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="C93" s="28" t="s">
         <v>7717</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="49" t="s">
+      <c r="D93" s="43" t="s">
+        <v>7683</v>
+      </c>
+      <c r="E93" s="28" t="s">
         <v>7718</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="F93" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="43" t="s">
         <v>7719</v>
       </c>
-      <c r="C93" s="28" t="s">
+      <c r="B94" s="0"/>
+      <c r="C94" s="28" t="s">
         <v>7720</v>
       </c>
-      <c r="F93" s="43" t="s">
+      <c r="D94" s="43" t="s">
+        <v>7721</v>
+      </c>
+      <c r="E94" s="28" t="s">
+        <v>7722</v>
+      </c>
+      <c r="F94" s="55" t="s">
+        <v>7723</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>7724</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="50" t="s">
+        <v>7725</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>7726</v>
+      </c>
+      <c r="C95" s="28" t="s">
+        <v>7727</v>
+      </c>
+      <c r="F95" s="43" t="s">
         <v>7496</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="G95" s="2" t="s">
         <v>7497</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="49" t="s">
-        <v>7721</v>
-      </c>
-      <c r="B94" s="53" t="s">
-        <v>7722</v>
-      </c>
-      <c r="C94" s="50" t="s">
-        <v>7723</v>
-      </c>
-      <c r="D94" s="0"/>
-      <c r="F94" s="43" t="s">
+    <row r="96" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="50" t="s">
+        <v>7728</v>
+      </c>
+      <c r="B96" s="51" t="s">
+        <v>7729</v>
+      </c>
+      <c r="C96" s="52" t="s">
+        <v>7730</v>
+      </c>
+      <c r="D96" s="0"/>
+      <c r="F96" s="43" t="s">
         <v>7496</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="G96" s="2" t="s">
         <v>7497</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="49"/>
-    </row>
-    <row r="96" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="43" t="s">
-        <v>7724</v>
-      </c>
-      <c r="B96" s="28"/>
-      <c r="D96" s="43"/>
-      <c r="E96" s="28"/>
-      <c r="F96" s="54"/>
-      <c r="G96" s="2"/>
-    </row>
-    <row r="97" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="47" t="n">
+    <row r="97" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="50"/>
+    </row>
+    <row r="98" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="43" t="s">
+        <v>7731</v>
+      </c>
+      <c r="B98" s="28"/>
+      <c r="D98" s="43"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="55"/>
+      <c r="G98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="47" t="n">
         <v>38164</v>
       </c>
-      <c r="B97" s="43" t="s">
-        <v>7725</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>7726</v>
-      </c>
-      <c r="D97" s="28" t="s">
-        <v>7727</v>
-      </c>
-      <c r="E97" s="28" t="s">
-        <v>7728</v>
-      </c>
-      <c r="F97" s="28" t="s">
-        <v>7729</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>7730</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="47" t="s">
-        <v>7731</v>
-      </c>
-      <c r="B98" s="55" t="s">
+      <c r="B99" s="43" t="s">
         <v>7732</v>
       </c>
-      <c r="C98" s="55" t="s">
+      <c r="C99" s="1" t="s">
         <v>7733</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D99" s="28" t="s">
         <v>7734</v>
       </c>
-      <c r="E98" s="49" t="s">
+      <c r="E99" s="28" t="s">
         <v>7735</v>
       </c>
-      <c r="F98" s="28" t="s">
+      <c r="F99" s="28" t="s">
         <v>7736</v>
       </c>
-      <c r="G98" s="1" t="s">
+      <c r="G99" s="2" t="s">
         <v>7737</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="47" t="s">
-        <v>7738</v>
-      </c>
-      <c r="B99" s="43" t="s">
-        <v>7739</v>
-      </c>
-      <c r="C99" s="28" t="s">
-        <v>7740</v>
-      </c>
-      <c r="D99" s="43" t="s">
-        <v>7741</v>
-      </c>
-      <c r="E99" s="43"/>
-      <c r="F99" s="43" t="s">
-        <v>7502</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>7503</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="47" t="s">
         <v>7738</v>
       </c>
-      <c r="B100" s="28" t="s">
+      <c r="B100" s="56" t="s">
+        <v>7739</v>
+      </c>
+      <c r="C100" s="56" t="s">
+        <v>7740</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>7741</v>
+      </c>
+      <c r="E100" s="50" t="s">
         <v>7742</v>
       </c>
-      <c r="C100" s="28" t="s">
+      <c r="F100" s="28" t="s">
         <v>7743</v>
       </c>
-      <c r="D100" s="28" t="s">
+      <c r="G100" s="1" t="s">
         <v>7744</v>
-      </c>
-      <c r="E100" s="28" t="s">
-        <v>7745</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>7746</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>7747</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="47" t="s">
+        <v>7745</v>
+      </c>
+      <c r="B101" s="43" t="s">
+        <v>7746</v>
+      </c>
+      <c r="C101" s="28" t="s">
+        <v>7747</v>
+      </c>
+      <c r="D101" s="43" t="s">
         <v>7748</v>
       </c>
-      <c r="B101" s="28" t="s">
-        <v>7742</v>
-      </c>
-      <c r="C101" s="28" t="s">
+      <c r="E101" s="43"/>
+      <c r="F101" s="43" t="s">
+        <v>7502</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>7503</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="47" t="s">
+        <v>7745</v>
+      </c>
+      <c r="B102" s="28" t="s">
         <v>7749</v>
       </c>
-      <c r="D101" s="28" t="s">
+      <c r="C102" s="28" t="s">
         <v>7750</v>
       </c>
-      <c r="E101" s="28"/>
-      <c r="F101" s="1" t="s">
-        <v>7746</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>7747</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="47" t="n">
+      <c r="D102" s="28" t="s">
+        <v>7751</v>
+      </c>
+      <c r="E102" s="28" t="s">
+        <v>7752</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>7753</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>7754</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="47" t="s">
+        <v>7755</v>
+      </c>
+      <c r="B103" s="28" t="s">
+        <v>7749</v>
+      </c>
+      <c r="C103" s="28" t="s">
+        <v>7756</v>
+      </c>
+      <c r="D103" s="28" t="s">
+        <v>7757</v>
+      </c>
+      <c r="E103" s="28"/>
+      <c r="F103" s="1" t="s">
+        <v>7753</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>7754</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="47" t="n">
         <v>42230</v>
       </c>
-      <c r="B102" s="28" t="s">
-        <v>7742</v>
-      </c>
-      <c r="C102" s="28" t="s">
-        <v>7751</v>
-      </c>
-      <c r="D102" s="28" t="s">
-        <v>7752</v>
-      </c>
-      <c r="E102" s="28" t="s">
+      <c r="B104" s="28" t="s">
+        <v>7749</v>
+      </c>
+      <c r="C104" s="28" t="s">
+        <v>7758</v>
+      </c>
+      <c r="D104" s="28" t="s">
+        <v>7759</v>
+      </c>
+      <c r="E104" s="28" t="s">
+        <v>7760</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>7753</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>7746</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>7747</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="43" t="s">
+      <c r="G104" s="2" t="s">
         <v>7754</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="47" t="n">
-        <v>42753</v>
-      </c>
-      <c r="B105" s="55" t="s">
-        <v>7755</v>
-      </c>
-      <c r="C105" s="43" t="s">
-        <v>7756</v>
-      </c>
-      <c r="D105" s="43" t="s">
-        <v>7757</v>
-      </c>
-      <c r="E105" s="43" t="s">
-        <v>7758</v>
-      </c>
-      <c r="F105" s="43" t="s">
-        <v>7502</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>7503</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="47" t="n">
-        <v>42753</v>
-      </c>
-      <c r="B106" s="55" t="s">
-        <v>7759</v>
-      </c>
-      <c r="C106" s="28" t="s">
-        <v>7760</v>
-      </c>
-      <c r="D106" s="43" t="s">
-        <v>7757</v>
-      </c>
-      <c r="E106" s="56" t="s">
+    <row r="105" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="43" t="s">
         <v>7761</v>
-      </c>
-      <c r="F106" s="43" t="s">
-        <v>7502</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>7503</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="47" t="n">
         <v>42753</v>
       </c>
-      <c r="B107" s="55" t="s">
-        <v>7759</v>
-      </c>
-      <c r="C107" s="55" t="s">
+      <c r="B107" s="56" t="s">
         <v>7762</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="C107" s="43" t="s">
         <v>7763</v>
       </c>
+      <c r="D107" s="43" t="s">
+        <v>7764</v>
+      </c>
       <c r="E107" s="43" t="s">
+        <v>7765</v>
+      </c>
+      <c r="F107" s="43" t="s">
+        <v>7502</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>7503</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="47" t="n">
+        <v>42753</v>
+      </c>
+      <c r="B108" s="56" t="s">
+        <v>7766</v>
+      </c>
+      <c r="C108" s="28" t="s">
+        <v>7767</v>
+      </c>
+      <c r="D108" s="43" t="s">
         <v>7764</v>
       </c>
-      <c r="F107" s="1" t="s">
-        <v>7765</v>
-      </c>
-      <c r="G107" s="2" t="s">
+      <c r="E108" s="57" t="s">
+        <v>7768</v>
+      </c>
+      <c r="F108" s="43" t="s">
+        <v>7502</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>7503</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="47" t="n">
+        <v>42753</v>
+      </c>
+      <c r="B109" s="56" t="s">
         <v>7766</v>
       </c>
-    </row>
-    <row r="108" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="47" t="n">
-        <v>43725</v>
-      </c>
-      <c r="B108" s="28" t="s">
-        <v>7767</v>
-      </c>
-      <c r="C108" s="28" t="s">
-        <v>7768</v>
-      </c>
-      <c r="D108" s="1" t="s">
+      <c r="C109" s="56" t="s">
         <v>7769</v>
       </c>
-      <c r="E108" s="28" t="s">
+      <c r="D109" s="1" t="s">
         <v>7770</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="E109" s="43" t="s">
         <v>7771</v>
       </c>
-      <c r="G108" s="1" t="s">
+      <c r="F109" s="1" t="s">
         <v>7772</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="47" t="n">
-        <v>44895</v>
-      </c>
-      <c r="B109" s="28" t="s">
+      <c r="G109" s="2" t="s">
         <v>7773</v>
-      </c>
-      <c r="C109" s="28" t="s">
-        <v>7774</v>
-      </c>
-      <c r="D109" s="43" t="s">
-        <v>7775</v>
-      </c>
-      <c r="E109" s="28" t="s">
-        <v>7776</v>
-      </c>
-      <c r="F109" s="28" t="s">
-        <v>7777</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>7778</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="47" t="n">
-        <v>45449</v>
+        <v>43725</v>
       </c>
       <c r="B110" s="28" t="s">
+        <v>7774</v>
+      </c>
+      <c r="C110" s="28" t="s">
+        <v>7775</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>7776</v>
+      </c>
+      <c r="E110" s="28" t="s">
+        <v>7777</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>7778</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>7779</v>
-      </c>
-      <c r="C110" s="28" t="s">
-        <v>7780</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>7781</v>
-      </c>
-      <c r="E110" s="28" t="s">
-        <v>7782</v>
-      </c>
-      <c r="F110" s="28" t="s">
-        <v>7783</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>7784</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="47" t="n">
-        <v>46017</v>
+        <v>44895</v>
       </c>
       <c r="B111" s="28" t="s">
+        <v>7780</v>
+      </c>
+      <c r="C111" s="28" t="s">
+        <v>7781</v>
+      </c>
+      <c r="D111" s="43" t="s">
+        <v>7782</v>
+      </c>
+      <c r="E111" s="28" t="s">
+        <v>7783</v>
+      </c>
+      <c r="F111" s="28" t="s">
+        <v>7784</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>7785</v>
       </c>
-      <c r="C111" s="28" t="s">
+    </row>
+    <row r="112" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="47" t="n">
+        <v>45449</v>
+      </c>
+      <c r="B112" s="28" t="s">
         <v>7786</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="C112" s="28" t="s">
         <v>7787</v>
       </c>
-      <c r="E111" s="28" t="s">
+      <c r="D112" s="1" t="s">
         <v>7788</v>
       </c>
-      <c r="F111" s="28" t="s">
+      <c r="E112" s="28" t="s">
         <v>7789</v>
       </c>
-      <c r="G111" s="2" t="s">
+      <c r="F112" s="28" t="s">
         <v>7790</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="47"/>
-      <c r="B112" s="28" t="s">
+      <c r="G112" s="2" t="s">
         <v>7791</v>
       </c>
-      <c r="C112" s="43" t="s">
-        <v>7792</v>
-      </c>
-      <c r="E112" s="28"/>
-      <c r="F112" s="28"/>
     </row>
     <row r="113" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="47" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B113" s="28" t="s">
+        <v>7792</v>
+      </c>
+      <c r="C113" s="28" t="s">
+        <v>7793</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>7794</v>
+      </c>
+      <c r="E113" s="28" t="s">
+        <v>7795</v>
+      </c>
+      <c r="F113" s="28" t="s">
+        <v>7796</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>7797</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="47"/>
+      <c r="B114" s="28" t="s">
+        <v>7798</v>
+      </c>
+      <c r="C114" s="43" t="s">
+        <v>7799</v>
+      </c>
+      <c r="E114" s="28"/>
+      <c r="F114" s="28"/>
+    </row>
+    <row r="115" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="47" t="n">
         <v>41741</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>7793</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>7794</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="47"/>
-      <c r="B117" s="28"/>
-      <c r="C117" s="28"/>
-      <c r="E117" s="28"/>
-      <c r="F117" s="28"/>
-      <c r="G117" s="2"/>
-    </row>
-    <row r="118" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="43" t="s">
-        <v>7795</v>
-      </c>
-      <c r="B118" s="28"/>
-      <c r="C118" s="28"/>
-      <c r="E118" s="28"/>
-      <c r="F118" s="28"/>
-      <c r="G118" s="2"/>
-    </row>
-    <row r="119" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="57" t="s">
-        <v>7796</v>
-      </c>
-      <c r="B119" s="43" t="s">
-        <v>7797</v>
-      </c>
-      <c r="C119" s="28" t="s">
-        <v>7798</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E119" s="28" t="s">
-        <v>7715</v>
-      </c>
-      <c r="F119" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G119" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="57" t="s">
-        <v>7799</v>
-      </c>
-      <c r="B120" s="43" t="s">
+      <c r="B115" s="1" t="s">
         <v>7800</v>
       </c>
-      <c r="C120" s="28" t="s">
+      <c r="G115" s="2" t="s">
         <v>7801</v>
       </c>
-      <c r="D120" s="1" t="s">
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="47"/>
+      <c r="B119" s="28"/>
+      <c r="C119" s="28"/>
+      <c r="E119" s="28"/>
+      <c r="F119" s="28"/>
+      <c r="G119" s="2"/>
+    </row>
+    <row r="120" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="43" t="s">
         <v>7802</v>
       </c>
-      <c r="F120" s="54" t="s">
-        <v>7716</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>7717</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="49" t="s">
+      <c r="B120" s="28"/>
+      <c r="C120" s="28"/>
+      <c r="E120" s="28"/>
+      <c r="F120" s="28"/>
+      <c r="G120" s="2"/>
+    </row>
+    <row r="121" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="58" t="s">
         <v>7803</v>
       </c>
-      <c r="B121" s="55" t="s">
+      <c r="B121" s="43" t="s">
         <v>7804</v>
       </c>
       <c r="C121" s="28" t="s">
@@ -84280,6 +84383,9 @@
       <c r="D121" s="1" t="s">
         <v>7515</v>
       </c>
+      <c r="E121" s="28" t="s">
+        <v>7722</v>
+      </c>
       <c r="F121" s="28" t="s">
         <v>7516</v>
       </c>
@@ -84287,40 +84393,39 @@
         <v>7517</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="57" t="s">
+    <row r="122" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="58" t="s">
         <v>7806</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="43" t="s">
         <v>7807</v>
       </c>
       <c r="C122" s="28" t="s">
         <v>7808</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E122" s="28" t="s">
         <v>7809</v>
       </c>
-      <c r="F122" s="28" t="s">
-        <v>7516</v>
+      <c r="F122" s="55" t="s">
+        <v>7723</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="57" t="s">
+        <v>7724</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="50" t="s">
         <v>7810</v>
       </c>
-      <c r="B123" s="28" t="s">
+      <c r="B123" s="56" t="s">
         <v>7811</v>
       </c>
       <c r="C123" s="28" t="s">
         <v>7812</v>
       </c>
-      <c r="E123" s="28"/>
+      <c r="D123" s="1" t="s">
+        <v>7515</v>
+      </c>
       <c r="F123" s="28" t="s">
         <v>7516</v>
       </c>
@@ -84329,990 +84434,1079 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="57" t="s">
+      <c r="A124" s="58" t="s">
         <v>7813</v>
       </c>
-      <c r="B124" s="28" t="s">
+      <c r="B124" s="1" t="s">
         <v>7814</v>
       </c>
       <c r="C124" s="28" t="s">
         <v>7815</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>7802</v>
-      </c>
-      <c r="E124" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="E124" s="28" t="s">
         <v>7816</v>
       </c>
-      <c r="F124" s="54" t="s">
-        <v>7716</v>
+      <c r="F124" s="28" t="s">
+        <v>7516</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>7717</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="47" t="n">
-        <v>44662</v>
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="58" t="s">
+        <v>7817</v>
       </c>
       <c r="B125" s="28" t="s">
-        <v>7817</v>
-      </c>
-      <c r="C125" s="1" t="s">
         <v>7818</v>
       </c>
-      <c r="D125" s="28" t="s">
+      <c r="C125" s="28" t="s">
         <v>7819</v>
       </c>
-      <c r="E125" s="28" t="s">
+      <c r="E125" s="28"/>
+      <c r="F125" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="58" t="s">
         <v>7820</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="B126" s="28" t="s">
         <v>7821</v>
       </c>
-      <c r="G125" s="1" t="s">
+      <c r="C126" s="28" t="s">
         <v>7822</v>
       </c>
-    </row>
-    <row r="126" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="57" t="s">
+      <c r="D126" s="1" t="s">
+        <v>7809</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>7823</v>
       </c>
-      <c r="B126" s="28" t="s">
-        <v>7824</v>
-      </c>
-      <c r="C126" s="28"/>
-      <c r="D126" s="1" t="s">
-        <v>7802</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>7825</v>
-      </c>
-      <c r="F126" s="54" t="s">
-        <v>7716</v>
+      <c r="F126" s="55" t="s">
+        <v>7723</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>7717</v>
+        <v>7724</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="47" t="n">
+        <v>44662</v>
+      </c>
+      <c r="B127" s="28" t="s">
+        <v>7824</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>7825</v>
+      </c>
+      <c r="D127" s="28" t="s">
+        <v>7826</v>
+      </c>
+      <c r="E127" s="28" t="s">
+        <v>7827</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>7828</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>7829</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="58" t="s">
+        <v>7830</v>
+      </c>
+      <c r="B128" s="28" t="s">
+        <v>7831</v>
+      </c>
+      <c r="C128" s="28"/>
+      <c r="D128" s="1" t="s">
+        <v>7809</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>7832</v>
+      </c>
+      <c r="F128" s="55" t="s">
+        <v>7723</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>7724</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="47" t="n">
         <v>44776</v>
       </c>
-      <c r="B127" s="28" t="s">
-        <v>7826</v>
-      </c>
-      <c r="C127" s="28" t="s">
-        <v>7827</v>
-      </c>
-      <c r="D127" s="28" t="s">
-        <v>7828</v>
-      </c>
-      <c r="E127" s="28" t="s">
-        <v>7829</v>
-      </c>
-      <c r="F127" s="28" t="s">
-        <v>7830</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>7831</v>
-      </c>
-    </row>
-    <row r="129" s="58" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1"/>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-      <c r="E129" s="1"/>
-      <c r="F129" s="1"/>
-      <c r="G129" s="1"/>
-      <c r="H129" s="1"/>
-      <c r="I129" s="1"/>
-      <c r="J129" s="1"/>
-      <c r="K129" s="1"/>
-      <c r="L129" s="1"/>
-      <c r="M129" s="1"/>
-      <c r="N129" s="1"/>
-      <c r="O129" s="1"/>
-      <c r="P129" s="1"/>
-      <c r="Q129" s="1"/>
-      <c r="R129" s="1"/>
-      <c r="S129" s="1"/>
-      <c r="T129" s="1"/>
-      <c r="U129" s="1"/>
-      <c r="V129" s="1"/>
-      <c r="W129" s="1"/>
-      <c r="X129" s="1"/>
-      <c r="Y129" s="1"/>
-      <c r="Z129" s="1"/>
-      <c r="AA129" s="1"/>
-      <c r="AB129" s="1"/>
-      <c r="AC129" s="1"/>
-      <c r="AD129" s="1"/>
-    </row>
-    <row r="130" s="58" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="47" t="s">
-        <v>7832</v>
-      </c>
-      <c r="B130" s="28"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
-      <c r="E130" s="1"/>
-      <c r="F130" s="28"/>
-      <c r="G130" s="2"/>
-      <c r="H130" s="1"/>
-      <c r="I130" s="1"/>
-      <c r="J130" s="1"/>
-      <c r="K130" s="1"/>
-      <c r="L130" s="1"/>
-      <c r="M130" s="1"/>
-      <c r="N130" s="1"/>
-      <c r="O130" s="1"/>
-      <c r="P130" s="1"/>
-      <c r="Q130" s="1"/>
-      <c r="R130" s="1"/>
-      <c r="S130" s="1"/>
-      <c r="T130" s="1"/>
-      <c r="U130" s="1"/>
-      <c r="V130" s="1"/>
-      <c r="W130" s="1"/>
-      <c r="X130" s="1"/>
-      <c r="Y130" s="1"/>
-      <c r="Z130" s="1"/>
-      <c r="AA130" s="1"/>
-      <c r="AB130" s="1"/>
-      <c r="AC130" s="1"/>
-      <c r="AD130" s="1"/>
-    </row>
-    <row r="131" s="58" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="59" t="n">
+      <c r="B129" s="28" t="s">
+        <v>7833</v>
+      </c>
+      <c r="C129" s="28" t="s">
+        <v>7834</v>
+      </c>
+      <c r="D129" s="28" t="s">
+        <v>7835</v>
+      </c>
+      <c r="E129" s="28" t="s">
+        <v>7836</v>
+      </c>
+      <c r="F129" s="28" t="s">
+        <v>7837</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>7838</v>
+      </c>
+    </row>
+    <row r="131" s="59" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+      <c r="K131" s="1"/>
+      <c r="L131" s="1"/>
+      <c r="M131" s="1"/>
+      <c r="N131" s="1"/>
+      <c r="O131" s="1"/>
+      <c r="P131" s="1"/>
+      <c r="Q131" s="1"/>
+      <c r="R131" s="1"/>
+      <c r="S131" s="1"/>
+      <c r="T131" s="1"/>
+      <c r="U131" s="1"/>
+      <c r="V131" s="1"/>
+      <c r="W131" s="1"/>
+      <c r="X131" s="1"/>
+      <c r="Y131" s="1"/>
+      <c r="Z131" s="1"/>
+      <c r="AA131" s="1"/>
+      <c r="AB131" s="1"/>
+      <c r="AC131" s="1"/>
+      <c r="AD131" s="1"/>
+    </row>
+    <row r="132" s="59" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="47" t="s">
+        <v>7839</v>
+      </c>
+      <c r="B132" s="28"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="28"/>
+      <c r="G132" s="2"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1"/>
+      <c r="L132" s="1"/>
+      <c r="M132" s="1"/>
+      <c r="N132" s="1"/>
+      <c r="O132" s="1"/>
+      <c r="P132" s="1"/>
+      <c r="Q132" s="1"/>
+      <c r="R132" s="1"/>
+      <c r="S132" s="1"/>
+      <c r="T132" s="1"/>
+      <c r="U132" s="1"/>
+      <c r="V132" s="1"/>
+      <c r="W132" s="1"/>
+      <c r="X132" s="1"/>
+      <c r="Y132" s="1"/>
+      <c r="Z132" s="1"/>
+      <c r="AA132" s="1"/>
+      <c r="AB132" s="1"/>
+      <c r="AC132" s="1"/>
+      <c r="AD132" s="1"/>
+    </row>
+    <row r="133" s="59" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="60" t="n">
         <v>45004</v>
       </c>
-      <c r="B131" s="58" t="s">
-        <v>7833</v>
-      </c>
-      <c r="C131" s="58" t="s">
-        <v>7834</v>
-      </c>
-      <c r="D131" s="58" t="s">
-        <v>7835</v>
-      </c>
-      <c r="E131" s="58" t="s">
-        <v>7836</v>
-      </c>
-      <c r="F131" s="60" t="s">
-        <v>7837</v>
-      </c>
-      <c r="G131" s="58" t="s">
-        <v>7838</v>
-      </c>
-    </row>
-    <row r="132" s="58" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="59" t="n">
+      <c r="B133" s="59" t="s">
+        <v>7840</v>
+      </c>
+      <c r="C133" s="59" t="s">
+        <v>7841</v>
+      </c>
+      <c r="D133" s="59" t="s">
+        <v>7842</v>
+      </c>
+      <c r="E133" s="59" t="s">
+        <v>7843</v>
+      </c>
+      <c r="F133" s="61" t="s">
+        <v>7844</v>
+      </c>
+      <c r="G133" s="59" t="s">
+        <v>7845</v>
+      </c>
+    </row>
+    <row r="134" s="59" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="60" t="n">
         <v>45005</v>
       </c>
-      <c r="B132" s="60" t="s">
-        <v>7839</v>
-      </c>
-      <c r="C132" s="58" t="s">
+      <c r="B134" s="61" t="s">
+        <v>7846</v>
+      </c>
+      <c r="C134" s="59" t="s">
+        <v>7847</v>
+      </c>
+      <c r="D134" s="59" t="s">
+        <v>7848</v>
+      </c>
+      <c r="E134" s="59" t="s">
+        <v>7849</v>
+      </c>
+      <c r="F134" s="61" t="s">
+        <v>7850</v>
+      </c>
+      <c r="G134" s="59" t="s">
+        <v>7851</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="60" t="n">
+        <v>45006</v>
+      </c>
+      <c r="B135" s="59" t="s">
         <v>7840</v>
       </c>
-      <c r="D132" s="58" t="s">
-        <v>7841</v>
-      </c>
-      <c r="E132" s="58" t="s">
-        <v>7842</v>
-      </c>
-      <c r="F132" s="60" t="s">
-        <v>7843</v>
-      </c>
-      <c r="G132" s="58" t="s">
-        <v>7844</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="59" t="n">
-        <v>45006</v>
-      </c>
-      <c r="B133" s="58" t="s">
-        <v>7833</v>
-      </c>
-      <c r="C133" s="58" t="s">
-        <v>7845</v>
-      </c>
-      <c r="D133" s="58" t="s">
-        <v>7846</v>
-      </c>
-      <c r="E133" s="61" t="s">
-        <v>7847</v>
-      </c>
-      <c r="F133" s="60" t="s">
-        <v>7848</v>
-      </c>
-      <c r="G133" s="58" t="s">
-        <v>7849</v>
-      </c>
-      <c r="H133" s="58"/>
-      <c r="I133" s="58"/>
-      <c r="J133" s="58"/>
-      <c r="K133" s="58"/>
-      <c r="L133" s="58"/>
-      <c r="M133" s="58"/>
-      <c r="N133" s="58"/>
-      <c r="O133" s="58"/>
-      <c r="P133" s="58"/>
-      <c r="Q133" s="58"/>
-      <c r="R133" s="58"/>
-      <c r="S133" s="58"/>
-      <c r="T133" s="58"/>
-      <c r="U133" s="58"/>
-      <c r="V133" s="58"/>
-      <c r="W133" s="58"/>
-      <c r="X133" s="58"/>
-      <c r="Y133" s="58"/>
-      <c r="Z133" s="58"/>
-      <c r="AA133" s="58"/>
-      <c r="AB133" s="58"/>
-      <c r="AC133" s="58"/>
-      <c r="AD133" s="58"/>
-    </row>
-    <row r="134" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="59" t="n">
+      <c r="C135" s="59" t="s">
+        <v>7852</v>
+      </c>
+      <c r="D135" s="59" t="s">
+        <v>7853</v>
+      </c>
+      <c r="E135" s="62" t="s">
+        <v>7854</v>
+      </c>
+      <c r="F135" s="61" t="s">
+        <v>7855</v>
+      </c>
+      <c r="G135" s="59" t="s">
+        <v>7856</v>
+      </c>
+      <c r="H135" s="59"/>
+      <c r="I135" s="59"/>
+      <c r="J135" s="59"/>
+      <c r="K135" s="59"/>
+      <c r="L135" s="59"/>
+      <c r="M135" s="59"/>
+      <c r="N135" s="59"/>
+      <c r="O135" s="59"/>
+      <c r="P135" s="59"/>
+      <c r="Q135" s="59"/>
+      <c r="R135" s="59"/>
+      <c r="S135" s="59"/>
+      <c r="T135" s="59"/>
+      <c r="U135" s="59"/>
+      <c r="V135" s="59"/>
+      <c r="W135" s="59"/>
+      <c r="X135" s="59"/>
+      <c r="Y135" s="59"/>
+      <c r="Z135" s="59"/>
+      <c r="AA135" s="59"/>
+      <c r="AB135" s="59"/>
+      <c r="AC135" s="59"/>
+      <c r="AD135" s="59"/>
+    </row>
+    <row r="136" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="60" t="n">
         <v>45036</v>
       </c>
-      <c r="B134" s="58" t="s">
-        <v>7850</v>
-      </c>
-      <c r="C134" s="58"/>
-      <c r="D134" s="58" t="s">
-        <v>7851</v>
-      </c>
-      <c r="E134" s="58" t="s">
-        <v>7852</v>
-      </c>
-      <c r="F134" s="58" t="s">
-        <v>7853</v>
-      </c>
-      <c r="G134" s="58" t="s">
-        <v>7854</v>
-      </c>
-      <c r="H134" s="58"/>
-      <c r="I134" s="58"/>
-      <c r="J134" s="58"/>
-      <c r="K134" s="58"/>
-      <c r="L134" s="58"/>
-      <c r="M134" s="58"/>
-      <c r="N134" s="58"/>
-      <c r="O134" s="58"/>
-      <c r="P134" s="58"/>
-      <c r="Q134" s="58"/>
-      <c r="R134" s="58"/>
-      <c r="S134" s="58"/>
-      <c r="T134" s="58"/>
-      <c r="U134" s="58"/>
-      <c r="V134" s="58"/>
-      <c r="W134" s="58"/>
-      <c r="X134" s="58"/>
-      <c r="Y134" s="58"/>
-      <c r="Z134" s="58"/>
-      <c r="AA134" s="58"/>
-      <c r="AB134" s="58"/>
-      <c r="AC134" s="58"/>
-      <c r="AD134" s="58"/>
-    </row>
-    <row r="135" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="62" t="n">
+      <c r="B136" s="59" t="s">
+        <v>7857</v>
+      </c>
+      <c r="C136" s="59"/>
+      <c r="D136" s="59" t="s">
+        <v>7858</v>
+      </c>
+      <c r="E136" s="59" t="s">
+        <v>7859</v>
+      </c>
+      <c r="F136" s="59" t="s">
+        <v>7860</v>
+      </c>
+      <c r="G136" s="59" t="s">
+        <v>7861</v>
+      </c>
+      <c r="H136" s="59"/>
+      <c r="I136" s="59"/>
+      <c r="J136" s="59"/>
+      <c r="K136" s="59"/>
+      <c r="L136" s="59"/>
+      <c r="M136" s="59"/>
+      <c r="N136" s="59"/>
+      <c r="O136" s="59"/>
+      <c r="P136" s="59"/>
+      <c r="Q136" s="59"/>
+      <c r="R136" s="59"/>
+      <c r="S136" s="59"/>
+      <c r="T136" s="59"/>
+      <c r="U136" s="59"/>
+      <c r="V136" s="59"/>
+      <c r="W136" s="59"/>
+      <c r="X136" s="59"/>
+      <c r="Y136" s="59"/>
+      <c r="Z136" s="59"/>
+      <c r="AA136" s="59"/>
+      <c r="AB136" s="59"/>
+      <c r="AC136" s="59"/>
+      <c r="AD136" s="59"/>
+    </row>
+    <row r="137" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="63" t="n">
         <v>45088</v>
       </c>
-      <c r="B135" s="48" t="s">
-        <v>7833</v>
-      </c>
-      <c r="C135" s="48" t="s">
-        <v>7855</v>
-      </c>
-      <c r="D135" s="48" t="s">
-        <v>7856</v>
-      </c>
-      <c r="E135" s="63" t="s">
-        <v>7857</v>
-      </c>
-      <c r="F135" s="48" t="s">
+      <c r="B137" s="48" t="s">
+        <v>7840</v>
+      </c>
+      <c r="C137" s="48" t="s">
+        <v>7862</v>
+      </c>
+      <c r="D137" s="48" t="s">
+        <v>7863</v>
+      </c>
+      <c r="E137" s="64" t="s">
+        <v>7864</v>
+      </c>
+      <c r="F137" s="48" t="s">
         <v>7549</v>
       </c>
-      <c r="G135" s="48" t="s">
+      <c r="G137" s="48" t="s">
         <v>7550</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="62" t="n">
+    <row r="138" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="63" t="n">
         <v>45025</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>7793</v>
-      </c>
-      <c r="C136" s="28" t="s">
-        <v>7858</v>
-      </c>
-      <c r="D136" s="43" t="s">
-        <v>7859</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>7860</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>7861</v>
-      </c>
-    </row>
-    <row r="137" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="1"/>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
-      <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
-      <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="1"/>
-      <c r="K137" s="1"/>
-      <c r="L137" s="1"/>
-      <c r="M137" s="1"/>
-      <c r="N137" s="1"/>
-      <c r="O137" s="1"/>
-      <c r="P137" s="1"/>
-      <c r="Q137" s="1"/>
-      <c r="R137" s="1"/>
-      <c r="S137" s="1"/>
-      <c r="T137" s="1"/>
-      <c r="U137" s="1"/>
-      <c r="V137" s="1"/>
-      <c r="W137" s="1"/>
-      <c r="X137" s="1"/>
-      <c r="Y137" s="1"/>
-      <c r="Z137" s="1"/>
-      <c r="AA137" s="1"/>
-      <c r="AB137" s="1"/>
-      <c r="AC137" s="1"/>
-      <c r="AD137" s="1"/>
-    </row>
-    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1" t="s">
-        <v>7862</v>
-      </c>
-      <c r="G138" s="1"/>
-      <c r="H138" s="1"/>
-      <c r="I138" s="1"/>
-      <c r="J138" s="1"/>
-      <c r="K138" s="1"/>
-      <c r="L138" s="1"/>
-      <c r="M138" s="1"/>
-      <c r="N138" s="1"/>
-      <c r="O138" s="1"/>
-      <c r="P138" s="1"/>
-      <c r="Q138" s="1"/>
-      <c r="R138" s="1"/>
-      <c r="S138" s="1"/>
-      <c r="T138" s="1"/>
-      <c r="U138" s="1"/>
-      <c r="V138" s="1"/>
-      <c r="W138" s="1"/>
-      <c r="X138" s="1"/>
-      <c r="Y138" s="1"/>
-      <c r="Z138" s="1"/>
-      <c r="AA138" s="1"/>
-      <c r="AB138" s="1"/>
-      <c r="AC138" s="1"/>
-      <c r="AD138" s="1"/>
-    </row>
-    <row r="139" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="64" t="n">
+      <c r="B138" s="1" t="s">
+        <v>7800</v>
+      </c>
+      <c r="C138" s="28" t="s">
+        <v>7865</v>
+      </c>
+      <c r="D138" s="43" t="s">
+        <v>7866</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>7867</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>7868</v>
+      </c>
+    </row>
+    <row r="139" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
+      <c r="E139" s="1"/>
+      <c r="F139" s="1"/>
+      <c r="G139" s="1"/>
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1"/>
+      <c r="K139" s="1"/>
+      <c r="L139" s="1"/>
+      <c r="M139" s="1"/>
+      <c r="N139" s="1"/>
+      <c r="O139" s="1"/>
+      <c r="P139" s="1"/>
+      <c r="Q139" s="1"/>
+      <c r="R139" s="1"/>
+      <c r="S139" s="1"/>
+      <c r="T139" s="1"/>
+      <c r="U139" s="1"/>
+      <c r="V139" s="1"/>
+      <c r="W139" s="1"/>
+      <c r="X139" s="1"/>
+      <c r="Y139" s="1"/>
+      <c r="Z139" s="1"/>
+      <c r="AA139" s="1"/>
+      <c r="AB139" s="1"/>
+      <c r="AC139" s="1"/>
+      <c r="AD139" s="1"/>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1" t="s">
+        <v>7869</v>
+      </c>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
+      <c r="K140" s="1"/>
+      <c r="L140" s="1"/>
+      <c r="M140" s="1"/>
+      <c r="N140" s="1"/>
+      <c r="O140" s="1"/>
+      <c r="P140" s="1"/>
+      <c r="Q140" s="1"/>
+      <c r="R140" s="1"/>
+      <c r="S140" s="1"/>
+      <c r="T140" s="1"/>
+      <c r="U140" s="1"/>
+      <c r="V140" s="1"/>
+      <c r="W140" s="1"/>
+      <c r="X140" s="1"/>
+      <c r="Y140" s="1"/>
+      <c r="Z140" s="1"/>
+      <c r="AA140" s="1"/>
+      <c r="AB140" s="1"/>
+      <c r="AC140" s="1"/>
+      <c r="AD140" s="1"/>
+    </row>
+    <row r="141" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="65" t="n">
         <v>39252</v>
       </c>
-      <c r="B139" s="41"/>
-      <c r="C139" s="41" t="s">
-        <v>7863</v>
-      </c>
-      <c r="D139" s="65" t="s">
-        <v>7864</v>
-      </c>
-      <c r="E139" s="41" t="s">
-        <v>7865</v>
-      </c>
-      <c r="F139" s="41" t="s">
-        <v>7866</v>
-      </c>
-      <c r="G139" s="41" t="s">
-        <v>7867</v>
-      </c>
-      <c r="H139" s="41"/>
-      <c r="I139" s="41"/>
-      <c r="J139" s="41"/>
-      <c r="K139" s="41"/>
-      <c r="L139" s="41"/>
-      <c r="M139" s="41"/>
-      <c r="N139" s="41"/>
-      <c r="O139" s="41"/>
-      <c r="P139" s="41"/>
-      <c r="Q139" s="41"/>
-      <c r="R139" s="41"/>
-      <c r="S139" s="41"/>
-      <c r="T139" s="41"/>
-      <c r="U139" s="41"/>
-      <c r="V139" s="41"/>
-      <c r="W139" s="41"/>
-      <c r="X139" s="41"/>
-      <c r="Y139" s="41"/>
-      <c r="Z139" s="41"/>
-      <c r="AA139" s="41"/>
-      <c r="AB139" s="41"/>
-      <c r="AC139" s="41"/>
-      <c r="AD139" s="41"/>
-    </row>
-    <row r="140" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="47" t="n">
+      <c r="B141" s="41"/>
+      <c r="C141" s="41" t="s">
+        <v>7870</v>
+      </c>
+      <c r="D141" s="66" t="s">
+        <v>7871</v>
+      </c>
+      <c r="E141" s="41" t="s">
+        <v>7872</v>
+      </c>
+      <c r="F141" s="41" t="s">
+        <v>7873</v>
+      </c>
+      <c r="G141" s="41" t="s">
+        <v>7874</v>
+      </c>
+      <c r="H141" s="41"/>
+      <c r="I141" s="41"/>
+      <c r="J141" s="41"/>
+      <c r="K141" s="41"/>
+      <c r="L141" s="41"/>
+      <c r="M141" s="41"/>
+      <c r="N141" s="41"/>
+      <c r="O141" s="41"/>
+      <c r="P141" s="41"/>
+      <c r="Q141" s="41"/>
+      <c r="R141" s="41"/>
+      <c r="S141" s="41"/>
+      <c r="T141" s="41"/>
+      <c r="U141" s="41"/>
+      <c r="V141" s="41"/>
+      <c r="W141" s="41"/>
+      <c r="X141" s="41"/>
+      <c r="Y141" s="41"/>
+      <c r="Z141" s="41"/>
+      <c r="AA141" s="41"/>
+      <c r="AB141" s="41"/>
+      <c r="AC141" s="41"/>
+      <c r="AD141" s="41"/>
+    </row>
+    <row r="142" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="47" t="n">
         <v>46241</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>7868</v>
-      </c>
-      <c r="C140" s="28" t="s">
-        <v>7869</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>7870</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>7871</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="47" t="s">
-        <v>7872</v>
-      </c>
-      <c r="B141" s="28" t="s">
-        <v>7873</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>7874</v>
-      </c>
-      <c r="D141" s="1" t="s">
+      <c r="B142" s="1" t="s">
         <v>7875</v>
       </c>
-      <c r="F141" s="28" t="s">
+      <c r="C142" s="28" t="s">
         <v>7876</v>
       </c>
-      <c r="G141" s="2" t="s">
+      <c r="F142" s="1" t="s">
         <v>7877</v>
       </c>
-    </row>
-    <row r="142" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="57" t="n">
+      <c r="G142" s="1" t="s">
+        <v>7878</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="47" t="s">
+        <v>7879</v>
+      </c>
+      <c r="B143" s="28" t="s">
+        <v>7880</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>7881</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>7882</v>
+      </c>
+      <c r="F143" s="28" t="s">
+        <v>7883</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>7884</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="58" t="n">
         <v>42866</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>7878</v>
-      </c>
-      <c r="C142" s="28" t="s">
-        <v>7879</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>7880</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>7881</v>
-      </c>
-      <c r="F142" s="28" t="s">
-        <v>7882</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>7883</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="145" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="2" t="s">
-        <v>7497</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>7884</v>
+      <c r="B144" s="1" t="s">
+        <v>7885</v>
+      </c>
+      <c r="C144" s="28" t="s">
+        <v>7886</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>7887</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>7888</v>
+      </c>
+      <c r="F144" s="28" t="s">
+        <v>7889</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>7890</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="147" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="58" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B147" s="51" t="s">
+        <v>7891</v>
+      </c>
+      <c r="C147" s="67" t="s">
+        <v>7892</v>
+      </c>
+      <c r="D147" s="52" t="s">
+        <v>7893</v>
+      </c>
+      <c r="E147" s="49" t="s">
+        <v>7894</v>
+      </c>
+      <c r="F147" s="49"/>
+      <c r="G147" s="54" t="s">
+        <v>7895</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1" t="s">
-        <v>7885</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="64" t="s">
-        <v>7886</v>
-      </c>
-      <c r="B149" s="41" t="s">
-        <v>7887</v>
-      </c>
-      <c r="C149" s="41" t="s">
-        <v>7888</v>
-      </c>
-      <c r="D149" s="41"/>
-      <c r="E149" s="41" t="s">
+      <c r="A148" s="58" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B148" s="51" t="s">
+        <v>7896</v>
+      </c>
+      <c r="C148" s="52"/>
+      <c r="D148" s="52"/>
+      <c r="E148" s="49"/>
+      <c r="F148" s="49"/>
+      <c r="G148" s="1" t="s">
+        <v>7897</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="58"/>
+      <c r="B149" s="51"/>
+      <c r="C149" s="52"/>
+      <c r="D149" s="52"/>
+      <c r="E149" s="49"/>
+      <c r="F149" s="49"/>
+      <c r="G149" s="1"/>
+    </row>
+    <row r="151" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="1" t="s">
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="65" t="s">
+        <v>7899</v>
+      </c>
+      <c r="B152" s="41" t="s">
+        <v>7900</v>
+      </c>
+      <c r="C152" s="41" t="s">
+        <v>7901</v>
+      </c>
+      <c r="D152" s="41"/>
+      <c r="E152" s="41" t="s">
+        <v>7902</v>
+      </c>
+      <c r="F152" s="41" t="s">
+        <v>7903</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>7904</v>
+      </c>
+    </row>
+    <row r="153" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
+        <v>7905</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>7906</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>7907</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>7908</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>7909</v>
+      </c>
+      <c r="F153" s="48" t="s">
+        <v>7910</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>7911</v>
+      </c>
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+      <c r="J153" s="1"/>
+      <c r="K153" s="1"/>
+      <c r="L153" s="1"/>
+      <c r="M153" s="1"/>
+      <c r="N153" s="1"/>
+      <c r="O153" s="1"/>
+      <c r="P153" s="1"/>
+      <c r="Q153" s="1"/>
+      <c r="R153" s="1"/>
+      <c r="S153" s="1"/>
+      <c r="T153" s="1"/>
+      <c r="U153" s="1"/>
+      <c r="V153" s="1"/>
+      <c r="W153" s="1"/>
+      <c r="X153" s="1"/>
+      <c r="Y153" s="1"/>
+      <c r="Z153" s="1"/>
+      <c r="AA153" s="1"/>
+      <c r="AB153" s="1"/>
+      <c r="AC153" s="1"/>
+      <c r="AD153" s="1"/>
+    </row>
+    <row r="154" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="65" t="s">
+        <v>7912</v>
+      </c>
+      <c r="B154" s="41" t="s">
+        <v>7913</v>
+      </c>
+      <c r="C154" s="41" t="s">
+        <v>7914</v>
+      </c>
+      <c r="D154" s="66" t="s">
+        <v>7915</v>
+      </c>
+      <c r="E154" s="41" t="s">
+        <v>7916</v>
+      </c>
+      <c r="F154" s="41" t="s">
+        <v>7903</v>
+      </c>
+      <c r="G154" s="41" t="s">
+        <v>7917</v>
+      </c>
+    </row>
+    <row r="155" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="68" t="n">
+        <v>42355</v>
+      </c>
+      <c r="B155" s="41" t="s">
+        <v>7918</v>
+      </c>
+      <c r="C155" s="41" t="s">
+        <v>7919</v>
+      </c>
+      <c r="D155" s="41" t="s">
+        <v>7920</v>
+      </c>
+      <c r="E155" s="41" t="s">
+        <v>7921</v>
+      </c>
+      <c r="F155" s="41" t="s">
+        <v>7922</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="65" t="n">
+        <v>43658</v>
+      </c>
+      <c r="B156" s="41" t="s">
+        <v>7923</v>
+      </c>
+      <c r="C156" s="41" t="s">
+        <v>7924</v>
+      </c>
+      <c r="D156" s="66" t="s">
+        <v>7925</v>
+      </c>
+      <c r="E156" s="41" t="s">
+        <v>7926</v>
+      </c>
+      <c r="F156" s="41" t="s">
+        <v>7923</v>
+      </c>
+      <c r="G156" s="41" t="s">
+        <v>7927</v>
+      </c>
+      <c r="H156" s="41"/>
+      <c r="I156" s="41"/>
+      <c r="J156" s="41"/>
+      <c r="K156" s="41"/>
+      <c r="L156" s="41"/>
+      <c r="M156" s="41"/>
+      <c r="N156" s="41"/>
+      <c r="O156" s="41"/>
+      <c r="P156" s="41"/>
+      <c r="Q156" s="41"/>
+      <c r="R156" s="41"/>
+      <c r="S156" s="41"/>
+      <c r="T156" s="41"/>
+      <c r="U156" s="41"/>
+      <c r="V156" s="41"/>
+      <c r="W156" s="41"/>
+      <c r="X156" s="41"/>
+      <c r="Y156" s="41"/>
+      <c r="Z156" s="41"/>
+      <c r="AA156" s="41"/>
+      <c r="AB156" s="41"/>
+      <c r="AC156" s="41"/>
+      <c r="AD156" s="41" t="s">
+        <v>7928</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="65" t="n">
+        <v>45581</v>
+      </c>
+      <c r="B157" s="41" t="s">
+        <v>7929</v>
+      </c>
+      <c r="C157" s="41" t="s">
+        <v>7930</v>
+      </c>
+      <c r="D157" s="41" t="s">
+        <v>7931</v>
+      </c>
+      <c r="E157" s="66" t="s">
+        <v>7932</v>
+      </c>
+      <c r="F157" s="41" t="s">
+        <v>7929</v>
+      </c>
+      <c r="G157" s="69" t="s">
+        <v>7933</v>
+      </c>
+      <c r="H157" s="41"/>
+      <c r="I157" s="41"/>
+      <c r="J157" s="41"/>
+      <c r="K157" s="41"/>
+      <c r="L157" s="41"/>
+      <c r="M157" s="41"/>
+      <c r="N157" s="41"/>
+      <c r="O157" s="41"/>
+      <c r="P157" s="41"/>
+      <c r="Q157" s="41"/>
+      <c r="R157" s="41"/>
+      <c r="S157" s="41"/>
+      <c r="T157" s="41"/>
+      <c r="U157" s="41"/>
+      <c r="V157" s="41"/>
+      <c r="W157" s="41"/>
+      <c r="X157" s="41"/>
+      <c r="Y157" s="41"/>
+      <c r="Z157" s="41"/>
+      <c r="AA157" s="41"/>
+      <c r="AB157" s="41"/>
+      <c r="AC157" s="41"/>
+      <c r="AD157" s="41"/>
+    </row>
+    <row r="158" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="68" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>7934</v>
+      </c>
+      <c r="C158" s="28" t="s">
+        <v>7935</v>
+      </c>
+      <c r="D158" s="28" t="s">
+        <v>7936</v>
+      </c>
+      <c r="E158" s="50" t="s">
+        <v>7937</v>
+      </c>
+      <c r="F158" s="28" t="s">
+        <v>7630</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>7631</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>7938</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="66" t="s">
+        <v>7939</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>7940</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>7941</v>
+      </c>
+      <c r="F161" s="1" t="s">
         <v>7889</v>
       </c>
-      <c r="F149" s="41" t="s">
-        <v>7890</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>7891</v>
-      </c>
-    </row>
-    <row r="150" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1" t="s">
-        <v>7892</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>7893</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>7894</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>7895</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>7896</v>
-      </c>
-      <c r="F150" s="48" t="s">
-        <v>7897</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>7898</v>
-      </c>
-      <c r="H150" s="1"/>
-      <c r="I150" s="1"/>
-      <c r="J150" s="1"/>
-      <c r="K150" s="1"/>
-      <c r="L150" s="1"/>
-      <c r="M150" s="1"/>
-      <c r="N150" s="1"/>
-      <c r="O150" s="1"/>
-      <c r="P150" s="1"/>
-      <c r="Q150" s="1"/>
-      <c r="R150" s="1"/>
-      <c r="S150" s="1"/>
-      <c r="T150" s="1"/>
-      <c r="U150" s="1"/>
-      <c r="V150" s="1"/>
-      <c r="W150" s="1"/>
-      <c r="X150" s="1"/>
-      <c r="Y150" s="1"/>
-      <c r="Z150" s="1"/>
-      <c r="AA150" s="1"/>
-      <c r="AB150" s="1"/>
-      <c r="AC150" s="1"/>
-      <c r="AD150" s="1"/>
-    </row>
-    <row r="151" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="64" t="s">
-        <v>7899</v>
-      </c>
-      <c r="B151" s="41" t="s">
-        <v>7900</v>
-      </c>
-      <c r="C151" s="41" t="s">
-        <v>7901</v>
-      </c>
-      <c r="D151" s="65" t="s">
-        <v>7902</v>
-      </c>
-      <c r="E151" s="41" t="s">
-        <v>7903</v>
-      </c>
-      <c r="F151" s="41" t="s">
-        <v>7890</v>
-      </c>
-      <c r="G151" s="41" t="s">
-        <v>7904</v>
-      </c>
-    </row>
-    <row r="152" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="66" t="n">
-        <v>42355</v>
-      </c>
-      <c r="B152" s="41" t="s">
-        <v>7905</v>
-      </c>
-      <c r="C152" s="41" t="s">
-        <v>7906</v>
-      </c>
-      <c r="D152" s="41" t="s">
-        <v>7907</v>
-      </c>
-      <c r="E152" s="41" t="s">
-        <v>7908</v>
-      </c>
-      <c r="F152" s="41" t="s">
-        <v>7909</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="64" t="n">
-        <v>43658</v>
-      </c>
-      <c r="B153" s="41" t="s">
-        <v>7910</v>
-      </c>
-      <c r="C153" s="41" t="s">
-        <v>7911</v>
-      </c>
-      <c r="D153" s="65" t="s">
-        <v>7912</v>
-      </c>
-      <c r="E153" s="41" t="s">
-        <v>7913</v>
-      </c>
-      <c r="F153" s="41" t="s">
-        <v>7910</v>
-      </c>
-      <c r="G153" s="41" t="s">
-        <v>7914</v>
-      </c>
-      <c r="H153" s="41"/>
-      <c r="I153" s="41"/>
-      <c r="J153" s="41"/>
-      <c r="K153" s="41"/>
-      <c r="L153" s="41"/>
-      <c r="M153" s="41"/>
-      <c r="N153" s="41"/>
-      <c r="O153" s="41"/>
-      <c r="P153" s="41"/>
-      <c r="Q153" s="41"/>
-      <c r="R153" s="41"/>
-      <c r="S153" s="41"/>
-      <c r="T153" s="41"/>
-      <c r="U153" s="41"/>
-      <c r="V153" s="41"/>
-      <c r="W153" s="41"/>
-      <c r="X153" s="41"/>
-      <c r="Y153" s="41"/>
-      <c r="Z153" s="41"/>
-      <c r="AA153" s="41"/>
-      <c r="AB153" s="41"/>
-      <c r="AC153" s="41"/>
-      <c r="AD153" s="41" t="s">
-        <v>7915</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="64" t="n">
-        <v>45581</v>
-      </c>
-      <c r="B154" s="41" t="s">
-        <v>7916</v>
-      </c>
-      <c r="C154" s="41" t="s">
-        <v>7917</v>
-      </c>
-      <c r="D154" s="41" t="s">
-        <v>7918</v>
-      </c>
-      <c r="E154" s="65" t="s">
-        <v>7919</v>
-      </c>
-      <c r="F154" s="41" t="s">
-        <v>7916</v>
-      </c>
-      <c r="G154" s="67" t="s">
-        <v>7920</v>
-      </c>
-      <c r="H154" s="41"/>
-      <c r="I154" s="41"/>
-      <c r="J154" s="41"/>
-      <c r="K154" s="41"/>
-      <c r="L154" s="41"/>
-      <c r="M154" s="41"/>
-      <c r="N154" s="41"/>
-      <c r="O154" s="41"/>
-      <c r="P154" s="41"/>
-      <c r="Q154" s="41"/>
-      <c r="R154" s="41"/>
-      <c r="S154" s="41"/>
-      <c r="T154" s="41"/>
-      <c r="U154" s="41"/>
-      <c r="V154" s="41"/>
-      <c r="W154" s="41"/>
-      <c r="X154" s="41"/>
-      <c r="Y154" s="41"/>
-      <c r="Z154" s="41"/>
-      <c r="AA154" s="41"/>
-      <c r="AB154" s="41"/>
-      <c r="AC154" s="41"/>
-      <c r="AD154" s="41"/>
-    </row>
-    <row r="155" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="66" t="n">
-        <v>45668</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>7921</v>
-      </c>
-      <c r="C155" s="28" t="s">
-        <v>7922</v>
-      </c>
-      <c r="D155" s="28" t="s">
-        <v>7923</v>
-      </c>
-      <c r="E155" s="49" t="s">
-        <v>7924</v>
-      </c>
-      <c r="F155" s="28" t="s">
-        <v>7625</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>7626</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="1" t="s">
-        <v>7925</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="65" t="s">
-        <v>7926</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>7927</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>7928</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>7882</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>7929</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="64" t="s">
-        <v>7930</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>7931</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>7882</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>7932</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="65" t="s">
-        <v>7926</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>7933</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>7934</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>7882</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>7935</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="28" t="s">
-        <v>7936</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>7937</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>7938</v>
-      </c>
-      <c r="F161" s="1" t="s">
+      <c r="G161" s="2" t="s">
+        <v>7942</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A162" s="65" t="s">
+        <v>7943</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>7944</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>7889</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>7945</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="66" t="s">
         <v>7939</v>
       </c>
-      <c r="G161" s="2" t="s">
-        <v>7915</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="1" t="s">
-        <v>7940</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>7941</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>7942</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>7939</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>7943</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="43" t="s">
-        <v>7944</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>7945</v>
+      <c r="B163" s="2" t="s">
+        <v>7946</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>7946</v>
+        <v>7947</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>7947</v>
+        <v>7889</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>7948</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="45" t="s">
+    <row r="164" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="28" t="s">
         <v>7949</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>7950</v>
       </c>
-      <c r="C164" s="49" t="s">
+      <c r="C164" s="1" t="s">
         <v>7951</v>
       </c>
+      <c r="F164" s="1" t="s">
+        <v>7952</v>
+      </c>
       <c r="G164" s="2" t="s">
-        <v>7952</v>
+        <v>7928</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>7940</v>
-      </c>
-      <c r="B165" s="1" t="s">
         <v>7953</v>
       </c>
-      <c r="C165" s="41" t="s">
+      <c r="B165" s="2" t="s">
         <v>7954</v>
       </c>
-      <c r="E165" s="1" t="s">
+      <c r="C165" s="1" t="s">
         <v>7955</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>7939</v>
-      </c>
-      <c r="G165" s="2" t="s">
-        <v>7943</v>
+        <v>7952</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>7956</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="28" t="s">
-        <v>7956</v>
-      </c>
-      <c r="B166" s="2" t="s">
+      <c r="A166" s="43" t="s">
         <v>7957</v>
       </c>
-      <c r="C166" s="41" t="s">
+      <c r="B166" s="1" t="s">
         <v>7958</v>
       </c>
-      <c r="D166" s="1" t="s">
+      <c r="C166" s="1" t="s">
         <v>7959</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>7939</v>
+        <v>7960</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>7960</v>
-      </c>
-      <c r="H166" s="1"/>
-    </row>
-    <row r="167" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="65" t="s">
-        <v>7926</v>
+        <v>7961</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="45" t="s">
+        <v>7962</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>7961</v>
-      </c>
-      <c r="D167" s="28" t="s">
-        <v>7962</v>
-      </c>
-      <c r="E167" s="1" t="s">
         <v>7963</v>
       </c>
-      <c r="F167" s="43" t="s">
+      <c r="C167" s="50" t="s">
         <v>7964</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>7965</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="68" t="s">
+    <row r="168" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
+        <v>7953</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>7966</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C168" s="41" t="s">
         <v>7967</v>
       </c>
-    </row>
-    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="0" t="s">
+      <c r="E168" s="1" t="s">
         <v>7968</v>
       </c>
-      <c r="B170" s="50" t="s">
+      <c r="F168" s="1" t="s">
+        <v>7952</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>7956</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="28" t="s">
         <v>7969</v>
       </c>
-      <c r="C170" s="1" t="s">
+      <c r="B169" s="2" t="s">
         <v>7970</v>
       </c>
-    </row>
-    <row r="173" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="43" t="s">
+      <c r="C169" s="41" t="s">
         <v>7971</v>
       </c>
-    </row>
-    <row r="174" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="1" t="s">
+      <c r="D169" s="1" t="s">
         <v>7972</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>7755</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>7882</v>
-      </c>
-      <c r="G174" s="2" t="s">
+      <c r="F169" s="1" t="s">
+        <v>7952</v>
+      </c>
+      <c r="G169" s="2" t="s">
         <v>7973</v>
+      </c>
+      <c r="H169" s="1"/>
+    </row>
+    <row r="170" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A170" s="66" t="s">
+        <v>7939</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>7974</v>
+      </c>
+      <c r="D170" s="28" t="s">
+        <v>7975</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>7976</v>
+      </c>
+      <c r="F170" s="43" t="s">
+        <v>7977</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>7978</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="70" t="s">
+        <v>7979</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="0" t="s">
+        <v>7981</v>
+      </c>
+      <c r="B173" s="52" t="s">
+        <v>7982</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>7983</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="52" t="s">
+        <v>7984</v>
+      </c>
+      <c r="B174" s="52" t="s">
+        <v>7985</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>7986</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="43" t="s">
+        <v>7987</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>7974</v>
+        <v>7988</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>7975</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="1" t="s">
-        <v>7976</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>7977</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="1" t="s">
-        <v>7978</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>7979</v>
-      </c>
-    </row>
-    <row r="183" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="43" t="s">
-        <v>7980</v>
+        <v>7762</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>7889</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>7989</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="1" t="s">
+        <v>7990</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>7991</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="1" t="s">
+        <v>7992</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>7993</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="s">
+        <v>7994</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>7995</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="43" t="s">
+        <v>7996</v>
       </c>
     </row>
   </sheetData>
@@ -85341,80 +85535,81 @@
     <hyperlink ref="G57" r:id="rId22" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
     <hyperlink ref="G59" r:id="rId23" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
     <hyperlink ref="G60" r:id="rId24" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G61" r:id="rId25" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="G64" r:id="rId26" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G65" r:id="rId27" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
-    <hyperlink ref="G66" r:id="rId28" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G67" r:id="rId29" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G68" r:id="rId30" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G69" r:id="rId31" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G70" r:id="rId32" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G73" r:id="rId33" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G74" r:id="rId34" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G75" r:id="rId35" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G78" r:id="rId36" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
-    <hyperlink ref="G79" r:id="rId37" display="https://www.dpm.org.cn/ancient"/>
-    <hyperlink ref="G80" r:id="rId38" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G82" r:id="rId39" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
-    <hyperlink ref="G83" r:id="rId40" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
-    <hyperlink ref="G84" r:id="rId41" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
-    <hyperlink ref="G85" r:id="rId42" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G86" r:id="rId43" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G87" r:id="rId44" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G88" r:id="rId45" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G89" r:id="rId46" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G90" r:id="rId47" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G91" r:id="rId48" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G92" r:id="rId49" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G93" r:id="rId50" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G94" r:id="rId51" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G97" r:id="rId52" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
-    <hyperlink ref="G99" r:id="rId53" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G100" r:id="rId54" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G101" r:id="rId55" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G102" r:id="rId56" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G105" r:id="rId57" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G106" r:id="rId58" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G109" r:id="rId59" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G110" r:id="rId60" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
-    <hyperlink ref="G111" r:id="rId61" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
-    <hyperlink ref="G113" r:id="rId62" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
-    <hyperlink ref="G119" r:id="rId63" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G120" r:id="rId64" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G121" r:id="rId65" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G122" r:id="rId66" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G123" r:id="rId67" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G124" r:id="rId68" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G126" r:id="rId69" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G127" r:id="rId70" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
-    <hyperlink ref="G131" r:id="rId71" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
-    <hyperlink ref="F133" r:id="rId72" display="中新网北京3月21日电 (记者 应妮) "/>
-    <hyperlink ref="G133" r:id="rId73" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
-    <hyperlink ref="G135" r:id="rId74" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G139" r:id="rId75" display="https://discovery.cctv.com/20070619/107154.shtml"/>
-    <hyperlink ref="G142" r:id="rId76" display="https://book.kongfz.com/102740/682706591"/>
-    <hyperlink ref="A145" r:id="rId77" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G149" r:id="rId78" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
-    <hyperlink ref="G150" r:id="rId79" display="https://book.kongfz.com/20791/3754198261"/>
-    <hyperlink ref="G153" r:id="rId80" display="https://www.ljstsg.cn/?p=6315"/>
-    <hyperlink ref="AD153" r:id="rId81" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="G154" r:id="rId82" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
-    <hyperlink ref="G155" r:id="rId83" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="B158" r:id="rId84" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
-    <hyperlink ref="G158" r:id="rId85" display="https://book.kongfz.com/536651/7839562954"/>
-    <hyperlink ref="B159" r:id="rId86" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
-    <hyperlink ref="G159" r:id="rId87" display="https://book.kongfz.com/23231/8186709240"/>
-    <hyperlink ref="B160" r:id="rId88" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
-    <hyperlink ref="G160" r:id="rId89" display="https://book.kongfz.com/536651/7839554296"/>
-    <hyperlink ref="G161" r:id="rId90" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="B162" r:id="rId91" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
-    <hyperlink ref="G163" r:id="rId92" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
-    <hyperlink ref="G164" r:id="rId93" display="https://book.kongfz.com/200249/1819262449/"/>
-    <hyperlink ref="G165" r:id="rId94" display="https://product.dangdang.com/11721366316.html"/>
-    <hyperlink ref="B166" r:id="rId95" display="出版社:宗教文化出版社 "/>
-    <hyperlink ref="G166" r:id="rId96" display="https://product.dangdang.com/22497432.html"/>
-    <hyperlink ref="G167" r:id="rId97" display="http://aiguji.net/3299.html"/>
-    <hyperlink ref="G174" r:id="rId98" display="https://book.kongfz.com/467603/10356350239"/>
+    <hyperlink ref="G62" r:id="rId25" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="G65" r:id="rId26" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G66" r:id="rId27" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
+    <hyperlink ref="G67" r:id="rId28" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G68" r:id="rId29" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G70" r:id="rId30" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G71" r:id="rId31" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G72" r:id="rId32" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G76" r:id="rId33" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G77" r:id="rId34" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G78" r:id="rId35" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G80" r:id="rId36" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
+    <hyperlink ref="G81" r:id="rId37" display="https://www.dpm.org.cn/ancient"/>
+    <hyperlink ref="G82" r:id="rId38" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G84" r:id="rId39" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
+    <hyperlink ref="G85" r:id="rId40" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
+    <hyperlink ref="G86" r:id="rId41" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
+    <hyperlink ref="G87" r:id="rId42" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G88" r:id="rId43" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G89" r:id="rId44" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G90" r:id="rId45" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G91" r:id="rId46" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G92" r:id="rId47" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G93" r:id="rId48" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G94" r:id="rId49" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G95" r:id="rId50" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G96" r:id="rId51" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G99" r:id="rId52" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
+    <hyperlink ref="G101" r:id="rId53" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G102" r:id="rId54" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G103" r:id="rId55" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G104" r:id="rId56" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G107" r:id="rId57" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G108" r:id="rId58" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G111" r:id="rId59" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G112" r:id="rId60" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
+    <hyperlink ref="G113" r:id="rId61" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
+    <hyperlink ref="G115" r:id="rId62" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
+    <hyperlink ref="G121" r:id="rId63" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G122" r:id="rId64" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G123" r:id="rId65" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G124" r:id="rId66" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G125" r:id="rId67" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G126" r:id="rId68" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G128" r:id="rId69" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G129" r:id="rId70" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
+    <hyperlink ref="G133" r:id="rId71" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
+    <hyperlink ref="F135" r:id="rId72" display="中新网北京3月21日电 (记者 应妮) "/>
+    <hyperlink ref="G135" r:id="rId73" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
+    <hyperlink ref="G137" r:id="rId74" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G141" r:id="rId75" display="https://discovery.cctv.com/20070619/107154.shtml"/>
+    <hyperlink ref="G144" r:id="rId76" display="https://book.kongfz.com/102740/682706591"/>
+    <hyperlink ref="C147" r:id="rId77" display="尊婆须蜜菩萨所集论十五卷"/>
+    <hyperlink ref="G147" r:id="rId78" display="https://baijiahao.baidu.com/s?id=1767494632561741658&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G152" r:id="rId79" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
+    <hyperlink ref="G153" r:id="rId80" display="https://book.kongfz.com/20791/3754198261"/>
+    <hyperlink ref="G156" r:id="rId81" display="https://www.ljstsg.cn/?p=6315"/>
+    <hyperlink ref="AD156" r:id="rId82" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="G157" r:id="rId83" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
+    <hyperlink ref="G158" r:id="rId84" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="B161" r:id="rId85" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
+    <hyperlink ref="G161" r:id="rId86" display="https://book.kongfz.com/536651/7839562954"/>
+    <hyperlink ref="B162" r:id="rId87" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
+    <hyperlink ref="G162" r:id="rId88" display="https://book.kongfz.com/23231/8186709240"/>
+    <hyperlink ref="B163" r:id="rId89" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
+    <hyperlink ref="G163" r:id="rId90" display="https://book.kongfz.com/536651/7839554296"/>
+    <hyperlink ref="G164" r:id="rId91" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="B165" r:id="rId92" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
+    <hyperlink ref="G166" r:id="rId93" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
+    <hyperlink ref="G167" r:id="rId94" display="https://book.kongfz.com/200249/1819262449/"/>
+    <hyperlink ref="G168" r:id="rId95" display="https://product.dangdang.com/11721366316.html"/>
+    <hyperlink ref="B169" r:id="rId96" display="出版社:宗教文化出版社 "/>
+    <hyperlink ref="G169" r:id="rId97" display="https://product.dangdang.com/22497432.html"/>
+    <hyperlink ref="G170" r:id="rId98" display="http://aiguji.net/3299.html"/>
+    <hyperlink ref="G177" r:id="rId99" display="https://book.kongfz.com/467603/10356350239"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -85434,120 +85629,120 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="69" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="71" width="12.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7981</v>
+        <v>7997</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="70" t="n">
+      <c r="A2" s="72" t="n">
         <v>1539</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7982</v>
+        <v>7998</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="70" t="n">
+      <c r="A3" s="72" t="n">
         <v>1615</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7983</v>
+        <v>7999</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="70" t="n">
+      <c r="A4" s="72" t="n">
         <v>1620</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7984</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="n">
+      <c r="A5" s="72" t="n">
         <v>1623</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7985</v>
+        <v>8001</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="70" t="n">
+      <c r="A6" s="72" t="n">
         <v>1653</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7986</v>
+        <v>8002</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>7987</v>
+        <v>8003</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7988</v>
+        <v>8004</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>7989</v>
+        <v>8005</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7990</v>
+        <v>8006</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>7991</v>
+        <v>8007</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7992</v>
+        <v>8008</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>7993</v>
+        <v>8009</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>7994</v>
+        <v>8010</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>7995</v>
+        <v>8011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7996</v>
+        <v>8012</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>7997</v>
+        <v>8013</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7998</v>
+        <v>8014</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85562,45 +85757,45 @@
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>7850</v>
+        <v>7857</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>7999</v>
+        <v>8015</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>8000</v>
+        <v>8016</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>8001</v>
+        <v>8017</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>8002</v>
+        <v>8018</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>8003</v>
+        <v>8019</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>8004</v>
+        <v>8020</v>
       </c>
       <c r="E23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>8005</v>
+        <v>8021</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>8006</v>
+        <v>8022</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
-        <v>7667</v>
+        <v>7674</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>8007</v>
+        <v>8023</v>
       </c>
     </row>
   </sheetData>
@@ -85632,84 +85827,84 @@
   </cols>
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="s">
-        <v>8008</v>
+      <c r="A8" s="73" t="s">
+        <v>8024</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="s">
-        <v>8009</v>
+      <c r="A9" s="73" t="s">
+        <v>8025</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="s">
-        <v>8010</v>
+      <c r="A10" s="73" t="s">
+        <v>8026</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="s">
-        <v>8011</v>
-      </c>
-      <c r="B12" s="72" t="n">
+      <c r="A12" s="73" t="s">
+        <v>8027</v>
+      </c>
+      <c r="B12" s="74" t="n">
         <v>45735</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8012</v>
+        <v>8028</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8013</v>
+        <v>8029</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="s">
-        <v>8014</v>
-      </c>
-      <c r="B13" s="72" t="n">
+      <c r="A13" s="73" t="s">
+        <v>8030</v>
+      </c>
+      <c r="B13" s="74" t="n">
         <v>45970</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8015</v>
+        <v>8031</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8016</v>
+        <v>8032</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="s">
-        <v>8017</v>
-      </c>
-      <c r="B14" s="72" t="n">
+      <c r="A14" s="73" t="s">
+        <v>8033</v>
+      </c>
+      <c r="B14" s="74" t="n">
         <v>45995</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8018</v>
+        <v>8034</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8019</v>
+        <v>8035</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="s">
-        <v>8020</v>
-      </c>
-      <c r="B15" s="72" t="n">
+      <c r="A15" s="73" t="s">
+        <v>8036</v>
+      </c>
+      <c r="B15" s="74" t="n">
         <v>46036</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8021</v>
+        <v>8037</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8022</v>
+        <v>8038</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>8023</v>
+        <v>8039</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>8024</v>
+        <v>8040</v>
       </c>
     </row>
   </sheetData>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10894" uniqueCount="8041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10896" uniqueCount="8043">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -28590,6 +28590,38 @@
   </si>
   <si>
     <t xml:space="preserve">http://aiguji.net/3299.html</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">正版 乾隆大藏经 精装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">120</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">册 清代官刻汉文大藏经 亦称龙藏 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://book.kongfz.com/714353/7542118911</t>
   </si>
   <si>
     <t xml:space="preserve">https://lib.dha.ac.cn/opac/book/41063?view=simple&amp;flag=printer https://vstudy.ruc.edu.cn/mystudy/search/detail/m20f248f0d88421bcaf7317dbb708eb82 </t>
@@ -85431,44 +85463,52 @@
         <v>7978</v>
       </c>
     </row>
+    <row r="171" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B171" s="52" t="s">
+        <v>7979</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>7980</v>
+      </c>
+    </row>
     <row r="172" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="70" t="s">
-        <v>7979</v>
+        <v>7981</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>7980</v>
+        <v>7982</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="s">
-        <v>7981</v>
+        <v>7983</v>
       </c>
       <c r="B173" s="52" t="s">
-        <v>7982</v>
+        <v>7984</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>7983</v>
+        <v>7985</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="52" t="s">
-        <v>7984</v>
+        <v>7986</v>
       </c>
       <c r="B174" s="52" t="s">
-        <v>7985</v>
+        <v>7987</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>7986</v>
+        <v>7988</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="43" t="s">
-        <v>7987</v>
+        <v>7989</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>7988</v>
+        <v>7990</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>7762</v>
@@ -85477,36 +85517,36 @@
         <v>7889</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>7989</v>
+        <v>7991</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>7990</v>
+        <v>7992</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>7991</v>
+        <v>7993</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>7992</v>
+        <v>7994</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>7993</v>
+        <v>7995</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>7994</v>
+        <v>7996</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>7995</v>
+        <v>7997</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="43" t="s">
-        <v>7996</v>
+        <v>7998</v>
       </c>
     </row>
   </sheetData>
@@ -85639,7 +85679,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7997</v>
+        <v>7999</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85650,7 +85690,7 @@
         <v>6766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7998</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85661,7 +85701,7 @@
         <v>7140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7999</v>
+        <v>8001</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85672,7 +85712,7 @@
         <v>7442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8000</v>
+        <v>8002</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85683,7 +85723,7 @@
         <v>7181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8001</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85694,55 +85734,55 @@
         <v>7329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8002</v>
+        <v>8004</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>8003</v>
+        <v>8005</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8004</v>
+        <v>8006</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>8005</v>
+        <v>8007</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8006</v>
+        <v>8008</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>8007</v>
+        <v>8009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8008</v>
+        <v>8010</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>8009</v>
+        <v>8011</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8010</v>
+        <v>8012</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>8011</v>
+        <v>8013</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8012</v>
+        <v>8014</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>8013</v>
+        <v>8015</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>8014</v>
+        <v>8016</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85760,42 +85800,42 @@
         <v>7857</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>8015</v>
+        <v>8017</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>8016</v>
+        <v>8018</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>8017</v>
+        <v>8019</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>8018</v>
+        <v>8020</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>8019</v>
+        <v>8021</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>8020</v>
+        <v>8022</v>
       </c>
       <c r="E23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>8021</v>
+        <v>8023</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>8022</v>
+        <v>8024</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
         <v>7674</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>8023</v>
+        <v>8025</v>
       </c>
     </row>
   </sheetData>
@@ -85828,83 +85868,83 @@
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="73" t="s">
-        <v>8024</v>
+        <v>8026</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="73" t="s">
-        <v>8025</v>
+        <v>8027</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="73" t="s">
-        <v>8026</v>
+        <v>8028</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="73" t="s">
-        <v>8027</v>
+        <v>8029</v>
       </c>
       <c r="B12" s="74" t="n">
         <v>45735</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8028</v>
+        <v>8030</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8029</v>
+        <v>8031</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="73" t="s">
-        <v>8030</v>
+        <v>8032</v>
       </c>
       <c r="B13" s="74" t="n">
         <v>45970</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8031</v>
+        <v>8033</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8032</v>
+        <v>8034</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="73" t="s">
-        <v>8033</v>
+        <v>8035</v>
       </c>
       <c r="B14" s="74" t="n">
         <v>45995</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8034</v>
+        <v>8036</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8035</v>
+        <v>8037</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="73" t="s">
-        <v>8036</v>
+        <v>8038</v>
       </c>
       <c r="B15" s="74" t="n">
         <v>46036</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8037</v>
+        <v>8039</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8038</v>
+        <v>8040</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>8039</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>8040</v>
+        <v>8042</v>
       </c>
     </row>
   </sheetData>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -23709,942 +23709,6 @@
     <t xml:space="preserve">柏林寺住持昆峰募款制备板架一百副以便庋置 </t>
   </si>
   <si>
-    <t xml:space="preserve">清朝-三次毁版</t>
-  </si>
-  <si>
-    <t xml:space="preserve">乾隆30/34/41年</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（三次撤经毁板事件）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">下旨 共撤毁了</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">800</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">余块经版和其对应的近百卷典籍。在这些撤毁的经版中，包括了钱谦益的著作，武则天、明永乐皇帝等前朝帝王撰写的文章等 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">乾隆三十年间</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1765</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1769</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1776</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">不久，《清藏》就发生了三次撤经毁板事件。第一次是乾隆三十年（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1765</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">），撤出钱谦益撰《楞严经疏解蒙钞》六十卷，毁经板</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">660</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">块。第二次是乾隆三十四年（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1769</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">），撤出《开元释教录略出》《辩伪录》《明仁孝皇后梦感佛说第一稀有大功德经》《永乐皇帝御制赞文》四种共</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">卷，毁掉经板</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">138</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">块。这时，全藏的实际数字是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">7168</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">册，经板</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">8238</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">块。第三次是乾隆四十一年（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1776</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">），抽出了《华严经》《大乘显识经》《入定不定印经》《方广大庄严经》《佛说契证大乘经》《大乘入楞伽经》等六部经前武则天撰写的序文。此次撤经文时，只有《华严经》前武则天序文的板被毁，其余五部经只抽出了武则天的序文，未毁经板。 </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">广西人文社会科学发展研究中心 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">清朝-初印本保存情况</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">乾隆三十二年（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1767</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">年） </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">潮州开元寺 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">静会和尚护送钦赐法宝归寺 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">开元寺藏乾隆版《大藏经》不仅是初印</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">103</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">部之一，更是乾隆年间三次撤板后存世的罕见完本。 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">乾隆三十二年（公元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1767</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">年）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">开元寺方丈静会老和尚以八十岁高龄，携师侄道昆 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨越200多年的守护与传承！潮州开元寺藏乾隆版《大藏经》从残卷到“新生”</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">它以明《永乐北藏》为底本，历时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">年雕刻完成，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">79036</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">块雕版收录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1667</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">部经典，总字数达</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">7600</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">万。每块版片双面刻字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">行，字体端庄规整，刀工细腻流畅。 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">公众号</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">潮州日报</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mp.weixin.qq.com/s?__biz=MzA3MDQyNzYzMQ==&amp;mid=2650896099&amp;idx=1&amp;sn=5e206cda95a2b42f84710c87f9e1a8b9&amp;chksm=85f8f7ac8edf80f601436d28734011e7713414efbfdcc77a2a6e62e00535a0bdabaea70e3bad&amp;scene=27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">时任开元寺方丈静会和尚请回 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">潮州开元寺乾隆版《大藏经》修复取得阶段性成果 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">乾隆版《大藏经》始刻于雍正十三年（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1735</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">年），竣工于乾隆三年（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1738</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">年），乾隆三十二年（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1767</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">年）由时任开元寺方丈静会和尚请回，共</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1667</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">卷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">7240</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">册，另有目录五卷，并有经橱、木函、令旗、和硕庄亲王手书“万德庄严”匾额及“钦赐宝藏”石碑等原件，是我国历代官刻大藏经中很重要的一部，具有很高的历史、文献和艺术价值。 </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">广东省文化和旅游厅 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://whly.gd.gov.cn/service_newwwbwg/content/post_4738424.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">光绪三十年</t>
-  </si>
-  <si>
-    <t xml:space="preserve">马来西亚槟城的极乐寺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妙莲老和尚入京申请的</t>
-  </si>
-  <si>
-    <t xml:space="preserve">除清雍正十一年至乾隆三年刻本之外，《清藏》其后虽有几次刷印，但经板迭有损毁，所以刷印出来的《乾隆大藏经》已经不是原来的模样了。迄今所知，保存完整的《乾隆大藏经》初刻本仅有四部：一部在日本龙谷大学图书馆，是清末慈禧太后寄赠日本西本愿寺的；一部在马来西亚槟城的极乐寺，是光绪三十年妙莲老和尚入京申请的；另外两部分别保存在中国香港和美国万佛城。 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">光绪年间</t>
-  </si>
-  <si>
-    <t xml:space="preserve">湖州道场山万寿寺藏经楼 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">光绪年间，法磬禅师赴京请藏，满载而归，不仅携龙藏归山，还获敕紫衣朝珠。 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">湖州佛教的宋韵迹忆（一）湖州道场山万寿寺 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">此《大藏经》为光绪三年之前的印本 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">公众号</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">湖州佛教</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mp.weixin.qq.com/s?__biz=MzAxNzE1NTQyMQ==&amp;mid=2652449729&amp;idx=1&amp;sn=d694e01e562d31e03fc36eca18025f45&amp;chksm=80045ff3b773d6e53f072c25255e32cfa4a2eceb25d98a8fe6d0abbb2c8e2f6e854aecef42dc&amp;scene=27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">清末</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日本龙谷大学图书馆</t>
-  </si>
-  <si>
-    <t xml:space="preserve">慈禧太后寄赠日本西本愿寺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中国香港和美国万佛城</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1990年</t>
-  </si>
-  <si>
-    <t xml:space="preserve">从南浔嘉业堂取回，御赐乾隆大藏经。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">百度知道顶级答主：誉祥祥知识 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">湖州万寿寺典故</t>
-  </si>
-  <si>
-    <t xml:space="preserve">百度知道</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://zhidao.baidu.com/question/444345690015218284.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1993年初</t>
-  </si>
-  <si>
-    <t xml:space="preserve">泰州光孝寺、扬州旌忠寺 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">全国政协副主席、中国佛教协会会长赵朴初</t>
-  </si>
-  <si>
-    <t xml:space="preserve">完整乾隆版《大藏经》国内“绝无仅有” </t>
-  </si>
-  <si>
-    <t xml:space="preserve">赵老称，像泰州光孝寺保存如此完好的，绝无仅有。 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 中国江苏网</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">北京白塔寺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">首都博物馆举办、白塔寺文保所承办的“佛典瑰宝”展 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">北京白塔寺可看“乾隆原版龙藏经” </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">此次在白塔寺展出的为清乾隆三年御制的《龙藏》，该书首次刊印于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1739</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">年，共印雕版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">79036</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">块，耗银</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">82000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">两，首次刊印了</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">部，每部计有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">724</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">函，收录佛教著作</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1625</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">种，连同目录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">7245</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">册，但目前存世完整的已所剩不多。 但白塔寺这部经已于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1753</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">年封于塔刹内，是惟一保存完整的大藏经原版本。 </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">新浪网转载自北京晨报</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://edu.sina.com.cn/wander/2000-09-25/12790.shtml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">沈阳慈恩寺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">辽宁省文旅厅、辽宁省图书馆、沈阳市委统战部等部门相关领导出席揭牌仪式。沈阳市佛教协会会长、慈恩寺方丈释盖忠致辞。沈阳文史馆馆员、著名学者初国卿介绍了沈阳慈恩寺藏明清藏经的详细情况。 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">沈阳慈恩寺举行全国古籍重点保护单位揭牌仪式</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">乾隆版大藏经七千一百六十七卷、永乐北藏六千三百六十一卷续藏四百十卷等</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">部古籍入选。 </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">央广网 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.cnr.cn/ln/ztgz/20231017/t20231017_526454148.shtml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">浙江图书馆南浔嘉业堂藏书楼 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">“佛典浙韵”浙图、径山寺两地开展！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">此次展出的《乾隆大藏经》保存于浙江图书馆南浔嘉业堂藏书楼，从经柜到藏经箱，均为原装旧匣。 </t>
-  </si>
-  <si>
     <t xml:space="preserve">民国</t>
   </si>
   <si>
@@ -25438,7 +24502,16 @@
     <t xml:space="preserve">泰州光孝寺</t>
   </si>
   <si>
+    <t xml:space="preserve">泰州光孝寺、扬州旌忠寺 </t>
+  </si>
+  <si>
     <t xml:space="preserve">藏经楼宣告落成， 终于补齐了《大藏经》</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 中国江苏网</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc</t>
   </si>
   <si>
     <r>
@@ -27275,357 +26348,6 @@
     <t xml:space="preserve">https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm</t>
   </si>
   <si>
-    <t xml:space="preserve">广西文科中心影印版</t>
-  </si>
-  <si>
-    <t xml:space="preserve">广化寺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中国佛教协会副会长宗性法师，广化寺监院广曙法师，北京什刹海书院秘书长吴安春，中国社科院世界宗教研究所研究员王志远，国家图书馆研究馆员李际宁，汉文大藏经研究院院长韩欣，善品堂创始人何德益先后在发布会上致辞 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">初版龙藏重光！全本《乾隆大藏经》宣纸线装版、精装版首发式在广化寺举行 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">中国佛教协会副会长宗性法师在发布会上首先对初版全本《乾隆大藏经》宣纸线装版、精装版的出版表示祝贺和肯定。他表示全本《乾隆大藏经》历经</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">年，在各方合力之下完成印制，是近年来唯一的全本再造，具有极高的文化学术意义，是文化界的一大盛事。 </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">凤凰新媒体 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://fo.ifeng.com/c/8OJFatCTn2p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">北京佛協駐地廣化寺 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">香港文匯報訊（記者 趙一存 北京報道 ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全本《乾隆大藏經》宣紙線裝版昨在京首發  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">日本龍谷大學圖書館藏的初刻初刷裝訂本為底本 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">香港文匯報 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.wenweipo.com/a/202303/20/AP64177312e4b0b6003c023241.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中原出版传媒集团中州古籍出版社 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">全本《乾隆大藏经》宣纸线装版、精装版在京首发 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1669</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">部，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">7168</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">卷，共用经版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">79036</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">块 </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">中新网北京3月21日电 (记者 应妮) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.chinanews.com/cul/2023/03-21/9975999.shtml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（互联网）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全本《乾隆大藏经》宣纸线装版在北京首发  </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">全本《乾隆大藏经》宣纸线装珍藏版，成书</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">137</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">函</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">808</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">册。为便于阅读和研究，新增《乾隆大藏经总目提要》</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">函</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF2A6099"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">册。 </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">公众号-印心剧场</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mp.weixin.qq.com/s?__biz=MzA5NDQ1NzczMg==&amp;mid=2650699887&amp;idx=2&amp;sn=5687de0a56d44d90e1b31d584ddcd276&amp;chksm=88448284bf330b9238786bb55a424ac08cf4f888a3a164007e13864bd63a571e4e8abf2e5df2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">广西人文社会科学发展研究中心汉文大藏经研究院院长韩欣带领团队历时十余年完成的重大成果 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">【中国新闻网】关注报道广西人文社会科学发展研究中心汉文大藏经研究院重大成果—初刻全本《乾隆大藏经》在京首发 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">采用简体横排的方式，所收佛经进行详细分段、加现代标点，采用现代排印、书册本与电子版配套的方式出版，使之更加符合现代人的阅读习惯 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">少林寺方丈释永信大和尚，广西人文社会科学发展研究中心汉文大藏经研究院院长韩欣先生，善品堂创始人兼董事长何德益先生，少林文化研究资深学者、出版家李阳泉先生，作曲家张鹤女士等，共同见证了此次全本《乾隆大藏经》线装版、精装版入藏少林寺仪式。 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">《乾隆大藏经》宣纸线装版、精装版入藏少林寺 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">百度-华网佛学</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://baijiahao.baidu.com/s?id=1762848641312271496&amp;wfr=spider&amp;for=pc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">其它版本</t>
-  </si>
-  <si>
-    <t xml:space="preserve">河北出版界佛学界</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中国人心中的另一个大敦煌――大藏经  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">河北出版界佛学界近年连续推出了中国学术界和佛学界急需的《乾隆大藏经》、《大正藏》和《蛀续编》，以一地之力，做了全国的社科宗教研究者、全国的佛学实践者渴盼多年的盛事。  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">中国中央电视台 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://discovery.cctv.com/20070619/107154.shtml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">广汉龙居寺 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">藏经楼内珍藏有台湾信徒陈正治、吴吉兴捐赠的‌全套《大藏经》‌ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">公众号-黄青微品汇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mp.weixin.qq.com/s?src=11&amp;timestamp=1790388857&amp;ver=6989&amp;signature=*HNoKq4itYlQyagEeQWbkil7hXCXxarkZmCAg6u-VDCyNcEy6Mxap65uQZkfZAZNmJcBN16**nBINk5WreKQjrygsQh89Sy-5watELrNzHVqr3Hdk25zaUt-gybJrKOx&amp;new=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2013年06月 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">非168册的版本。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">河北省佛教协会、东方出版社 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">乾隆大藏经（16开线装 全814函6516册） </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">当当</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">.com</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">https://product.dangdang.com/11534449004.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">文物出版社(二〇一六年十二月)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">乾隆大藏经原雕版刷印 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">单行本</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原雕版刷印，全部手工制作。限量三百部。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">孔夫子旧书网</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://book.kongfz.com/102740/682706591</t>
-  </si>
-  <si>
     <t xml:space="preserve">民族文化宫图书馆 </t>
   </si>
   <si>
@@ -28012,6 +26734,9 @@
   </si>
   <si>
     <t xml:space="preserve">页码是一样的。就是我的版本缺了两页—居然。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">孔夫子旧书网</t>
   </si>
   <si>
     <t xml:space="preserve">https://book.kongfz.com/536651/7839562954</t>
@@ -28678,6 +27403,1281 @@
     <t xml:space="preserve">《至元辨伪录》 </t>
   </si>
   <si>
+    <t xml:space="preserve">清朝-三次毁版</t>
+  </si>
+  <si>
+    <t xml:space="preserve">乾隆30/34/41年</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（三次撤经毁板事件）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">下旨 共撤毁了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">800</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">余块经版和其对应的近百卷典籍。在这些撤毁的经版中，包括了钱谦益的著作，武则天、明永乐皇帝等前朝帝王撰写的文章等 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">乾隆三十年间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1765</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1769</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1776</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">不久，《清藏》就发生了三次撤经毁板事件。第一次是乾隆三十年（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1765</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">），撤出钱谦益撰《楞严经疏解蒙钞》六十卷，毁经板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">660</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">块。第二次是乾隆三十四年（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1769</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">），撤出《开元释教录略出》《辩伪录》《明仁孝皇后梦感佛说第一稀有大功德经》《永乐皇帝御制赞文》四种共</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">卷，毁掉经板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">138</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">块。这时，全藏的实际数字是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">7168</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">册，经板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">8238</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">块。第三次是乾隆四十一年（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1776</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">），抽出了《华严经》《大乘显识经》《入定不定印经》《方广大庄严经》《佛说契证大乘经》《大乘入楞伽经》等六部经前武则天撰写的序文。此次撤经文时，只有《华严经》前武则天序文的板被毁，其余五部经只抽出了武则天的序文，未毁经板。 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">广西人文社会科学发展研究中心 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">清朝-初印本保存情况</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">乾隆三十二年（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1767</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年） </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">潮州开元寺 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">静会和尚护送钦赐法宝归寺 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">开元寺藏乾隆版《大藏经》不仅是初印</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">103</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">部之一，更是乾隆年间三次撤板后存世的罕见完本。 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">乾隆三十二年（公元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1767</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">开元寺方丈静会老和尚以八十岁高龄，携师侄道昆 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">跨越200多年的守护与传承！潮州开元寺藏乾隆版《大藏经》从残卷到“新生”</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">它以明《永乐北藏》为底本，历时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年雕刻完成，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">79036</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">块雕版收录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1667</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">部经典，总字数达</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">7600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">万。每块版片双面刻字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">行，字体端庄规整，刀工细腻流畅。 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">公众号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">潮州日报</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mp.weixin.qq.com/s?__biz=MzA3MDQyNzYzMQ==&amp;mid=2650896099&amp;idx=1&amp;sn=5e206cda95a2b42f84710c87f9e1a8b9&amp;chksm=85f8f7ac8edf80f601436d28734011e7713414efbfdcc77a2a6e62e00535a0bdabaea70e3bad&amp;scene=27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">时任开元寺方丈静会和尚请回 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">潮州开元寺乾隆版《大藏经》修复取得阶段性成果 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">乾隆版《大藏经》始刻于雍正十三年（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1735</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年），竣工于乾隆三年（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1738</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年），乾隆三十二年（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1767</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年）由时任开元寺方丈静会和尚请回，共</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1667</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">卷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">7240</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">册，另有目录五卷，并有经橱、木函、令旗、和硕庄亲王手书“万德庄严”匾额及“钦赐宝藏”石碑等原件，是我国历代官刻大藏经中很重要的一部，具有很高的历史、文献和艺术价值。 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">广东省文化和旅游厅 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://whly.gd.gov.cn/service_newwwbwg/content/post_4738424.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">光绪三十年</t>
+  </si>
+  <si>
+    <t xml:space="preserve">马来西亚槟城的极乐寺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妙莲老和尚入京申请的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">除清雍正十一年至乾隆三年刻本之外，《清藏》其后虽有几次刷印，但经板迭有损毁，所以刷印出来的《乾隆大藏经》已经不是原来的模样了。迄今所知，保存完整的《乾隆大藏经》初刻本仅有四部：一部在日本龙谷大学图书馆，是清末慈禧太后寄赠日本西本愿寺的；一部在马来西亚槟城的极乐寺，是光绪三十年妙莲老和尚入京申请的；另外两部分别保存在中国香港和美国万佛城。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">光绪年间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">湖州道场山万寿寺藏经楼 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">光绪年间，法磬禅师赴京请藏，满载而归，不仅携龙藏归山，还获敕紫衣朝珠。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">湖州佛教的宋韵迹忆（一）湖州道场山万寿寺 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">此《大藏经》为光绪三年之前的印本 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">公众号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">湖州佛教</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mp.weixin.qq.com/s?__biz=MzAxNzE1NTQyMQ==&amp;mid=2652449729&amp;idx=1&amp;sn=d694e01e562d31e03fc36eca18025f45&amp;chksm=80045ff3b773d6e53f072c25255e32cfa4a2eceb25d98a8fe6d0abbb2c8e2f6e854aecef42dc&amp;scene=27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">清末</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日本龙谷大学图书馆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">慈禧太后寄赠日本西本愿寺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中国香港和美国万佛城</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1990年</t>
+  </si>
+  <si>
+    <t xml:space="preserve">从南浔嘉业堂取回，御赐乾隆大藏经。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">百度知道顶级答主：誉祥祥知识 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">湖州万寿寺典故</t>
+  </si>
+  <si>
+    <t xml:space="preserve">百度知道</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://zhidao.baidu.com/question/444345690015218284.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1993年初</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全国政协副主席、中国佛教协会会长赵朴初</t>
+  </si>
+  <si>
+    <t xml:space="preserve">完整乾隆版《大藏经》国内“绝无仅有” </t>
+  </si>
+  <si>
+    <t xml:space="preserve">赵老称，像泰州光孝寺保存如此完好的，绝无仅有。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">北京白塔寺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">首都博物馆举办、白塔寺文保所承办的“佛典瑰宝”展 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">北京白塔寺可看“乾隆原版龙藏经” </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">此次在白塔寺展出的为清乾隆三年御制的《龙藏》，该书首次刊印于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1739</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年，共印雕版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">79036</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">块，耗银</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">82000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">两，首次刊印了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">部，每部计有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">724</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">函，收录佛教著作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1625</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">种，连同目录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">7245</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">册，但目前存世完整的已所剩不多。 但白塔寺这部经已于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1753</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年封于塔刹内，是惟一保存完整的大藏经原版本。 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">新浪网转载自北京晨报</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://edu.sina.com.cn/wander/2000-09-25/12790.shtml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">沈阳慈恩寺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">辽宁省文旅厅、辽宁省图书馆、沈阳市委统战部等部门相关领导出席揭牌仪式。沈阳市佛教协会会长、慈恩寺方丈释盖忠致辞。沈阳文史馆馆员、著名学者初国卿介绍了沈阳慈恩寺藏明清藏经的详细情况。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">沈阳慈恩寺举行全国古籍重点保护单位揭牌仪式</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">乾隆版大藏经七千一百六十七卷、永乐北藏六千三百六十一卷续藏四百十卷等</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">部古籍入选。 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">央广网 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cnr.cn/ln/ztgz/20231017/t20231017_526454148.shtml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">浙江图书馆南浔嘉业堂藏书楼 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">“佛典浙韵”浙图、径山寺两地开展！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">此次展出的《乾隆大藏经》保存于浙江图书馆南浔嘉业堂藏书楼，从经柜到藏经箱，均为原装旧匣。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">广西文科中心影印版</t>
+  </si>
+  <si>
+    <t xml:space="preserve">广化寺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中国佛教协会副会长宗性法师，广化寺监院广曙法师，北京什刹海书院秘书长吴安春，中国社科院世界宗教研究所研究员王志远，国家图书馆研究馆员李际宁，汉文大藏经研究院院长韩欣，善品堂创始人何德益先后在发布会上致辞 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">初版龙藏重光！全本《乾隆大藏经》宣纸线装版、精装版首发式在广化寺举行 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">中国佛教协会副会长宗性法师在发布会上首先对初版全本《乾隆大藏经》宣纸线装版、精装版的出版表示祝贺和肯定。他表示全本《乾隆大藏经》历经</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年，在各方合力之下完成印制，是近年来唯一的全本再造，具有极高的文化学术意义，是文化界的一大盛事。 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">凤凰新媒体 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fo.ifeng.com/c/8OJFatCTn2p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">北京佛協駐地廣化寺 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">香港文匯報訊（記者 趙一存 北京報道 ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全本《乾隆大藏經》宣紙線裝版昨在京首發  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">日本龍谷大學圖書館藏的初刻初刷裝訂本為底本 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">香港文匯報 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.wenweipo.com/a/202303/20/AP64177312e4b0b6003c023241.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中原出版传媒集团中州古籍出版社 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">全本《乾隆大藏经》宣纸线装版、精装版在京首发 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1669</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">部，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">7168</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">卷，共用经版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">79036</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">块 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">中新网北京3月21日电 (记者 应妮) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.chinanews.com/cul/2023/03-21/9975999.shtml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（互联网）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全本《乾隆大藏经》宣纸线装版在北京首发  </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">全本《乾隆大藏经》宣纸线装珍藏版，成书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">137</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">函</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">808</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">册。为便于阅读和研究，新增《乾隆大藏经总目提要》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">函</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF2A6099"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">册。 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">公众号-印心剧场</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mp.weixin.qq.com/s?__biz=MzA5NDQ1NzczMg==&amp;mid=2650699887&amp;idx=2&amp;sn=5687de0a56d44d90e1b31d584ddcd276&amp;chksm=88448284bf330b9238786bb55a424ac08cf4f888a3a164007e13864bd63a571e4e8abf2e5df2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">广西人文社会科学发展研究中心汉文大藏经研究院院长韩欣带领团队历时十余年完成的重大成果 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">【中国新闻网】关注报道广西人文社会科学发展研究中心汉文大藏经研究院重大成果—初刻全本《乾隆大藏经》在京首发 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">采用简体横排的方式，所收佛经进行详细分段、加现代标点，采用现代排印、书册本与电子版配套的方式出版，使之更加符合现代人的阅读习惯 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">少林寺方丈释永信大和尚，广西人文社会科学发展研究中心汉文大藏经研究院院长韩欣先生，善品堂创始人兼董事长何德益先生，少林文化研究资深学者、出版家李阳泉先生，作曲家张鹤女士等，共同见证了此次全本《乾隆大藏经》线装版、精装版入藏少林寺仪式。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">《乾隆大藏经》宣纸线装版、精装版入藏少林寺 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">百度-华网佛学</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://baijiahao.baidu.com/s?id=1762848641312271496&amp;wfr=spider&amp;for=pc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">其它版本</t>
+  </si>
+  <si>
+    <t xml:space="preserve">河北出版界佛学界</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中国人心中的另一个大敦煌――大藏经  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">河北出版界佛学界近年连续推出了中国学术界和佛学界急需的《乾隆大藏经》、《大正藏》和《蛀续编》，以一地之力，做了全国的社科宗教研究者、全国的佛学实践者渴盼多年的盛事。  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">中国中央电视台 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://discovery.cctv.com/20070619/107154.shtml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">广汉龙居寺 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">藏经楼内珍藏有台湾信徒陈正治、吴吉兴捐赠的‌全套《大藏经》‌ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">公众号-黄青微品汇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mp.weixin.qq.com/s?src=11&amp;timestamp=1790388857&amp;ver=6989&amp;signature=*HNoKq4itYlQyagEeQWbkil7hXCXxarkZmCAg6u-VDCyNcEy6Mxap65uQZkfZAZNmJcBN16**nBINk5WreKQjrygsQh89Sy-5watELrNzHVqr3Hdk25zaUt-gybJrKOx&amp;new=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013年06月 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">非168册的版本。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">河北省佛教协会、东方出版社 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">乾隆大藏经（16开线装 全814函6516册） </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">当当</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.com</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://product.dangdang.com/11534449004.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文物出版社(二〇一六年十二月)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">乾隆大藏经原雕版刷印 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">单行本</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原雕版刷印，全部手工制作。限量三百部。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://book.kongfz.com/102740/682706591</t>
+  </si>
+  <si>
     <t xml:space="preserve">此土注释</t>
   </si>
   <si>
@@ -28939,13 +28939,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF2A6099"/>
-      <name val="Noto Sans SC"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Segoe UI"/>
       <family val="2"/>
       <charset val="134"/>
@@ -28966,15 +28959,8 @@
     <font>
       <sz val="10"/>
       <color rgb="FF2A6099"/>
-      <name val="Segoe UI"/>
+      <name val="Noto Sans SC"/>
       <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF2A6099"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="134"/>
     </font>
     <font>
@@ -28996,6 +28982,20 @@
       <color rgb="FFFF4000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A6099"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A6099"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -29414,26 +29414,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29442,11 +29422,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -29454,11 +29438,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -29474,52 +29458,68 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -82561,7 +82561,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:AD186"/>
+  <dimension ref="A3:AD202"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.85"/>
@@ -82986,354 +82986,338 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E35" s="28"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
         <v>7543</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="44" t="s">
+      <c r="F36" s="28"/>
+    </row>
+    <row r="37" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="28" t="s">
         <v>7544</v>
       </c>
-      <c r="D37" s="44" t="s">
+      <c r="B37" s="28" t="s">
         <v>7545</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="F37" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="28" t="s">
         <v>7546</v>
       </c>
-      <c r="F37" s="45" t="s">
-        <v>7502</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>7503</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="44" t="s">
+      <c r="C38" s="28" t="s">
         <v>7547</v>
       </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="44" t="s">
-        <v>7545</v>
-      </c>
-      <c r="E38" s="44" t="s">
+      <c r="F38" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="28" t="s">
         <v>7548</v>
       </c>
-      <c r="F38" s="46" t="s">
+      <c r="D39" s="28" t="s">
         <v>7549</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="E39" s="28" t="s">
         <v>7550</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="F39" s="43" t="s">
+        <v>7537</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>7538</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="28" t="s">
         <v>7551</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="28" t="s">
+        <v>7552</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>7553</v>
+      </c>
+      <c r="E40" s="28"/>
+      <c r="F40" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>7552</v>
+        <v>7554</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>7553</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>7554</v>
-      </c>
-      <c r="D41" s="28" t="s">
-        <v>7529</v>
-      </c>
-      <c r="E41" s="28" t="s">
         <v>7555</v>
       </c>
-      <c r="F41" s="28" t="s">
-        <v>7530</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>7531</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
         <v>7556</v>
       </c>
-      <c r="B42" s="28" t="s">
-        <v>7553</v>
-      </c>
-      <c r="C42" s="28" t="s">
+      <c r="B42" s="44" t="s">
+        <v>7552</v>
+      </c>
+      <c r="C42" s="0" t="s">
         <v>7557</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>7558</v>
       </c>
-      <c r="E42" s="28" t="s">
+      <c r="E42" s="28"/>
+      <c r="F42" s="0" t="s">
         <v>7559</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="G42" s="2" t="s">
         <v>7560</v>
       </c>
-      <c r="G42" s="1" t="s">
+    </row>
+    <row r="43" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="28" t="s">
         <v>7561</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="28" t="s">
-        <v>7552</v>
-      </c>
-      <c r="B43" s="28" t="s">
-        <v>7553</v>
-      </c>
-      <c r="C43" s="28" t="s">
+      <c r="D43" s="28" t="s">
         <v>7562</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="28"/>
+      <c r="F43" s="28" t="s">
         <v>7563</v>
       </c>
-      <c r="E43" s="28" t="s">
+      <c r="G43" s="2" t="s">
         <v>7564</v>
       </c>
-      <c r="F43" s="28" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="43"/>
+    </row>
+    <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
         <v>7565</v>
       </c>
-      <c r="G43" s="2" t="s">
+    </row>
+    <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="43" t="s">
         <v>7566</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="47" t="s">
+      <c r="B46" s="28" t="s">
         <v>7567</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="F46" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="28" t="s">
         <v>7568</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="B47" s="28" t="s">
         <v>7569</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="C47" s="28" t="s">
         <v>7570</v>
       </c>
-      <c r="F44" s="28" t="s">
-        <v>7549</v>
-      </c>
-      <c r="G44" s="48" t="s">
-        <v>7550</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="47" t="s">
+      <c r="D47" s="1" t="s">
         <v>7571</v>
       </c>
-      <c r="B45" s="43" t="s">
+      <c r="E47" s="28" t="s">
         <v>7572</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="F47" s="43" t="s">
         <v>7573</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="G47" s="2" t="s">
         <v>7574</v>
       </c>
-      <c r="E45" s="28" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="28" t="s">
         <v>7575</v>
       </c>
-      <c r="F45" s="28" t="s">
+      <c r="B48" s="28" t="s">
         <v>7576</v>
       </c>
-      <c r="G45" s="48" t="s">
+      <c r="C48" s="28"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="28" t="s">
         <v>7577</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="F48" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="28" t="s">
         <v>7578</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B49" s="28" t="s">
         <v>7579</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C49" s="28"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="28" t="s">
+        <v>7578</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="0" t="s">
+        <v>7559</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>7560</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="45" t="s">
         <v>7580</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>7570</v>
-      </c>
-      <c r="F46" s="28" t="s">
-        <v>7549</v>
-      </c>
-      <c r="G46" s="48" t="s">
-        <v>7550</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="1" t="s">
+      <c r="B51" s="28" t="s">
         <v>7581</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>7570</v>
-      </c>
-      <c r="F47" s="28" t="s">
-        <v>7549</v>
-      </c>
-      <c r="G47" s="48" t="s">
-        <v>7550</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="C51" s="28" t="s">
         <v>7582</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="D51" s="43"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="43" t="s">
+        <v>7496</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="45" t="s">
+        <v>7580</v>
+      </c>
+      <c r="B52" s="28" t="s">
         <v>7583</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C52" s="28" t="s">
         <v>7584</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D52" s="43"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="45" t="s">
         <v>7585</v>
       </c>
-      <c r="F48" s="28" t="s">
+      <c r="B53" s="28" t="s">
         <v>7586</v>
       </c>
-      <c r="G48" s="48" t="s">
+      <c r="C53" s="28"/>
+      <c r="D53" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="45"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="28" t="s">
         <v>7587</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="C55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="45" t="s">
         <v>7588</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B56" s="46" t="s">
         <v>7589</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C56" s="45" t="s">
         <v>7590</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D56" s="1" t="s">
+        <v>7558</v>
+      </c>
+      <c r="E56" s="28"/>
+      <c r="F56" s="0" t="s">
+        <v>7559</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>7560</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="45" t="s">
+        <v>7588</v>
+      </c>
+      <c r="B57" s="28" t="s">
         <v>7591</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="C57" s="28" t="s">
         <v>7592</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="E57" s="28" t="s">
         <v>7593</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>7594</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="47" t="n">
-        <v>36795</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7595</v>
-      </c>
-      <c r="C50" s="28" t="s">
-        <v>7596</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>7597</v>
-      </c>
-      <c r="E50" s="28" t="s">
-        <v>7598</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>7599</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>7600</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="47" t="n">
-        <v>45216</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7601</v>
-      </c>
-      <c r="C51" s="28" t="s">
-        <v>7602</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>7603</v>
-      </c>
-      <c r="E51" s="28" t="s">
-        <v>7604</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>7605</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>7606</v>
-      </c>
-    </row>
-    <row r="52" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="47" t="n">
-        <v>45458</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7607</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>7608</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>7468</v>
-      </c>
-      <c r="E52" s="28" t="s">
-        <v>7609</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>7470</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>7471</v>
-      </c>
-    </row>
-    <row r="54" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E54" s="28"/>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="28" t="s">
-        <v>7610</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="F55" s="28"/>
-    </row>
-    <row r="56" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="28" t="s">
-        <v>7611</v>
-      </c>
-      <c r="B56" s="28" t="s">
-        <v>7612</v>
-      </c>
-      <c r="F56" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="28" t="s">
-        <v>7613</v>
-      </c>
-      <c r="C57" s="28" t="s">
-        <v>7614</v>
       </c>
       <c r="F57" s="43" t="s">
         <v>7496</v>
@@ -83342,202 +83326,262 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="28" t="s">
+    <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="45" t="s">
+        <v>7594</v>
+      </c>
+      <c r="B58" s="28" t="s">
+        <v>7595</v>
+      </c>
+      <c r="C58" s="28"/>
+      <c r="D58" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="28" t="s">
+        <v>7596</v>
+      </c>
+      <c r="B59" s="28" t="s">
+        <v>7597</v>
+      </c>
+      <c r="C59" s="28"/>
+      <c r="E59" s="43" t="s">
+        <v>7598</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>7599</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="47" t="n">
+        <v>32140</v>
+      </c>
+      <c r="B60" s="43" t="s">
+        <v>7600</v>
+      </c>
+      <c r="C60" s="48" t="s">
+        <v>7601</v>
+      </c>
+      <c r="E60" s="43"/>
+      <c r="F60" s="28" t="s">
+        <v>7602</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>7603</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="47" t="n">
+        <v>32140</v>
+      </c>
+      <c r="B61" s="43" t="s">
+        <v>7600</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>7604</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>7605</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>7606</v>
+      </c>
+      <c r="F61" s="43" t="s">
+        <v>7607</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>7608</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="47" t="s">
+        <v>7609</v>
+      </c>
+      <c r="B62" s="28" t="s">
+        <v>7610</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>7611</v>
+      </c>
+      <c r="E62" s="49" t="s">
+        <v>7612</v>
+      </c>
+      <c r="F62" s="43" t="s">
+        <v>7537</v>
+      </c>
+      <c r="G62" s="50" t="s">
+        <v>7613</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="47" t="s">
+        <v>7614</v>
+      </c>
+      <c r="B63" s="28" t="s">
+        <v>7597</v>
+      </c>
+      <c r="C63" s="28" t="s">
         <v>7615</v>
       </c>
-      <c r="D58" s="28" t="s">
+      <c r="D63" s="43" t="s">
         <v>7616</v>
       </c>
-      <c r="E58" s="28" t="s">
+      <c r="E63" s="28" t="s">
         <v>7617</v>
       </c>
-      <c r="F58" s="43" t="s">
-        <v>7537</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>7538</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="28" t="s">
+      <c r="F63" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="48" t="s">
         <v>7618</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="D64" s="0" t="s">
         <v>7619</v>
       </c>
-      <c r="D59" s="28" t="s">
+      <c r="E64" s="46" t="s">
         <v>7620</v>
       </c>
-      <c r="E59" s="28"/>
-      <c r="F59" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="28" t="s">
+      <c r="F64" s="46" t="s">
         <v>7621</v>
       </c>
-      <c r="B60" s="28" t="s">
+      <c r="G64" s="2" t="s">
         <v>7622</v>
       </c>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="28" t="s">
+    </row>
+    <row r="65" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>7623</v>
       </c>
-      <c r="B61" s="49" t="s">
-        <v>7619</v>
-      </c>
-      <c r="C61" s="0" t="s">
+      <c r="C65" s="28" t="s">
         <v>7624</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D65" s="28" t="s">
         <v>7625</v>
       </c>
-      <c r="E61" s="28"/>
-      <c r="F61" s="0" t="s">
+      <c r="E65" s="49"/>
+      <c r="F65" s="43" t="s">
+        <v>7573</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>7574</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B66" s="28" t="s">
         <v>7626</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="C66" s="28" t="s">
         <v>7627</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="28" t="s">
+      <c r="D66" s="28" t="s">
         <v>7628</v>
       </c>
-      <c r="D62" s="28" t="s">
+      <c r="E66" s="28"/>
+      <c r="F66" s="1" t="s">
         <v>7629</v>
       </c>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28" t="s">
+      <c r="G66" s="2" t="s">
         <v>7630</v>
       </c>
-      <c r="G62" s="2" t="s">
+    </row>
+    <row r="67" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B67" s="28" t="s">
         <v>7631</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="43"/>
-    </row>
-    <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="C67" s="28" t="s">
         <v>7632</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="43" t="s">
+      <c r="D67" s="1" t="s">
         <v>7633</v>
       </c>
-      <c r="B65" s="28" t="s">
+      <c r="E67" s="28"/>
+      <c r="F67" s="28" t="s">
+        <v>7607</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>7634</v>
       </c>
-      <c r="F65" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="28" t="s">
+    </row>
+    <row r="68" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B68" s="28" t="s">
+        <v>7631</v>
+      </c>
+      <c r="C68" s="28" t="s">
         <v>7635</v>
       </c>
-      <c r="B66" s="28" t="s">
+      <c r="D68" s="1" t="s">
+        <v>7633</v>
+      </c>
+      <c r="E68" s="28" t="s">
         <v>7636</v>
       </c>
-      <c r="C66" s="28" t="s">
+      <c r="F68" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="47" t="n">
+        <v>32517</v>
+      </c>
+      <c r="B69" s="28" t="s">
         <v>7637</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="C69" s="28" t="s">
         <v>7638</v>
       </c>
-      <c r="E66" s="28" t="s">
+      <c r="D69" s="28" t="s">
         <v>7639</v>
       </c>
-      <c r="F66" s="43" t="s">
+      <c r="E69" s="28"/>
+      <c r="F69" s="1" t="s">
         <v>7640</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G69" s="2" t="s">
         <v>7641</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="28" t="s">
+    <row r="70" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="47"/>
+      <c r="B70" s="28" t="s">
         <v>7642</v>
       </c>
-      <c r="B67" s="28" t="s">
-        <v>7643</v>
-      </c>
-      <c r="C67" s="28"/>
-      <c r="D67" s="43"/>
-      <c r="E67" s="28" t="s">
-        <v>7644</v>
-      </c>
-      <c r="F67" s="28" t="s">
-        <v>7521</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="28" t="s">
-        <v>7645</v>
-      </c>
-      <c r="B68" s="28" t="s">
-        <v>7646</v>
-      </c>
-      <c r="C68" s="28"/>
-      <c r="D68" s="43"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="28" t="s">
-        <v>7645</v>
-      </c>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="43"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="0" t="s">
-        <v>7626</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>7627</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="50" t="s">
-        <v>7647</v>
-      </c>
-      <c r="B70" s="28" t="s">
-        <v>7648</v>
-      </c>
-      <c r="C70" s="28" t="s">
-        <v>7649</v>
-      </c>
-      <c r="D70" s="43"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
       <c r="E70" s="28"/>
       <c r="F70" s="43" t="s">
         <v>7496</v>
@@ -83546,94 +83590,122 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="50" t="s">
-        <v>7647</v>
+    <row r="71" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="47" t="s">
+        <v>7643</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>7650</v>
+        <v>7644</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>7651</v>
-      </c>
-      <c r="D71" s="43"/>
+        <v>7645</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>7515</v>
+      </c>
       <c r="E71" s="28"/>
       <c r="F71" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="47" t="s">
+        <v>7646</v>
+      </c>
+      <c r="B72" s="28" t="s">
+        <v>7597</v>
+      </c>
+      <c r="C72" s="28"/>
+      <c r="D72" s="43" t="s">
+        <v>7616</v>
+      </c>
+      <c r="E72" s="28" t="s">
+        <v>7647</v>
+      </c>
+      <c r="F72" s="28" t="s">
         <v>7521</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G72" s="2" t="s">
         <v>7522</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="50" t="s">
+    <row r="73" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="47" t="s">
+        <v>7648</v>
+      </c>
+      <c r="B73" s="28" t="s">
+        <v>7649</v>
+      </c>
+      <c r="C73" s="28"/>
+      <c r="D73" s="43" t="s">
+        <v>7616</v>
+      </c>
+      <c r="E73" s="28" t="s">
+        <v>7650</v>
+      </c>
+      <c r="F73" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="47" t="s">
+        <v>7651</v>
+      </c>
+      <c r="B74" s="28" t="s">
         <v>7652</v>
       </c>
-      <c r="B72" s="28" t="s">
+      <c r="C74" s="28" t="s">
         <v>7653</v>
       </c>
-      <c r="C72" s="28"/>
-      <c r="D72" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="50"/>
-      <c r="B73" s="28"/>
-      <c r="C73" s="28"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="2"/>
-    </row>
-    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="28" t="s">
+      <c r="D74" s="43" t="s">
+        <v>7616</v>
+      </c>
+      <c r="E74" s="28" t="s">
         <v>7654</v>
       </c>
-      <c r="C74" s="28"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="28"/>
-      <c r="G74" s="2"/>
-    </row>
-    <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="50" t="s">
+      <c r="F74" s="28" t="s">
+        <v>7521</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>7522</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="43" t="s">
         <v>7655</v>
       </c>
-      <c r="B75" s="51" t="s">
+      <c r="B75" s="0"/>
+      <c r="C75" s="28" t="s">
         <v>7656</v>
       </c>
-      <c r="C75" s="50" t="s">
+      <c r="D75" s="43" t="s">
         <v>7657</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>7625</v>
-      </c>
-      <c r="E75" s="28"/>
-      <c r="F75" s="0" t="s">
-        <v>7626</v>
+      <c r="E75" s="28" t="s">
+        <v>7658</v>
+      </c>
+      <c r="F75" s="51" t="s">
+        <v>7659</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>7627</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="50" t="s">
-        <v>7655</v>
-      </c>
-      <c r="B76" s="28" t="s">
-        <v>7658</v>
+        <v>7660</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="45" t="s">
+        <v>7661</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>7662</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>7659</v>
-      </c>
-      <c r="E76" s="28" t="s">
-        <v>7660</v>
+        <v>7663</v>
       </c>
       <c r="F76" s="43" t="s">
         <v>7496</v>
@@ -83642,175 +83714,154 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="50" t="s">
-        <v>7661</v>
-      </c>
-      <c r="B77" s="28" t="s">
-        <v>7662</v>
-      </c>
-      <c r="C77" s="28"/>
-      <c r="D77" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E77" s="28"/>
-      <c r="F77" s="28" t="s">
-        <v>7516</v>
+    <row r="77" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="45" t="s">
+        <v>7664</v>
+      </c>
+      <c r="B77" s="46" t="s">
+        <v>7665</v>
+      </c>
+      <c r="C77" s="48" t="s">
+        <v>7666</v>
+      </c>
+      <c r="D77" s="0"/>
+      <c r="F77" s="43" t="s">
+        <v>7496</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="28" t="s">
-        <v>7663</v>
-      </c>
-      <c r="B78" s="28" t="s">
-        <v>7664</v>
-      </c>
-      <c r="C78" s="28"/>
-      <c r="E78" s="43" t="s">
-        <v>7665</v>
-      </c>
-      <c r="F78" s="0" t="s">
-        <v>7666</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="47" t="n">
-        <v>32140</v>
-      </c>
-      <c r="B79" s="43" t="s">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="45"/>
+    </row>
+    <row r="79" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="43" t="s">
         <v>7667</v>
       </c>
-      <c r="C79" s="52" t="s">
+      <c r="B79" s="28"/>
+      <c r="D79" s="43"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="51"/>
+      <c r="G79" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="47" t="n">
+        <v>38164</v>
+      </c>
+      <c r="B80" s="43" t="s">
         <v>7668</v>
       </c>
-      <c r="E79" s="43"/>
-      <c r="F79" s="28" t="s">
+      <c r="C80" s="1" t="s">
         <v>7669</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="D80" s="28" t="s">
         <v>7670</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="47" t="n">
-        <v>32140</v>
-      </c>
-      <c r="B80" s="43" t="s">
-        <v>7667</v>
-      </c>
-      <c r="C80" s="28" t="s">
+      <c r="E80" s="28" t="s">
         <v>7671</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="F80" s="28" t="s">
         <v>7672</v>
       </c>
-      <c r="E80" s="28" t="s">
+      <c r="G80" s="2" t="s">
         <v>7673</v>
       </c>
-      <c r="F80" s="43" t="s">
+    </row>
+    <row r="81" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="47" t="s">
         <v>7674</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="B81" s="52" t="s">
         <v>7675</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="47" t="s">
+      <c r="C81" s="52" t="s">
         <v>7676</v>
       </c>
-      <c r="B81" s="28" t="s">
+      <c r="D81" s="1" t="s">
         <v>7677</v>
       </c>
-      <c r="D81" s="28" t="s">
+      <c r="E81" s="45" t="s">
         <v>7678</v>
       </c>
-      <c r="E81" s="53" t="s">
+      <c r="F81" s="28" t="s">
         <v>7679</v>
       </c>
-      <c r="F81" s="43" t="s">
-        <v>7537</v>
-      </c>
-      <c r="G81" s="54" t="s">
+      <c r="G81" s="1" t="s">
         <v>7680</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="47" t="s">
         <v>7681</v>
       </c>
-      <c r="B82" s="28" t="s">
-        <v>7664</v>
+      <c r="B82" s="43" t="s">
+        <v>7682</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>7682</v>
+        <v>7683</v>
       </c>
       <c r="D82" s="43" t="s">
-        <v>7683</v>
-      </c>
-      <c r="E82" s="28" t="s">
         <v>7684</v>
       </c>
-      <c r="F82" s="28" t="s">
-        <v>7521</v>
+      <c r="E82" s="43"/>
+      <c r="F82" s="43" t="s">
+        <v>7502</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="47" t="n">
-        <v>32471</v>
-      </c>
-      <c r="B83" s="28"/>
-      <c r="C83" s="52" t="s">
+        <v>7503</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="47" t="s">
+        <v>7681</v>
+      </c>
+      <c r="B83" s="28" t="s">
         <v>7685</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="C83" s="28" t="s">
         <v>7686</v>
       </c>
-      <c r="E83" s="51" t="s">
+      <c r="D83" s="28" t="s">
         <v>7687</v>
       </c>
-      <c r="F83" s="51" t="s">
+      <c r="E83" s="28" t="s">
         <v>7688</v>
       </c>
+      <c r="F83" s="1" t="s">
+        <v>7689</v>
+      </c>
       <c r="G83" s="2" t="s">
+        <v>7690</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="47" t="s">
+        <v>7691</v>
+      </c>
+      <c r="B84" s="28" t="s">
+        <v>7685</v>
+      </c>
+      <c r="C84" s="28" t="s">
+        <v>7692</v>
+      </c>
+      <c r="D84" s="28" t="s">
+        <v>7693</v>
+      </c>
+      <c r="E84" s="28"/>
+      <c r="F84" s="1" t="s">
         <v>7689</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="47" t="n">
-        <v>32471</v>
-      </c>
-      <c r="B84" s="1" t="s">
+      <c r="G84" s="2" t="s">
         <v>7690</v>
       </c>
-      <c r="C84" s="28" t="s">
-        <v>7691</v>
-      </c>
-      <c r="D84" s="28" t="s">
-        <v>7692</v>
-      </c>
-      <c r="E84" s="53"/>
-      <c r="F84" s="43" t="s">
-        <v>7640</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>7641</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="85" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="47" t="n">
-        <v>32471</v>
+        <v>42230</v>
       </c>
       <c r="B85" s="28" t="s">
-        <v>7693</v>
+        <v>7685</v>
       </c>
       <c r="C85" s="28" t="s">
         <v>7694</v>
@@ -83818,1734 +83869,1787 @@
       <c r="D85" s="28" t="s">
         <v>7695</v>
       </c>
-      <c r="E85" s="28"/>
+      <c r="E85" s="28" t="s">
+        <v>7696</v>
+      </c>
       <c r="F85" s="1" t="s">
-        <v>7696</v>
+        <v>7689</v>
       </c>
       <c r="G85" s="2" t="s">
+        <v>7690</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="87" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="43" t="s">
         <v>7697</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="47" t="n">
-        <v>32471</v>
-      </c>
-      <c r="B86" s="28" t="s">
+    <row r="88" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="47" t="n">
+        <v>42753</v>
+      </c>
+      <c r="B88" s="52" t="s">
         <v>7698</v>
       </c>
-      <c r="C86" s="28" t="s">
+      <c r="C88" s="43" t="s">
         <v>7699</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D88" s="43" t="s">
         <v>7700</v>
       </c>
-      <c r="E86" s="28"/>
-      <c r="F86" s="28" t="s">
-        <v>7674</v>
-      </c>
-      <c r="G86" s="2" t="s">
+      <c r="E88" s="43" t="s">
         <v>7701</v>
       </c>
-    </row>
-    <row r="87" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="47" t="n">
-        <v>32471</v>
-      </c>
-      <c r="B87" s="28" t="s">
-        <v>7698</v>
-      </c>
-      <c r="C87" s="28" t="s">
+      <c r="F88" s="43" t="s">
+        <v>7502</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>7503</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="47" t="n">
+        <v>42753</v>
+      </c>
+      <c r="B89" s="52" t="s">
         <v>7702</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="C89" s="28" t="s">
+        <v>7703</v>
+      </c>
+      <c r="D89" s="43" t="s">
         <v>7700</v>
       </c>
-      <c r="E87" s="28" t="s">
-        <v>7703</v>
-      </c>
-      <c r="F87" s="28" t="s">
-        <v>7521</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="47" t="n">
-        <v>32517</v>
-      </c>
-      <c r="B88" s="28" t="s">
+      <c r="E89" s="53" t="s">
         <v>7704</v>
       </c>
-      <c r="C88" s="28" t="s">
-        <v>7589</v>
-      </c>
-      <c r="D88" s="28" t="s">
+      <c r="F89" s="43" t="s">
+        <v>7502</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>7503</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="47" t="n">
+        <v>42753</v>
+      </c>
+      <c r="B90" s="52" t="s">
+        <v>7702</v>
+      </c>
+      <c r="C90" s="52" t="s">
         <v>7705</v>
       </c>
-      <c r="E88" s="28"/>
-      <c r="F88" s="1" t="s">
-        <v>7593</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>7594</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="47"/>
-      <c r="B89" s="28" t="s">
+      <c r="D90" s="1" t="s">
         <v>7706</v>
       </c>
-      <c r="C89" s="28"/>
-      <c r="D89" s="28"/>
-      <c r="E89" s="28"/>
-      <c r="F89" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="47" t="s">
+      <c r="E90" s="43" t="s">
         <v>7707</v>
       </c>
-      <c r="B90" s="28" t="s">
+      <c r="F90" s="1" t="s">
         <v>7708</v>
       </c>
-      <c r="C90" s="28" t="s">
+      <c r="G90" s="2" t="s">
         <v>7709</v>
       </c>
-      <c r="D90" s="1" t="s">
+    </row>
+    <row r="91" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="47" t="n">
+        <v>43725</v>
+      </c>
+      <c r="B91" s="28" t="s">
+        <v>7710</v>
+      </c>
+      <c r="C91" s="28" t="s">
+        <v>7711</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>7712</v>
+      </c>
+      <c r="E91" s="28" t="s">
+        <v>7713</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>7714</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>7715</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="47" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B92" s="28" t="s">
+        <v>7716</v>
+      </c>
+      <c r="C92" s="28" t="s">
+        <v>7717</v>
+      </c>
+      <c r="D92" s="43" t="s">
+        <v>7718</v>
+      </c>
+      <c r="E92" s="28" t="s">
+        <v>7719</v>
+      </c>
+      <c r="F92" s="28" t="s">
+        <v>7720</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>7721</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="47" t="n">
+        <v>45449</v>
+      </c>
+      <c r="B93" s="28" t="s">
+        <v>7722</v>
+      </c>
+      <c r="C93" s="28" t="s">
+        <v>7723</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>7724</v>
+      </c>
+      <c r="E93" s="28" t="s">
+        <v>7725</v>
+      </c>
+      <c r="F93" s="28" t="s">
+        <v>7726</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>7727</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="47" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B94" s="28" t="s">
+        <v>7728</v>
+      </c>
+      <c r="C94" s="28" t="s">
+        <v>7729</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>7730</v>
+      </c>
+      <c r="E94" s="28" t="s">
+        <v>7731</v>
+      </c>
+      <c r="F94" s="28" t="s">
+        <v>7732</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>7733</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="47"/>
+      <c r="B95" s="28" t="s">
+        <v>7734</v>
+      </c>
+      <c r="C95" s="43" t="s">
+        <v>7735</v>
+      </c>
+      <c r="E95" s="28"/>
+      <c r="F95" s="28"/>
+    </row>
+    <row r="96" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="47" t="n">
+        <v>41741</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7736</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>7737</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="47"/>
+      <c r="B100" s="28"/>
+      <c r="C100" s="28"/>
+      <c r="E100" s="28"/>
+      <c r="F100" s="28"/>
+      <c r="G100" s="2"/>
+    </row>
+    <row r="101" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="43" t="s">
+        <v>7738</v>
+      </c>
+      <c r="B101" s="28"/>
+      <c r="C101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="54" t="s">
+        <v>7739</v>
+      </c>
+      <c r="B102" s="43" t="s">
+        <v>7740</v>
+      </c>
+      <c r="C102" s="28" t="s">
+        <v>7741</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>7515</v>
       </c>
-      <c r="E90" s="28"/>
-      <c r="F90" s="28" t="s">
+      <c r="E102" s="28" t="s">
+        <v>7658</v>
+      </c>
+      <c r="F102" s="28" t="s">
         <v>7516</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G102" s="2" t="s">
         <v>7517</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="47" t="s">
-        <v>7710</v>
-      </c>
-      <c r="B91" s="28" t="s">
-        <v>7664</v>
-      </c>
-      <c r="C91" s="28"/>
-      <c r="D91" s="43" t="s">
-        <v>7683</v>
-      </c>
-      <c r="E91" s="28" t="s">
-        <v>7711</v>
-      </c>
-      <c r="F91" s="28" t="s">
-        <v>7521</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="47" t="s">
-        <v>7712</v>
-      </c>
-      <c r="B92" s="28" t="s">
-        <v>7713</v>
-      </c>
-      <c r="C92" s="28"/>
-      <c r="D92" s="43" t="s">
-        <v>7683</v>
-      </c>
-      <c r="E92" s="28" t="s">
-        <v>7714</v>
-      </c>
-      <c r="F92" s="28" t="s">
-        <v>7521</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="47" t="s">
-        <v>7715</v>
-      </c>
-      <c r="B93" s="28" t="s">
-        <v>7716</v>
-      </c>
-      <c r="C93" s="28" t="s">
-        <v>7717</v>
-      </c>
-      <c r="D93" s="43" t="s">
-        <v>7683</v>
-      </c>
-      <c r="E93" s="28" t="s">
-        <v>7718</v>
-      </c>
-      <c r="F93" s="28" t="s">
-        <v>7521</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="43" t="s">
-        <v>7719</v>
-      </c>
-      <c r="B94" s="0"/>
-      <c r="C94" s="28" t="s">
-        <v>7720</v>
-      </c>
-      <c r="D94" s="43" t="s">
-        <v>7721</v>
-      </c>
-      <c r="E94" s="28" t="s">
-        <v>7722</v>
-      </c>
-      <c r="F94" s="55" t="s">
-        <v>7723</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>7724</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="50" t="s">
-        <v>7725</v>
-      </c>
-      <c r="B95" s="0" t="s">
-        <v>7726</v>
-      </c>
-      <c r="C95" s="28" t="s">
-        <v>7727</v>
-      </c>
-      <c r="F95" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="50" t="s">
-        <v>7728</v>
-      </c>
-      <c r="B96" s="51" t="s">
-        <v>7729</v>
-      </c>
-      <c r="C96" s="52" t="s">
-        <v>7730</v>
-      </c>
-      <c r="D96" s="0"/>
-      <c r="F96" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="50"/>
-    </row>
-    <row r="98" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="43" t="s">
-        <v>7731</v>
-      </c>
-      <c r="B98" s="28"/>
-      <c r="D98" s="43"/>
-      <c r="E98" s="28"/>
-      <c r="F98" s="55"/>
-      <c r="G98" s="2"/>
-    </row>
-    <row r="99" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="47" t="n">
-        <v>38164</v>
-      </c>
-      <c r="B99" s="43" t="s">
-        <v>7732</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>7733</v>
-      </c>
-      <c r="D99" s="28" t="s">
-        <v>7734</v>
-      </c>
-      <c r="E99" s="28" t="s">
-        <v>7735</v>
-      </c>
-      <c r="F99" s="28" t="s">
-        <v>7736</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>7737</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="47" t="s">
-        <v>7738</v>
-      </c>
-      <c r="B100" s="56" t="s">
-        <v>7739</v>
-      </c>
-      <c r="C100" s="56" t="s">
-        <v>7740</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>7741</v>
-      </c>
-      <c r="E100" s="50" t="s">
+    <row r="103" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="54" t="s">
         <v>7742</v>
       </c>
-      <c r="F100" s="28" t="s">
+      <c r="B103" s="43" t="s">
         <v>7743</v>
       </c>
-      <c r="G100" s="1" t="s">
+      <c r="C103" s="28" t="s">
         <v>7744</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="47" t="s">
+      <c r="D103" s="1" t="s">
         <v>7745</v>
       </c>
-      <c r="B101" s="43" t="s">
+      <c r="F103" s="51" t="s">
+        <v>7659</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>7660</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="45" t="s">
         <v>7746</v>
       </c>
-      <c r="C101" s="28" t="s">
+      <c r="B104" s="52" t="s">
         <v>7747</v>
       </c>
-      <c r="D101" s="43" t="s">
+      <c r="C104" s="28" t="s">
         <v>7748</v>
       </c>
-      <c r="E101" s="43"/>
-      <c r="F101" s="43" t="s">
-        <v>7502</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>7503</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="47" t="s">
+      <c r="D104" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="F104" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="54" t="s">
+        <v>7749</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>7750</v>
+      </c>
+      <c r="C105" s="28" t="s">
+        <v>7751</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>7515</v>
+      </c>
+      <c r="E105" s="28" t="s">
+        <v>7752</v>
+      </c>
+      <c r="F105" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="54" t="s">
+        <v>7753</v>
+      </c>
+      <c r="B106" s="28" t="s">
+        <v>7754</v>
+      </c>
+      <c r="C106" s="28" t="s">
+        <v>7755</v>
+      </c>
+      <c r="E106" s="28"/>
+      <c r="F106" s="28" t="s">
+        <v>7516</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>7517</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="54" t="s">
+        <v>7756</v>
+      </c>
+      <c r="B107" s="28" t="s">
+        <v>7757</v>
+      </c>
+      <c r="C107" s="28" t="s">
+        <v>7758</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>7745</v>
       </c>
-      <c r="B102" s="28" t="s">
-        <v>7749</v>
-      </c>
-      <c r="C102" s="28" t="s">
-        <v>7750</v>
-      </c>
-      <c r="D102" s="28" t="s">
-        <v>7751</v>
-      </c>
-      <c r="E102" s="28" t="s">
-        <v>7752</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>7753</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>7754</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="47" t="s">
-        <v>7755</v>
-      </c>
-      <c r="B103" s="28" t="s">
-        <v>7749</v>
-      </c>
-      <c r="C103" s="28" t="s">
-        <v>7756</v>
-      </c>
-      <c r="D103" s="28" t="s">
-        <v>7757</v>
-      </c>
-      <c r="E103" s="28"/>
-      <c r="F103" s="1" t="s">
-        <v>7753</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>7754</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="47" t="n">
-        <v>42230</v>
-      </c>
-      <c r="B104" s="28" t="s">
-        <v>7749</v>
-      </c>
-      <c r="C104" s="28" t="s">
-        <v>7758</v>
-      </c>
-      <c r="D104" s="28" t="s">
+      <c r="E107" s="1" t="s">
         <v>7759</v>
       </c>
-      <c r="E104" s="28" t="s">
+      <c r="F107" s="51" t="s">
+        <v>7659</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>7660</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="47" t="n">
+        <v>44662</v>
+      </c>
+      <c r="B108" s="28" t="s">
         <v>7760</v>
       </c>
-      <c r="F104" s="1" t="s">
-        <v>7753</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>7754</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="106" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="43" t="s">
+      <c r="C108" s="1" t="s">
         <v>7761</v>
       </c>
-    </row>
-    <row r="107" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="47" t="n">
-        <v>42753</v>
-      </c>
-      <c r="B107" s="56" t="s">
+      <c r="D108" s="28" t="s">
         <v>7762</v>
       </c>
-      <c r="C107" s="43" t="s">
+      <c r="E108" s="28" t="s">
         <v>7763</v>
       </c>
-      <c r="D107" s="43" t="s">
+      <c r="F108" s="1" t="s">
         <v>7764</v>
       </c>
-      <c r="E107" s="43" t="s">
+      <c r="G108" s="1" t="s">
         <v>7765</v>
       </c>
-      <c r="F107" s="43" t="s">
-        <v>7502</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>7503</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="47" t="n">
-        <v>42753</v>
-      </c>
-      <c r="B108" s="56" t="s">
+    </row>
+    <row r="109" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="54" t="s">
         <v>7766</v>
       </c>
-      <c r="C108" s="28" t="s">
+      <c r="B109" s="28" t="s">
         <v>7767</v>
       </c>
-      <c r="D108" s="43" t="s">
-        <v>7764</v>
-      </c>
-      <c r="E108" s="57" t="s">
+      <c r="C109" s="28"/>
+      <c r="D109" s="1" t="s">
+        <v>7745</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>7768</v>
       </c>
-      <c r="F108" s="43" t="s">
-        <v>7502</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>7503</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="47" t="n">
-        <v>42753</v>
-      </c>
-      <c r="B109" s="56" t="s">
-        <v>7766</v>
-      </c>
-      <c r="C109" s="56" t="s">
-        <v>7769</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>7770</v>
-      </c>
-      <c r="E109" s="43" t="s">
-        <v>7771</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>7772</v>
+      <c r="F109" s="51" t="s">
+        <v>7659</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>7773</v>
+        <v>7660</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="47" t="n">
-        <v>43725</v>
+        <v>44776</v>
       </c>
       <c r="B110" s="28" t="s">
+        <v>7769</v>
+      </c>
+      <c r="C110" s="28" t="s">
+        <v>7770</v>
+      </c>
+      <c r="D110" s="28" t="s">
+        <v>7771</v>
+      </c>
+      <c r="E110" s="28" t="s">
+        <v>7772</v>
+      </c>
+      <c r="F110" s="28" t="s">
+        <v>7773</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>7774</v>
       </c>
-      <c r="C110" s="28" t="s">
+    </row>
+    <row r="112" s="55" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1"/>
+      <c r="N112" s="1"/>
+      <c r="O112" s="1"/>
+      <c r="P112" s="1"/>
+      <c r="Q112" s="1"/>
+      <c r="R112" s="1"/>
+      <c r="S112" s="1"/>
+      <c r="T112" s="1"/>
+      <c r="U112" s="1"/>
+      <c r="V112" s="1"/>
+      <c r="W112" s="1"/>
+      <c r="X112" s="1"/>
+      <c r="Y112" s="1"/>
+      <c r="Z112" s="1"/>
+      <c r="AA112" s="1"/>
+      <c r="AB112" s="1"/>
+      <c r="AC112" s="1"/>
+      <c r="AD112" s="1"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0"/>
+      <c r="B113" s="0"/>
+      <c r="C113" s="0"/>
+      <c r="D113" s="0"/>
+      <c r="E113" s="0"/>
+      <c r="F113" s="0"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0"/>
+      <c r="B114" s="0"/>
+      <c r="C114" s="0"/>
+      <c r="D114" s="0"/>
+      <c r="E114" s="0"/>
+      <c r="F114" s="0"/>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0"/>
+      <c r="B115" s="0"/>
+      <c r="C115" s="0"/>
+      <c r="D115" s="0"/>
+      <c r="E115" s="0"/>
+      <c r="F115" s="0"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0"/>
+      <c r="B116" s="0"/>
+      <c r="C116" s="0"/>
+      <c r="D116" s="0"/>
+      <c r="E116" s="0"/>
+      <c r="F116" s="0"/>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0"/>
+      <c r="B117" s="0"/>
+      <c r="C117" s="0"/>
+      <c r="D117" s="0"/>
+      <c r="E117" s="0"/>
+      <c r="F117" s="0"/>
+    </row>
+    <row r="118" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0"/>
+      <c r="B118" s="0"/>
+      <c r="C118" s="0"/>
+      <c r="D118" s="0"/>
+      <c r="E118" s="0"/>
+      <c r="F118" s="0"/>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0"/>
+      <c r="B119" s="0"/>
+      <c r="C119" s="0"/>
+      <c r="D119" s="0"/>
+      <c r="E119" s="0"/>
+      <c r="F119" s="0"/>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0"/>
+      <c r="B120" s="0"/>
+      <c r="C120" s="0"/>
+      <c r="D120" s="0"/>
+      <c r="E120" s="0"/>
+      <c r="F120" s="0"/>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0"/>
+      <c r="B121" s="0"/>
+      <c r="C121" s="0"/>
+      <c r="D121" s="0"/>
+      <c r="E121" s="0"/>
+      <c r="F121" s="0"/>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0"/>
+      <c r="B122" s="0"/>
+      <c r="C122" s="0"/>
+      <c r="D122" s="0"/>
+      <c r="E122" s="0"/>
+      <c r="F122" s="0"/>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0"/>
+      <c r="B123" s="0"/>
+      <c r="C123" s="0"/>
+      <c r="D123" s="0"/>
+      <c r="E123" s="0"/>
+      <c r="F123" s="0"/>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0"/>
+      <c r="B124" s="0"/>
+      <c r="C124" s="0"/>
+      <c r="D124" s="0"/>
+      <c r="E124" s="0"/>
+      <c r="F124" s="0"/>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0"/>
+      <c r="B125" s="0"/>
+      <c r="C125" s="0"/>
+      <c r="D125" s="0"/>
+      <c r="E125" s="0"/>
+      <c r="F125" s="0"/>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0"/>
+      <c r="B126" s="0"/>
+      <c r="C126" s="0"/>
+      <c r="D126" s="0"/>
+      <c r="E126" s="0"/>
+      <c r="F126" s="0"/>
+    </row>
+    <row r="127" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="54" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B128" s="46" t="s">
         <v>7775</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="C128" s="56" t="s">
         <v>7776</v>
       </c>
-      <c r="E110" s="28" t="s">
+      <c r="D128" s="48" t="s">
         <v>7777</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="E128" s="44" t="s">
         <v>7778</v>
       </c>
-      <c r="G110" s="1" t="s">
+      <c r="F128" s="44"/>
+      <c r="G128" s="50" t="s">
         <v>7779</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="47" t="n">
-        <v>44895</v>
-      </c>
-      <c r="B111" s="28" t="s">
+    <row r="129" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="54" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B129" s="46" t="s">
         <v>7780</v>
       </c>
-      <c r="C111" s="28" t="s">
+      <c r="C129" s="48"/>
+      <c r="D129" s="48"/>
+      <c r="E129" s="44"/>
+      <c r="F129" s="44"/>
+      <c r="G129" s="1" t="s">
         <v>7781</v>
       </c>
-      <c r="D111" s="43" t="s">
+    </row>
+    <row r="130" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="54"/>
+      <c r="B130" s="46"/>
+      <c r="C130" s="48"/>
+      <c r="D130" s="48"/>
+      <c r="E130" s="44"/>
+      <c r="F130" s="44"/>
+      <c r="G130" s="1"/>
+    </row>
+    <row r="132" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
         <v>7782</v>
       </c>
-      <c r="E111" s="28" t="s">
+    </row>
+    <row r="133" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="57" t="s">
         <v>7783</v>
       </c>
-      <c r="F111" s="28" t="s">
+      <c r="B133" s="41" t="s">
         <v>7784</v>
       </c>
-      <c r="G111" s="2" t="s">
+      <c r="C133" s="41" t="s">
         <v>7785</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="47" t="n">
-        <v>45449</v>
-      </c>
-      <c r="B112" s="28" t="s">
+      <c r="D133" s="41"/>
+      <c r="E133" s="41" t="s">
         <v>7786</v>
       </c>
-      <c r="C112" s="28" t="s">
+      <c r="F133" s="41" t="s">
         <v>7787</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="G133" s="2" t="s">
         <v>7788</v>
       </c>
-      <c r="E112" s="28" t="s">
+    </row>
+    <row r="134" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
         <v>7789</v>
       </c>
-      <c r="F112" s="28" t="s">
+      <c r="B134" s="1" t="s">
         <v>7790</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="C134" s="1" t="s">
         <v>7791</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="47" t="n">
-        <v>46017</v>
-      </c>
-      <c r="B113" s="28" t="s">
+      <c r="D134" s="1" t="s">
         <v>7792</v>
       </c>
-      <c r="C113" s="28" t="s">
+      <c r="E134" s="1" t="s">
         <v>7793</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="F134" s="58" t="s">
         <v>7794</v>
       </c>
-      <c r="E113" s="28" t="s">
+      <c r="G134" s="2" t="s">
         <v>7795</v>
       </c>
-      <c r="F113" s="28" t="s">
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1"/>
+      <c r="K134" s="1"/>
+      <c r="L134" s="1"/>
+      <c r="M134" s="1"/>
+      <c r="N134" s="1"/>
+      <c r="O134" s="1"/>
+      <c r="P134" s="1"/>
+      <c r="Q134" s="1"/>
+      <c r="R134" s="1"/>
+      <c r="S134" s="1"/>
+      <c r="T134" s="1"/>
+      <c r="U134" s="1"/>
+      <c r="V134" s="1"/>
+      <c r="W134" s="1"/>
+      <c r="X134" s="1"/>
+      <c r="Y134" s="1"/>
+      <c r="Z134" s="1"/>
+      <c r="AA134" s="1"/>
+      <c r="AB134" s="1"/>
+      <c r="AC134" s="1"/>
+      <c r="AD134" s="1"/>
+    </row>
+    <row r="135" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="57" t="s">
         <v>7796</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="B135" s="41" t="s">
         <v>7797</v>
       </c>
-    </row>
-    <row r="114" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="47"/>
-      <c r="B114" s="28" t="s">
+      <c r="C135" s="41" t="s">
         <v>7798</v>
       </c>
-      <c r="C114" s="43" t="s">
+      <c r="D135" s="59" t="s">
         <v>7799</v>
       </c>
-      <c r="E114" s="28"/>
-      <c r="F114" s="28"/>
-    </row>
-    <row r="115" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="47" t="n">
-        <v>41741</v>
-      </c>
-      <c r="B115" s="1" t="s">
+      <c r="E135" s="41" t="s">
         <v>7800</v>
       </c>
-      <c r="G115" s="2" t="s">
+      <c r="F135" s="41" t="s">
+        <v>7787</v>
+      </c>
+      <c r="G135" s="41" t="s">
         <v>7801</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="47"/>
-      <c r="B119" s="28"/>
-      <c r="C119" s="28"/>
-      <c r="E119" s="28"/>
-      <c r="F119" s="28"/>
-      <c r="G119" s="2"/>
-    </row>
-    <row r="120" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="43" t="s">
+    <row r="136" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="60" t="n">
+        <v>42355</v>
+      </c>
+      <c r="B136" s="41" t="s">
         <v>7802</v>
       </c>
-      <c r="B120" s="28"/>
-      <c r="C120" s="28"/>
-      <c r="E120" s="28"/>
-      <c r="F120" s="28"/>
-      <c r="G120" s="2"/>
-    </row>
-    <row r="121" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="58" t="s">
+      <c r="C136" s="41" t="s">
         <v>7803</v>
       </c>
-      <c r="B121" s="43" t="s">
+      <c r="D136" s="41" t="s">
         <v>7804</v>
       </c>
-      <c r="C121" s="28" t="s">
+      <c r="E136" s="41" t="s">
         <v>7805</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E121" s="28" t="s">
-        <v>7722</v>
-      </c>
-      <c r="F121" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="58" t="s">
+      <c r="F136" s="41" t="s">
         <v>7806</v>
       </c>
-      <c r="B122" s="43" t="s">
+    </row>
+    <row r="137" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="57" t="n">
+        <v>43658</v>
+      </c>
+      <c r="B137" s="41" t="s">
         <v>7807</v>
       </c>
-      <c r="C122" s="28" t="s">
+      <c r="C137" s="41" t="s">
         <v>7808</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D137" s="59" t="s">
         <v>7809</v>
       </c>
-      <c r="F122" s="55" t="s">
-        <v>7723</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>7724</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="50" t="s">
+      <c r="E137" s="41" t="s">
         <v>7810</v>
       </c>
-      <c r="B123" s="56" t="s">
+      <c r="F137" s="41" t="s">
+        <v>7807</v>
+      </c>
+      <c r="G137" s="41" t="s">
         <v>7811</v>
       </c>
-      <c r="C123" s="28" t="s">
+      <c r="H137" s="41"/>
+      <c r="I137" s="41"/>
+      <c r="J137" s="41"/>
+      <c r="K137" s="41"/>
+      <c r="L137" s="41"/>
+      <c r="M137" s="41"/>
+      <c r="N137" s="41"/>
+      <c r="O137" s="41"/>
+      <c r="P137" s="41"/>
+      <c r="Q137" s="41"/>
+      <c r="R137" s="41"/>
+      <c r="S137" s="41"/>
+      <c r="T137" s="41"/>
+      <c r="U137" s="41"/>
+      <c r="V137" s="41"/>
+      <c r="W137" s="41"/>
+      <c r="X137" s="41"/>
+      <c r="Y137" s="41"/>
+      <c r="Z137" s="41"/>
+      <c r="AA137" s="41"/>
+      <c r="AB137" s="41"/>
+      <c r="AC137" s="41"/>
+      <c r="AD137" s="41" t="s">
         <v>7812</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="F123" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="58" t="s">
+    </row>
+    <row r="138" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="57" t="n">
+        <v>45581</v>
+      </c>
+      <c r="B138" s="41" t="s">
         <v>7813</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="C138" s="41" t="s">
         <v>7814</v>
       </c>
-      <c r="C124" s="28" t="s">
+      <c r="D138" s="41" t="s">
         <v>7815</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E124" s="28" t="s">
+      <c r="E138" s="59" t="s">
         <v>7816</v>
       </c>
-      <c r="F124" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="58" t="s">
+      <c r="F138" s="41" t="s">
+        <v>7813</v>
+      </c>
+      <c r="G138" s="61" t="s">
         <v>7817</v>
       </c>
-      <c r="B125" s="28" t="s">
+      <c r="H138" s="41"/>
+      <c r="I138" s="41"/>
+      <c r="J138" s="41"/>
+      <c r="K138" s="41"/>
+      <c r="L138" s="41"/>
+      <c r="M138" s="41"/>
+      <c r="N138" s="41"/>
+      <c r="O138" s="41"/>
+      <c r="P138" s="41"/>
+      <c r="Q138" s="41"/>
+      <c r="R138" s="41"/>
+      <c r="S138" s="41"/>
+      <c r="T138" s="41"/>
+      <c r="U138" s="41"/>
+      <c r="V138" s="41"/>
+      <c r="W138" s="41"/>
+      <c r="X138" s="41"/>
+      <c r="Y138" s="41"/>
+      <c r="Z138" s="41"/>
+      <c r="AA138" s="41"/>
+      <c r="AB138" s="41"/>
+      <c r="AC138" s="41"/>
+      <c r="AD138" s="41"/>
+    </row>
+    <row r="139" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="60" t="n">
+        <v>45668</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>7818</v>
       </c>
-      <c r="C125" s="28" t="s">
+      <c r="C139" s="28" t="s">
         <v>7819</v>
       </c>
-      <c r="E125" s="28"/>
-      <c r="F125" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="58" t="s">
+      <c r="D139" s="28" t="s">
         <v>7820</v>
       </c>
-      <c r="B126" s="28" t="s">
+      <c r="E139" s="45" t="s">
         <v>7821</v>
       </c>
-      <c r="C126" s="28" t="s">
+      <c r="F139" s="28" t="s">
+        <v>7563</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>7564</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
         <v>7822</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>7809</v>
-      </c>
-      <c r="E126" s="1" t="s">
+    </row>
+    <row r="142" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="59" t="s">
         <v>7823</v>
       </c>
-      <c r="F126" s="55" t="s">
-        <v>7723</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>7724</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="47" t="n">
-        <v>44662</v>
-      </c>
-      <c r="B127" s="28" t="s">
+      <c r="B142" s="2" t="s">
         <v>7824</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C142" s="1" t="s">
         <v>7825</v>
       </c>
-      <c r="D127" s="28" t="s">
+      <c r="F142" s="1" t="s">
         <v>7826</v>
       </c>
-      <c r="E127" s="28" t="s">
+      <c r="G142" s="2" t="s">
         <v>7827</v>
       </c>
-      <c r="F127" s="1" t="s">
+    </row>
+    <row r="143" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="57" t="s">
         <v>7828</v>
       </c>
-      <c r="G127" s="1" t="s">
+      <c r="B143" s="2" t="s">
         <v>7829</v>
       </c>
-    </row>
-    <row r="128" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="58" t="s">
+      <c r="F143" s="1" t="s">
+        <v>7826</v>
+      </c>
+      <c r="G143" s="2" t="s">
         <v>7830</v>
       </c>
-      <c r="B128" s="28" t="s">
+    </row>
+    <row r="144" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="59" t="s">
+        <v>7823</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>7831</v>
       </c>
-      <c r="C128" s="28"/>
-      <c r="D128" s="1" t="s">
-        <v>7809</v>
-      </c>
-      <c r="E128" s="1" t="s">
+      <c r="C144" s="1" t="s">
         <v>7832</v>
       </c>
-      <c r="F128" s="55" t="s">
-        <v>7723</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>7724</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="47" t="n">
-        <v>44776</v>
-      </c>
-      <c r="B129" s="28" t="s">
+      <c r="F144" s="1" t="s">
+        <v>7826</v>
+      </c>
+      <c r="G144" s="2" t="s">
         <v>7833</v>
       </c>
-      <c r="C129" s="28" t="s">
+    </row>
+    <row r="145" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="28" t="s">
         <v>7834</v>
       </c>
-      <c r="D129" s="28" t="s">
+      <c r="B145" s="1" t="s">
         <v>7835</v>
       </c>
-      <c r="E129" s="28" t="s">
+      <c r="C145" s="1" t="s">
         <v>7836</v>
       </c>
-      <c r="F129" s="28" t="s">
+      <c r="F145" s="1" t="s">
         <v>7837</v>
       </c>
-      <c r="G129" s="2" t="s">
+      <c r="G145" s="2" t="s">
+        <v>7812</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
         <v>7838</v>
       </c>
-    </row>
-    <row r="131" s="59" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
-      <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-      <c r="K131" s="1"/>
-      <c r="L131" s="1"/>
-      <c r="M131" s="1"/>
-      <c r="N131" s="1"/>
-      <c r="O131" s="1"/>
-      <c r="P131" s="1"/>
-      <c r="Q131" s="1"/>
-      <c r="R131" s="1"/>
-      <c r="S131" s="1"/>
-      <c r="T131" s="1"/>
-      <c r="U131" s="1"/>
-      <c r="V131" s="1"/>
-      <c r="W131" s="1"/>
-      <c r="X131" s="1"/>
-      <c r="Y131" s="1"/>
-      <c r="Z131" s="1"/>
-      <c r="AA131" s="1"/>
-      <c r="AB131" s="1"/>
-      <c r="AC131" s="1"/>
-      <c r="AD131" s="1"/>
-    </row>
-    <row r="132" s="59" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="47" t="s">
+      <c r="B146" s="2" t="s">
         <v>7839</v>
       </c>
-      <c r="B132" s="28"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-      <c r="E132" s="1"/>
-      <c r="F132" s="28"/>
-      <c r="G132" s="2"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-      <c r="J132" s="1"/>
-      <c r="K132" s="1"/>
-      <c r="L132" s="1"/>
-      <c r="M132" s="1"/>
-      <c r="N132" s="1"/>
-      <c r="O132" s="1"/>
-      <c r="P132" s="1"/>
-      <c r="Q132" s="1"/>
-      <c r="R132" s="1"/>
-      <c r="S132" s="1"/>
-      <c r="T132" s="1"/>
-      <c r="U132" s="1"/>
-      <c r="V132" s="1"/>
-      <c r="W132" s="1"/>
-      <c r="X132" s="1"/>
-      <c r="Y132" s="1"/>
-      <c r="Z132" s="1"/>
-      <c r="AA132" s="1"/>
-      <c r="AB132" s="1"/>
-      <c r="AC132" s="1"/>
-      <c r="AD132" s="1"/>
-    </row>
-    <row r="133" s="59" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="60" t="n">
-        <v>45004</v>
-      </c>
-      <c r="B133" s="59" t="s">
+      <c r="C146" s="1" t="s">
         <v>7840</v>
       </c>
-      <c r="C133" s="59" t="s">
+      <c r="F146" s="1" t="s">
+        <v>7837</v>
+      </c>
+      <c r="G146" s="1" t="s">
         <v>7841</v>
       </c>
-      <c r="D133" s="59" t="s">
+    </row>
+    <row r="147" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="43" t="s">
         <v>7842</v>
       </c>
-      <c r="E133" s="59" t="s">
+      <c r="B147" s="1" t="s">
         <v>7843</v>
       </c>
-      <c r="F133" s="61" t="s">
+      <c r="C147" s="1" t="s">
         <v>7844</v>
       </c>
-      <c r="G133" s="59" t="s">
+      <c r="F147" s="1" t="s">
         <v>7845</v>
       </c>
-    </row>
-    <row r="134" s="59" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="60" t="n">
-        <v>45005</v>
-      </c>
-      <c r="B134" s="61" t="s">
+      <c r="G147" s="2" t="s">
         <v>7846</v>
       </c>
-      <c r="C134" s="59" t="s">
+    </row>
+    <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="62" t="s">
         <v>7847</v>
       </c>
-      <c r="D134" s="59" t="s">
+      <c r="B148" s="1" t="s">
         <v>7848</v>
       </c>
-      <c r="E134" s="59" t="s">
+      <c r="C148" s="45" t="s">
         <v>7849</v>
       </c>
-      <c r="F134" s="61" t="s">
+      <c r="G148" s="2" t="s">
         <v>7850</v>
       </c>
-      <c r="G134" s="59" t="s">
+    </row>
+    <row r="149" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="1" t="s">
+        <v>7838</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>7851</v>
       </c>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="60" t="n">
-        <v>45006</v>
-      </c>
-      <c r="B135" s="59" t="s">
-        <v>7840</v>
-      </c>
-      <c r="C135" s="59" t="s">
+      <c r="C149" s="41" t="s">
         <v>7852</v>
       </c>
-      <c r="D135" s="59" t="s">
+      <c r="E149" s="1" t="s">
         <v>7853</v>
       </c>
-      <c r="E135" s="62" t="s">
+      <c r="F149" s="1" t="s">
+        <v>7837</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>7841</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="28" t="s">
         <v>7854</v>
       </c>
-      <c r="F135" s="61" t="s">
+      <c r="B150" s="2" t="s">
         <v>7855</v>
       </c>
-      <c r="G135" s="59" t="s">
+      <c r="C150" s="41" t="s">
         <v>7856</v>
       </c>
-      <c r="H135" s="59"/>
-      <c r="I135" s="59"/>
-      <c r="J135" s="59"/>
-      <c r="K135" s="59"/>
-      <c r="L135" s="59"/>
-      <c r="M135" s="59"/>
-      <c r="N135" s="59"/>
-      <c r="O135" s="59"/>
-      <c r="P135" s="59"/>
-      <c r="Q135" s="59"/>
-      <c r="R135" s="59"/>
-      <c r="S135" s="59"/>
-      <c r="T135" s="59"/>
-      <c r="U135" s="59"/>
-      <c r="V135" s="59"/>
-      <c r="W135" s="59"/>
-      <c r="X135" s="59"/>
-      <c r="Y135" s="59"/>
-      <c r="Z135" s="59"/>
-      <c r="AA135" s="59"/>
-      <c r="AB135" s="59"/>
-      <c r="AC135" s="59"/>
-      <c r="AD135" s="59"/>
-    </row>
-    <row r="136" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="60" t="n">
-        <v>45036</v>
-      </c>
-      <c r="B136" s="59" t="s">
+      <c r="D150" s="1" t="s">
         <v>7857</v>
       </c>
-      <c r="C136" s="59"/>
-      <c r="D136" s="59" t="s">
+      <c r="F150" s="1" t="s">
+        <v>7837</v>
+      </c>
+      <c r="G150" s="2" t="s">
         <v>7858</v>
       </c>
-      <c r="E136" s="59" t="s">
+      <c r="H150" s="1"/>
+    </row>
+    <row r="151" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="59" t="s">
+        <v>7823</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>7859</v>
       </c>
-      <c r="F136" s="59" t="s">
+      <c r="D151" s="28" t="s">
         <v>7860</v>
       </c>
-      <c r="G136" s="59" t="s">
+      <c r="E151" s="1" t="s">
         <v>7861</v>
       </c>
-      <c r="H136" s="59"/>
-      <c r="I136" s="59"/>
-      <c r="J136" s="59"/>
-      <c r="K136" s="59"/>
-      <c r="L136" s="59"/>
-      <c r="M136" s="59"/>
-      <c r="N136" s="59"/>
-      <c r="O136" s="59"/>
-      <c r="P136" s="59"/>
-      <c r="Q136" s="59"/>
-      <c r="R136" s="59"/>
-      <c r="S136" s="59"/>
-      <c r="T136" s="59"/>
-      <c r="U136" s="59"/>
-      <c r="V136" s="59"/>
-      <c r="W136" s="59"/>
-      <c r="X136" s="59"/>
-      <c r="Y136" s="59"/>
-      <c r="Z136" s="59"/>
-      <c r="AA136" s="59"/>
-      <c r="AB136" s="59"/>
-      <c r="AC136" s="59"/>
-      <c r="AD136" s="59"/>
-    </row>
-    <row r="137" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="63" t="n">
-        <v>45088</v>
-      </c>
-      <c r="B137" s="48" t="s">
-        <v>7840</v>
-      </c>
-      <c r="C137" s="48" t="s">
+      <c r="F151" s="43" t="s">
         <v>7862</v>
       </c>
-      <c r="D137" s="48" t="s">
+      <c r="G151" s="2" t="s">
         <v>7863</v>
       </c>
-      <c r="E137" s="64" t="s">
+    </row>
+    <row r="152" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B152" s="48" t="s">
         <v>7864</v>
       </c>
-      <c r="F137" s="48" t="s">
-        <v>7549</v>
-      </c>
-      <c r="G137" s="48" t="s">
-        <v>7550</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="63" t="n">
-        <v>45025</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>7800</v>
-      </c>
-      <c r="C138" s="28" t="s">
+      <c r="C152" s="1" t="s">
         <v>7865</v>
       </c>
-      <c r="D138" s="43" t="s">
+    </row>
+    <row r="153" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="63" t="s">
         <v>7866</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="B153" s="1" t="s">
         <v>7867</v>
       </c>
-      <c r="G138" s="1" t="s">
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="s">
         <v>7868</v>
       </c>
-    </row>
-    <row r="139" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
-      <c r="E139" s="1"/>
-      <c r="F139" s="1"/>
-      <c r="G139" s="1"/>
-      <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
-      <c r="J139" s="1"/>
-      <c r="K139" s="1"/>
-      <c r="L139" s="1"/>
-      <c r="M139" s="1"/>
-      <c r="N139" s="1"/>
-      <c r="O139" s="1"/>
-      <c r="P139" s="1"/>
-      <c r="Q139" s="1"/>
-      <c r="R139" s="1"/>
-      <c r="S139" s="1"/>
-      <c r="T139" s="1"/>
-      <c r="U139" s="1"/>
-      <c r="V139" s="1"/>
-      <c r="W139" s="1"/>
-      <c r="X139" s="1"/>
-      <c r="Y139" s="1"/>
-      <c r="Z139" s="1"/>
-      <c r="AA139" s="1"/>
-      <c r="AB139" s="1"/>
-      <c r="AC139" s="1"/>
-      <c r="AD139" s="1"/>
-    </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1" t="s">
+      <c r="B154" s="48" t="s">
         <v>7869</v>
       </c>
-      <c r="G140" s="1"/>
-      <c r="H140" s="1"/>
-      <c r="I140" s="1"/>
-      <c r="J140" s="1"/>
-      <c r="K140" s="1"/>
-      <c r="L140" s="1"/>
-      <c r="M140" s="1"/>
-      <c r="N140" s="1"/>
-      <c r="O140" s="1"/>
-      <c r="P140" s="1"/>
-      <c r="Q140" s="1"/>
-      <c r="R140" s="1"/>
-      <c r="S140" s="1"/>
-      <c r="T140" s="1"/>
-      <c r="U140" s="1"/>
-      <c r="V140" s="1"/>
-      <c r="W140" s="1"/>
-      <c r="X140" s="1"/>
-      <c r="Y140" s="1"/>
-      <c r="Z140" s="1"/>
-      <c r="AA140" s="1"/>
-      <c r="AB140" s="1"/>
-      <c r="AC140" s="1"/>
-      <c r="AD140" s="1"/>
-    </row>
-    <row r="141" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="65" t="n">
-        <v>39252</v>
-      </c>
-      <c r="B141" s="41"/>
-      <c r="C141" s="41" t="s">
+      <c r="C154" s="1" t="s">
         <v>7870</v>
       </c>
-      <c r="D141" s="66" t="s">
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="48" t="s">
         <v>7871</v>
       </c>
-      <c r="E141" s="41" t="s">
+      <c r="B155" s="48" t="s">
         <v>7872</v>
       </c>
-      <c r="F141" s="41" t="s">
+      <c r="C155" s="1" t="s">
         <v>7873</v>
       </c>
-      <c r="G141" s="41" t="s">
+    </row>
+    <row r="157" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="43" t="s">
         <v>7874</v>
       </c>
-      <c r="H141" s="41"/>
-      <c r="I141" s="41"/>
-      <c r="J141" s="41"/>
-      <c r="K141" s="41"/>
-      <c r="L141" s="41"/>
-      <c r="M141" s="41"/>
-      <c r="N141" s="41"/>
-      <c r="O141" s="41"/>
-      <c r="P141" s="41"/>
-      <c r="Q141" s="41"/>
-      <c r="R141" s="41"/>
-      <c r="S141" s="41"/>
-      <c r="T141" s="41"/>
-      <c r="U141" s="41"/>
-      <c r="V141" s="41"/>
-      <c r="W141" s="41"/>
-      <c r="X141" s="41"/>
-      <c r="Y141" s="41"/>
-      <c r="Z141" s="41"/>
-      <c r="AA141" s="41"/>
-      <c r="AB141" s="41"/>
-      <c r="AC141" s="41"/>
-      <c r="AD141" s="41"/>
-    </row>
-    <row r="142" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="47" t="n">
-        <v>46241</v>
-      </c>
-      <c r="B142" s="1" t="s">
+    </row>
+    <row r="158" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
         <v>7875</v>
       </c>
-      <c r="C142" s="28" t="s">
+      <c r="B158" s="1" t="s">
+        <v>7698</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>7826</v>
+      </c>
+      <c r="G158" s="2" t="s">
         <v>7876</v>
       </c>
-      <c r="F142" s="1" t="s">
+    </row>
+    <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
         <v>7877</v>
       </c>
-      <c r="G142" s="1" t="s">
+      <c r="B161" s="1" t="s">
         <v>7878</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="47" t="s">
+    <row r="162" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
         <v>7879</v>
       </c>
-      <c r="B143" s="28" t="s">
+      <c r="B162" s="1" t="s">
         <v>7880</v>
       </c>
-      <c r="C143" s="1" t="s">
+    </row>
+    <row r="163" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
         <v>7881</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="B163" s="1" t="s">
         <v>7882</v>
       </c>
-      <c r="F143" s="28" t="s">
+    </row>
+    <row r="167" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="43" t="s">
         <v>7883</v>
       </c>
-      <c r="G143" s="2" t="s">
+    </row>
+    <row r="171" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="28" t="s">
         <v>7884</v>
       </c>
-    </row>
-    <row r="144" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="58" t="n">
-        <v>42866</v>
-      </c>
-      <c r="B144" s="1" t="s">
+      <c r="B171" s="28"/>
+      <c r="C171" s="28"/>
+      <c r="D171" s="28"/>
+      <c r="F171" s="43"/>
+      <c r="G171" s="2"/>
+    </row>
+    <row r="172" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="64" t="s">
         <v>7885</v>
       </c>
-      <c r="C144" s="28" t="s">
+      <c r="D172" s="64" t="s">
         <v>7886</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="E172" s="64" t="s">
         <v>7887</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="F172" s="62" t="s">
+        <v>7502</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>7503</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="64" t="s">
         <v>7888</v>
       </c>
-      <c r="F144" s="28" t="s">
+      <c r="C173" s="28"/>
+      <c r="D173" s="64" t="s">
+        <v>7886</v>
+      </c>
+      <c r="E173" s="64" t="s">
         <v>7889</v>
       </c>
-      <c r="G144" s="2" t="s">
+      <c r="F173" s="65" t="s">
         <v>7890</v>
       </c>
-    </row>
-    <row r="146" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="147" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="58" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B147" s="51" t="s">
+      <c r="G173" s="2" t="s">
         <v>7891</v>
       </c>
-      <c r="C147" s="67" t="s">
+    </row>
+    <row r="175" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="1" t="s">
         <v>7892</v>
       </c>
-      <c r="D147" s="52" t="s">
+    </row>
+    <row r="176" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="28" t="s">
         <v>7893</v>
       </c>
-      <c r="E147" s="49" t="s">
+      <c r="B176" s="28" t="s">
         <v>7894</v>
       </c>
-      <c r="F147" s="49"/>
-      <c r="G147" s="54" t="s">
+      <c r="C176" s="28" t="s">
         <v>7895</v>
       </c>
-    </row>
-    <row r="148" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="58" t="n">
-        <v>45138</v>
-      </c>
-      <c r="B148" s="51" t="s">
+      <c r="D176" s="28" t="s">
+        <v>7529</v>
+      </c>
+      <c r="E176" s="28" t="s">
         <v>7896</v>
       </c>
-      <c r="C148" s="52"/>
-      <c r="D148" s="52"/>
-      <c r="E148" s="49"/>
-      <c r="F148" s="49"/>
-      <c r="G148" s="1" t="s">
+      <c r="F176" s="28" t="s">
+        <v>7530</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>7531</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="28" t="s">
         <v>7897</v>
       </c>
-    </row>
-    <row r="149" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="58"/>
-      <c r="B149" s="51"/>
-      <c r="C149" s="52"/>
-      <c r="D149" s="52"/>
-      <c r="E149" s="49"/>
-      <c r="F149" s="49"/>
-      <c r="G149" s="1"/>
-    </row>
-    <row r="151" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="1" t="s">
+      <c r="B177" s="28" t="s">
+        <v>7894</v>
+      </c>
+      <c r="C177" s="28" t="s">
         <v>7898</v>
       </c>
-    </row>
-    <row r="152" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="65" t="s">
+      <c r="D177" s="1" t="s">
         <v>7899</v>
       </c>
-      <c r="B152" s="41" t="s">
+      <c r="E177" s="28" t="s">
         <v>7900</v>
       </c>
-      <c r="C152" s="41" t="s">
+      <c r="F177" s="28" t="s">
         <v>7901</v>
       </c>
-      <c r="D152" s="41"/>
-      <c r="E152" s="41" t="s">
+      <c r="G177" s="1" t="s">
         <v>7902</v>
       </c>
-      <c r="F152" s="41" t="s">
+    </row>
+    <row r="178" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="28" t="s">
+        <v>7893</v>
+      </c>
+      <c r="B178" s="28" t="s">
+        <v>7894</v>
+      </c>
+      <c r="C178" s="28" t="s">
         <v>7903</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="D178" s="1" t="s">
         <v>7904</v>
       </c>
-    </row>
-    <row r="153" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
+      <c r="E178" s="28" t="s">
         <v>7905</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="F178" s="28" t="s">
         <v>7906</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="G178" s="2" t="s">
         <v>7907</v>
       </c>
-      <c r="D153" s="1" t="s">
+    </row>
+    <row r="179" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="47" t="s">
         <v>7908</v>
       </c>
-      <c r="E153" s="1" t="s">
+      <c r="B179" s="28" t="s">
         <v>7909</v>
       </c>
-      <c r="F153" s="48" t="s">
+      <c r="C179" s="1" t="s">
         <v>7910</v>
       </c>
-      <c r="G153" s="2" t="s">
+      <c r="E179" s="1" t="s">
         <v>7911</v>
       </c>
-      <c r="H153" s="1"/>
-      <c r="I153" s="1"/>
-      <c r="J153" s="1"/>
-      <c r="K153" s="1"/>
-      <c r="L153" s="1"/>
-      <c r="M153" s="1"/>
-      <c r="N153" s="1"/>
-      <c r="O153" s="1"/>
-      <c r="P153" s="1"/>
-      <c r="Q153" s="1"/>
-      <c r="R153" s="1"/>
-      <c r="S153" s="1"/>
-      <c r="T153" s="1"/>
-      <c r="U153" s="1"/>
-      <c r="V153" s="1"/>
-      <c r="W153" s="1"/>
-      <c r="X153" s="1"/>
-      <c r="Y153" s="1"/>
-      <c r="Z153" s="1"/>
-      <c r="AA153" s="1"/>
-      <c r="AB153" s="1"/>
-      <c r="AC153" s="1"/>
-      <c r="AD153" s="1"/>
-    </row>
-    <row r="154" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="65" t="s">
+      <c r="F179" s="28" t="s">
+        <v>7890</v>
+      </c>
+      <c r="G179" s="58" t="s">
+        <v>7891</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="47" t="s">
         <v>7912</v>
       </c>
-      <c r="B154" s="41" t="s">
+      <c r="B180" s="43" t="s">
         <v>7913</v>
       </c>
-      <c r="C154" s="41" t="s">
+      <c r="C180" s="1" t="s">
         <v>7914</v>
       </c>
-      <c r="D154" s="66" t="s">
+      <c r="D180" s="1" t="s">
         <v>7915</v>
       </c>
-      <c r="E154" s="41" t="s">
+      <c r="E180" s="28" t="s">
         <v>7916</v>
       </c>
-      <c r="F154" s="41" t="s">
-        <v>7903</v>
-      </c>
-      <c r="G154" s="41" t="s">
+      <c r="F180" s="28" t="s">
         <v>7917</v>
       </c>
-    </row>
-    <row r="155" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="68" t="n">
-        <v>42355</v>
-      </c>
-      <c r="B155" s="41" t="s">
+      <c r="G180" s="58" t="s">
         <v>7918</v>
-      </c>
-      <c r="C155" s="41" t="s">
-        <v>7919</v>
-      </c>
-      <c r="D155" s="41" t="s">
-        <v>7920</v>
-      </c>
-      <c r="E155" s="41" t="s">
-        <v>7921</v>
-      </c>
-      <c r="F155" s="41" t="s">
-        <v>7922</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="65" t="n">
-        <v>43658</v>
-      </c>
-      <c r="B156" s="41" t="s">
-        <v>7923</v>
-      </c>
-      <c r="C156" s="41" t="s">
-        <v>7924</v>
-      </c>
-      <c r="D156" s="66" t="s">
-        <v>7925</v>
-      </c>
-      <c r="E156" s="41" t="s">
-        <v>7926</v>
-      </c>
-      <c r="F156" s="41" t="s">
-        <v>7923</v>
-      </c>
-      <c r="G156" s="41" t="s">
-        <v>7927</v>
-      </c>
-      <c r="H156" s="41"/>
-      <c r="I156" s="41"/>
-      <c r="J156" s="41"/>
-      <c r="K156" s="41"/>
-      <c r="L156" s="41"/>
-      <c r="M156" s="41"/>
-      <c r="N156" s="41"/>
-      <c r="O156" s="41"/>
-      <c r="P156" s="41"/>
-      <c r="Q156" s="41"/>
-      <c r="R156" s="41"/>
-      <c r="S156" s="41"/>
-      <c r="T156" s="41"/>
-      <c r="U156" s="41"/>
-      <c r="V156" s="41"/>
-      <c r="W156" s="41"/>
-      <c r="X156" s="41"/>
-      <c r="Y156" s="41"/>
-      <c r="Z156" s="41"/>
-      <c r="AA156" s="41"/>
-      <c r="AB156" s="41"/>
-      <c r="AC156" s="41"/>
-      <c r="AD156" s="41" t="s">
-        <v>7928</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="65" t="n">
-        <v>45581</v>
-      </c>
-      <c r="B157" s="41" t="s">
-        <v>7929</v>
-      </c>
-      <c r="C157" s="41" t="s">
-        <v>7930</v>
-      </c>
-      <c r="D157" s="41" t="s">
-        <v>7931</v>
-      </c>
-      <c r="E157" s="66" t="s">
-        <v>7932</v>
-      </c>
-      <c r="F157" s="41" t="s">
-        <v>7929</v>
-      </c>
-      <c r="G157" s="69" t="s">
-        <v>7933</v>
-      </c>
-      <c r="H157" s="41"/>
-      <c r="I157" s="41"/>
-      <c r="J157" s="41"/>
-      <c r="K157" s="41"/>
-      <c r="L157" s="41"/>
-      <c r="M157" s="41"/>
-      <c r="N157" s="41"/>
-      <c r="O157" s="41"/>
-      <c r="P157" s="41"/>
-      <c r="Q157" s="41"/>
-      <c r="R157" s="41"/>
-      <c r="S157" s="41"/>
-      <c r="T157" s="41"/>
-      <c r="U157" s="41"/>
-      <c r="V157" s="41"/>
-      <c r="W157" s="41"/>
-      <c r="X157" s="41"/>
-      <c r="Y157" s="41"/>
-      <c r="Z157" s="41"/>
-      <c r="AA157" s="41"/>
-      <c r="AB157" s="41"/>
-      <c r="AC157" s="41"/>
-      <c r="AD157" s="41"/>
-    </row>
-    <row r="158" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="68" t="n">
-        <v>45668</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>7934</v>
-      </c>
-      <c r="C158" s="28" t="s">
-        <v>7935</v>
-      </c>
-      <c r="D158" s="28" t="s">
-        <v>7936</v>
-      </c>
-      <c r="E158" s="50" t="s">
-        <v>7937</v>
-      </c>
-      <c r="F158" s="28" t="s">
-        <v>7630</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>7631</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1" t="s">
-        <v>7938</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="66" t="s">
-        <v>7939</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>7940</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>7941</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>7889</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>7942</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="65" t="s">
-        <v>7943</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>7944</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>7889</v>
-      </c>
-      <c r="G162" s="2" t="s">
-        <v>7945</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="66" t="s">
-        <v>7939</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>7946</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>7947</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>7889</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>7948</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="28" t="s">
-        <v>7949</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>7950</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>7951</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>7952</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>7928</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1" t="s">
-        <v>7953</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>7954</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>7955</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>7952</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>7956</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="43" t="s">
-        <v>7957</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>7958</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>7959</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>7960</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>7961</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="45" t="s">
-        <v>7962</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>7963</v>
-      </c>
-      <c r="C167" s="50" t="s">
-        <v>7964</v>
-      </c>
-      <c r="G167" s="2" t="s">
-        <v>7965</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="1" t="s">
-        <v>7953</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>7966</v>
-      </c>
-      <c r="C168" s="41" t="s">
-        <v>7967</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>7968</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>7952</v>
-      </c>
-      <c r="G168" s="2" t="s">
-        <v>7956</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="28" t="s">
-        <v>7969</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>7970</v>
-      </c>
-      <c r="C169" s="41" t="s">
-        <v>7971</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>7972</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>7952</v>
-      </c>
-      <c r="G169" s="2" t="s">
-        <v>7973</v>
-      </c>
-      <c r="H169" s="1"/>
-    </row>
-    <row r="170" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="66" t="s">
-        <v>7939</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>7974</v>
-      </c>
-      <c r="D170" s="28" t="s">
-        <v>7975</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>7976</v>
-      </c>
-      <c r="F170" s="43" t="s">
-        <v>7977</v>
-      </c>
-      <c r="G170" s="2" t="s">
-        <v>7978</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="52" t="s">
-        <v>7979</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>7980</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="70" t="s">
-        <v>7981</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>7982</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="0" t="s">
-        <v>7983</v>
-      </c>
-      <c r="B173" s="52" t="s">
-        <v>7984</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>7985</v>
-      </c>
-    </row>
-    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="52" t="s">
-        <v>7986</v>
-      </c>
-      <c r="B174" s="52" t="s">
-        <v>7987</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>7988</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="43" t="s">
-        <v>7989</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="1" t="s">
-        <v>7990</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>7762</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>7889</v>
-      </c>
-      <c r="G177" s="2" t="s">
-        <v>7991</v>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="1" t="s">
-        <v>7992</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>7993</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
+        <v>7919</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>7920</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>7921</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>7911</v>
+      </c>
+      <c r="F181" s="28" t="s">
+        <v>7890</v>
+      </c>
+      <c r="G181" s="58" t="s">
+        <v>7891</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B182" s="1" t="s">
+        <v>7922</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>7911</v>
+      </c>
+      <c r="F182" s="28" t="s">
+        <v>7890</v>
+      </c>
+      <c r="G182" s="58" t="s">
+        <v>7891</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="1" t="s">
+        <v>7923</v>
+      </c>
+      <c r="B183" s="28" t="s">
+        <v>7924</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>7925</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>7926</v>
+      </c>
+      <c r="F183" s="28" t="s">
+        <v>7927</v>
+      </c>
+      <c r="G183" s="58" t="s">
+        <v>7928</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A184" s="1" t="s">
+        <v>7929</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>7638</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>7930</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>7931</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>7932</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>7640</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>7641</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="47" t="n">
+        <v>36795</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>7933</v>
+      </c>
+      <c r="C185" s="28" t="s">
+        <v>7934</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>7935</v>
+      </c>
+      <c r="E185" s="28" t="s">
+        <v>7936</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>7937</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>7938</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="47" t="n">
+        <v>45216</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>7939</v>
+      </c>
+      <c r="C186" s="28" t="s">
+        <v>7940</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>7941</v>
+      </c>
+      <c r="E186" s="28" t="s">
+        <v>7942</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>7943</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>7944</v>
+      </c>
+    </row>
+    <row r="187" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A187" s="47" t="n">
+        <v>45458</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>7945</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>7946</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>7468</v>
+      </c>
+      <c r="E187" s="28" t="s">
+        <v>7947</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>7470</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>7471</v>
+      </c>
+    </row>
+    <row r="190" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="47" t="s">
+        <v>7948</v>
+      </c>
+      <c r="B190" s="28"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
+      <c r="E190" s="1"/>
+      <c r="F190" s="28"/>
+      <c r="G190" s="2"/>
+      <c r="H190" s="1"/>
+      <c r="I190" s="1"/>
+      <c r="J190" s="1"/>
+      <c r="K190" s="1"/>
+      <c r="L190" s="1"/>
+      <c r="M190" s="1"/>
+      <c r="N190" s="1"/>
+      <c r="O190" s="1"/>
+      <c r="P190" s="1"/>
+      <c r="Q190" s="1"/>
+      <c r="R190" s="1"/>
+      <c r="S190" s="1"/>
+      <c r="T190" s="1"/>
+      <c r="U190" s="1"/>
+      <c r="V190" s="1"/>
+      <c r="W190" s="1"/>
+      <c r="X190" s="1"/>
+      <c r="Y190" s="1"/>
+      <c r="Z190" s="1"/>
+      <c r="AA190" s="1"/>
+      <c r="AB190" s="1"/>
+      <c r="AC190" s="1"/>
+      <c r="AD190" s="1"/>
+    </row>
+    <row r="191" s="55" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="66" t="n">
+        <v>45004</v>
+      </c>
+      <c r="B191" s="55" t="s">
+        <v>7949</v>
+      </c>
+      <c r="C191" s="55" t="s">
+        <v>7950</v>
+      </c>
+      <c r="D191" s="55" t="s">
+        <v>7951</v>
+      </c>
+      <c r="E191" s="55" t="s">
+        <v>7952</v>
+      </c>
+      <c r="F191" s="67" t="s">
+        <v>7953</v>
+      </c>
+      <c r="G191" s="55" t="s">
+        <v>7954</v>
+      </c>
+    </row>
+    <row r="192" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="66" t="n">
+        <v>45005</v>
+      </c>
+      <c r="B192" s="67" t="s">
+        <v>7955</v>
+      </c>
+      <c r="C192" s="55" t="s">
+        <v>7956</v>
+      </c>
+      <c r="D192" s="55" t="s">
+        <v>7957</v>
+      </c>
+      <c r="E192" s="55" t="s">
+        <v>7958</v>
+      </c>
+      <c r="F192" s="67" t="s">
+        <v>7959</v>
+      </c>
+      <c r="G192" s="55" t="s">
+        <v>7960</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="66" t="n">
+        <v>45006</v>
+      </c>
+      <c r="B193" s="55" t="s">
+        <v>7949</v>
+      </c>
+      <c r="C193" s="55" t="s">
+        <v>7961</v>
+      </c>
+      <c r="D193" s="55" t="s">
+        <v>7962</v>
+      </c>
+      <c r="E193" s="68" t="s">
+        <v>7963</v>
+      </c>
+      <c r="F193" s="67" t="s">
+        <v>7964</v>
+      </c>
+      <c r="G193" s="55" t="s">
+        <v>7965</v>
+      </c>
+      <c r="H193" s="55"/>
+      <c r="I193" s="55"/>
+      <c r="J193" s="55"/>
+      <c r="K193" s="55"/>
+      <c r="L193" s="55"/>
+      <c r="M193" s="55"/>
+      <c r="N193" s="55"/>
+      <c r="O193" s="55"/>
+      <c r="P193" s="55"/>
+      <c r="Q193" s="55"/>
+      <c r="R193" s="55"/>
+      <c r="S193" s="55"/>
+      <c r="T193" s="55"/>
+      <c r="U193" s="55"/>
+      <c r="V193" s="55"/>
+      <c r="W193" s="55"/>
+      <c r="X193" s="55"/>
+      <c r="Y193" s="55"/>
+      <c r="Z193" s="55"/>
+      <c r="AA193" s="55"/>
+      <c r="AB193" s="55"/>
+      <c r="AC193" s="55"/>
+      <c r="AD193" s="55"/>
+    </row>
+    <row r="194" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="66" t="n">
+        <v>45036</v>
+      </c>
+      <c r="B194" s="55" t="s">
+        <v>7966</v>
+      </c>
+      <c r="C194" s="55"/>
+      <c r="D194" s="55" t="s">
+        <v>7967</v>
+      </c>
+      <c r="E194" s="55" t="s">
+        <v>7968</v>
+      </c>
+      <c r="F194" s="55" t="s">
+        <v>7969</v>
+      </c>
+      <c r="G194" s="55" t="s">
+        <v>7970</v>
+      </c>
+      <c r="H194" s="55"/>
+      <c r="I194" s="55"/>
+      <c r="J194" s="55"/>
+      <c r="K194" s="55"/>
+      <c r="L194" s="55"/>
+      <c r="M194" s="55"/>
+      <c r="N194" s="55"/>
+      <c r="O194" s="55"/>
+      <c r="P194" s="55"/>
+      <c r="Q194" s="55"/>
+      <c r="R194" s="55"/>
+      <c r="S194" s="55"/>
+      <c r="T194" s="55"/>
+      <c r="U194" s="55"/>
+      <c r="V194" s="55"/>
+      <c r="W194" s="55"/>
+      <c r="X194" s="55"/>
+      <c r="Y194" s="55"/>
+      <c r="Z194" s="55"/>
+      <c r="AA194" s="55"/>
+      <c r="AB194" s="55"/>
+      <c r="AC194" s="55"/>
+      <c r="AD194" s="55"/>
+    </row>
+    <row r="195" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="69" t="n">
+        <v>45088</v>
+      </c>
+      <c r="B195" s="58" t="s">
+        <v>7949</v>
+      </c>
+      <c r="C195" s="58" t="s">
+        <v>7971</v>
+      </c>
+      <c r="D195" s="58" t="s">
+        <v>7972</v>
+      </c>
+      <c r="E195" s="70" t="s">
+        <v>7973</v>
+      </c>
+      <c r="F195" s="58" t="s">
+        <v>7890</v>
+      </c>
+      <c r="G195" s="58" t="s">
+        <v>7891</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="69" t="n">
+        <v>45025</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>7736</v>
+      </c>
+      <c r="C196" s="28" t="s">
+        <v>7974</v>
+      </c>
+      <c r="D196" s="43" t="s">
+        <v>7975</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>7976</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>7977</v>
+      </c>
+    </row>
+    <row r="197" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+      <c r="E197" s="1"/>
+      <c r="F197" s="1"/>
+      <c r="G197" s="1"/>
+      <c r="H197" s="1"/>
+      <c r="I197" s="1"/>
+      <c r="J197" s="1"/>
+      <c r="K197" s="1"/>
+      <c r="L197" s="1"/>
+      <c r="M197" s="1"/>
+      <c r="N197" s="1"/>
+      <c r="O197" s="1"/>
+      <c r="P197" s="1"/>
+      <c r="Q197" s="1"/>
+      <c r="R197" s="1"/>
+      <c r="S197" s="1"/>
+      <c r="T197" s="1"/>
+      <c r="U197" s="1"/>
+      <c r="V197" s="1"/>
+      <c r="W197" s="1"/>
+      <c r="X197" s="1"/>
+      <c r="Y197" s="1"/>
+      <c r="Z197" s="1"/>
+      <c r="AA197" s="1"/>
+      <c r="AB197" s="1"/>
+      <c r="AC197" s="1"/>
+      <c r="AD197" s="1"/>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="1" t="s">
+        <v>7978</v>
+      </c>
+      <c r="G198" s="1"/>
+      <c r="H198" s="1"/>
+      <c r="I198" s="1"/>
+      <c r="J198" s="1"/>
+      <c r="K198" s="1"/>
+      <c r="L198" s="1"/>
+      <c r="M198" s="1"/>
+      <c r="N198" s="1"/>
+      <c r="O198" s="1"/>
+      <c r="P198" s="1"/>
+      <c r="Q198" s="1"/>
+      <c r="R198" s="1"/>
+      <c r="S198" s="1"/>
+      <c r="T198" s="1"/>
+      <c r="U198" s="1"/>
+      <c r="V198" s="1"/>
+      <c r="W198" s="1"/>
+      <c r="X198" s="1"/>
+      <c r="Y198" s="1"/>
+      <c r="Z198" s="1"/>
+      <c r="AA198" s="1"/>
+      <c r="AB198" s="1"/>
+      <c r="AC198" s="1"/>
+      <c r="AD198" s="1"/>
+    </row>
+    <row r="199" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="57" t="n">
+        <v>39252</v>
+      </c>
+      <c r="B199" s="41"/>
+      <c r="C199" s="41" t="s">
+        <v>7979</v>
+      </c>
+      <c r="D199" s="59" t="s">
+        <v>7980</v>
+      </c>
+      <c r="E199" s="41" t="s">
+        <v>7981</v>
+      </c>
+      <c r="F199" s="41" t="s">
+        <v>7982</v>
+      </c>
+      <c r="G199" s="41" t="s">
+        <v>7983</v>
+      </c>
+      <c r="H199" s="41"/>
+      <c r="I199" s="41"/>
+      <c r="J199" s="41"/>
+      <c r="K199" s="41"/>
+      <c r="L199" s="41"/>
+      <c r="M199" s="41"/>
+      <c r="N199" s="41"/>
+      <c r="O199" s="41"/>
+      <c r="P199" s="41"/>
+      <c r="Q199" s="41"/>
+      <c r="R199" s="41"/>
+      <c r="S199" s="41"/>
+      <c r="T199" s="41"/>
+      <c r="U199" s="41"/>
+      <c r="V199" s="41"/>
+      <c r="W199" s="41"/>
+      <c r="X199" s="41"/>
+      <c r="Y199" s="41"/>
+      <c r="Z199" s="41"/>
+      <c r="AA199" s="41"/>
+      <c r="AB199" s="41"/>
+      <c r="AC199" s="41"/>
+      <c r="AD199" s="41"/>
+    </row>
+    <row r="200" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="47" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>7984</v>
+      </c>
+      <c r="C200" s="28" t="s">
+        <v>7985</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>7986</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>7987</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="47" t="s">
+        <v>7988</v>
+      </c>
+      <c r="B201" s="28" t="s">
+        <v>7989</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>7990</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>7991</v>
+      </c>
+      <c r="F201" s="28" t="s">
+        <v>7992</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>7993</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="54" t="n">
+        <v>42866</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>7994</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C202" s="28" t="s">
         <v>7995</v>
       </c>
-    </row>
-    <row r="182" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="1" t="s">
+      <c r="D202" s="1" t="s">
         <v>7996</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="E202" s="1" t="s">
         <v>7997</v>
       </c>
-    </row>
-    <row r="186" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="43" t="s">
+      <c r="F202" s="28" t="s">
+        <v>7826</v>
+      </c>
+      <c r="G202" s="2" t="s">
         <v>7998</v>
       </c>
     </row>
@@ -85564,92 +85668,92 @@
     <hyperlink ref="G29" r:id="rId11" display="https://www.dpm.org.cn/ancient/special/148432.html"/>
     <hyperlink ref="G30" r:id="rId12" display="https://baijiahao.baidu.com/s?id=1853719866750900952&amp;wfr=spider&amp;for=pc"/>
     <hyperlink ref="G31" r:id="rId13" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G37" r:id="rId14" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G38" r:id="rId15" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G43" r:id="rId16" display="https://whly.gd.gov.cn/service_newwwbwg/content/post_4738424.html"/>
-    <hyperlink ref="G44" r:id="rId17" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G46" r:id="rId18" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G47" r:id="rId19" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G50" r:id="rId20" display="https://edu.sina.com.cn/wander/2000-09-25/12790.shtml"/>
-    <hyperlink ref="G56" r:id="rId21" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G57" r:id="rId22" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G59" r:id="rId23" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G60" r:id="rId24" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G62" r:id="rId25" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="G65" r:id="rId26" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G66" r:id="rId27" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
-    <hyperlink ref="G67" r:id="rId28" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G68" r:id="rId29" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G70" r:id="rId30" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G71" r:id="rId31" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G72" r:id="rId32" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G76" r:id="rId33" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G77" r:id="rId34" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G78" r:id="rId35" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G80" r:id="rId36" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
-    <hyperlink ref="G81" r:id="rId37" display="https://www.dpm.org.cn/ancient"/>
-    <hyperlink ref="G82" r:id="rId38" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G84" r:id="rId39" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
-    <hyperlink ref="G85" r:id="rId40" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
-    <hyperlink ref="G86" r:id="rId41" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
-    <hyperlink ref="G87" r:id="rId42" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G88" r:id="rId43" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G89" r:id="rId44" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G90" r:id="rId45" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G91" r:id="rId46" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G92" r:id="rId47" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G93" r:id="rId48" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G94" r:id="rId49" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G95" r:id="rId50" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G96" r:id="rId51" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G99" r:id="rId52" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
-    <hyperlink ref="G101" r:id="rId53" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G102" r:id="rId54" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G103" r:id="rId55" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G104" r:id="rId56" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G107" r:id="rId57" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G108" r:id="rId58" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G111" r:id="rId59" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G112" r:id="rId60" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
-    <hyperlink ref="G113" r:id="rId61" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
-    <hyperlink ref="G115" r:id="rId62" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
-    <hyperlink ref="G121" r:id="rId63" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G122" r:id="rId64" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G123" r:id="rId65" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G124" r:id="rId66" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G125" r:id="rId67" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G126" r:id="rId68" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G128" r:id="rId69" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G129" r:id="rId70" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
-    <hyperlink ref="G133" r:id="rId71" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
-    <hyperlink ref="F135" r:id="rId72" display="中新网北京3月21日电 (记者 应妮) "/>
-    <hyperlink ref="G135" r:id="rId73" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
-    <hyperlink ref="G137" r:id="rId74" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G141" r:id="rId75" display="https://discovery.cctv.com/20070619/107154.shtml"/>
-    <hyperlink ref="G144" r:id="rId76" display="https://book.kongfz.com/102740/682706591"/>
-    <hyperlink ref="C147" r:id="rId77" display="尊婆须蜜菩萨所集论十五卷"/>
-    <hyperlink ref="G147" r:id="rId78" display="https://baijiahao.baidu.com/s?id=1767494632561741658&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G152" r:id="rId79" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
-    <hyperlink ref="G153" r:id="rId80" display="https://book.kongfz.com/20791/3754198261"/>
-    <hyperlink ref="G156" r:id="rId81" display="https://www.ljstsg.cn/?p=6315"/>
-    <hyperlink ref="AD156" r:id="rId82" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="G157" r:id="rId83" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
-    <hyperlink ref="G158" r:id="rId84" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="B161" r:id="rId85" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
-    <hyperlink ref="G161" r:id="rId86" display="https://book.kongfz.com/536651/7839562954"/>
-    <hyperlink ref="B162" r:id="rId87" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
-    <hyperlink ref="G162" r:id="rId88" display="https://book.kongfz.com/23231/8186709240"/>
-    <hyperlink ref="B163" r:id="rId89" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
-    <hyperlink ref="G163" r:id="rId90" display="https://book.kongfz.com/536651/7839554296"/>
-    <hyperlink ref="G164" r:id="rId91" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="B165" r:id="rId92" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
-    <hyperlink ref="G166" r:id="rId93" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
-    <hyperlink ref="G167" r:id="rId94" display="https://book.kongfz.com/200249/1819262449/"/>
-    <hyperlink ref="G168" r:id="rId95" display="https://product.dangdang.com/11721366316.html"/>
-    <hyperlink ref="B169" r:id="rId96" display="出版社:宗教文化出版社 "/>
-    <hyperlink ref="G169" r:id="rId97" display="https://product.dangdang.com/22497432.html"/>
-    <hyperlink ref="G170" r:id="rId98" display="http://aiguji.net/3299.html"/>
-    <hyperlink ref="G177" r:id="rId99" display="https://book.kongfz.com/467603/10356350239"/>
+    <hyperlink ref="G37" r:id="rId14" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G38" r:id="rId15" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G40" r:id="rId16" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G41" r:id="rId17" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G43" r:id="rId18" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="G46" r:id="rId19" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G47" r:id="rId20" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
+    <hyperlink ref="G48" r:id="rId21" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G49" r:id="rId22" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G51" r:id="rId23" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G52" r:id="rId24" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G53" r:id="rId25" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G57" r:id="rId26" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G58" r:id="rId27" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G59" r:id="rId28" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G61" r:id="rId29" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
+    <hyperlink ref="G62" r:id="rId30" display="https://www.dpm.org.cn/ancient"/>
+    <hyperlink ref="G63" r:id="rId31" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G65" r:id="rId32" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
+    <hyperlink ref="G66" r:id="rId33" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
+    <hyperlink ref="G67" r:id="rId34" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
+    <hyperlink ref="G68" r:id="rId35" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G69" r:id="rId36" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G70" r:id="rId37" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G71" r:id="rId38" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G72" r:id="rId39" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G73" r:id="rId40" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G74" r:id="rId41" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G75" r:id="rId42" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G76" r:id="rId43" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G77" r:id="rId44" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G80" r:id="rId45" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
+    <hyperlink ref="G82" r:id="rId46" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G83" r:id="rId47" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G84" r:id="rId48" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G85" r:id="rId49" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G88" r:id="rId50" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G89" r:id="rId51" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G92" r:id="rId52" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G93" r:id="rId53" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
+    <hyperlink ref="G94" r:id="rId54" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
+    <hyperlink ref="G96" r:id="rId55" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
+    <hyperlink ref="G102" r:id="rId56" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G103" r:id="rId57" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G104" r:id="rId58" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G105" r:id="rId59" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G106" r:id="rId60" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G107" r:id="rId61" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G109" r:id="rId62" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G110" r:id="rId63" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
+    <hyperlink ref="C128" r:id="rId64" display="尊婆须蜜菩萨所集论十五卷"/>
+    <hyperlink ref="G128" r:id="rId65" display="https://baijiahao.baidu.com/s?id=1767494632561741658&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G133" r:id="rId66" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
+    <hyperlink ref="G134" r:id="rId67" display="https://book.kongfz.com/20791/3754198261"/>
+    <hyperlink ref="G137" r:id="rId68" display="https://www.ljstsg.cn/?p=6315"/>
+    <hyperlink ref="AD137" r:id="rId69" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="G138" r:id="rId70" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
+    <hyperlink ref="G139" r:id="rId71" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="B142" r:id="rId72" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
+    <hyperlink ref="G142" r:id="rId73" display="https://book.kongfz.com/536651/7839562954"/>
+    <hyperlink ref="B143" r:id="rId74" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
+    <hyperlink ref="G143" r:id="rId75" display="https://book.kongfz.com/23231/8186709240"/>
+    <hyperlink ref="B144" r:id="rId76" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
+    <hyperlink ref="G144" r:id="rId77" display="https://book.kongfz.com/536651/7839554296"/>
+    <hyperlink ref="G145" r:id="rId78" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="B146" r:id="rId79" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
+    <hyperlink ref="G147" r:id="rId80" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
+    <hyperlink ref="G148" r:id="rId81" display="https://book.kongfz.com/200249/1819262449/"/>
+    <hyperlink ref="G149" r:id="rId82" display="https://product.dangdang.com/11721366316.html"/>
+    <hyperlink ref="B150" r:id="rId83" display="出版社:宗教文化出版社 "/>
+    <hyperlink ref="G150" r:id="rId84" display="https://product.dangdang.com/22497432.html"/>
+    <hyperlink ref="G151" r:id="rId85" display="http://aiguji.net/3299.html"/>
+    <hyperlink ref="G158" r:id="rId86" display="https://book.kongfz.com/467603/10356350239"/>
+    <hyperlink ref="G172" r:id="rId87" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G173" r:id="rId88" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G178" r:id="rId89" display="https://whly.gd.gov.cn/service_newwwbwg/content/post_4738424.html"/>
+    <hyperlink ref="G179" r:id="rId90" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G181" r:id="rId91" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G182" r:id="rId92" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G185" r:id="rId93" display="https://edu.sina.com.cn/wander/2000-09-25/12790.shtml"/>
+    <hyperlink ref="G191" r:id="rId94" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
+    <hyperlink ref="F193" r:id="rId95" display="中新网北京3月21日电 (记者 应妮) "/>
+    <hyperlink ref="G193" r:id="rId96" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
+    <hyperlink ref="G195" r:id="rId97" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G199" r:id="rId98" display="https://discovery.cctv.com/20070619/107154.shtml"/>
+    <hyperlink ref="G202" r:id="rId99" display="https://book.kongfz.com/102740/682706591"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -85797,7 +85901,7 @@
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>7857</v>
+        <v>7966</v>
       </c>
       <c r="C22" s="28" t="s">
         <v>8017</v>
@@ -85832,7 +85936,7 @@
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
-        <v>7674</v>
+        <v>7607</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>8025</v>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10896" uniqueCount="8043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10937" uniqueCount="8075">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -22762,6 +22762,33 @@
   </si>
   <si>
     <t xml:space="preserve">色貽厥嘉猷勉 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">001-88上，大清三藏圣教目录中，无此文目录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">001-151下，汇记中无此文目录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天台传佛心印记一卷(包括净土境观要门，没有单独一部)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">001-89下，大清三藏圣教目录中，净土境观要门是单独一部。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">001-152下，汇记中有净土境观要门</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大乘百法明门论一卷(附唯识三十颂)（非单独一部）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">001-153下（汇记中无此文目录，没有唯识三十颂，没有单独列出）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">唯识三十颂(附)（大清三藏圣教目录中，是单独一列）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">001-90，大清三藏圣教目录中，无此文目录。虽然没有，但是大家都知道初刻版是有的。</t>
   </si>
   <si>
     <t xml:space="preserve">时间</t>
@@ -28678,7 +28705,1146 @@
     <t xml:space="preserve">https://book.kongfz.com/102740/682706591</t>
   </si>
   <si>
-    <t xml:space="preserve">此土注释</t>
+    <t xml:space="preserve">《中国汉文大藏经补编》——遍搜历代大藏经经本</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://iwr.cssn.cn/xw/201312/t20131220_3047709.shtml#1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">《龍藏．維摩詰所說經》之重修 ──核心人物及其他</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://cbsweb.fgu.edu.tw/file_center/get_file.php?type=newspaper_menu&amp;id=JDgwIQ==&amp;file=2018091909263480.pdf#7#8#7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赵朴初：重印《清龙藏》序</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fo.ifeng.com/c/7hD5ERjvvcw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">龍谷大学所蔵の龍蔵について </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">https://opac.ryukoku.ac.jp/iwjs0005opc/bdyview.do?bodyid=BD00000117&amp;elmid=Body&amp;fname=r-rn_471_006.pdf&amp;loginflg=on&amp;once=true#4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">#4#4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">北京智化寺蔵板 文物出版社刷印 乾隆版大蔵径一一 《乾隆版大重量径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">又称《清蔵》、 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">((A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">毅》。清薙正十ー年至乾隆三年殿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">日。凡 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">724</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">函、 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">7 240</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">腸，牧表併，教典籍 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1675</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">部，是我国古代規模最大的官刻双文大厳重圭之ー。 在中国係教協会和北京市文物局、北京市智化寺文物管理所支持下，文物出版社特 用智化寺蔵原刻板片刷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">fn.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">井按乾隆四年初版本争ト全曽被撤銭的部分内容，以見其全貌。 本事按照原来的函、加用六ヨ干宣自主刷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">fn.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">明黄色布函径折装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.il[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">布函套。国内定伶 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">86 880</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">元。叶刻子 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1989</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">月前刷印完半。本有由文物出版社自亦宏行，預</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">iT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">亦法主日 下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">青向え</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">出版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">土皮行朴預</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">了。預 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.;T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">吋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">司自 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">19874'-9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">日ゑ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">日止</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">. d.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">比 期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">司預 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.;T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">宏保証供』主。 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">耳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">了者預付定金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">5000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">え，以后毎皮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">， 布状</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-1'i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">款 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-;J:::..</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">， え金五釆后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-;J&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">布</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.tk.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">宇 和除。預 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">iT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-1'i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">イ介占。有利主</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">~. ;J</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">長例主</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">后突昨え</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">介結昇。 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3. D!.;T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">吋一次イ十</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">青全部告扶者事受九祈仇怠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">. ~~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">，争套突什 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">78 912Jt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">。今后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-1'i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">イ介占。 有湖整，不手ト交差額。 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. 1ÞJ;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">丁后中途不舟 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">J~ì</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">旦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">了。分科什供者占。不投叶イサ款</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">. e~ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">中ム友ー担，定金不再 込迂。 文物出版社地社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">z </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">北京五回大街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">号 銀行紙号</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">z </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">中国工商銀行北京王府井分理主主</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4601-10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">「乾隆版大蔵経</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.Il([1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">飽蔵</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.Il)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">出版予告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">([1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">文物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.Il1987</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">年第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">期 </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">民国年间《清藏》的印刷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.zgfxy.cn/ztjj/fhty/fxwd__yjcg/zgx/fx/zdsseqeyen/content_1279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">藏在王府井旁的旧影：贤良寺最后的低语</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://baijiahao.baidu.com/s?id=1863338751830848606&amp;wfr=spider&amp;for=pc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">龙藏</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.fodian.cc/f01/441.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">民国时期晚清官书局刻本的印刷与流通 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nlc.cn/upload/attachments/2025-01-07/2d9bce53.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">《清藏》研究</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://xueshu.baidu.com/ndscholar/browse/detail?paperid=5e132d3c7f07d86aa62059c5d8d8c632&amp;site=xueshu_se</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20070325唐师曾：我爷的佛教图书馆有一部《清藏》 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://blog.sina.com.cn/s/blog_4ab76145010008yl.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南京国民政府与《清藏》的印刷 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.semanticscholar.org/paper/%E5%8D%97%E4%BA%AC%E5%9B%BD%E6%B0%91%E6%94%BF%E5%BA%9C%E4%B8%8E%E3%80%8A%E6%B8%85%E8%97%8F%E3%80%8B%E7%9A%84%E5%8D%B0%E5%88%B7-Chen/cbb651672512ef007d418d2d901703073cc7abe6#related-papers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">都属于“此土注释”部分</t>
   </si>
   <si>
     <t xml:space="preserve">俊一、俊二、俊三、俊四、俊五</t>
@@ -29237,7 +30403,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -29522,16 +30688,20 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -82160,7 +83330,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.28"/>
@@ -82542,8 +83712,75 @@
         <v>7330</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="28"/>
+    <row r="34" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>6926</v>
+      </c>
+      <c r="B34" s="41" t="s">
+        <v>6928</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>7457</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>7458</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="42" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7459</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>7436</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>7437</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="41" t="s">
+        <v>7439</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>7460</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>7461</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="27" t="s">
+        <v>7207</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7462</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>7450</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>7463</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="27"/>
+      <c r="C40" s="1" t="s">
+        <v>7464</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>7164</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7442</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>7465</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -82561,7 +83798,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:AD202"/>
+  <dimension ref="A3:AD217"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.85"/>
@@ -82574,25 +83811,25 @@
   <sheetData>
     <row r="3" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>7457</v>
+        <v>7466</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7458</v>
+        <v>7467</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7459</v>
+        <v>7468</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7460</v>
+        <v>7469</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>7461</v>
+        <v>7470</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7462</v>
+        <v>7471</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>7463</v>
+        <v>7472</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -82603,74 +83840,74 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>7464</v>
+        <v>7473</v>
       </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>7465</v>
+        <v>7474</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>7466</v>
+        <v>7475</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>7467</v>
+        <v>7476</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>7468</v>
+        <v>7477</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>7469</v>
+        <v>7478</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>7470</v>
+        <v>7479</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>7471</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>7472</v>
+        <v>7481</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7473</v>
+        <v>7482</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>7474</v>
+        <v>7483</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>7475</v>
+        <v>7484</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>7476</v>
+        <v>7485</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>7477</v>
+        <v>7486</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>7478</v>
+        <v>7487</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>7479</v>
+        <v>7488</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7480</v>
+        <v>7489</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>7475</v>
+        <v>7484</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>7481</v>
+        <v>7490</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>7477</v>
+        <v>7486</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>7478</v>
+        <v>7487</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -82686,55 +83923,55 @@
     </row>
     <row r="12" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>7482</v>
+        <v>7491</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="28"/>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>7483</v>
+        <v>7492</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>7484</v>
+        <v>7493</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>7485</v>
+        <v>7494</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>7468</v>
+        <v>7477</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>7486</v>
+        <v>7495</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>7470</v>
+        <v>7479</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>7471</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="43" t="s">
-        <v>7487</v>
+        <v>7496</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>7488</v>
+        <v>7497</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>7489</v>
+        <v>7498</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>7468</v>
+        <v>7477</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>7490</v>
+        <v>7499</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>7470</v>
+        <v>7479</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>7471</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -82746,81 +83983,81 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>7491</v>
+        <v>7500</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>7492</v>
+        <v>7501</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>7493</v>
+        <v>7502</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>7494</v>
+        <v>7503</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>7495</v>
+        <v>7504</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>7496</v>
+        <v>7505</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>7497</v>
+        <v>7506</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>7498</v>
+        <v>7507</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>7499</v>
+        <v>7508</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>7500</v>
+        <v>7509</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>7501</v>
+        <v>7510</v>
       </c>
       <c r="F19" s="43" t="s">
-        <v>7502</v>
+        <v>7511</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>7503</v>
+        <v>7512</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>7504</v>
+        <v>7513</v>
       </c>
       <c r="B20" s="28" t="s">
+        <v>7514</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>7515</v>
+      </c>
+      <c r="F20" s="43" t="s">
         <v>7505</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="G20" s="2" t="s">
         <v>7506</v>
-      </c>
-      <c r="F20" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>7497</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
-        <v>7507</v>
+        <v>7516</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
       <c r="D21" s="1" t="s">
-        <v>7508</v>
+        <v>7517</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>7502</v>
+        <v>7511</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>7503</v>
+        <v>7512</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -82832,7 +84069,7 @@
     </row>
     <row r="23" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>7509</v>
+        <v>7518</v>
       </c>
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
@@ -82841,652 +84078,691 @@
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>7510</v>
+        <v>7519</v>
       </c>
       <c r="B24" s="28" t="s">
+        <v>7520</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>7509</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>7521</v>
+      </c>
+      <c r="F24" s="43" t="s">
         <v>7511</v>
       </c>
-      <c r="C24" s="28" t="s">
-        <v>7500</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="G24" s="2" t="s">
         <v>7512</v>
-      </c>
-      <c r="F24" s="43" t="s">
-        <v>7502</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>7503</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>7513</v>
+        <v>7522</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>7514</v>
+        <v>7523</v>
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="1" t="s">
-        <v>7515</v>
+        <v>7524</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>7516</v>
+        <v>7525</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>7517</v>
+        <v>7526</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>7518</v>
+        <v>7527</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>7519</v>
+        <v>7528</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>7520</v>
+        <v>7529</v>
       </c>
       <c r="D26" s="28"/>
       <c r="F26" s="28" t="s">
-        <v>7521</v>
+        <v>7530</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>7522</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>7523</v>
+        <v>7532</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>7524</v>
+        <v>7533</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>7525</v>
+        <v>7534</v>
       </c>
       <c r="D27" s="28"/>
       <c r="F27" s="43" t="s">
-        <v>7496</v>
+        <v>7505</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>7497</v>
+        <v>7506</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>7526</v>
+        <v>7535</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>7527</v>
+        <v>7536</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>7528</v>
+        <v>7537</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>7529</v>
+        <v>7538</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>7530</v>
+        <v>7539</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>7531</v>
+        <v>7540</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>7532</v>
+        <v>7541</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>7533</v>
+        <v>7542</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>7534</v>
+        <v>7543</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>7535</v>
+        <v>7544</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>7536</v>
+        <v>7545</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>7537</v>
+        <v>7546</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>7538</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>7539</v>
+        <v>7548</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28" t="s">
-        <v>7540</v>
+        <v>7549</v>
       </c>
       <c r="D30" s="28"/>
       <c r="F30" s="43" t="s">
-        <v>7530</v>
+        <v>7539</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>7531</v>
+        <v>7540</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>7541</v>
+        <v>7550</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>7542</v>
+        <v>7551</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>7496</v>
+        <v>7505</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="35" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E35" s="28"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7506</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28" t="s">
+        <v>7552</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="35" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="28" t="s">
+        <v>7553</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>7554</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>7505</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>7506</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>7543</v>
-      </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="F36" s="28"/>
-    </row>
-    <row r="37" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7555</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>7556</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>7505</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>7506</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>7544</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>7545</v>
+        <v>7557</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>7558</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>7559</v>
       </c>
       <c r="F37" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7546</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>7547</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>7546</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>7547</v>
-      </c>
+        <v>7560</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>7561</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>7562</v>
+      </c>
+      <c r="E38" s="28"/>
       <c r="F38" s="43" t="s">
-        <v>7496</v>
+        <v>7505</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>7497</v>
+        <v>7506</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>7548</v>
-      </c>
-      <c r="D39" s="28" t="s">
-        <v>7549</v>
-      </c>
-      <c r="E39" s="28" t="s">
-        <v>7550</v>
-      </c>
+        <v>7563</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>7564</v>
+      </c>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
       <c r="F39" s="43" t="s">
-        <v>7537</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>7538</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7505</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>7506</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="28" t="s">
-        <v>7551</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>7552</v>
-      </c>
-      <c r="D40" s="28" t="s">
-        <v>7553</v>
+        <v>7565</v>
+      </c>
+      <c r="B40" s="44" t="s">
+        <v>7561</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>7566</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>7567</v>
       </c>
       <c r="E40" s="28"/>
-      <c r="F40" s="43" t="s">
-        <v>7496</v>
+      <c r="F40" s="0" t="s">
+        <v>7568</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>7497</v>
+        <v>7569</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="28" t="s">
-        <v>7554</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>7555</v>
-      </c>
-      <c r="D41" s="28"/>
+        <v>7570</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>7571</v>
+      </c>
       <c r="E41" s="28"/>
-      <c r="F41" s="43" t="s">
-        <v>7496</v>
+      <c r="F41" s="28" t="s">
+        <v>7572</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>7497</v>
+        <v>7573</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="28" t="s">
-        <v>7556</v>
-      </c>
-      <c r="B42" s="44" t="s">
-        <v>7552</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>7557</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>7558</v>
-      </c>
+      <c r="D42" s="28"/>
       <c r="E42" s="28"/>
-      <c r="F42" s="0" t="s">
-        <v>7559</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>7560</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="28" t="s">
-        <v>7561</v>
-      </c>
-      <c r="D43" s="28" t="s">
-        <v>7562</v>
-      </c>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28" t="s">
-        <v>7563</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>7564</v>
+      <c r="F42" s="43"/>
+    </row>
+    <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>7574</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="43"/>
+      <c r="A44" s="43" t="s">
+        <v>7575</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>7576</v>
+      </c>
+      <c r="F44" s="43" t="s">
+        <v>7505</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>7506</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>7565</v>
+      <c r="A45" s="28" t="s">
+        <v>7577</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>7578</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>7579</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>7580</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>7581</v>
+      </c>
+      <c r="F45" s="43" t="s">
+        <v>7582</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>7583</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="43" t="s">
-        <v>7566</v>
+      <c r="A46" s="28" t="s">
+        <v>7584</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>7567</v>
-      </c>
-      <c r="F46" s="43" t="s">
-        <v>7496</v>
+        <v>7585</v>
+      </c>
+      <c r="C46" s="28"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="28" t="s">
+        <v>7586</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>7530</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>7497</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="28" t="s">
-        <v>7568</v>
+        <v>7587</v>
       </c>
       <c r="B47" s="28" t="s">
-        <v>7569</v>
-      </c>
-      <c r="C47" s="28" t="s">
-        <v>7570</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>7571</v>
-      </c>
-      <c r="E47" s="28" t="s">
-        <v>7572</v>
-      </c>
+        <v>7588</v>
+      </c>
+      <c r="C47" s="28"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="28"/>
       <c r="F47" s="43" t="s">
-        <v>7573</v>
+        <v>7505</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>7574</v>
+        <v>7506</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="28" t="s">
-        <v>7575</v>
-      </c>
-      <c r="B48" s="28" t="s">
-        <v>7576</v>
-      </c>
+        <v>7587</v>
+      </c>
+      <c r="B48" s="28"/>
       <c r="C48" s="28"/>
       <c r="D48" s="43"/>
-      <c r="E48" s="28" t="s">
-        <v>7577</v>
-      </c>
-      <c r="F48" s="28" t="s">
-        <v>7521</v>
+      <c r="E48" s="28"/>
+      <c r="F48" s="0" t="s">
+        <v>7568</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>7522</v>
+        <v>7569</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="28" t="s">
-        <v>7578</v>
+      <c r="A49" s="45" t="s">
+        <v>7589</v>
       </c>
       <c r="B49" s="28" t="s">
-        <v>7579</v>
-      </c>
-      <c r="C49" s="28"/>
+        <v>7590</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>7591</v>
+      </c>
       <c r="D49" s="43"/>
       <c r="E49" s="28"/>
       <c r="F49" s="43" t="s">
-        <v>7496</v>
+        <v>7505</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>7497</v>
+        <v>7506</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="28" t="s">
-        <v>7578</v>
-      </c>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
+      <c r="A50" s="45" t="s">
+        <v>7589</v>
+      </c>
+      <c r="B50" s="28" t="s">
+        <v>7592</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>7593</v>
+      </c>
       <c r="D50" s="43"/>
       <c r="E50" s="28"/>
-      <c r="F50" s="0" t="s">
-        <v>7559</v>
+      <c r="F50" s="28" t="s">
+        <v>7530</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>7560</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="45" t="s">
-        <v>7580</v>
+        <v>7594</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>7581</v>
-      </c>
-      <c r="C51" s="28" t="s">
-        <v>7582</v>
-      </c>
-      <c r="D51" s="43"/>
+        <v>7595</v>
+      </c>
+      <c r="C51" s="28"/>
+      <c r="D51" s="1" t="s">
+        <v>7524</v>
+      </c>
       <c r="E51" s="28"/>
-      <c r="F51" s="43" t="s">
-        <v>7496</v>
+      <c r="F51" s="28" t="s">
+        <v>7525</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>7497</v>
+        <v>7526</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="45" t="s">
-        <v>7580</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>7583</v>
-      </c>
-      <c r="C52" s="28" t="s">
-        <v>7584</v>
-      </c>
-      <c r="D52" s="43"/>
+      <c r="A52" s="45"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
       <c r="E52" s="28"/>
-      <c r="F52" s="28" t="s">
-        <v>7521</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>7522</v>
-      </c>
+      <c r="F52" s="28"/>
+      <c r="G52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="45" t="s">
-        <v>7585</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>7586</v>
+      <c r="A53" s="28" t="s">
+        <v>7596</v>
       </c>
       <c r="C53" s="28"/>
-      <c r="D53" s="1" t="s">
-        <v>7515</v>
-      </c>
       <c r="E53" s="28"/>
-      <c r="F53" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>7517</v>
-      </c>
+      <c r="F53" s="28"/>
+      <c r="G53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="45"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
+      <c r="A54" s="45" t="s">
+        <v>7597</v>
+      </c>
+      <c r="B54" s="46" t="s">
+        <v>7598</v>
+      </c>
+      <c r="C54" s="45" t="s">
+        <v>7599</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>7567</v>
+      </c>
       <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="2"/>
+      <c r="F54" s="0" t="s">
+        <v>7568</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>7569</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="28" t="s">
-        <v>7587</v>
-      </c>
-      <c r="C55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="2"/>
+      <c r="A55" s="45" t="s">
+        <v>7597</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>7600</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>7601</v>
+      </c>
+      <c r="E55" s="28" t="s">
+        <v>7602</v>
+      </c>
+      <c r="F55" s="43" t="s">
+        <v>7505</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>7506</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="45" t="s">
-        <v>7588</v>
-      </c>
-      <c r="B56" s="46" t="s">
-        <v>7589</v>
-      </c>
-      <c r="C56" s="45" t="s">
-        <v>7590</v>
-      </c>
+        <v>7603</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>7604</v>
+      </c>
+      <c r="C56" s="28"/>
       <c r="D56" s="1" t="s">
-        <v>7558</v>
+        <v>7524</v>
       </c>
       <c r="E56" s="28"/>
-      <c r="F56" s="0" t="s">
-        <v>7559</v>
+      <c r="F56" s="28" t="s">
+        <v>7525</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>7560</v>
+        <v>7526</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="45" t="s">
-        <v>7588</v>
+      <c r="A57" s="28" t="s">
+        <v>7605</v>
       </c>
       <c r="B57" s="28" t="s">
-        <v>7591</v>
-      </c>
-      <c r="C57" s="28" t="s">
-        <v>7592</v>
-      </c>
-      <c r="E57" s="28" t="s">
-        <v>7593</v>
-      </c>
-      <c r="F57" s="43" t="s">
-        <v>7496</v>
+        <v>7606</v>
+      </c>
+      <c r="C57" s="28"/>
+      <c r="E57" s="43" t="s">
+        <v>7607</v>
+      </c>
+      <c r="F57" s="0" t="s">
+        <v>7608</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>7497</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="45" t="s">
-        <v>7594</v>
-      </c>
-      <c r="B58" s="28" t="s">
-        <v>7595</v>
-      </c>
-      <c r="C58" s="28"/>
-      <c r="D58" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E58" s="28"/>
+      <c r="A58" s="47" t="n">
+        <v>32140</v>
+      </c>
+      <c r="B58" s="43" t="s">
+        <v>7609</v>
+      </c>
+      <c r="C58" s="48" t="s">
+        <v>7610</v>
+      </c>
+      <c r="E58" s="43"/>
       <c r="F58" s="28" t="s">
-        <v>7516</v>
+        <v>7611</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>7517</v>
+        <v>7612</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="28" t="s">
-        <v>7596</v>
-      </c>
-      <c r="B59" s="28" t="s">
-        <v>7597</v>
-      </c>
-      <c r="C59" s="28"/>
-      <c r="E59" s="43" t="s">
-        <v>7598</v>
-      </c>
-      <c r="F59" s="0" t="s">
-        <v>7599</v>
+      <c r="A59" s="47" t="n">
+        <v>32140</v>
+      </c>
+      <c r="B59" s="43" t="s">
+        <v>7609</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>7613</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>7614</v>
+      </c>
+      <c r="E59" s="28" t="s">
+        <v>7615</v>
+      </c>
+      <c r="F59" s="43" t="s">
+        <v>7616</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="47" t="n">
-        <v>32140</v>
-      </c>
-      <c r="B60" s="43" t="s">
-        <v>7600</v>
-      </c>
-      <c r="C60" s="48" t="s">
-        <v>7601</v>
-      </c>
-      <c r="E60" s="43"/>
-      <c r="F60" s="28" t="s">
-        <v>7602</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>7603</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="n">
-        <v>32140</v>
-      </c>
-      <c r="B61" s="43" t="s">
-        <v>7600</v>
+        <v>7617</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="47" t="s">
+        <v>7618</v>
+      </c>
+      <c r="B60" s="28" t="s">
+        <v>7619</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>7620</v>
+      </c>
+      <c r="E60" s="49" t="s">
+        <v>7621</v>
+      </c>
+      <c r="F60" s="43" t="s">
+        <v>7546</v>
+      </c>
+      <c r="G60" s="50" t="s">
+        <v>7622</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="47" t="s">
+        <v>7623</v>
+      </c>
+      <c r="B61" s="28" t="s">
+        <v>7606</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>7604</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>7605</v>
+        <v>7624</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>7625</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>7606</v>
-      </c>
-      <c r="F61" s="43" t="s">
-        <v>7607</v>
+        <v>7626</v>
+      </c>
+      <c r="F61" s="28" t="s">
+        <v>7530</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>7608</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="47" t="s">
-        <v>7609</v>
-      </c>
-      <c r="B62" s="28" t="s">
-        <v>7610</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>7611</v>
-      </c>
-      <c r="E62" s="49" t="s">
-        <v>7612</v>
-      </c>
-      <c r="F62" s="43" t="s">
-        <v>7537</v>
-      </c>
-      <c r="G62" s="50" t="s">
-        <v>7613</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="47" t="s">
-        <v>7614</v>
-      </c>
-      <c r="B63" s="28" t="s">
-        <v>7597</v>
+      <c r="A62" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B62" s="28"/>
+      <c r="C62" s="48" t="s">
+        <v>7627</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>7628</v>
+      </c>
+      <c r="E62" s="46" t="s">
+        <v>7629</v>
+      </c>
+      <c r="F62" s="46" t="s">
+        <v>7630</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>7631</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="47" t="n">
+        <v>32471</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7632</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>7615</v>
-      </c>
-      <c r="D63" s="43" t="s">
-        <v>7616</v>
-      </c>
-      <c r="E63" s="28" t="s">
-        <v>7617</v>
-      </c>
-      <c r="F63" s="28" t="s">
-        <v>7521</v>
+        <v>7633</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>7634</v>
+      </c>
+      <c r="E63" s="49"/>
+      <c r="F63" s="43" t="s">
+        <v>7582</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7583</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="47" t="n">
         <v>32471</v>
       </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="48" t="s">
-        <v>7618</v>
-      </c>
-      <c r="D64" s="0" t="s">
-        <v>7619</v>
-      </c>
-      <c r="E64" s="46" t="s">
-        <v>7620</v>
-      </c>
-      <c r="F64" s="46" t="s">
-        <v>7621</v>
+      <c r="B64" s="28" t="s">
+        <v>7635</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>7636</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>7637</v>
+      </c>
+      <c r="E64" s="28"/>
+      <c r="F64" s="1" t="s">
+        <v>7638</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>7622</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7639</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="47" t="n">
         <v>32471</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>7623</v>
+      <c r="B65" s="28" t="s">
+        <v>7640</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>7624</v>
-      </c>
-      <c r="D65" s="28" t="s">
-        <v>7625</v>
-      </c>
-      <c r="E65" s="49"/>
-      <c r="F65" s="43" t="s">
-        <v>7573</v>
+        <v>7641</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>7642</v>
+      </c>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28" t="s">
+        <v>7616</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>7574</v>
+        <v>7643</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -83494,395 +84770,399 @@
         <v>32471</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>7626</v>
+        <v>7640</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>7627</v>
-      </c>
-      <c r="D66" s="28" t="s">
-        <v>7628</v>
-      </c>
-      <c r="E66" s="28"/>
-      <c r="F66" s="1" t="s">
-        <v>7629</v>
+        <v>7644</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>7642</v>
+      </c>
+      <c r="E66" s="28" t="s">
+        <v>7645</v>
+      </c>
+      <c r="F66" s="28" t="s">
+        <v>7530</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>7630</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="47" t="n">
-        <v>32471</v>
+        <v>32517</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>7631</v>
+        <v>7646</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>7632</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>7633</v>
+        <v>7647</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>7648</v>
       </c>
       <c r="E67" s="28"/>
-      <c r="F67" s="28" t="s">
-        <v>7607</v>
+      <c r="F67" s="1" t="s">
+        <v>7649</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>7634</v>
+        <v>7650</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="47" t="n">
-        <v>32471</v>
-      </c>
+      <c r="A68" s="47"/>
       <c r="B68" s="28" t="s">
-        <v>7631</v>
-      </c>
-      <c r="C68" s="28" t="s">
-        <v>7635</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>7633</v>
-      </c>
-      <c r="E68" s="28" t="s">
-        <v>7636</v>
-      </c>
-      <c r="F68" s="28" t="s">
-        <v>7521</v>
+        <v>7651</v>
+      </c>
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="43" t="s">
+        <v>7505</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>7522</v>
+        <v>7506</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="47" t="n">
-        <v>32517</v>
+      <c r="A69" s="47" t="s">
+        <v>7652</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>7637</v>
+        <v>7653</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>7638</v>
-      </c>
-      <c r="D69" s="28" t="s">
-        <v>7639</v>
+        <v>7654</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>7524</v>
       </c>
       <c r="E69" s="28"/>
-      <c r="F69" s="1" t="s">
-        <v>7640</v>
+      <c r="F69" s="28" t="s">
+        <v>7525</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>7641</v>
+        <v>7526</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="47"/>
+      <c r="A70" s="47" t="s">
+        <v>7655</v>
+      </c>
       <c r="B70" s="28" t="s">
-        <v>7642</v>
+        <v>7606</v>
       </c>
       <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="43" t="s">
-        <v>7496</v>
+      <c r="D70" s="43" t="s">
+        <v>7625</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>7656</v>
+      </c>
+      <c r="F70" s="28" t="s">
+        <v>7530</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>7497</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="47" t="s">
-        <v>7643</v>
+        <v>7657</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>7644</v>
-      </c>
-      <c r="C71" s="28" t="s">
-        <v>7645</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E71" s="28"/>
+        <v>7658</v>
+      </c>
+      <c r="C71" s="28"/>
+      <c r="D71" s="43" t="s">
+        <v>7625</v>
+      </c>
+      <c r="E71" s="28" t="s">
+        <v>7659</v>
+      </c>
       <c r="F71" s="28" t="s">
-        <v>7516</v>
+        <v>7530</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>7517</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="47" t="s">
-        <v>7646</v>
+        <v>7660</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>7597</v>
-      </c>
-      <c r="C72" s="28"/>
+        <v>7661</v>
+      </c>
+      <c r="C72" s="28" t="s">
+        <v>7662</v>
+      </c>
       <c r="D72" s="43" t="s">
-        <v>7616</v>
+        <v>7625</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>7647</v>
+        <v>7663</v>
       </c>
       <c r="F72" s="28" t="s">
-        <v>7521</v>
+        <v>7530</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="47" t="s">
-        <v>7648</v>
-      </c>
-      <c r="B73" s="28" t="s">
-        <v>7649</v>
-      </c>
-      <c r="C73" s="28"/>
+        <v>7531</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="43" t="s">
+        <v>7664</v>
+      </c>
+      <c r="B73" s="0"/>
+      <c r="C73" s="28" t="s">
+        <v>7665</v>
+      </c>
       <c r="D73" s="43" t="s">
-        <v>7616</v>
+        <v>7666</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>7650</v>
-      </c>
-      <c r="F73" s="28" t="s">
-        <v>7521</v>
+        <v>7667</v>
+      </c>
+      <c r="F73" s="51" t="s">
+        <v>7668</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>7522</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="47" t="s">
-        <v>7651</v>
-      </c>
-      <c r="B74" s="28" t="s">
-        <v>7652</v>
+        <v>7669</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="45" t="s">
+        <v>7670</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>7671</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>7653</v>
-      </c>
-      <c r="D74" s="43" t="s">
-        <v>7616</v>
-      </c>
-      <c r="E74" s="28" t="s">
-        <v>7654</v>
-      </c>
-      <c r="F74" s="28" t="s">
-        <v>7521</v>
+        <v>7672</v>
+      </c>
+      <c r="F74" s="43" t="s">
+        <v>7505</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>7522</v>
+        <v>7506</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="43" t="s">
-        <v>7655</v>
-      </c>
-      <c r="B75" s="0"/>
-      <c r="C75" s="28" t="s">
-        <v>7656</v>
-      </c>
-      <c r="D75" s="43" t="s">
-        <v>7657</v>
-      </c>
-      <c r="E75" s="28" t="s">
-        <v>7658</v>
-      </c>
-      <c r="F75" s="51" t="s">
-        <v>7659</v>
+      <c r="A75" s="45" t="s">
+        <v>7673</v>
+      </c>
+      <c r="B75" s="46" t="s">
+        <v>7674</v>
+      </c>
+      <c r="C75" s="48" t="s">
+        <v>7675</v>
+      </c>
+      <c r="D75" s="0"/>
+      <c r="F75" s="43" t="s">
+        <v>7505</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>7660</v>
+        <v>7506</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="45" t="s">
-        <v>7661</v>
-      </c>
-      <c r="B76" s="0" t="s">
-        <v>7662</v>
-      </c>
-      <c r="C76" s="28" t="s">
-        <v>7663</v>
-      </c>
-      <c r="F76" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>7497</v>
-      </c>
+      <c r="A76" s="45"/>
     </row>
     <row r="77" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="45" t="s">
-        <v>7664</v>
-      </c>
-      <c r="B77" s="46" t="s">
-        <v>7665</v>
-      </c>
-      <c r="C77" s="48" t="s">
-        <v>7666</v>
-      </c>
-      <c r="D77" s="0"/>
-      <c r="F77" s="43" t="s">
-        <v>7496</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>7497</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="45"/>
-    </row>
-    <row r="79" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="43" t="s">
-        <v>7667</v>
-      </c>
-      <c r="B79" s="28"/>
-      <c r="D79" s="43"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="51"/>
-      <c r="G79" s="2"/>
+      <c r="A77" s="43" t="s">
+        <v>7676</v>
+      </c>
+      <c r="B77" s="28"/>
+      <c r="D77" s="43"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="51"/>
+      <c r="G77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="47" t="n">
+        <v>38164</v>
+      </c>
+      <c r="B78" s="43" t="s">
+        <v>7677</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>7678</v>
+      </c>
+      <c r="D78" s="28" t="s">
+        <v>7679</v>
+      </c>
+      <c r="E78" s="28" t="s">
+        <v>7680</v>
+      </c>
+      <c r="F78" s="28" t="s">
+        <v>7681</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>7682</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="47" t="s">
+        <v>7683</v>
+      </c>
+      <c r="B79" s="52" t="s">
+        <v>7684</v>
+      </c>
+      <c r="C79" s="52" t="s">
+        <v>7685</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>7686</v>
+      </c>
+      <c r="E79" s="45" t="s">
+        <v>7687</v>
+      </c>
+      <c r="F79" s="28" t="s">
+        <v>7688</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>7689</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="47" t="n">
-        <v>38164</v>
+      <c r="A80" s="47" t="s">
+        <v>7690</v>
       </c>
       <c r="B80" s="43" t="s">
-        <v>7668</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>7669</v>
-      </c>
-      <c r="D80" s="28" t="s">
-        <v>7670</v>
-      </c>
-      <c r="E80" s="28" t="s">
-        <v>7671</v>
-      </c>
-      <c r="F80" s="28" t="s">
-        <v>7672</v>
+        <v>7691</v>
+      </c>
+      <c r="C80" s="28" t="s">
+        <v>7692</v>
+      </c>
+      <c r="D80" s="43" t="s">
+        <v>7693</v>
+      </c>
+      <c r="E80" s="43"/>
+      <c r="F80" s="43" t="s">
+        <v>7511</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>7673</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7512</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="47" t="s">
-        <v>7674</v>
-      </c>
-      <c r="B81" s="52" t="s">
-        <v>7675</v>
-      </c>
-      <c r="C81" s="52" t="s">
-        <v>7676</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>7677</v>
-      </c>
-      <c r="E81" s="45" t="s">
-        <v>7678</v>
-      </c>
-      <c r="F81" s="28" t="s">
-        <v>7679</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>7680</v>
+        <v>7690</v>
+      </c>
+      <c r="B81" s="28" t="s">
+        <v>7694</v>
+      </c>
+      <c r="C81" s="28" t="s">
+        <v>7695</v>
+      </c>
+      <c r="D81" s="28" t="s">
+        <v>7696</v>
+      </c>
+      <c r="E81" s="28" t="s">
+        <v>7697</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>7698</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>7699</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="47" t="s">
-        <v>7681</v>
-      </c>
-      <c r="B82" s="43" t="s">
-        <v>7682</v>
+        <v>7700</v>
+      </c>
+      <c r="B82" s="28" t="s">
+        <v>7694</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>7683</v>
-      </c>
-      <c r="D82" s="43" t="s">
-        <v>7684</v>
-      </c>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43" t="s">
-        <v>7502</v>
+        <v>7701</v>
+      </c>
+      <c r="D82" s="28" t="s">
+        <v>7702</v>
+      </c>
+      <c r="E82" s="28"/>
+      <c r="F82" s="1" t="s">
+        <v>7698</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>7503</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="47" t="s">
-        <v>7681</v>
+        <v>7699</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="47" t="n">
+        <v>42230</v>
       </c>
       <c r="B83" s="28" t="s">
-        <v>7685</v>
+        <v>7694</v>
       </c>
       <c r="C83" s="28" t="s">
-        <v>7686</v>
+        <v>7703</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>7687</v>
+        <v>7704</v>
       </c>
       <c r="E83" s="28" t="s">
-        <v>7688</v>
+        <v>7705</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>7689</v>
+        <v>7698</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>7690</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="47" t="s">
-        <v>7691</v>
-      </c>
-      <c r="B84" s="28" t="s">
-        <v>7685</v>
-      </c>
-      <c r="C84" s="28" t="s">
-        <v>7692</v>
-      </c>
-      <c r="D84" s="28" t="s">
-        <v>7693</v>
-      </c>
-      <c r="E84" s="28"/>
-      <c r="F84" s="1" t="s">
-        <v>7689</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>7690</v>
-      </c>
-    </row>
+        <v>7699</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="85" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="47" t="n">
-        <v>42230</v>
-      </c>
-      <c r="B85" s="28" t="s">
-        <v>7685</v>
-      </c>
-      <c r="C85" s="28" t="s">
-        <v>7694</v>
-      </c>
-      <c r="D85" s="28" t="s">
-        <v>7695</v>
-      </c>
-      <c r="E85" s="28" t="s">
-        <v>7696</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>7689</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>7690</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="87" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="43" t="s">
-        <v>7697</v>
+      <c r="A85" s="43" t="s">
+        <v>7706</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="47" t="n">
+        <v>42753</v>
+      </c>
+      <c r="B86" s="52" t="s">
+        <v>7707</v>
+      </c>
+      <c r="C86" s="43" t="s">
+        <v>7708</v>
+      </c>
+      <c r="D86" s="43" t="s">
+        <v>7709</v>
+      </c>
+      <c r="E86" s="43" t="s">
+        <v>7710</v>
+      </c>
+      <c r="F86" s="43" t="s">
+        <v>7511</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>7512</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="47" t="n">
+        <v>42753</v>
+      </c>
+      <c r="B87" s="52" t="s">
+        <v>7711</v>
+      </c>
+      <c r="C87" s="28" t="s">
+        <v>7712</v>
+      </c>
+      <c r="D87" s="43" t="s">
+        <v>7709</v>
+      </c>
+      <c r="E87" s="53" t="s">
+        <v>7713</v>
+      </c>
+      <c r="F87" s="43" t="s">
+        <v>7511</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>7512</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -83890,427 +85170,397 @@
         <v>42753</v>
       </c>
       <c r="B88" s="52" t="s">
-        <v>7698</v>
-      </c>
-      <c r="C88" s="43" t="s">
-        <v>7699</v>
-      </c>
-      <c r="D88" s="43" t="s">
-        <v>7700</v>
+        <v>7711</v>
+      </c>
+      <c r="C88" s="52" t="s">
+        <v>7714</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>7715</v>
       </c>
       <c r="E88" s="43" t="s">
-        <v>7701</v>
-      </c>
-      <c r="F88" s="43" t="s">
-        <v>7502</v>
+        <v>7716</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>7717</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>7503</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7718</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="47" t="n">
-        <v>42753</v>
-      </c>
-      <c r="B89" s="52" t="s">
-        <v>7702</v>
+        <v>43725</v>
+      </c>
+      <c r="B89" s="28" t="s">
+        <v>7719</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>7703</v>
-      </c>
-      <c r="D89" s="43" t="s">
-        <v>7700</v>
-      </c>
-      <c r="E89" s="53" t="s">
-        <v>7704</v>
-      </c>
-      <c r="F89" s="43" t="s">
-        <v>7502</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>7503</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7720</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>7721</v>
+      </c>
+      <c r="E89" s="28" t="s">
+        <v>7722</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>7723</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>7724</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="47" t="n">
-        <v>42753</v>
-      </c>
-      <c r="B90" s="52" t="s">
-        <v>7702</v>
-      </c>
-      <c r="C90" s="52" t="s">
-        <v>7705</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>7706</v>
-      </c>
-      <c r="E90" s="43" t="s">
-        <v>7707</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>7708</v>
+        <v>44895</v>
+      </c>
+      <c r="B90" s="28" t="s">
+        <v>7725</v>
+      </c>
+      <c r="C90" s="28" t="s">
+        <v>7726</v>
+      </c>
+      <c r="D90" s="43" t="s">
+        <v>7727</v>
+      </c>
+      <c r="E90" s="28" t="s">
+        <v>7728</v>
+      </c>
+      <c r="F90" s="28" t="s">
+        <v>7729</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>7709</v>
+        <v>7730</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="47" t="n">
-        <v>43725</v>
+        <v>45449</v>
       </c>
       <c r="B91" s="28" t="s">
-        <v>7710</v>
+        <v>7731</v>
       </c>
       <c r="C91" s="28" t="s">
-        <v>7711</v>
+        <v>7732</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>7712</v>
+        <v>7733</v>
       </c>
       <c r="E91" s="28" t="s">
-        <v>7713</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>7714</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>7715</v>
+        <v>7734</v>
+      </c>
+      <c r="F91" s="28" t="s">
+        <v>7735</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>7736</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="47" t="n">
-        <v>44895</v>
+        <v>46017</v>
       </c>
       <c r="B92" s="28" t="s">
-        <v>7716</v>
+        <v>7737</v>
       </c>
       <c r="C92" s="28" t="s">
-        <v>7717</v>
-      </c>
-      <c r="D92" s="43" t="s">
-        <v>7718</v>
+        <v>7738</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>7739</v>
       </c>
       <c r="E92" s="28" t="s">
-        <v>7719</v>
+        <v>7740</v>
       </c>
       <c r="F92" s="28" t="s">
-        <v>7720</v>
+        <v>7741</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>7721</v>
+        <v>7742</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="47" t="n">
-        <v>45449</v>
-      </c>
+      <c r="A93" s="47"/>
       <c r="B93" s="28" t="s">
-        <v>7722</v>
-      </c>
-      <c r="C93" s="28" t="s">
-        <v>7723</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>7724</v>
-      </c>
-      <c r="E93" s="28" t="s">
-        <v>7725</v>
-      </c>
-      <c r="F93" s="28" t="s">
-        <v>7726</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>7727</v>
-      </c>
+        <v>7743</v>
+      </c>
+      <c r="C93" s="43" t="s">
+        <v>7744</v>
+      </c>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
     </row>
     <row r="94" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="47" t="n">
-        <v>46017</v>
-      </c>
-      <c r="B94" s="28" t="s">
-        <v>7728</v>
-      </c>
-      <c r="C94" s="28" t="s">
-        <v>7729</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>7730</v>
-      </c>
-      <c r="E94" s="28" t="s">
-        <v>7731</v>
-      </c>
-      <c r="F94" s="28" t="s">
-        <v>7732</v>
+        <v>41741</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7745</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>7733</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="47"/>
-      <c r="B95" s="28" t="s">
-        <v>7734</v>
-      </c>
-      <c r="C95" s="43" t="s">
-        <v>7735</v>
-      </c>
-      <c r="E95" s="28"/>
-      <c r="F95" s="28"/>
-    </row>
-    <row r="96" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="47" t="n">
-        <v>41741</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>7736</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>7737</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="47"/>
-      <c r="B100" s="28"/>
-      <c r="C100" s="28"/>
-      <c r="E100" s="28"/>
-      <c r="F100" s="28"/>
-      <c r="G100" s="2"/>
-    </row>
-    <row r="101" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="43" t="s">
-        <v>7738</v>
-      </c>
-      <c r="B101" s="28"/>
-      <c r="C101" s="28"/>
-      <c r="E101" s="28"/>
-      <c r="F101" s="28"/>
-      <c r="G101" s="2"/>
-    </row>
-    <row r="102" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="54" t="s">
-        <v>7739</v>
-      </c>
-      <c r="B102" s="43" t="s">
-        <v>7740</v>
+        <v>7746</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="47"/>
+      <c r="B98" s="28"/>
+      <c r="C98" s="28"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="2"/>
+    </row>
+    <row r="99" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="43" t="s">
+        <v>7747</v>
+      </c>
+      <c r="B99" s="28"/>
+      <c r="C99" s="28"/>
+      <c r="E99" s="28"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="54" t="s">
+        <v>7748</v>
+      </c>
+      <c r="B100" s="43" t="s">
+        <v>7749</v>
+      </c>
+      <c r="C100" s="28" t="s">
+        <v>7750</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>7524</v>
+      </c>
+      <c r="E100" s="28" t="s">
+        <v>7667</v>
+      </c>
+      <c r="F100" s="28" t="s">
+        <v>7525</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>7526</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="54" t="s">
+        <v>7751</v>
+      </c>
+      <c r="B101" s="43" t="s">
+        <v>7752</v>
+      </c>
+      <c r="C101" s="28" t="s">
+        <v>7753</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>7754</v>
+      </c>
+      <c r="F101" s="51" t="s">
+        <v>7668</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>7669</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="45" t="s">
+        <v>7755</v>
+      </c>
+      <c r="B102" s="52" t="s">
+        <v>7756</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>7741</v>
+        <v>7757</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E102" s="28" t="s">
-        <v>7658</v>
+        <v>7524</v>
       </c>
       <c r="F102" s="28" t="s">
-        <v>7516</v>
+        <v>7525</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7526</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="54" t="s">
-        <v>7742</v>
-      </c>
-      <c r="B103" s="43" t="s">
-        <v>7743</v>
+        <v>7758</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>7759</v>
       </c>
       <c r="C103" s="28" t="s">
-        <v>7744</v>
+        <v>7760</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>7745</v>
-      </c>
-      <c r="F103" s="51" t="s">
-        <v>7659</v>
+        <v>7524</v>
+      </c>
+      <c r="E103" s="28" t="s">
+        <v>7761</v>
+      </c>
+      <c r="F103" s="28" t="s">
+        <v>7525</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>7660</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="45" t="s">
-        <v>7746</v>
-      </c>
-      <c r="B104" s="52" t="s">
-        <v>7747</v>
+        <v>7526</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="54" t="s">
+        <v>7762</v>
+      </c>
+      <c r="B104" s="28" t="s">
+        <v>7763</v>
       </c>
       <c r="C104" s="28" t="s">
-        <v>7748</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>7515</v>
-      </c>
+        <v>7764</v>
+      </c>
+      <c r="E104" s="28"/>
       <c r="F104" s="28" t="s">
-        <v>7516</v>
+        <v>7525</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>7517</v>
+        <v>7526</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="54" t="s">
-        <v>7749</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>7750</v>
+        <v>7765</v>
+      </c>
+      <c r="B105" s="28" t="s">
+        <v>7766</v>
       </c>
       <c r="C105" s="28" t="s">
-        <v>7751</v>
+        <v>7767</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>7515</v>
-      </c>
-      <c r="E105" s="28" t="s">
-        <v>7752</v>
-      </c>
-      <c r="F105" s="28" t="s">
-        <v>7516</v>
+        <v>7754</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>7768</v>
+      </c>
+      <c r="F105" s="51" t="s">
+        <v>7668</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>7517</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="54" t="s">
-        <v>7753</v>
+        <v>7669</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="47" t="n">
+        <v>44662</v>
       </c>
       <c r="B106" s="28" t="s">
-        <v>7754</v>
-      </c>
-      <c r="C106" s="28" t="s">
-        <v>7755</v>
-      </c>
-      <c r="E106" s="28"/>
-      <c r="F106" s="28" t="s">
-        <v>7516</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>7517</v>
+        <v>7769</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>7770</v>
+      </c>
+      <c r="D106" s="28" t="s">
+        <v>7771</v>
+      </c>
+      <c r="E106" s="28" t="s">
+        <v>7772</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>7773</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>7774</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="54" t="s">
-        <v>7756</v>
+        <v>7775</v>
       </c>
       <c r="B107" s="28" t="s">
-        <v>7757</v>
-      </c>
-      <c r="C107" s="28" t="s">
-        <v>7758</v>
-      </c>
+        <v>7776</v>
+      </c>
+      <c r="C107" s="28"/>
       <c r="D107" s="1" t="s">
-        <v>7745</v>
+        <v>7754</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>7759</v>
+        <v>7777</v>
       </c>
       <c r="F107" s="51" t="s">
-        <v>7659</v>
+        <v>7668</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>7660</v>
+        <v>7669</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="47" t="n">
-        <v>44662</v>
+        <v>44776</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>7760</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>7761</v>
+        <v>7778</v>
+      </c>
+      <c r="C108" s="28" t="s">
+        <v>7779</v>
       </c>
       <c r="D108" s="28" t="s">
-        <v>7762</v>
+        <v>7780</v>
       </c>
       <c r="E108" s="28" t="s">
-        <v>7763</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>7764</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>7765</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="54" t="s">
-        <v>7766</v>
-      </c>
-      <c r="B109" s="28" t="s">
-        <v>7767</v>
-      </c>
-      <c r="C109" s="28"/>
-      <c r="D109" s="1" t="s">
-        <v>7745</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>7768</v>
-      </c>
-      <c r="F109" s="51" t="s">
-        <v>7659</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>7660</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="47" t="n">
-        <v>44776</v>
-      </c>
-      <c r="B110" s="28" t="s">
-        <v>7769</v>
-      </c>
-      <c r="C110" s="28" t="s">
-        <v>7770</v>
-      </c>
-      <c r="D110" s="28" t="s">
-        <v>7771</v>
-      </c>
-      <c r="E110" s="28" t="s">
-        <v>7772</v>
-      </c>
-      <c r="F110" s="28" t="s">
-        <v>7773</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>7774</v>
-      </c>
-    </row>
-    <row r="112" s="55" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="1"/>
-      <c r="K112" s="1"/>
-      <c r="L112" s="1"/>
-      <c r="M112" s="1"/>
-      <c r="N112" s="1"/>
-      <c r="O112" s="1"/>
-      <c r="P112" s="1"/>
-      <c r="Q112" s="1"/>
-      <c r="R112" s="1"/>
-      <c r="S112" s="1"/>
-      <c r="T112" s="1"/>
-      <c r="U112" s="1"/>
-      <c r="V112" s="1"/>
-      <c r="W112" s="1"/>
-      <c r="X112" s="1"/>
-      <c r="Y112" s="1"/>
-      <c r="Z112" s="1"/>
-      <c r="AA112" s="1"/>
-      <c r="AB112" s="1"/>
-      <c r="AC112" s="1"/>
-      <c r="AD112" s="1"/>
+        <v>7781</v>
+      </c>
+      <c r="F108" s="28" t="s">
+        <v>7782</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>7783</v>
+      </c>
+    </row>
+    <row r="110" s="55" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+      <c r="N110" s="1"/>
+      <c r="O110" s="1"/>
+      <c r="P110" s="1"/>
+      <c r="Q110" s="1"/>
+      <c r="R110" s="1"/>
+      <c r="S110" s="1"/>
+      <c r="T110" s="1"/>
+      <c r="U110" s="1"/>
+      <c r="V110" s="1"/>
+      <c r="W110" s="1"/>
+      <c r="X110" s="1"/>
+      <c r="Y110" s="1"/>
+      <c r="Z110" s="1"/>
+      <c r="AA110" s="1"/>
+      <c r="AB110" s="1"/>
+      <c r="AC110" s="1"/>
+      <c r="AD110" s="1"/>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0"/>
+      <c r="B111" s="0"/>
+      <c r="C111" s="0"/>
+      <c r="D111" s="0"/>
+      <c r="E111" s="0"/>
+      <c r="F111" s="0"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0"/>
+      <c r="B112" s="0"/>
+      <c r="C112" s="0"/>
+      <c r="D112" s="0"/>
+      <c r="E112" s="0"/>
+      <c r="F112" s="0"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0"/>
@@ -84320,7 +85570,7 @@
       <c r="E113" s="0"/>
       <c r="F113" s="0"/>
     </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="0"/>
       <c r="B114" s="0"/>
       <c r="C114" s="0"/>
@@ -84336,7 +85586,7 @@
       <c r="E115" s="0"/>
       <c r="F115" s="0"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="0"/>
       <c r="B116" s="0"/>
       <c r="C116" s="0"/>
@@ -84352,7 +85602,7 @@
       <c r="E117" s="0"/>
       <c r="F117" s="0"/>
     </row>
-    <row r="118" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0"/>
       <c r="B118" s="0"/>
       <c r="C118" s="0"/>
@@ -84408,1249 +85658,1324 @@
       <c r="E124" s="0"/>
       <c r="F124" s="0"/>
     </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0"/>
-      <c r="B125" s="0"/>
-      <c r="C125" s="0"/>
-      <c r="D125" s="0"/>
-      <c r="E125" s="0"/>
-      <c r="F125" s="0"/>
-    </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0"/>
-      <c r="B126" s="0"/>
-      <c r="C126" s="0"/>
-      <c r="D126" s="0"/>
-      <c r="E126" s="0"/>
-      <c r="F126" s="0"/>
-    </row>
-    <row r="127" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="54" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B126" s="46" t="s">
+        <v>7784</v>
+      </c>
+      <c r="C126" s="56" t="s">
+        <v>7785</v>
+      </c>
+      <c r="D126" s="48" t="s">
+        <v>7786</v>
+      </c>
+      <c r="E126" s="44" t="s">
+        <v>7787</v>
+      </c>
+      <c r="F126" s="44"/>
+      <c r="G126" s="50" t="s">
+        <v>7788</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="54" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B127" s="46" t="s">
+        <v>7789</v>
+      </c>
+      <c r="C127" s="48"/>
+      <c r="D127" s="48"/>
+      <c r="E127" s="44"/>
+      <c r="F127" s="44"/>
+      <c r="G127" s="1" t="s">
+        <v>7790</v>
+      </c>
+    </row>
     <row r="128" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="54" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B128" s="46" t="s">
-        <v>7775</v>
-      </c>
-      <c r="C128" s="56" t="s">
-        <v>7776</v>
-      </c>
-      <c r="D128" s="48" t="s">
-        <v>7777</v>
-      </c>
-      <c r="E128" s="44" t="s">
-        <v>7778</v>
-      </c>
+      <c r="A128" s="54"/>
+      <c r="B128" s="46"/>
+      <c r="C128" s="48"/>
+      <c r="D128" s="48"/>
+      <c r="E128" s="44"/>
       <c r="F128" s="44"/>
-      <c r="G128" s="50" t="s">
-        <v>7779</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="54" t="n">
-        <v>45138</v>
-      </c>
-      <c r="B129" s="46" t="s">
-        <v>7780</v>
-      </c>
-      <c r="C129" s="48"/>
-      <c r="D129" s="48"/>
-      <c r="E129" s="44"/>
-      <c r="F129" s="44"/>
-      <c r="G129" s="1" t="s">
-        <v>7781</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="54"/>
-      <c r="B130" s="46"/>
-      <c r="C130" s="48"/>
-      <c r="D130" s="48"/>
-      <c r="E130" s="44"/>
-      <c r="F130" s="44"/>
-      <c r="G130" s="1"/>
-    </row>
-    <row r="132" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G128" s="1"/>
+    </row>
+    <row r="130" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>7791</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="57" t="s">
+        <v>7792</v>
+      </c>
+      <c r="B131" s="41" t="s">
+        <v>7793</v>
+      </c>
+      <c r="C131" s="41" t="s">
+        <v>7794</v>
+      </c>
+      <c r="D131" s="41"/>
+      <c r="E131" s="41" t="s">
+        <v>7795</v>
+      </c>
+      <c r="F131" s="41" t="s">
+        <v>7796</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>7797</v>
+      </c>
+    </row>
+    <row r="132" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>7782</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>7798</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>7799</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>7800</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>7801</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>7802</v>
+      </c>
+      <c r="F132" s="58" t="s">
+        <v>7803</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>7804</v>
+      </c>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1"/>
+      <c r="L132" s="1"/>
+      <c r="M132" s="1"/>
+      <c r="N132" s="1"/>
+      <c r="O132" s="1"/>
+      <c r="P132" s="1"/>
+      <c r="Q132" s="1"/>
+      <c r="R132" s="1"/>
+      <c r="S132" s="1"/>
+      <c r="T132" s="1"/>
+      <c r="U132" s="1"/>
+      <c r="V132" s="1"/>
+      <c r="W132" s="1"/>
+      <c r="X132" s="1"/>
+      <c r="Y132" s="1"/>
+      <c r="Z132" s="1"/>
+      <c r="AA132" s="1"/>
+      <c r="AB132" s="1"/>
+      <c r="AC132" s="1"/>
+      <c r="AD132" s="1"/>
+    </row>
+    <row r="133" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="57" t="s">
-        <v>7783</v>
+        <v>7805</v>
       </c>
       <c r="B133" s="41" t="s">
-        <v>7784</v>
+        <v>7806</v>
       </c>
       <c r="C133" s="41" t="s">
-        <v>7785</v>
-      </c>
-      <c r="D133" s="41"/>
+        <v>7807</v>
+      </c>
+      <c r="D133" s="59" t="s">
+        <v>7808</v>
+      </c>
       <c r="E133" s="41" t="s">
-        <v>7786</v>
+        <v>7809</v>
       </c>
       <c r="F133" s="41" t="s">
-        <v>7787</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>7788</v>
+        <v>7796</v>
+      </c>
+      <c r="G133" s="41" t="s">
+        <v>7810</v>
       </c>
     </row>
     <row r="134" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="s">
-        <v>7789</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>7790</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>7791</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>7792</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>7793</v>
-      </c>
-      <c r="F134" s="58" t="s">
-        <v>7794</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>7795</v>
-      </c>
-      <c r="H134" s="1"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="1"/>
-      <c r="K134" s="1"/>
-      <c r="L134" s="1"/>
-      <c r="M134" s="1"/>
-      <c r="N134" s="1"/>
-      <c r="O134" s="1"/>
-      <c r="P134" s="1"/>
-      <c r="Q134" s="1"/>
-      <c r="R134" s="1"/>
-      <c r="S134" s="1"/>
-      <c r="T134" s="1"/>
-      <c r="U134" s="1"/>
-      <c r="V134" s="1"/>
-      <c r="W134" s="1"/>
-      <c r="X134" s="1"/>
-      <c r="Y134" s="1"/>
-      <c r="Z134" s="1"/>
-      <c r="AA134" s="1"/>
-      <c r="AB134" s="1"/>
-      <c r="AC134" s="1"/>
-      <c r="AD134" s="1"/>
-    </row>
-    <row r="135" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="57" t="s">
-        <v>7796</v>
+      <c r="A134" s="60" t="n">
+        <v>42355</v>
+      </c>
+      <c r="B134" s="41" t="s">
+        <v>7811</v>
+      </c>
+      <c r="C134" s="41" t="s">
+        <v>7812</v>
+      </c>
+      <c r="D134" s="41" t="s">
+        <v>7813</v>
+      </c>
+      <c r="E134" s="41" t="s">
+        <v>7814</v>
+      </c>
+      <c r="F134" s="41" t="s">
+        <v>7815</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="57" t="n">
+        <v>43658</v>
       </c>
       <c r="B135" s="41" t="s">
-        <v>7797</v>
+        <v>7816</v>
       </c>
       <c r="C135" s="41" t="s">
-        <v>7798</v>
+        <v>7817</v>
       </c>
       <c r="D135" s="59" t="s">
-        <v>7799</v>
+        <v>7818</v>
       </c>
       <c r="E135" s="41" t="s">
-        <v>7800</v>
+        <v>7819</v>
       </c>
       <c r="F135" s="41" t="s">
-        <v>7787</v>
+        <v>7816</v>
       </c>
       <c r="G135" s="41" t="s">
-        <v>7801</v>
-      </c>
-    </row>
-    <row r="136" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="60" t="n">
-        <v>42355</v>
+        <v>7820</v>
+      </c>
+      <c r="H135" s="41"/>
+      <c r="I135" s="41"/>
+      <c r="J135" s="41"/>
+      <c r="K135" s="41"/>
+      <c r="L135" s="41"/>
+      <c r="M135" s="41"/>
+      <c r="N135" s="41"/>
+      <c r="O135" s="41"/>
+      <c r="P135" s="41"/>
+      <c r="Q135" s="41"/>
+      <c r="R135" s="41"/>
+      <c r="S135" s="41"/>
+      <c r="T135" s="41"/>
+      <c r="U135" s="41"/>
+      <c r="V135" s="41"/>
+      <c r="W135" s="41"/>
+      <c r="X135" s="41"/>
+      <c r="Y135" s="41"/>
+      <c r="Z135" s="41"/>
+      <c r="AA135" s="41"/>
+      <c r="AB135" s="41"/>
+      <c r="AC135" s="41"/>
+      <c r="AD135" s="41" t="s">
+        <v>7821</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="57" t="n">
+        <v>45581</v>
       </c>
       <c r="B136" s="41" t="s">
-        <v>7802</v>
+        <v>7822</v>
       </c>
       <c r="C136" s="41" t="s">
-        <v>7803</v>
+        <v>7823</v>
       </c>
       <c r="D136" s="41" t="s">
-        <v>7804</v>
-      </c>
-      <c r="E136" s="41" t="s">
-        <v>7805</v>
+        <v>7824</v>
+      </c>
+      <c r="E136" s="59" t="s">
+        <v>7825</v>
       </c>
       <c r="F136" s="41" t="s">
-        <v>7806</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="57" t="n">
-        <v>43658</v>
-      </c>
-      <c r="B137" s="41" t="s">
-        <v>7807</v>
-      </c>
-      <c r="C137" s="41" t="s">
-        <v>7808</v>
-      </c>
-      <c r="D137" s="59" t="s">
-        <v>7809</v>
-      </c>
-      <c r="E137" s="41" t="s">
-        <v>7810</v>
-      </c>
-      <c r="F137" s="41" t="s">
-        <v>7807</v>
-      </c>
-      <c r="G137" s="41" t="s">
-        <v>7811</v>
-      </c>
-      <c r="H137" s="41"/>
-      <c r="I137" s="41"/>
-      <c r="J137" s="41"/>
-      <c r="K137" s="41"/>
-      <c r="L137" s="41"/>
-      <c r="M137" s="41"/>
-      <c r="N137" s="41"/>
-      <c r="O137" s="41"/>
-      <c r="P137" s="41"/>
-      <c r="Q137" s="41"/>
-      <c r="R137" s="41"/>
-      <c r="S137" s="41"/>
-      <c r="T137" s="41"/>
-      <c r="U137" s="41"/>
-      <c r="V137" s="41"/>
-      <c r="W137" s="41"/>
-      <c r="X137" s="41"/>
-      <c r="Y137" s="41"/>
-      <c r="Z137" s="41"/>
-      <c r="AA137" s="41"/>
-      <c r="AB137" s="41"/>
-      <c r="AC137" s="41"/>
-      <c r="AD137" s="41" t="s">
-        <v>7812</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="57" t="n">
-        <v>45581</v>
-      </c>
-      <c r="B138" s="41" t="s">
-        <v>7813</v>
-      </c>
-      <c r="C138" s="41" t="s">
-        <v>7814</v>
-      </c>
-      <c r="D138" s="41" t="s">
-        <v>7815</v>
-      </c>
-      <c r="E138" s="59" t="s">
-        <v>7816</v>
-      </c>
-      <c r="F138" s="41" t="s">
-        <v>7813</v>
-      </c>
-      <c r="G138" s="61" t="s">
-        <v>7817</v>
-      </c>
-      <c r="H138" s="41"/>
-      <c r="I138" s="41"/>
-      <c r="J138" s="41"/>
-      <c r="K138" s="41"/>
-      <c r="L138" s="41"/>
-      <c r="M138" s="41"/>
-      <c r="N138" s="41"/>
-      <c r="O138" s="41"/>
-      <c r="P138" s="41"/>
-      <c r="Q138" s="41"/>
-      <c r="R138" s="41"/>
-      <c r="S138" s="41"/>
-      <c r="T138" s="41"/>
-      <c r="U138" s="41"/>
-      <c r="V138" s="41"/>
-      <c r="W138" s="41"/>
-      <c r="X138" s="41"/>
-      <c r="Y138" s="41"/>
-      <c r="Z138" s="41"/>
-      <c r="AA138" s="41"/>
-      <c r="AB138" s="41"/>
-      <c r="AC138" s="41"/>
-      <c r="AD138" s="41"/>
-    </row>
-    <row r="139" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="60" t="n">
+        <v>7822</v>
+      </c>
+      <c r="G136" s="61" t="s">
+        <v>7826</v>
+      </c>
+      <c r="H136" s="41"/>
+      <c r="I136" s="41"/>
+      <c r="J136" s="41"/>
+      <c r="K136" s="41"/>
+      <c r="L136" s="41"/>
+      <c r="M136" s="41"/>
+      <c r="N136" s="41"/>
+      <c r="O136" s="41"/>
+      <c r="P136" s="41"/>
+      <c r="Q136" s="41"/>
+      <c r="R136" s="41"/>
+      <c r="S136" s="41"/>
+      <c r="T136" s="41"/>
+      <c r="U136" s="41"/>
+      <c r="V136" s="41"/>
+      <c r="W136" s="41"/>
+      <c r="X136" s="41"/>
+      <c r="Y136" s="41"/>
+      <c r="Z136" s="41"/>
+      <c r="AA136" s="41"/>
+      <c r="AB136" s="41"/>
+      <c r="AC136" s="41"/>
+      <c r="AD136" s="41"/>
+    </row>
+    <row r="137" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="60" t="n">
         <v>45668</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>7818</v>
-      </c>
-      <c r="C139" s="28" t="s">
-        <v>7819</v>
-      </c>
-      <c r="D139" s="28" t="s">
-        <v>7820</v>
-      </c>
-      <c r="E139" s="45" t="s">
-        <v>7821</v>
-      </c>
-      <c r="F139" s="28" t="s">
-        <v>7563</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>7564</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1" t="s">
-        <v>7822</v>
+      <c r="B137" s="1" t="s">
+        <v>7827</v>
+      </c>
+      <c r="C137" s="28" t="s">
+        <v>7828</v>
+      </c>
+      <c r="D137" s="28" t="s">
+        <v>7829</v>
+      </c>
+      <c r="E137" s="45" t="s">
+        <v>7830</v>
+      </c>
+      <c r="F137" s="28" t="s">
+        <v>7572</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>7573</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="1" t="s">
+        <v>7831</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="59" t="s">
+        <v>7832</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>7833</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>7834</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>7835</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>7836</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="57" t="s">
+        <v>7837</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>7838</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>7835</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>7839</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="59" t="s">
-        <v>7823</v>
+        <v>7832</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>7824</v>
+        <v>7840</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>7825</v>
+        <v>7841</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>7826</v>
+        <v>7835</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>7827</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="57" t="s">
-        <v>7828</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>7829</v>
+        <v>7842</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="28" t="s">
+        <v>7843</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>7844</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>7845</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>7826</v>
+        <v>7846</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>7830</v>
+        <v>7821</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="59" t="s">
-        <v>7823</v>
+      <c r="A144" s="1" t="s">
+        <v>7847</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>7831</v>
+        <v>7848</v>
       </c>
       <c r="C144" s="1" t="s">
+        <v>7849</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>7846</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>7850</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="43" t="s">
+        <v>7851</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>7852</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>7853</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>7854</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>7855</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="62" t="s">
+        <v>7856</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>7857</v>
+      </c>
+      <c r="C146" s="45" t="s">
+        <v>7858</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>7859</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="s">
+        <v>7847</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>7860</v>
+      </c>
+      <c r="C147" s="41" t="s">
+        <v>7861</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>7862</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>7846</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>7850</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="28" t="s">
+        <v>7863</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>7864</v>
+      </c>
+      <c r="C148" s="41" t="s">
+        <v>7865</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>7866</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>7846</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>7867</v>
+      </c>
+      <c r="H148" s="1"/>
+    </row>
+    <row r="149" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="59" t="s">
         <v>7832</v>
       </c>
-      <c r="F144" s="1" t="s">
-        <v>7826</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>7833</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="28" t="s">
-        <v>7834</v>
-      </c>
-      <c r="B145" s="1" t="s">
+      <c r="B149" s="1" t="s">
+        <v>7868</v>
+      </c>
+      <c r="D149" s="28" t="s">
+        <v>7869</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>7870</v>
+      </c>
+      <c r="F149" s="43" t="s">
+        <v>7871</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>7872</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="48" t="s">
+        <v>7873</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>7874</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="63" t="s">
+        <v>7875</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>7876</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="s">
+        <v>7877</v>
+      </c>
+      <c r="B152" s="48" t="s">
+        <v>7878</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>7879</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="48" t="s">
+        <v>7880</v>
+      </c>
+      <c r="B153" s="48" t="s">
+        <v>7881</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="43" t="s">
+        <v>7883</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>7884</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>7707</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>7835</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>7836</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>7837</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>7812</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
-        <v>7838</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>7839</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>7840</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>7837</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>7841</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="43" t="s">
-        <v>7842</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>7843</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>7844</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>7845</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>7846</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="62" t="s">
-        <v>7847</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>7848</v>
-      </c>
-      <c r="C148" s="45" t="s">
-        <v>7849</v>
-      </c>
-      <c r="G148" s="2" t="s">
-        <v>7850</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="1" t="s">
-        <v>7838</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>7851</v>
-      </c>
-      <c r="C149" s="41" t="s">
-        <v>7852</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>7853</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>7837</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>7841</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="28" t="s">
-        <v>7854</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>7855</v>
-      </c>
-      <c r="C150" s="41" t="s">
-        <v>7856</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>7857</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>7837</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>7858</v>
-      </c>
-      <c r="H150" s="1"/>
-    </row>
-    <row r="151" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="59" t="s">
-        <v>7823</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>7859</v>
-      </c>
-      <c r="D151" s="28" t="s">
-        <v>7860</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>7861</v>
-      </c>
-      <c r="F151" s="43" t="s">
-        <v>7862</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>7863</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="48" t="s">
-        <v>7864</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>7865</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="63" t="s">
-        <v>7866</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>7867</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="0" t="s">
-        <v>7868</v>
-      </c>
-      <c r="B154" s="48" t="s">
-        <v>7869</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>7870</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="48" t="s">
-        <v>7871</v>
-      </c>
-      <c r="B155" s="48" t="s">
-        <v>7872</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>7873</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="43" t="s">
-        <v>7874</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="s">
-        <v>7875</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>7698</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>7826</v>
-      </c>
-      <c r="G158" s="2" t="s">
-        <v>7876</v>
+      <c r="G156" s="2" t="s">
+        <v>7885</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="s">
+        <v>7886</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>7887</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>7888</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>7889</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>7877</v>
+        <v>7890</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>7878</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="1" t="s">
-        <v>7879</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>7880</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="1" t="s">
-        <v>7881</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>7882</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="43" t="s">
-        <v>7883</v>
+        <v>7891</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="43" t="s">
+        <v>7892</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="28" t="s">
+        <v>7893</v>
+      </c>
+      <c r="B169" s="28"/>
+      <c r="C169" s="28"/>
+      <c r="D169" s="28"/>
+      <c r="F169" s="43"/>
+      <c r="G169" s="2"/>
+    </row>
+    <row r="170" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A170" s="64" t="s">
+        <v>7894</v>
+      </c>
+      <c r="D170" s="64" t="s">
+        <v>7895</v>
+      </c>
+      <c r="E170" s="64" t="s">
+        <v>7896</v>
+      </c>
+      <c r="F170" s="62" t="s">
+        <v>7511</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>7512</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="28" t="s">
-        <v>7884</v>
-      </c>
-      <c r="B171" s="28"/>
+      <c r="A171" s="64" t="s">
+        <v>7897</v>
+      </c>
       <c r="C171" s="28"/>
-      <c r="D171" s="28"/>
-      <c r="F171" s="43"/>
-      <c r="G171" s="2"/>
-    </row>
-    <row r="172" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="64" t="s">
-        <v>7885</v>
-      </c>
-      <c r="D172" s="64" t="s">
-        <v>7886</v>
-      </c>
-      <c r="E172" s="64" t="s">
-        <v>7887</v>
-      </c>
-      <c r="F172" s="62" t="s">
-        <v>7502</v>
-      </c>
-      <c r="G172" s="2" t="s">
-        <v>7503</v>
+      <c r="D171" s="64" t="s">
+        <v>7895</v>
+      </c>
+      <c r="E171" s="64" t="s">
+        <v>7898</v>
+      </c>
+      <c r="F171" s="65" t="s">
+        <v>7899</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>7900</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="64" t="s">
-        <v>7888</v>
-      </c>
-      <c r="C173" s="28"/>
-      <c r="D173" s="64" t="s">
-        <v>7886</v>
-      </c>
-      <c r="E173" s="64" t="s">
-        <v>7889</v>
-      </c>
-      <c r="F173" s="65" t="s">
-        <v>7890</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>7891</v>
+      <c r="A173" s="1" t="s">
+        <v>7901</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="28" t="s">
+        <v>7902</v>
+      </c>
+      <c r="B174" s="28" t="s">
+        <v>7903</v>
+      </c>
+      <c r="C174" s="28" t="s">
+        <v>7904</v>
+      </c>
+      <c r="D174" s="28" t="s">
+        <v>7538</v>
+      </c>
+      <c r="E174" s="28" t="s">
+        <v>7905</v>
+      </c>
+      <c r="F174" s="28" t="s">
+        <v>7539</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>7540</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="1" t="s">
-        <v>7892</v>
+      <c r="A175" s="28" t="s">
+        <v>7906</v>
+      </c>
+      <c r="B175" s="28" t="s">
+        <v>7903</v>
+      </c>
+      <c r="C175" s="28" t="s">
+        <v>7907</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>7908</v>
+      </c>
+      <c r="E175" s="28" t="s">
+        <v>7909</v>
+      </c>
+      <c r="F175" s="28" t="s">
+        <v>7910</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>7911</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="28" t="s">
-        <v>7893</v>
+        <v>7902</v>
       </c>
       <c r="B176" s="28" t="s">
-        <v>7894</v>
+        <v>7903</v>
       </c>
       <c r="C176" s="28" t="s">
-        <v>7895</v>
-      </c>
-      <c r="D176" s="28" t="s">
-        <v>7529</v>
+        <v>7912</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>7913</v>
       </c>
       <c r="E176" s="28" t="s">
-        <v>7896</v>
+        <v>7914</v>
       </c>
       <c r="F176" s="28" t="s">
-        <v>7530</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>7531</v>
+        <v>7915</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>7916</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="28" t="s">
-        <v>7897</v>
+      <c r="A177" s="47" t="s">
+        <v>7917</v>
       </c>
       <c r="B177" s="28" t="s">
-        <v>7894</v>
-      </c>
-      <c r="C177" s="28" t="s">
-        <v>7898</v>
-      </c>
-      <c r="D177" s="1" t="s">
+        <v>7918</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>7919</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>7920</v>
+      </c>
+      <c r="F177" s="28" t="s">
         <v>7899</v>
       </c>
-      <c r="E177" s="28" t="s">
+      <c r="G177" s="58" t="s">
         <v>7900</v>
       </c>
-      <c r="F177" s="28" t="s">
-        <v>7901</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>7902</v>
-      </c>
     </row>
     <row r="178" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="28" t="s">
-        <v>7893</v>
-      </c>
-      <c r="B178" s="28" t="s">
-        <v>7894</v>
-      </c>
-      <c r="C178" s="28" t="s">
-        <v>7903</v>
+      <c r="A178" s="47" t="s">
+        <v>7921</v>
+      </c>
+      <c r="B178" s="43" t="s">
+        <v>7922</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>7923</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>7904</v>
+        <v>7924</v>
       </c>
       <c r="E178" s="28" t="s">
-        <v>7905</v>
+        <v>7925</v>
       </c>
       <c r="F178" s="28" t="s">
-        <v>7906</v>
-      </c>
-      <c r="G178" s="2" t="s">
-        <v>7907</v>
+        <v>7926</v>
+      </c>
+      <c r="G178" s="58" t="s">
+        <v>7927</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="47" t="s">
-        <v>7908</v>
-      </c>
-      <c r="B179" s="28" t="s">
-        <v>7909</v>
+      <c r="A179" s="1" t="s">
+        <v>7928</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>7929</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>7910</v>
+        <v>7930</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>7911</v>
+        <v>7920</v>
       </c>
       <c r="F179" s="28" t="s">
-        <v>7890</v>
+        <v>7899</v>
       </c>
       <c r="G179" s="58" t="s">
-        <v>7891</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="47" t="s">
-        <v>7912</v>
-      </c>
-      <c r="B180" s="43" t="s">
-        <v>7913</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>7914</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>7915</v>
-      </c>
-      <c r="E180" s="28" t="s">
-        <v>7916</v>
+      <c r="B180" s="1" t="s">
+        <v>7931</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>7920</v>
       </c>
       <c r="F180" s="28" t="s">
-        <v>7917</v>
+        <v>7899</v>
       </c>
       <c r="G180" s="58" t="s">
-        <v>7918</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>7919</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>7920</v>
+        <v>7932</v>
+      </c>
+      <c r="B181" s="28" t="s">
+        <v>7933</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>7921</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>7911</v>
+        <v>7934</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>7935</v>
       </c>
       <c r="F181" s="28" t="s">
-        <v>7890</v>
+        <v>7936</v>
       </c>
       <c r="G181" s="58" t="s">
-        <v>7891</v>
-      </c>
-    </row>
-    <row r="182" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7937</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="s">
+        <v>7938</v>
+      </c>
       <c r="B182" s="1" t="s">
-        <v>7922</v>
+        <v>7647</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>7939</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>7940</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>7911</v>
-      </c>
-      <c r="F182" s="28" t="s">
-        <v>7890</v>
-      </c>
-      <c r="G182" s="58" t="s">
-        <v>7891</v>
+        <v>7941</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>7649</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>7650</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="1" t="s">
-        <v>7923</v>
-      </c>
-      <c r="B183" s="28" t="s">
-        <v>7924</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>7925</v>
+      <c r="A183" s="47" t="n">
+        <v>36795</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>7942</v>
+      </c>
+      <c r="C183" s="28" t="s">
+        <v>7943</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>7926</v>
-      </c>
-      <c r="F183" s="28" t="s">
-        <v>7927</v>
-      </c>
-      <c r="G183" s="58" t="s">
-        <v>7928</v>
-      </c>
-    </row>
-    <row r="184" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="1" t="s">
-        <v>7929</v>
+        <v>7944</v>
+      </c>
+      <c r="E183" s="28" t="s">
+        <v>7945</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>7946</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>7947</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="47" t="n">
+        <v>45216</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>7638</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>7930</v>
+        <v>7948</v>
+      </c>
+      <c r="C184" s="28" t="s">
+        <v>7949</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>7931</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>7932</v>
+        <v>7950</v>
+      </c>
+      <c r="E184" s="28" t="s">
+        <v>7951</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>7640</v>
+        <v>7952</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>7641</v>
-      </c>
-    </row>
-    <row r="185" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7953</v>
+      </c>
+    </row>
+    <row r="185" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="47" t="n">
-        <v>36795</v>
+        <v>45458</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>7933</v>
-      </c>
-      <c r="C185" s="28" t="s">
-        <v>7934</v>
+        <v>7954</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>7955</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>7935</v>
+        <v>7477</v>
       </c>
       <c r="E185" s="28" t="s">
-        <v>7936</v>
+        <v>7956</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>7937</v>
-      </c>
-      <c r="G185" s="2" t="s">
-        <v>7938</v>
-      </c>
-    </row>
-    <row r="186" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="47" t="n">
-        <v>45216</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>7939</v>
-      </c>
-      <c r="C186" s="28" t="s">
-        <v>7940</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>7941</v>
-      </c>
-      <c r="E186" s="28" t="s">
-        <v>7942</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>7943</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>7944</v>
-      </c>
-    </row>
-    <row r="187" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="47" t="n">
-        <v>45458</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>7945</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>7946</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>7468</v>
-      </c>
-      <c r="E187" s="28" t="s">
-        <v>7947</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>7470</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>7471</v>
+        <v>7479</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>7480</v>
+      </c>
+    </row>
+    <row r="188" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="47" t="s">
+        <v>7957</v>
+      </c>
+      <c r="B188" s="28"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="28"/>
+      <c r="G188" s="2"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="K188" s="1"/>
+      <c r="L188" s="1"/>
+      <c r="M188" s="1"/>
+      <c r="N188" s="1"/>
+      <c r="O188" s="1"/>
+      <c r="P188" s="1"/>
+      <c r="Q188" s="1"/>
+      <c r="R188" s="1"/>
+      <c r="S188" s="1"/>
+      <c r="T188" s="1"/>
+      <c r="U188" s="1"/>
+      <c r="V188" s="1"/>
+      <c r="W188" s="1"/>
+      <c r="X188" s="1"/>
+      <c r="Y188" s="1"/>
+      <c r="Z188" s="1"/>
+      <c r="AA188" s="1"/>
+      <c r="AB188" s="1"/>
+      <c r="AC188" s="1"/>
+      <c r="AD188" s="1"/>
+    </row>
+    <row r="189" s="55" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="66" t="n">
+        <v>45004</v>
+      </c>
+      <c r="B189" s="55" t="s">
+        <v>7958</v>
+      </c>
+      <c r="C189" s="55" t="s">
+        <v>7959</v>
+      </c>
+      <c r="D189" s="55" t="s">
+        <v>7960</v>
+      </c>
+      <c r="E189" s="55" t="s">
+        <v>7961</v>
+      </c>
+      <c r="F189" s="67" t="s">
+        <v>7962</v>
+      </c>
+      <c r="G189" s="55" t="s">
+        <v>7963</v>
       </c>
     </row>
     <row r="190" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="47" t="s">
-        <v>7948</v>
-      </c>
-      <c r="B190" s="28"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
-      <c r="E190" s="1"/>
-      <c r="F190" s="28"/>
-      <c r="G190" s="2"/>
-      <c r="H190" s="1"/>
-      <c r="I190" s="1"/>
-      <c r="J190" s="1"/>
-      <c r="K190" s="1"/>
-      <c r="L190" s="1"/>
-      <c r="M190" s="1"/>
-      <c r="N190" s="1"/>
-      <c r="O190" s="1"/>
-      <c r="P190" s="1"/>
-      <c r="Q190" s="1"/>
-      <c r="R190" s="1"/>
-      <c r="S190" s="1"/>
-      <c r="T190" s="1"/>
-      <c r="U190" s="1"/>
-      <c r="V190" s="1"/>
-      <c r="W190" s="1"/>
-      <c r="X190" s="1"/>
-      <c r="Y190" s="1"/>
-      <c r="Z190" s="1"/>
-      <c r="AA190" s="1"/>
-      <c r="AB190" s="1"/>
-      <c r="AC190" s="1"/>
-      <c r="AD190" s="1"/>
-    </row>
-    <row r="191" s="55" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="66" t="n">
+        <v>45005</v>
+      </c>
+      <c r="B190" s="67" t="s">
+        <v>7964</v>
+      </c>
+      <c r="C190" s="55" t="s">
+        <v>7965</v>
+      </c>
+      <c r="D190" s="55" t="s">
+        <v>7966</v>
+      </c>
+      <c r="E190" s="55" t="s">
+        <v>7967</v>
+      </c>
+      <c r="F190" s="67" t="s">
+        <v>7968</v>
+      </c>
+      <c r="G190" s="55" t="s">
+        <v>7969</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="66" t="n">
-        <v>45004</v>
+        <v>45006</v>
       </c>
       <c r="B191" s="55" t="s">
-        <v>7949</v>
+        <v>7958</v>
       </c>
       <c r="C191" s="55" t="s">
-        <v>7950</v>
+        <v>7970</v>
       </c>
       <c r="D191" s="55" t="s">
-        <v>7951</v>
-      </c>
-      <c r="E191" s="55" t="s">
-        <v>7952</v>
+        <v>7971</v>
+      </c>
+      <c r="E191" s="68" t="s">
+        <v>7972</v>
       </c>
       <c r="F191" s="67" t="s">
-        <v>7953</v>
+        <v>7973</v>
       </c>
       <c r="G191" s="55" t="s">
-        <v>7954</v>
-      </c>
-    </row>
-    <row r="192" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7974</v>
+      </c>
+      <c r="H191" s="55"/>
+      <c r="I191" s="55"/>
+      <c r="J191" s="55"/>
+      <c r="K191" s="55"/>
+      <c r="L191" s="55"/>
+      <c r="M191" s="55"/>
+      <c r="N191" s="55"/>
+      <c r="O191" s="55"/>
+      <c r="P191" s="55"/>
+      <c r="Q191" s="55"/>
+      <c r="R191" s="55"/>
+      <c r="S191" s="55"/>
+      <c r="T191" s="55"/>
+      <c r="U191" s="55"/>
+      <c r="V191" s="55"/>
+      <c r="W191" s="55"/>
+      <c r="X191" s="55"/>
+      <c r="Y191" s="55"/>
+      <c r="Z191" s="55"/>
+      <c r="AA191" s="55"/>
+      <c r="AB191" s="55"/>
+      <c r="AC191" s="55"/>
+      <c r="AD191" s="55"/>
+    </row>
+    <row r="192" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="66" t="n">
-        <v>45005</v>
-      </c>
-      <c r="B192" s="67" t="s">
-        <v>7955</v>
-      </c>
-      <c r="C192" s="55" t="s">
-        <v>7956</v>
-      </c>
+        <v>45036</v>
+      </c>
+      <c r="B192" s="55" t="s">
+        <v>7975</v>
+      </c>
+      <c r="C192" s="55"/>
       <c r="D192" s="55" t="s">
-        <v>7957</v>
+        <v>7976</v>
       </c>
       <c r="E192" s="55" t="s">
+        <v>7977</v>
+      </c>
+      <c r="F192" s="55" t="s">
+        <v>7978</v>
+      </c>
+      <c r="G192" s="55" t="s">
+        <v>7979</v>
+      </c>
+      <c r="H192" s="55"/>
+      <c r="I192" s="55"/>
+      <c r="J192" s="55"/>
+      <c r="K192" s="55"/>
+      <c r="L192" s="55"/>
+      <c r="M192" s="55"/>
+      <c r="N192" s="55"/>
+      <c r="O192" s="55"/>
+      <c r="P192" s="55"/>
+      <c r="Q192" s="55"/>
+      <c r="R192" s="55"/>
+      <c r="S192" s="55"/>
+      <c r="T192" s="55"/>
+      <c r="U192" s="55"/>
+      <c r="V192" s="55"/>
+      <c r="W192" s="55"/>
+      <c r="X192" s="55"/>
+      <c r="Y192" s="55"/>
+      <c r="Z192" s="55"/>
+      <c r="AA192" s="55"/>
+      <c r="AB192" s="55"/>
+      <c r="AC192" s="55"/>
+      <c r="AD192" s="55"/>
+    </row>
+    <row r="193" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="69" t="n">
+        <v>45088</v>
+      </c>
+      <c r="B193" s="58" t="s">
         <v>7958</v>
       </c>
-      <c r="F192" s="67" t="s">
-        <v>7959</v>
-      </c>
-      <c r="G192" s="55" t="s">
-        <v>7960</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="66" t="n">
-        <v>45006</v>
-      </c>
-      <c r="B193" s="55" t="s">
-        <v>7949</v>
-      </c>
-      <c r="C193" s="55" t="s">
-        <v>7961</v>
-      </c>
-      <c r="D193" s="55" t="s">
-        <v>7962</v>
-      </c>
-      <c r="E193" s="68" t="s">
-        <v>7963</v>
-      </c>
-      <c r="F193" s="67" t="s">
-        <v>7964</v>
-      </c>
-      <c r="G193" s="55" t="s">
-        <v>7965</v>
-      </c>
-      <c r="H193" s="55"/>
-      <c r="I193" s="55"/>
-      <c r="J193" s="55"/>
-      <c r="K193" s="55"/>
-      <c r="L193" s="55"/>
-      <c r="M193" s="55"/>
-      <c r="N193" s="55"/>
-      <c r="O193" s="55"/>
-      <c r="P193" s="55"/>
-      <c r="Q193" s="55"/>
-      <c r="R193" s="55"/>
-      <c r="S193" s="55"/>
-      <c r="T193" s="55"/>
-      <c r="U193" s="55"/>
-      <c r="V193" s="55"/>
-      <c r="W193" s="55"/>
-      <c r="X193" s="55"/>
-      <c r="Y193" s="55"/>
-      <c r="Z193" s="55"/>
-      <c r="AA193" s="55"/>
-      <c r="AB193" s="55"/>
-      <c r="AC193" s="55"/>
-      <c r="AD193" s="55"/>
+      <c r="C193" s="58" t="s">
+        <v>7980</v>
+      </c>
+      <c r="D193" s="58" t="s">
+        <v>7981</v>
+      </c>
+      <c r="E193" s="70" t="s">
+        <v>7982</v>
+      </c>
+      <c r="F193" s="58" t="s">
+        <v>7899</v>
+      </c>
+      <c r="G193" s="58" t="s">
+        <v>7900</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="66" t="n">
-        <v>45036</v>
-      </c>
-      <c r="B194" s="55" t="s">
-        <v>7966</v>
-      </c>
-      <c r="C194" s="55"/>
-      <c r="D194" s="55" t="s">
-        <v>7967</v>
-      </c>
-      <c r="E194" s="55" t="s">
-        <v>7968</v>
-      </c>
-      <c r="F194" s="55" t="s">
-        <v>7969</v>
-      </c>
-      <c r="G194" s="55" t="s">
-        <v>7970</v>
-      </c>
-      <c r="H194" s="55"/>
-      <c r="I194" s="55"/>
-      <c r="J194" s="55"/>
-      <c r="K194" s="55"/>
-      <c r="L194" s="55"/>
-      <c r="M194" s="55"/>
-      <c r="N194" s="55"/>
-      <c r="O194" s="55"/>
-      <c r="P194" s="55"/>
-      <c r="Q194" s="55"/>
-      <c r="R194" s="55"/>
-      <c r="S194" s="55"/>
-      <c r="T194" s="55"/>
-      <c r="U194" s="55"/>
-      <c r="V194" s="55"/>
-      <c r="W194" s="55"/>
-      <c r="X194" s="55"/>
-      <c r="Y194" s="55"/>
-      <c r="Z194" s="55"/>
-      <c r="AA194" s="55"/>
-      <c r="AB194" s="55"/>
-      <c r="AC194" s="55"/>
-      <c r="AD194" s="55"/>
-    </row>
-    <row r="195" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="69" t="n">
-        <v>45088</v>
-      </c>
-      <c r="B195" s="58" t="s">
-        <v>7949</v>
-      </c>
-      <c r="C195" s="58" t="s">
-        <v>7971</v>
-      </c>
-      <c r="D195" s="58" t="s">
-        <v>7972</v>
-      </c>
-      <c r="E195" s="70" t="s">
-        <v>7973</v>
-      </c>
-      <c r="F195" s="58" t="s">
-        <v>7890</v>
-      </c>
-      <c r="G195" s="58" t="s">
-        <v>7891</v>
-      </c>
-    </row>
-    <row r="196" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="69" t="n">
+      <c r="A194" s="69" t="n">
         <v>45025</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>7736</v>
-      </c>
-      <c r="C196" s="28" t="s">
-        <v>7974</v>
-      </c>
-      <c r="D196" s="43" t="s">
-        <v>7975</v>
-      </c>
-      <c r="F196" s="1" t="s">
-        <v>7976</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>7977</v>
-      </c>
-    </row>
-    <row r="197" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="1"/>
-      <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
-      <c r="E197" s="1"/>
-      <c r="F197" s="1"/>
-      <c r="G197" s="1"/>
-      <c r="H197" s="1"/>
-      <c r="I197" s="1"/>
-      <c r="J197" s="1"/>
-      <c r="K197" s="1"/>
-      <c r="L197" s="1"/>
-      <c r="M197" s="1"/>
-      <c r="N197" s="1"/>
-      <c r="O197" s="1"/>
-      <c r="P197" s="1"/>
-      <c r="Q197" s="1"/>
-      <c r="R197" s="1"/>
-      <c r="S197" s="1"/>
-      <c r="T197" s="1"/>
-      <c r="U197" s="1"/>
-      <c r="V197" s="1"/>
-      <c r="W197" s="1"/>
-      <c r="X197" s="1"/>
-      <c r="Y197" s="1"/>
-      <c r="Z197" s="1"/>
-      <c r="AA197" s="1"/>
-      <c r="AB197" s="1"/>
-      <c r="AC197" s="1"/>
-      <c r="AD197" s="1"/>
-    </row>
-    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="1" t="s">
-        <v>7978</v>
-      </c>
-      <c r="G198" s="1"/>
-      <c r="H198" s="1"/>
-      <c r="I198" s="1"/>
-      <c r="J198" s="1"/>
-      <c r="K198" s="1"/>
-      <c r="L198" s="1"/>
-      <c r="M198" s="1"/>
-      <c r="N198" s="1"/>
-      <c r="O198" s="1"/>
-      <c r="P198" s="1"/>
-      <c r="Q198" s="1"/>
-      <c r="R198" s="1"/>
-      <c r="S198" s="1"/>
-      <c r="T198" s="1"/>
-      <c r="U198" s="1"/>
-      <c r="V198" s="1"/>
-      <c r="W198" s="1"/>
-      <c r="X198" s="1"/>
-      <c r="Y198" s="1"/>
-      <c r="Z198" s="1"/>
-      <c r="AA198" s="1"/>
-      <c r="AB198" s="1"/>
-      <c r="AC198" s="1"/>
-      <c r="AD198" s="1"/>
-    </row>
-    <row r="199" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="57" t="n">
+      <c r="B194" s="1" t="s">
+        <v>7745</v>
+      </c>
+      <c r="C194" s="28" t="s">
+        <v>7983</v>
+      </c>
+      <c r="D194" s="43" t="s">
+        <v>7984</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>7985</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>7986</v>
+      </c>
+    </row>
+    <row r="195" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+      <c r="E195" s="1"/>
+      <c r="F195" s="1"/>
+      <c r="G195" s="1"/>
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+      <c r="J195" s="1"/>
+      <c r="K195" s="1"/>
+      <c r="L195" s="1"/>
+      <c r="M195" s="1"/>
+      <c r="N195" s="1"/>
+      <c r="O195" s="1"/>
+      <c r="P195" s="1"/>
+      <c r="Q195" s="1"/>
+      <c r="R195" s="1"/>
+      <c r="S195" s="1"/>
+      <c r="T195" s="1"/>
+      <c r="U195" s="1"/>
+      <c r="V195" s="1"/>
+      <c r="W195" s="1"/>
+      <c r="X195" s="1"/>
+      <c r="Y195" s="1"/>
+      <c r="Z195" s="1"/>
+      <c r="AA195" s="1"/>
+      <c r="AB195" s="1"/>
+      <c r="AC195" s="1"/>
+      <c r="AD195" s="1"/>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1" t="s">
+        <v>7987</v>
+      </c>
+      <c r="G196" s="1"/>
+      <c r="H196" s="1"/>
+      <c r="I196" s="1"/>
+      <c r="J196" s="1"/>
+      <c r="K196" s="1"/>
+      <c r="L196" s="1"/>
+      <c r="M196" s="1"/>
+      <c r="N196" s="1"/>
+      <c r="O196" s="1"/>
+      <c r="P196" s="1"/>
+      <c r="Q196" s="1"/>
+      <c r="R196" s="1"/>
+      <c r="S196" s="1"/>
+      <c r="T196" s="1"/>
+      <c r="U196" s="1"/>
+      <c r="V196" s="1"/>
+      <c r="W196" s="1"/>
+      <c r="X196" s="1"/>
+      <c r="Y196" s="1"/>
+      <c r="Z196" s="1"/>
+      <c r="AA196" s="1"/>
+      <c r="AB196" s="1"/>
+      <c r="AC196" s="1"/>
+      <c r="AD196" s="1"/>
+    </row>
+    <row r="197" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="57" t="n">
         <v>39252</v>
       </c>
-      <c r="B199" s="41"/>
-      <c r="C199" s="41" t="s">
-        <v>7979</v>
-      </c>
-      <c r="D199" s="59" t="s">
-        <v>7980</v>
-      </c>
-      <c r="E199" s="41" t="s">
-        <v>7981</v>
-      </c>
-      <c r="F199" s="41" t="s">
-        <v>7982</v>
-      </c>
-      <c r="G199" s="41" t="s">
-        <v>7983</v>
-      </c>
-      <c r="H199" s="41"/>
-      <c r="I199" s="41"/>
-      <c r="J199" s="41"/>
-      <c r="K199" s="41"/>
-      <c r="L199" s="41"/>
-      <c r="M199" s="41"/>
-      <c r="N199" s="41"/>
-      <c r="O199" s="41"/>
-      <c r="P199" s="41"/>
-      <c r="Q199" s="41"/>
-      <c r="R199" s="41"/>
-      <c r="S199" s="41"/>
-      <c r="T199" s="41"/>
-      <c r="U199" s="41"/>
-      <c r="V199" s="41"/>
-      <c r="W199" s="41"/>
-      <c r="X199" s="41"/>
-      <c r="Y199" s="41"/>
-      <c r="Z199" s="41"/>
-      <c r="AA199" s="41"/>
-      <c r="AB199" s="41"/>
-      <c r="AC199" s="41"/>
-      <c r="AD199" s="41"/>
+      <c r="B197" s="41"/>
+      <c r="C197" s="41" t="s">
+        <v>7988</v>
+      </c>
+      <c r="D197" s="59" t="s">
+        <v>7989</v>
+      </c>
+      <c r="E197" s="41" t="s">
+        <v>7990</v>
+      </c>
+      <c r="F197" s="41" t="s">
+        <v>7991</v>
+      </c>
+      <c r="G197" s="41" t="s">
+        <v>7992</v>
+      </c>
+      <c r="H197" s="41"/>
+      <c r="I197" s="41"/>
+      <c r="J197" s="41"/>
+      <c r="K197" s="41"/>
+      <c r="L197" s="41"/>
+      <c r="M197" s="41"/>
+      <c r="N197" s="41"/>
+      <c r="O197" s="41"/>
+      <c r="P197" s="41"/>
+      <c r="Q197" s="41"/>
+      <c r="R197" s="41"/>
+      <c r="S197" s="41"/>
+      <c r="T197" s="41"/>
+      <c r="U197" s="41"/>
+      <c r="V197" s="41"/>
+      <c r="W197" s="41"/>
+      <c r="X197" s="41"/>
+      <c r="Y197" s="41"/>
+      <c r="Z197" s="41"/>
+      <c r="AA197" s="41"/>
+      <c r="AB197" s="41"/>
+      <c r="AC197" s="41"/>
+      <c r="AD197" s="41"/>
+    </row>
+    <row r="198" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="47" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>7993</v>
+      </c>
+      <c r="C198" s="28" t="s">
+        <v>7994</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>7995</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>7996</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="47" t="s">
+        <v>7997</v>
+      </c>
+      <c r="B199" s="28" t="s">
+        <v>7998</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>7999</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>8000</v>
+      </c>
+      <c r="F199" s="28" t="s">
+        <v>8001</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>8002</v>
+      </c>
     </row>
     <row r="200" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="47" t="n">
-        <v>46241</v>
+      <c r="A200" s="54" t="n">
+        <v>42866</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>7984</v>
+        <v>8003</v>
       </c>
       <c r="C200" s="28" t="s">
-        <v>7985</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>7986</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>7987</v>
-      </c>
-    </row>
-    <row r="201" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="47" t="s">
-        <v>7988</v>
-      </c>
-      <c r="B201" s="28" t="s">
-        <v>7989</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>7990</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>7991</v>
-      </c>
-      <c r="F201" s="28" t="s">
-        <v>7992</v>
-      </c>
-      <c r="G201" s="2" t="s">
-        <v>7993</v>
-      </c>
-    </row>
-    <row r="202" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="54" t="n">
-        <v>42866</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>7994</v>
-      </c>
-      <c r="C202" s="28" t="s">
-        <v>7995</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>7996</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>7997</v>
-      </c>
-      <c r="F202" s="28" t="s">
-        <v>7826</v>
-      </c>
-      <c r="G202" s="2" t="s">
-        <v>7998</v>
+        <v>8004</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>8005</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>8006</v>
+      </c>
+      <c r="F200" s="28" t="s">
+        <v>7835</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>8007</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B204" s="63" t="s">
+        <v>8008</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>8009</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B205" s="1" t="s">
+        <v>8010</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>8011</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B206" s="0" t="s">
+        <v>8012</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>8013</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B207" s="63" t="s">
+        <v>8014</v>
+      </c>
+      <c r="C207" s="50" t="s">
+        <v>8015</v>
+      </c>
+      <c r="F207" s="48" t="s">
+        <v>8016</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B209" s="71" t="s">
+        <v>8017</v>
+      </c>
+      <c r="C209" s="72" t="s">
+        <v>8018</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B210" s="1" t="s">
+        <v>8019</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>8020</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B212" s="1" t="s">
+        <v>8021</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>8022</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B213" s="48" t="s">
+        <v>8023</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>8024</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B214" s="56" t="s">
+        <v>8025</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>8026</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B216" s="63" t="s">
+        <v>8027</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>8028</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B217" s="0" t="s">
+        <v>8029</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>8030</v>
       </c>
     </row>
   </sheetData>
@@ -85668,92 +86993,94 @@
     <hyperlink ref="G29" r:id="rId11" display="https://www.dpm.org.cn/ancient/special/148432.html"/>
     <hyperlink ref="G30" r:id="rId12" display="https://baijiahao.baidu.com/s?id=1853719866750900952&amp;wfr=spider&amp;for=pc"/>
     <hyperlink ref="G31" r:id="rId13" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G37" r:id="rId14" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G38" r:id="rId15" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G40" r:id="rId16" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G41" r:id="rId17" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G43" r:id="rId18" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="G46" r:id="rId19" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G47" r:id="rId20" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
-    <hyperlink ref="G48" r:id="rId21" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G49" r:id="rId22" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G51" r:id="rId23" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G52" r:id="rId24" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G53" r:id="rId25" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G57" r:id="rId26" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G58" r:id="rId27" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G59" r:id="rId28" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G61" r:id="rId29" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
-    <hyperlink ref="G62" r:id="rId30" display="https://www.dpm.org.cn/ancient"/>
-    <hyperlink ref="G63" r:id="rId31" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G65" r:id="rId32" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
-    <hyperlink ref="G66" r:id="rId33" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
-    <hyperlink ref="G67" r:id="rId34" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
-    <hyperlink ref="G68" r:id="rId35" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G69" r:id="rId36" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G70" r:id="rId37" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G71" r:id="rId38" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G72" r:id="rId39" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G73" r:id="rId40" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G74" r:id="rId41" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
-    <hyperlink ref="G75" r:id="rId42" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G76" r:id="rId43" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G77" r:id="rId44" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
-    <hyperlink ref="G80" r:id="rId45" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
-    <hyperlink ref="G82" r:id="rId46" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G83" r:id="rId47" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G84" r:id="rId48" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G85" r:id="rId49" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
-    <hyperlink ref="G88" r:id="rId50" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G89" r:id="rId51" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G92" r:id="rId52" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G93" r:id="rId53" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
-    <hyperlink ref="G94" r:id="rId54" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
-    <hyperlink ref="G96" r:id="rId55" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
-    <hyperlink ref="G102" r:id="rId56" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G103" r:id="rId57" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G104" r:id="rId58" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G105" r:id="rId59" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G106" r:id="rId60" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
-    <hyperlink ref="G107" r:id="rId61" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G109" r:id="rId62" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
-    <hyperlink ref="G110" r:id="rId63" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
-    <hyperlink ref="C128" r:id="rId64" display="尊婆须蜜菩萨所集论十五卷"/>
-    <hyperlink ref="G128" r:id="rId65" display="https://baijiahao.baidu.com/s?id=1767494632561741658&amp;wfr=spider&amp;for=pc"/>
-    <hyperlink ref="G133" r:id="rId66" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
-    <hyperlink ref="G134" r:id="rId67" display="https://book.kongfz.com/20791/3754198261"/>
-    <hyperlink ref="G137" r:id="rId68" display="https://www.ljstsg.cn/?p=6315"/>
-    <hyperlink ref="AD137" r:id="rId69" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="G138" r:id="rId70" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
-    <hyperlink ref="G139" r:id="rId71" display="https://www.toutiao.com/w/1820926958169100/"/>
-    <hyperlink ref="B142" r:id="rId72" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
-    <hyperlink ref="G142" r:id="rId73" display="https://book.kongfz.com/536651/7839562954"/>
-    <hyperlink ref="B143" r:id="rId74" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
-    <hyperlink ref="G143" r:id="rId75" display="https://book.kongfz.com/23231/8186709240"/>
-    <hyperlink ref="B144" r:id="rId76" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
-    <hyperlink ref="G144" r:id="rId77" display="https://book.kongfz.com/536651/7839554296"/>
-    <hyperlink ref="G145" r:id="rId78" display="https://product.dangdang.com/11084474556.html"/>
-    <hyperlink ref="B146" r:id="rId79" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
-    <hyperlink ref="G147" r:id="rId80" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
-    <hyperlink ref="G148" r:id="rId81" display="https://book.kongfz.com/200249/1819262449/"/>
-    <hyperlink ref="G149" r:id="rId82" display="https://product.dangdang.com/11721366316.html"/>
-    <hyperlink ref="B150" r:id="rId83" display="出版社:宗教文化出版社 "/>
-    <hyperlink ref="G150" r:id="rId84" display="https://product.dangdang.com/22497432.html"/>
-    <hyperlink ref="G151" r:id="rId85" display="http://aiguji.net/3299.html"/>
-    <hyperlink ref="G158" r:id="rId86" display="https://book.kongfz.com/467603/10356350239"/>
-    <hyperlink ref="G172" r:id="rId87" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
-    <hyperlink ref="G173" r:id="rId88" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G178" r:id="rId89" display="https://whly.gd.gov.cn/service_newwwbwg/content/post_4738424.html"/>
-    <hyperlink ref="G179" r:id="rId90" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G181" r:id="rId91" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G182" r:id="rId92" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G185" r:id="rId93" display="https://edu.sina.com.cn/wander/2000-09-25/12790.shtml"/>
-    <hyperlink ref="G191" r:id="rId94" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
-    <hyperlink ref="F193" r:id="rId95" display="中新网北京3月21日电 (记者 应妮) "/>
-    <hyperlink ref="G193" r:id="rId96" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
-    <hyperlink ref="G195" r:id="rId97" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G199" r:id="rId98" display="https://discovery.cctv.com/20070619/107154.shtml"/>
-    <hyperlink ref="G202" r:id="rId99" display="https://book.kongfz.com/102740/682706591"/>
+    <hyperlink ref="G35" r:id="rId14" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G36" r:id="rId15" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G38" r:id="rId16" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G39" r:id="rId17" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G41" r:id="rId18" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="G44" r:id="rId19" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G45" r:id="rId20" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
+    <hyperlink ref="G46" r:id="rId21" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G47" r:id="rId22" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G49" r:id="rId23" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G50" r:id="rId24" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G51" r:id="rId25" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G55" r:id="rId26" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G56" r:id="rId27" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G57" r:id="rId28" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G59" r:id="rId29" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198803029.htm"/>
+    <hyperlink ref="G60" r:id="rId30" display="https://www.dpm.org.cn/ancient"/>
+    <hyperlink ref="G61" r:id="rId31" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G63" r:id="rId32" display="http://iwr.cass.cn/qt/xsdt/xw/201308/t20130827_3048563.html"/>
+    <hyperlink ref="G64" r:id="rId33" display="https://mp.weixin.qq.com/s?__biz=MzA3OTg2MTI4OQ==&amp;mid=2650601944&amp;idx=1&amp;sn=ee37085e59412dd579bba81b3606d454&amp;chksm=87a55a9eb0d2d388bb6f083e807b1d5b535c207cd2f4ce0a461448a51e94d72fcb28309e5b05&amp;scene=27"/>
+    <hyperlink ref="G65" r:id="rId34" display="https://www.cnki.com.cn/Article/CJFDTOTAL-FYZZ198902019.htm"/>
+    <hyperlink ref="G66" r:id="rId35" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G67" r:id="rId36" display="https://baijiahao.baidu.com/s?id=1596152937093134294&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G68" r:id="rId37" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G69" r:id="rId38" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G70" r:id="rId39" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G71" r:id="rId40" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G72" r:id="rId41" display="https://fo.ifeng.com/zhuanti/shijiefojiaoluntan2/lingshanhuichang/fabaozhiguang/200903/0328_353_54347.shtml"/>
+    <hyperlink ref="G73" r:id="rId42" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G74" r:id="rId43" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G75" r:id="rId44" display="https://mp.weixin.qq.com/s?__biz=MjM5ODI3NzkzOQ==&amp;mid=2651563704&amp;idx=1&amp;sn=e4523f79ba2536b8a6b0c5bb4eb26f59&amp;chksm=bd3220e48a45a9f25af6cb7a8484701971f4a27ed5c6de3f3cea76d346efddffcdf5facefa3e&amp;scene=27"/>
+    <hyperlink ref="G78" r:id="rId45" display="https://www.chinanews.com.cn/news/2004year/2004-06-27/26/452929.shtml"/>
+    <hyperlink ref="G80" r:id="rId46" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G81" r:id="rId47" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G82" r:id="rId48" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G83" r:id="rId49" display="https://paper.people.com.cn/rmrbhwb/html/2015-08/14/content_1598881.htm"/>
+    <hyperlink ref="G86" r:id="rId50" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G87" r:id="rId51" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G90" r:id="rId52" display="https://baijiahao.baidu.com/s?id=1750883197524212547&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G91" r:id="rId53" display="https://mp.weixin.qq.com/s?__biz=MzA5NTA0NDYwOQ==&amp;mid=2652754148&amp;idx=1&amp;sn=7207d8281c4ee0bcb9006a8111de12d7&amp;chksm=8bac258abcdbac9cb6e4283687a46bd71746703a8b829bdda34e038b02ad5f7856e59716ba02&amp;scene=27"/>
+    <hyperlink ref="G92" r:id="rId54" display="https://fuedf.fudan.edu.cn/a8/ca/c29744a764106/page.htm"/>
+    <hyperlink ref="G94" r:id="rId55" display="https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml"/>
+    <hyperlink ref="G100" r:id="rId56" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G101" r:id="rId57" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G102" r:id="rId58" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G103" r:id="rId59" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G104" r:id="rId60" display="https://wwj.beijing.gov.cn/bjww/362760/362767/bwgxh/spzl/325959169/index.html"/>
+    <hyperlink ref="G105" r:id="rId61" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G107" r:id="rId62" display="https://mp.weixin.qq.com/s?__biz=MzA5MDY5NjEzOA==&amp;mid=2649515752&amp;idx=1&amp;sn=23dbccc0e96dc5c3270b1a8c048319c5&amp;chksm=89e18f051bc5309d676fa91430702a90ec481e7c651f1bd27737af64807ac719594a1794fd43&amp;scene=27"/>
+    <hyperlink ref="G108" r:id="rId63" display="https://epaper.gmw.cn/gmrb/html/2022-08/03/nw.D110000gmrb_20220803_2-07.htm"/>
+    <hyperlink ref="C126" r:id="rId64" display="尊婆须蜜菩萨所集论十五卷"/>
+    <hyperlink ref="G126" r:id="rId65" display="https://baijiahao.baidu.com/s?id=1767494632561741658&amp;wfr=spider&amp;for=pc"/>
+    <hyperlink ref="G131" r:id="rId66" display="https://www.zjlib.cn/search?q=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%8E%E7%AC%AC1%E5%86%8C%EF%BC%8C%E5%A4%A7%E4%B9%98%E7%BB%8F+%E8%88%AC%E8%8B%A5%E9%83%A8(%E4%B8%80)&amp;searchWay=1955822119611236354&amp;searchMode=2"/>
+    <hyperlink ref="G132" r:id="rId67" display="https://book.kongfz.com/20791/3754198261"/>
+    <hyperlink ref="G135" r:id="rId68" display="https://www.ljstsg.cn/?p=6315"/>
+    <hyperlink ref="AD135" r:id="rId69" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="G136" r:id="rId70" display="http://lib.nufe.edu.cn/2024/1016/c345a9172/page.htm"/>
+    <hyperlink ref="G137" r:id="rId71" display="https://www.toutiao.com/w/1820926958169100/"/>
+    <hyperlink ref="B140" r:id="rId72" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第149册 此土著述（三九） "/>
+    <hyperlink ref="G140" r:id="rId73" display="https://book.kongfz.com/536651/7839562954"/>
+    <hyperlink ref="B141" r:id="rId74" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第58册 "/>
+    <hyperlink ref="G141" r:id="rId75" display="https://book.kongfz.com/23231/8186709240"/>
+    <hyperlink ref="B142" r:id="rId76" display="全国图书馆文献缩微复制中心出版，乾隆大藏经第142册 此土著述（三二）  "/>
+    <hyperlink ref="G142" r:id="rId77" display="https://book.kongfz.com/536651/7839554296"/>
+    <hyperlink ref="G143" r:id="rId78" display="https://product.dangdang.com/11084474556.html"/>
+    <hyperlink ref="B144" r:id="rId79" display="中国书店出版，乾隆大藏经(共168册)典藏版精装清藏龙藏中国书店正版新版龙藏封面采用金黄色织锦乾隆大藏经 "/>
+    <hyperlink ref="G145" r:id="rId80" display="https://baike.sogou.com/v85368376.htm?fromTitle=%E4%B9%BE%E9%9A%86%E5%A4%A7%E8%97%8F%E7%BB%8F%EF%BC%88%E4%BC%A0%E4%B8%96%E5%85%B8%E8%97%8F%E7%89%88%EF%BC%89"/>
+    <hyperlink ref="G146" r:id="rId81" display="https://book.kongfz.com/200249/1819262449/"/>
+    <hyperlink ref="G147" r:id="rId82" display="https://product.dangdang.com/11721366316.html"/>
+    <hyperlink ref="B148" r:id="rId83" display="出版社:宗教文化出版社 "/>
+    <hyperlink ref="G148" r:id="rId84" display="https://product.dangdang.com/22497432.html"/>
+    <hyperlink ref="G149" r:id="rId85" display="http://aiguji.net/3299.html"/>
+    <hyperlink ref="G156" r:id="rId86" display="https://book.kongfz.com/467603/10356350239"/>
+    <hyperlink ref="G170" r:id="rId87" display="https://www.mct.gov.cn/whzx/tpxw/201701/t20170118_829685.htm"/>
+    <hyperlink ref="G171" r:id="rId88" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G176" r:id="rId89" display="https://whly.gd.gov.cn/service_newwwbwg/content/post_4738424.html"/>
+    <hyperlink ref="G177" r:id="rId90" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G179" r:id="rId91" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G180" r:id="rId92" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G183" r:id="rId93" display="https://edu.sina.com.cn/wander/2000-09-25/12790.shtml"/>
+    <hyperlink ref="G189" r:id="rId94" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
+    <hyperlink ref="F191" r:id="rId95" display="中新网北京3月21日电 (记者 应妮) "/>
+    <hyperlink ref="G191" r:id="rId96" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
+    <hyperlink ref="G193" r:id="rId97" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G197" r:id="rId98" display="https://discovery.cctv.com/20070619/107154.shtml"/>
+    <hyperlink ref="G200" r:id="rId99" display="https://book.kongfz.com/102740/682706591"/>
+    <hyperlink ref="C207" r:id="rId100" location="4" display="https://opac.ryukoku.ac.jp/iwjs0005opc/bdyview.do?bodyid=BD00000117&amp;elmid=Body&amp;fname=r-rn_471_006.pdf&amp;loginflg=on&amp;once=true#4"/>
+    <hyperlink ref="B214" r:id="rId101" display="《清藏》研究"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -85773,120 +87100,120 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="71" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="73" width="12.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7999</v>
+        <v>8031</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="72" t="n">
+      <c r="A2" s="74" t="n">
         <v>1539</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8000</v>
+        <v>8032</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="72" t="n">
+      <c r="A3" s="74" t="n">
         <v>1615</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8001</v>
+        <v>8033</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="72" t="n">
+      <c r="A4" s="74" t="n">
         <v>1620</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8002</v>
+        <v>8034</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="72" t="n">
+      <c r="A5" s="74" t="n">
         <v>1623</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8003</v>
+        <v>8035</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="72" t="n">
+      <c r="A6" s="74" t="n">
         <v>1653</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8004</v>
+        <v>8036</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>8005</v>
+        <v>8037</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8006</v>
+        <v>8038</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>8007</v>
+        <v>8039</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8008</v>
+        <v>8040</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>8009</v>
+        <v>8041</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8010</v>
+        <v>8042</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>8011</v>
+        <v>8043</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8012</v>
+        <v>8044</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>8013</v>
+        <v>8045</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8014</v>
+        <v>8046</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>8015</v>
+        <v>8047</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>8016</v>
+        <v>8048</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -85901,45 +87228,45 @@
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>7966</v>
+        <v>7975</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>8017</v>
+        <v>8049</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>8018</v>
+        <v>8050</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>8019</v>
+        <v>8051</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>8020</v>
+        <v>8052</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>8021</v>
+        <v>8053</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>8022</v>
+        <v>8054</v>
       </c>
       <c r="E23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>8023</v>
+        <v>8055</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>8024</v>
+        <v>8056</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
-        <v>7607</v>
+        <v>7616</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>8025</v>
+        <v>8057</v>
       </c>
     </row>
   </sheetData>
@@ -85971,84 +87298,84 @@
   </cols>
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="73" t="s">
-        <v>8026</v>
+      <c r="A8" s="72" t="s">
+        <v>8058</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="73" t="s">
-        <v>8027</v>
+      <c r="A9" s="72" t="s">
+        <v>8059</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73" t="s">
-        <v>8028</v>
+      <c r="A10" s="72" t="s">
+        <v>8060</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="73" t="s">
-        <v>8029</v>
-      </c>
-      <c r="B12" s="74" t="n">
+      <c r="A12" s="72" t="s">
+        <v>8061</v>
+      </c>
+      <c r="B12" s="75" t="n">
         <v>45735</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8030</v>
+        <v>8062</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8031</v>
+        <v>8063</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="73" t="s">
-        <v>8032</v>
-      </c>
-      <c r="B13" s="74" t="n">
+      <c r="A13" s="72" t="s">
+        <v>8064</v>
+      </c>
+      <c r="B13" s="75" t="n">
         <v>45970</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8033</v>
+        <v>8065</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8034</v>
+        <v>8066</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="73" t="s">
-        <v>8035</v>
-      </c>
-      <c r="B14" s="74" t="n">
+      <c r="A14" s="72" t="s">
+        <v>8067</v>
+      </c>
+      <c r="B14" s="75" t="n">
         <v>45995</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8036</v>
+        <v>8068</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8037</v>
+        <v>8069</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="73" t="s">
-        <v>8038</v>
-      </c>
-      <c r="B15" s="74" t="n">
+      <c r="A15" s="72" t="s">
+        <v>8070</v>
+      </c>
+      <c r="B15" s="75" t="n">
         <v>46036</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8039</v>
+        <v>8071</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8040</v>
+        <v>8072</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>8041</v>
+        <v>8073</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>8042</v>
+        <v>8074</v>
       </c>
     </row>
   </sheetData>

--- a/docs/用大藏经自带总目录校对.xlsx
+++ b/docs/用大藏经自带总目录校对.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10937" uniqueCount="8075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10947" uniqueCount="8083">
   <si>
     <t xml:space="preserve">经号</t>
   </si>
@@ -25825,6 +25825,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.chinanews.com.cn/cul/2014/04-12/6057103.shtml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">北京华育图书发行公司向大开元寺赠送折版宣纸乾隆大藏经一部 </t>
   </si>
   <si>
     <r>
@@ -28101,6 +28104,18 @@
     <t xml:space="preserve">慈禧太后寄赠日本西本愿寺</t>
   </si>
   <si>
+    <t xml:space="preserve">1899年（明治32年） </t>
+  </si>
+  <si>
+    <t xml:space="preserve">董炳月｜两种《西域旅行日记》的知识谱系</t>
+  </si>
+  <si>
+    <t xml:space="preserve">董炳月：中国社会科学院文学研究所，公众号开放时代杂志</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mp.weixin.qq.com/s?__biz=MzA4Mjg3MTYyMA==&amp;mid=2660548999&amp;idx=1&amp;sn=9383152200ca614fafffe06c97cd96f5</t>
+  </si>
+  <si>
     <t xml:space="preserve">中国香港和美国万佛城</t>
   </si>
   <si>
@@ -28703,6 +28718,15 @@
   </si>
   <si>
     <t xml:space="preserve">https://book.kongfz.com/102740/682706591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">邢台大开元寺落成开光暨明憨法师升座庆典举行</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 上海大菩文化传播有限公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pusa123.com/pusa/news/dujia/57171.shtml</t>
   </si>
   <si>
     <t xml:space="preserve">《中国汉文大藏经补编》——遍搜历代大藏经经本</t>
@@ -30620,6 +30644,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -30654,10 +30682,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -83798,7 +83822,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:AD217"/>
+  <dimension ref="A3:AD218"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.85"/>
@@ -85302,6 +85326,11 @@
         <v>7746</v>
       </c>
     </row>
+    <row r="96" customFormat="false" ht="26" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="54" t="s">
+        <v>7747</v>
+      </c>
+    </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="47"/>
       <c r="B98" s="28"/>
@@ -85312,7 +85341,7 @@
     </row>
     <row r="99" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="43" t="s">
-        <v>7747</v>
+        <v>7748</v>
       </c>
       <c r="B99" s="28"/>
       <c r="C99" s="28"/>
@@ -85321,14 +85350,14 @@
       <c r="G99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="54" t="s">
-        <v>7748</v>
+      <c r="A100" s="55" t="s">
+        <v>7749</v>
       </c>
       <c r="B100" s="43" t="s">
-        <v>7749</v>
+        <v>7750</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>7750</v>
+        <v>7751</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>7524</v>
@@ -85344,17 +85373,17 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="54" t="s">
-        <v>7751</v>
+      <c r="A101" s="55" t="s">
+        <v>7752</v>
       </c>
       <c r="B101" s="43" t="s">
-        <v>7752</v>
+        <v>7753</v>
       </c>
       <c r="C101" s="28" t="s">
-        <v>7753</v>
+        <v>7754</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>7754</v>
+        <v>7755</v>
       </c>
       <c r="F101" s="51" t="s">
         <v>7668</v>
@@ -85365,13 +85394,13 @@
     </row>
     <row r="102" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="45" t="s">
-        <v>7755</v>
+        <v>7756</v>
       </c>
       <c r="B102" s="52" t="s">
-        <v>7756</v>
+        <v>7757</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>7757</v>
+        <v>7758</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>7524</v>
@@ -85384,20 +85413,20 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="54" t="s">
-        <v>7758</v>
+      <c r="A103" s="55" t="s">
+        <v>7759</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>7759</v>
+        <v>7760</v>
       </c>
       <c r="C103" s="28" t="s">
-        <v>7760</v>
+        <v>7761</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>7524</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>7761</v>
+        <v>7762</v>
       </c>
       <c r="F103" s="28" t="s">
         <v>7525</v>
@@ -85407,14 +85436,14 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="54" t="s">
-        <v>7762</v>
+      <c r="A104" s="55" t="s">
+        <v>7763</v>
       </c>
       <c r="B104" s="28" t="s">
-        <v>7763</v>
+        <v>7764</v>
       </c>
       <c r="C104" s="28" t="s">
-        <v>7764</v>
+        <v>7765</v>
       </c>
       <c r="E104" s="28"/>
       <c r="F104" s="28" t="s">
@@ -85425,20 +85454,20 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="54" t="s">
-        <v>7765</v>
+      <c r="A105" s="55" t="s">
+        <v>7766</v>
       </c>
       <c r="B105" s="28" t="s">
-        <v>7766</v>
+        <v>7767</v>
       </c>
       <c r="C105" s="28" t="s">
-        <v>7767</v>
+        <v>7768</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>7754</v>
+        <v>7755</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>7768</v>
+        <v>7769</v>
       </c>
       <c r="F105" s="51" t="s">
         <v>7668</v>
@@ -85452,37 +85481,37 @@
         <v>44662</v>
       </c>
       <c r="B106" s="28" t="s">
-        <v>7769</v>
+        <v>7770</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>7770</v>
+        <v>7771</v>
       </c>
       <c r="D106" s="28" t="s">
-        <v>7771</v>
+        <v>7772</v>
       </c>
       <c r="E106" s="28" t="s">
-        <v>7772</v>
+        <v>7773</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>7773</v>
+        <v>7774</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>7774</v>
+        <v>7775</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="54" t="s">
-        <v>7775</v>
+      <c r="A107" s="55" t="s">
+        <v>7776</v>
       </c>
       <c r="B107" s="28" t="s">
-        <v>7776</v>
+        <v>7777</v>
       </c>
       <c r="C107" s="28"/>
       <c r="D107" s="1" t="s">
-        <v>7754</v>
+        <v>7755</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>7777</v>
+        <v>7778</v>
       </c>
       <c r="F107" s="51" t="s">
         <v>7668</v>
@@ -85496,25 +85525,25 @@
         <v>44776</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>7778</v>
+        <v>7779</v>
       </c>
       <c r="C108" s="28" t="s">
-        <v>7779</v>
+        <v>7780</v>
       </c>
       <c r="D108" s="28" t="s">
-        <v>7780</v>
+        <v>7781</v>
       </c>
       <c r="E108" s="28" t="s">
-        <v>7781</v>
+        <v>7782</v>
       </c>
       <c r="F108" s="28" t="s">
-        <v>7782</v>
+        <v>7783</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>7783</v>
-      </c>
-    </row>
-    <row r="110" s="55" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>7784</v>
+      </c>
+    </row>
+    <row r="110" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -85660,43 +85689,43 @@
     </row>
     <row r="125" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="126" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="54" t="n">
+      <c r="A126" s="55" t="n">
         <v>45078</v>
       </c>
       <c r="B126" s="46" t="s">
-        <v>7784</v>
-      </c>
-      <c r="C126" s="56" t="s">
         <v>7785</v>
       </c>
+      <c r="C126" s="57" t="s">
+        <v>7786</v>
+      </c>
       <c r="D126" s="48" t="s">
-        <v>7786</v>
+        <v>7787</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>7787</v>
+        <v>7788</v>
       </c>
       <c r="F126" s="44"/>
       <c r="G126" s="50" t="s">
-        <v>7788</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="54" t="n">
+      <c r="A127" s="55" t="n">
         <v>45138</v>
       </c>
       <c r="B127" s="46" t="s">
-        <v>7789</v>
+        <v>7790</v>
       </c>
       <c r="C127" s="48"/>
       <c r="D127" s="48"/>
       <c r="E127" s="44"/>
       <c r="F127" s="44"/>
       <c r="G127" s="1" t="s">
-        <v>7790</v>
+        <v>7791</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="54"/>
+      <c r="A128" s="55"/>
       <c r="B128" s="46"/>
       <c r="C128" s="48"/>
       <c r="D128" s="48"/>
@@ -85706,51 +85735,51 @@
     </row>
     <row r="130" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>7791</v>
+        <v>7792</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="57" t="s">
-        <v>7792</v>
+      <c r="A131" s="58" t="s">
+        <v>7793</v>
       </c>
       <c r="B131" s="41" t="s">
-        <v>7793</v>
+        <v>7794</v>
       </c>
       <c r="C131" s="41" t="s">
-        <v>7794</v>
+        <v>7795</v>
       </c>
       <c r="D131" s="41"/>
       <c r="E131" s="41" t="s">
-        <v>7795</v>
+        <v>7796</v>
       </c>
       <c r="F131" s="41" t="s">
-        <v>7796</v>
+        <v>7797</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>7797</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="132" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>7798</v>
+        <v>7799</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>7799</v>
+        <v>7800</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>7800</v>
+        <v>7801</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>7801</v>
+        <v>7802</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>7802</v>
-      </c>
-      <c r="F132" s="58" t="s">
         <v>7803</v>
       </c>
+      <c r="F132" s="59" t="s">
+        <v>7804</v>
+      </c>
       <c r="G132" s="2" t="s">
-        <v>7804</v>
+        <v>7805</v>
       </c>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
@@ -85777,69 +85806,69 @@
       <c r="AD132" s="1"/>
     </row>
     <row r="133" s="41" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="57" t="s">
-        <v>7805</v>
+      <c r="A133" s="58" t="s">
+        <v>7806</v>
       </c>
       <c r="B133" s="41" t="s">
-        <v>7806</v>
+        <v>7807</v>
       </c>
       <c r="C133" s="41" t="s">
-        <v>7807</v>
-      </c>
-      <c r="D133" s="59" t="s">
         <v>7808</v>
       </c>
+      <c r="D133" s="60" t="s">
+        <v>7809</v>
+      </c>
       <c r="E133" s="41" t="s">
-        <v>7809</v>
+        <v>7810</v>
       </c>
       <c r="F133" s="41" t="s">
-        <v>7796</v>
+        <v>7797</v>
       </c>
       <c r="G133" s="41" t="s">
-        <v>7810</v>
+        <v>7811</v>
       </c>
     </row>
     <row r="134" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="60" t="n">
+      <c r="A134" s="61" t="n">
         <v>42355</v>
       </c>
       <c r="B134" s="41" t="s">
-        <v>7811</v>
+        <v>7812</v>
       </c>
       <c r="C134" s="41" t="s">
-        <v>7812</v>
+        <v>7813</v>
       </c>
       <c r="D134" s="41" t="s">
-        <v>7813</v>
+        <v>7814</v>
       </c>
       <c r="E134" s="41" t="s">
-        <v>7814</v>
+        <v>7815</v>
       </c>
       <c r="F134" s="41" t="s">
-        <v>7815</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="57" t="n">
+      <c r="A135" s="58" t="n">
         <v>43658</v>
       </c>
       <c r="B135" s="41" t="s">
-        <v>7816</v>
+        <v>7817</v>
       </c>
       <c r="C135" s="41" t="s">
+        <v>7818</v>
+      </c>
+      <c r="D135" s="60" t="s">
+        <v>7819</v>
+      </c>
+      <c r="E135" s="41" t="s">
+        <v>7820</v>
+      </c>
+      <c r="F135" s="41" t="s">
         <v>7817</v>
       </c>
-      <c r="D135" s="59" t="s">
-        <v>7818</v>
-      </c>
-      <c r="E135" s="41" t="s">
-        <v>7819</v>
-      </c>
-      <c r="F135" s="41" t="s">
-        <v>7816</v>
-      </c>
       <c r="G135" s="41" t="s">
-        <v>7820</v>
+        <v>7821</v>
       </c>
       <c r="H135" s="41"/>
       <c r="I135" s="41"/>
@@ -85864,30 +85893,30 @@
       <c r="AB135" s="41"/>
       <c r="AC135" s="41"/>
       <c r="AD135" s="41" t="s">
-        <v>7821</v>
+        <v>7822</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="57" t="n">
+      <c r="A136" s="58" t="n">
         <v>45581</v>
       </c>
       <c r="B136" s="41" t="s">
-        <v>7822</v>
+        <v>7823</v>
       </c>
       <c r="C136" s="41" t="s">
+        <v>7824</v>
+      </c>
+      <c r="D136" s="41" t="s">
+        <v>7825</v>
+      </c>
+      <c r="E136" s="60" t="s">
+        <v>7826</v>
+      </c>
+      <c r="F136" s="41" t="s">
         <v>7823</v>
       </c>
-      <c r="D136" s="41" t="s">
-        <v>7824</v>
-      </c>
-      <c r="E136" s="59" t="s">
-        <v>7825</v>
-      </c>
-      <c r="F136" s="41" t="s">
-        <v>7822</v>
-      </c>
-      <c r="G136" s="61" t="s">
-        <v>7826</v>
+      <c r="G136" s="62" t="s">
+        <v>7827</v>
       </c>
       <c r="H136" s="41"/>
       <c r="I136" s="41"/>
@@ -85914,20 +85943,20 @@
       <c r="AD136" s="41"/>
     </row>
     <row r="137" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="60" t="n">
+      <c r="A137" s="61" t="n">
         <v>45668</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>7827</v>
+        <v>7828</v>
       </c>
       <c r="C137" s="28" t="s">
-        <v>7828</v>
+        <v>7829</v>
       </c>
       <c r="D137" s="28" t="s">
-        <v>7829</v>
+        <v>7830</v>
       </c>
       <c r="E137" s="45" t="s">
-        <v>7830</v>
+        <v>7831</v>
       </c>
       <c r="F137" s="28" t="s">
         <v>7572</v>
@@ -85938,272 +85967,272 @@
     </row>
     <row r="139" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>7831</v>
+        <v>7832</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="59" t="s">
-        <v>7832</v>
+      <c r="A140" s="60" t="s">
+        <v>7833</v>
       </c>
       <c r="B140" s="2" t="s">
+        <v>7834</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>7835</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>7836</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>7837</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="58" t="s">
+        <v>7838</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>7839</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>7836</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>7840</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="60" t="s">
         <v>7833</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>7834</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>7835</v>
-      </c>
-      <c r="G140" s="2" t="s">
+      <c r="B142" s="2" t="s">
+        <v>7841</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>7842</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>7836</v>
       </c>
-    </row>
-    <row r="141" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="57" t="s">
-        <v>7837</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>7838</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>7835</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>7839</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="59" t="s">
-        <v>7832</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>7840</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>7841</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>7835</v>
-      </c>
       <c r="G142" s="2" t="s">
-        <v>7842</v>
+        <v>7843</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="28" t="s">
-        <v>7843</v>
+        <v>7844</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>7844</v>
+        <v>7845</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>7845</v>
+        <v>7846</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>7846</v>
+        <v>7847</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>7821</v>
+        <v>7822</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
+        <v>7848</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>7849</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>7850</v>
+      </c>
+      <c r="F144" s="1" t="s">
         <v>7847</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>7848</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>7849</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>7846</v>
-      </c>
       <c r="G144" s="1" t="s">
-        <v>7850</v>
+        <v>7851</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="43" t="s">
-        <v>7851</v>
+        <v>7852</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>7852</v>
+        <v>7853</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>7853</v>
+        <v>7854</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>7854</v>
+        <v>7855</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>7855</v>
+        <v>7856</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="62" t="s">
-        <v>7856</v>
+      <c r="A146" s="63" t="s">
+        <v>7857</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>7857</v>
+        <v>7858</v>
       </c>
       <c r="C146" s="45" t="s">
-        <v>7858</v>
+        <v>7859</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>7859</v>
+        <v>7860</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
+        <v>7848</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>7861</v>
+      </c>
+      <c r="C147" s="41" t="s">
+        <v>7862</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>7863</v>
+      </c>
+      <c r="F147" s="1" t="s">
         <v>7847</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>7860</v>
-      </c>
-      <c r="C147" s="41" t="s">
-        <v>7861</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>7862</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>7846</v>
-      </c>
       <c r="G147" s="2" t="s">
-        <v>7850</v>
+        <v>7851</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="28" t="s">
-        <v>7863</v>
+        <v>7864</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>7864</v>
+        <v>7865</v>
       </c>
       <c r="C148" s="41" t="s">
-        <v>7865</v>
+        <v>7866</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>7866</v>
+        <v>7867</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>7846</v>
+        <v>7847</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>7867</v>
+        <v>7868</v>
       </c>
       <c r="H148" s="1"/>
     </row>
     <row r="149" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="59" t="s">
-        <v>7832</v>
+      <c r="A149" s="60" t="s">
+        <v>7833</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>7868</v>
+        <v>7869</v>
       </c>
       <c r="D149" s="28" t="s">
-        <v>7869</v>
+        <v>7870</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>7870</v>
+        <v>7871</v>
       </c>
       <c r="F149" s="43" t="s">
-        <v>7871</v>
+        <v>7872</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>7872</v>
+        <v>7873</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B150" s="48" t="s">
-        <v>7873</v>
+        <v>7874</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>7874</v>
+        <v>7875</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="62" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="63" t="s">
-        <v>7875</v>
+      <c r="A151" s="54" t="s">
+        <v>7876</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>7876</v>
+        <v>7877</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>7877</v>
+        <v>7878</v>
       </c>
       <c r="B152" s="48" t="s">
-        <v>7878</v>
+        <v>7879</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>7879</v>
+        <v>7880</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="48" t="s">
-        <v>7880</v>
+        <v>7881</v>
       </c>
       <c r="B153" s="48" t="s">
-        <v>7881</v>
+        <v>7882</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>7882</v>
+        <v>7883</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="43" t="s">
-        <v>7883</v>
+        <v>7884</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>7884</v>
+        <v>7885</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>7707</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>7835</v>
+        <v>7836</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>7885</v>
+        <v>7886</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>7886</v>
+        <v>7887</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>7887</v>
+        <v>7888</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>7888</v>
+        <v>7889</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>7889</v>
+        <v>7890</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>7890</v>
+        <v>7891</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>7891</v>
+        <v>7892</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="43" t="s">
-        <v>7892</v>
+        <v>7893</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="28" t="s">
-        <v>7893</v>
+        <v>7894</v>
       </c>
       <c r="B169" s="28"/>
       <c r="C169" s="28"/>
@@ -86213,15 +86242,15 @@
     </row>
     <row r="170" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="64" t="s">
-        <v>7894</v>
+        <v>7895</v>
       </c>
       <c r="D170" s="64" t="s">
-        <v>7895</v>
+        <v>7896</v>
       </c>
       <c r="E170" s="64" t="s">
-        <v>7896</v>
-      </c>
-      <c r="F170" s="62" t="s">
+        <v>7897</v>
+      </c>
+      <c r="F170" s="63" t="s">
         <v>7511</v>
       </c>
       <c r="G170" s="2" t="s">
@@ -86230,42 +86259,42 @@
     </row>
     <row r="171" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="64" t="s">
-        <v>7897</v>
+        <v>7898</v>
       </c>
       <c r="C171" s="28"/>
       <c r="D171" s="64" t="s">
-        <v>7895</v>
+        <v>7896</v>
       </c>
       <c r="E171" s="64" t="s">
-        <v>7898</v>
+        <v>7899</v>
       </c>
       <c r="F171" s="65" t="s">
-        <v>7899</v>
+        <v>7900</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>7900</v>
+        <v>7901</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>7901</v>
+        <v>7902</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="28" t="s">
-        <v>7902</v>
+        <v>7903</v>
       </c>
       <c r="B174" s="28" t="s">
-        <v>7903</v>
+        <v>7904</v>
       </c>
       <c r="C174" s="28" t="s">
-        <v>7904</v>
+        <v>7905</v>
       </c>
       <c r="D174" s="28" t="s">
         <v>7538</v>
       </c>
       <c r="E174" s="28" t="s">
-        <v>7905</v>
+        <v>7906</v>
       </c>
       <c r="F174" s="28" t="s">
         <v>7539</v>
@@ -86276,153 +86305,151 @@
     </row>
     <row r="175" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="28" t="s">
-        <v>7906</v>
+        <v>7907</v>
       </c>
       <c r="B175" s="28" t="s">
-        <v>7903</v>
+        <v>7904</v>
       </c>
       <c r="C175" s="28" t="s">
-        <v>7907</v>
+        <v>7908</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>7908</v>
+        <v>7909</v>
       </c>
       <c r="E175" s="28" t="s">
-        <v>7909</v>
+        <v>7910</v>
       </c>
       <c r="F175" s="28" t="s">
-        <v>7910</v>
+        <v>7911</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>7911</v>
+        <v>7912</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="28" t="s">
-        <v>7902</v>
+        <v>7903</v>
       </c>
       <c r="B176" s="28" t="s">
-        <v>7903</v>
+        <v>7904</v>
       </c>
       <c r="C176" s="28" t="s">
-        <v>7912</v>
+        <v>7913</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>7913</v>
+        <v>7914</v>
       </c>
       <c r="E176" s="28" t="s">
-        <v>7914</v>
+        <v>7915</v>
       </c>
       <c r="F176" s="28" t="s">
-        <v>7915</v>
+        <v>7916</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>7916</v>
+        <v>7917</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="47" t="s">
-        <v>7917</v>
+        <v>7918</v>
       </c>
       <c r="B177" s="28" t="s">
-        <v>7918</v>
+        <v>7919</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>7919</v>
+        <v>7920</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>7920</v>
+        <v>7921</v>
       </c>
       <c r="F177" s="28" t="s">
-        <v>7899</v>
-      </c>
-      <c r="G177" s="58" t="s">
         <v>7900</v>
+      </c>
+      <c r="G177" s="59" t="s">
+        <v>7901</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="47" t="s">
-        <v>7921</v>
+        <v>7922</v>
       </c>
       <c r="B178" s="43" t="s">
-        <v>7922</v>
+        <v>7923</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>7923</v>
+        <v>7924</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>7924</v>
+        <v>7925</v>
       </c>
       <c r="E178" s="28" t="s">
-        <v>7925</v>
+        <v>7926</v>
       </c>
       <c r="F178" s="28" t="s">
-        <v>7926</v>
-      </c>
-      <c r="G178" s="58" t="s">
         <v>7927</v>
+      </c>
+      <c r="G178" s="59" t="s">
+        <v>7928</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>7928</v>
+        <v>7929</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>7929</v>
+        <v>7930</v>
       </c>
       <c r="C179" s="1" t="s">
+        <v>7931</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>7921</v>
+      </c>
+      <c r="F179" s="28" t="s">
+        <v>7900</v>
+      </c>
+      <c r="G179" s="59" t="s">
+        <v>7901</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="1" t="s">
+        <v>7932</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>7930</v>
       </c>
-      <c r="E179" s="1" t="s">
-        <v>7920</v>
-      </c>
-      <c r="F179" s="28" t="s">
-        <v>7899</v>
-      </c>
-      <c r="G179" s="58" t="s">
+      <c r="D180" s="0" t="s">
+        <v>7933</v>
+      </c>
+      <c r="F180" s="48" t="s">
+        <v>7934</v>
+      </c>
+      <c r="G180" s="59" t="s">
+        <v>7935</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B181" s="1" t="s">
+        <v>7936</v>
+      </c>
+      <c r="D181" s="44"/>
+      <c r="E181" s="1" t="s">
+        <v>7921</v>
+      </c>
+      <c r="F181" s="28" t="s">
         <v>7900</v>
       </c>
-    </row>
-    <row r="180" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B180" s="1" t="s">
-        <v>7931</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>7920</v>
-      </c>
-      <c r="F180" s="28" t="s">
-        <v>7899</v>
-      </c>
-      <c r="G180" s="58" t="s">
-        <v>7900</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="1" t="s">
-        <v>7932</v>
-      </c>
-      <c r="B181" s="28" t="s">
-        <v>7933</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>7934</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>7935</v>
-      </c>
-      <c r="F181" s="28" t="s">
-        <v>7936</v>
-      </c>
-      <c r="G181" s="58" t="s">
+      <c r="G181" s="59" t="s">
+        <v>7901</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="s">
         <v>7937</v>
       </c>
-    </row>
-    <row r="182" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="1" t="s">
+      <c r="B182" s="28" t="s">
         <v>7938</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>7647</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>7939</v>
@@ -86430,334 +86457,325 @@
       <c r="D182" s="1" t="s">
         <v>7940</v>
       </c>
-      <c r="E182" s="1" t="s">
+      <c r="F182" s="28" t="s">
         <v>7941</v>
       </c>
-      <c r="F182" s="1" t="s">
+      <c r="G182" s="59" t="s">
+        <v>7942</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A183" s="1" t="s">
+        <v>7943</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>7647</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>7944</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>7945</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>7946</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>7649</v>
       </c>
-      <c r="G182" s="1" t="s">
+      <c r="G183" s="1" t="s">
         <v>7650</v>
-      </c>
-    </row>
-    <row r="183" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="47" t="n">
-        <v>36795</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>7942</v>
-      </c>
-      <c r="C183" s="28" t="s">
-        <v>7943</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>7944</v>
-      </c>
-      <c r="E183" s="28" t="s">
-        <v>7945</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>7946</v>
-      </c>
-      <c r="G183" s="2" t="s">
-        <v>7947</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="47" t="n">
+        <v>36795</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>7947</v>
+      </c>
+      <c r="C184" s="28" t="s">
+        <v>7948</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>7949</v>
+      </c>
+      <c r="E184" s="28" t="s">
+        <v>7950</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>7951</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>7952</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="47" t="n">
         <v>45216</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>7948</v>
-      </c>
-      <c r="C184" s="28" t="s">
-        <v>7949</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>7950</v>
-      </c>
-      <c r="E184" s="28" t="s">
-        <v>7951</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>7952</v>
-      </c>
-      <c r="G184" s="1" t="s">
+      <c r="B185" s="1" t="s">
         <v>7953</v>
       </c>
-    </row>
-    <row r="185" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="47" t="n">
-        <v>45458</v>
-      </c>
-      <c r="B185" s="1" t="s">
+      <c r="C185" s="28" t="s">
         <v>7954</v>
       </c>
-      <c r="C185" s="1" t="s">
+      <c r="D185" s="1" t="s">
         <v>7955</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>7477</v>
       </c>
       <c r="E185" s="28" t="s">
         <v>7956</v>
       </c>
       <c r="F185" s="1" t="s">
+        <v>7957</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>7958</v>
+      </c>
+    </row>
+    <row r="186" s="41" customFormat="true" ht="16" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A186" s="47" t="n">
+        <v>45458</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>7959</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>7960</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>7477</v>
+      </c>
+      <c r="E186" s="28" t="s">
+        <v>7961</v>
+      </c>
+      <c r="F186" s="1" t="s">
         <v>7479</v>
       </c>
-      <c r="G185" s="1" t="s">
+      <c r="G186" s="1" t="s">
         <v>7480</v>
       </c>
     </row>
-    <row r="188" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="47" t="s">
-        <v>7957</v>
-      </c>
-      <c r="B188" s="28"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
-      <c r="E188" s="1"/>
-      <c r="F188" s="28"/>
-      <c r="G188" s="2"/>
-      <c r="H188" s="1"/>
-      <c r="I188" s="1"/>
-      <c r="J188" s="1"/>
-      <c r="K188" s="1"/>
-      <c r="L188" s="1"/>
-      <c r="M188" s="1"/>
-      <c r="N188" s="1"/>
-      <c r="O188" s="1"/>
-      <c r="P188" s="1"/>
-      <c r="Q188" s="1"/>
-      <c r="R188" s="1"/>
-      <c r="S188" s="1"/>
-      <c r="T188" s="1"/>
-      <c r="U188" s="1"/>
-      <c r="V188" s="1"/>
-      <c r="W188" s="1"/>
-      <c r="X188" s="1"/>
-      <c r="Y188" s="1"/>
-      <c r="Z188" s="1"/>
-      <c r="AA188" s="1"/>
-      <c r="AB188" s="1"/>
-      <c r="AC188" s="1"/>
-      <c r="AD188" s="1"/>
-    </row>
-    <row r="189" s="55" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="66" t="n">
+    <row r="189" s="56" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="47" t="s">
+        <v>7962</v>
+      </c>
+      <c r="B189" s="28"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="1"/>
+      <c r="F189" s="28"/>
+      <c r="G189" s="2"/>
+      <c r="H189" s="1"/>
+      <c r="I189" s="1"/>
+      <c r="J189" s="1"/>
+      <c r="K189" s="1"/>
+      <c r="L189" s="1"/>
+      <c r="M189" s="1"/>
+      <c r="N189" s="1"/>
+      <c r="O189" s="1"/>
+      <c r="P189" s="1"/>
+      <c r="Q189" s="1"/>
+      <c r="R189" s="1"/>
+      <c r="S189" s="1"/>
+      <c r="T189" s="1"/>
+      <c r="U189" s="1"/>
+      <c r="V189" s="1"/>
+      <c r="W189" s="1"/>
+      <c r="X189" s="1"/>
+      <c r="Y189" s="1"/>
+      <c r="Z189" s="1"/>
+      <c r="AA189" s="1"/>
+      <c r="AB189" s="1"/>
+      <c r="AC189" s="1"/>
+      <c r="AD189" s="1"/>
+    </row>
+    <row r="190" s="56" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="66" t="n">
         <v>45004</v>
       </c>
-      <c r="B189" s="55" t="s">
-        <v>7958</v>
-      </c>
-      <c r="C189" s="55" t="s">
-        <v>7959</v>
-      </c>
-      <c r="D189" s="55" t="s">
-        <v>7960</v>
-      </c>
-      <c r="E189" s="55" t="s">
-        <v>7961</v>
-      </c>
-      <c r="F189" s="67" t="s">
-        <v>7962</v>
-      </c>
-      <c r="G189" s="55" t="s">
+      <c r="B190" s="56" t="s">
         <v>7963</v>
       </c>
-    </row>
-    <row r="190" s="55" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="66" t="n">
+      <c r="C190" s="56" t="s">
+        <v>7964</v>
+      </c>
+      <c r="D190" s="56" t="s">
+        <v>7965</v>
+      </c>
+      <c r="E190" s="56" t="s">
+        <v>7966</v>
+      </c>
+      <c r="F190" s="67" t="s">
+        <v>7967</v>
+      </c>
+      <c r="G190" s="56" t="s">
+        <v>7968</v>
+      </c>
+    </row>
+    <row r="191" s="56" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="66" t="n">
         <v>45005</v>
       </c>
-      <c r="B190" s="67" t="s">
-        <v>7964</v>
-      </c>
-      <c r="C190" s="55" t="s">
-        <v>7965</v>
-      </c>
-      <c r="D190" s="55" t="s">
-        <v>7966</v>
-      </c>
-      <c r="E190" s="55" t="s">
-        <v>7967</v>
-      </c>
-      <c r="F190" s="67" t="s">
-        <v>7968</v>
-      </c>
-      <c r="G190" s="55" t="s">
+      <c r="B191" s="67" t="s">
         <v>7969</v>
       </c>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="66" t="n">
-        <v>45006</v>
-      </c>
-      <c r="B191" s="55" t="s">
-        <v>7958</v>
-      </c>
-      <c r="C191" s="55" t="s">
+      <c r="C191" s="56" t="s">
         <v>7970</v>
       </c>
-      <c r="D191" s="55" t="s">
+      <c r="D191" s="56" t="s">
         <v>7971</v>
       </c>
-      <c r="E191" s="68" t="s">
+      <c r="E191" s="56" t="s">
         <v>7972</v>
       </c>
       <c r="F191" s="67" t="s">
         <v>7973</v>
       </c>
-      <c r="G191" s="55" t="s">
+      <c r="G191" s="56" t="s">
         <v>7974</v>
       </c>
-      <c r="H191" s="55"/>
-      <c r="I191" s="55"/>
-      <c r="J191" s="55"/>
-      <c r="K191" s="55"/>
-      <c r="L191" s="55"/>
-      <c r="M191" s="55"/>
-      <c r="N191" s="55"/>
-      <c r="O191" s="55"/>
-      <c r="P191" s="55"/>
-      <c r="Q191" s="55"/>
-      <c r="R191" s="55"/>
-      <c r="S191" s="55"/>
-      <c r="T191" s="55"/>
-      <c r="U191" s="55"/>
-      <c r="V191" s="55"/>
-      <c r="W191" s="55"/>
-      <c r="X191" s="55"/>
-      <c r="Y191" s="55"/>
-      <c r="Z191" s="55"/>
-      <c r="AA191" s="55"/>
-      <c r="AB191" s="55"/>
-      <c r="AC191" s="55"/>
-      <c r="AD191" s="55"/>
-    </row>
-    <row r="192" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="66" t="n">
+        <v>45006</v>
+      </c>
+      <c r="B192" s="56" t="s">
+        <v>7963</v>
+      </c>
+      <c r="C192" s="56" t="s">
+        <v>7975</v>
+      </c>
+      <c r="D192" s="56" t="s">
+        <v>7976</v>
+      </c>
+      <c r="E192" s="68" t="s">
+        <v>7977</v>
+      </c>
+      <c r="F192" s="67" t="s">
+        <v>7978</v>
+      </c>
+      <c r="G192" s="56" t="s">
+        <v>7979</v>
+      </c>
+      <c r="H192" s="56"/>
+      <c r="I192" s="56"/>
+      <c r="J192" s="56"/>
+      <c r="K192" s="56"/>
+      <c r="L192" s="56"/>
+      <c r="M192" s="56"/>
+      <c r="N192" s="56"/>
+      <c r="O192" s="56"/>
+      <c r="P192" s="56"/>
+      <c r="Q192" s="56"/>
+      <c r="R192" s="56"/>
+      <c r="S192" s="56"/>
+      <c r="T192" s="56"/>
+      <c r="U192" s="56"/>
+      <c r="V192" s="56"/>
+      <c r="W192" s="56"/>
+      <c r="X192" s="56"/>
+      <c r="Y192" s="56"/>
+      <c r="Z192" s="56"/>
+      <c r="AA192" s="56"/>
+      <c r="AB192" s="56"/>
+      <c r="AC192" s="56"/>
+      <c r="AD192" s="56"/>
+    </row>
+    <row r="193" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="66" t="n">
         <v>45036</v>
       </c>
-      <c r="B192" s="55" t="s">
-        <v>7975</v>
-      </c>
-      <c r="C192" s="55"/>
-      <c r="D192" s="55" t="s">
-        <v>7976</v>
-      </c>
-      <c r="E192" s="55" t="s">
-        <v>7977</v>
-      </c>
-      <c r="F192" s="55" t="s">
-        <v>7978</v>
-      </c>
-      <c r="G192" s="55" t="s">
-        <v>7979</v>
-      </c>
-      <c r="H192" s="55"/>
-      <c r="I192" s="55"/>
-      <c r="J192" s="55"/>
-      <c r="K192" s="55"/>
-      <c r="L192" s="55"/>
-      <c r="M192" s="55"/>
-      <c r="N192" s="55"/>
-      <c r="O192" s="55"/>
-      <c r="P192" s="55"/>
-      <c r="Q192" s="55"/>
-      <c r="R192" s="55"/>
-      <c r="S192" s="55"/>
-      <c r="T192" s="55"/>
-      <c r="U192" s="55"/>
-      <c r="V192" s="55"/>
-      <c r="W192" s="55"/>
-      <c r="X192" s="55"/>
-      <c r="Y192" s="55"/>
-      <c r="Z192" s="55"/>
-      <c r="AA192" s="55"/>
-      <c r="AB192" s="55"/>
-      <c r="AC192" s="55"/>
-      <c r="AD192" s="55"/>
-    </row>
-    <row r="193" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="69" t="n">
+      <c r="B193" s="56" t="s">
+        <v>7980</v>
+      </c>
+      <c r="C193" s="56"/>
+      <c r="D193" s="56" t="s">
+        <v>7981</v>
+      </c>
+      <c r="E193" s="56" t="s">
+        <v>7982</v>
+      </c>
+      <c r="F193" s="56" t="s">
+        <v>7983</v>
+      </c>
+      <c r="G193" s="56" t="s">
+        <v>7984</v>
+      </c>
+      <c r="H193" s="56"/>
+      <c r="I193" s="56"/>
+      <c r="J193" s="56"/>
+      <c r="K193" s="56"/>
+      <c r="L193" s="56"/>
+      <c r="M193" s="56"/>
+      <c r="N193" s="56"/>
+      <c r="O193" s="56"/>
+      <c r="P193" s="56"/>
+      <c r="Q193" s="56"/>
+      <c r="R193" s="56"/>
+      <c r="S193" s="56"/>
+      <c r="T193" s="56"/>
+      <c r="U193" s="56"/>
+      <c r="V193" s="56"/>
+      <c r="W193" s="56"/>
+      <c r="X193" s="56"/>
+      <c r="Y193" s="56"/>
+      <c r="Z193" s="56"/>
+      <c r="AA193" s="56"/>
+      <c r="AB193" s="56"/>
+      <c r="AC193" s="56"/>
+      <c r="AD193" s="56"/>
+    </row>
+    <row r="194" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A194" s="69" t="n">
         <v>45088</v>
       </c>
-      <c r="B193" s="58" t="s">
-        <v>7958</v>
-      </c>
-      <c r="C193" s="58" t="s">
-        <v>7980</v>
-      </c>
-      <c r="D193" s="58" t="s">
-        <v>7981</v>
-      </c>
-      <c r="E193" s="70" t="s">
-        <v>7982</v>
-      </c>
-      <c r="F193" s="58" t="s">
-        <v>7899</v>
-      </c>
-      <c r="G193" s="58" t="s">
+      <c r="B194" s="59" t="s">
+        <v>7963</v>
+      </c>
+      <c r="C194" s="59" t="s">
+        <v>7985</v>
+      </c>
+      <c r="D194" s="59" t="s">
+        <v>7986</v>
+      </c>
+      <c r="E194" s="70" t="s">
+        <v>7987</v>
+      </c>
+      <c r="F194" s="59" t="s">
         <v>7900</v>
       </c>
-    </row>
-    <row r="194" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="69" t="n">
+      <c r="G194" s="59" t="s">
+        <v>7901</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="69" t="n">
         <v>45025</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="B195" s="1" t="s">
         <v>7745</v>
       </c>
-      <c r="C194" s="28" t="s">
-        <v>7983</v>
-      </c>
-      <c r="D194" s="43" t="s">
-        <v>7984</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>7985</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>7986</v>
-      </c>
-    </row>
-    <row r="195" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1"/>
-      <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
-      <c r="E195" s="1"/>
-      <c r="F195" s="1"/>
-      <c r="G195" s="1"/>
-      <c r="H195" s="1"/>
-      <c r="I195" s="1"/>
-      <c r="J195" s="1"/>
-      <c r="K195" s="1"/>
-      <c r="L195" s="1"/>
-      <c r="M195" s="1"/>
-      <c r="N195" s="1"/>
-      <c r="O195" s="1"/>
-      <c r="P195" s="1"/>
-      <c r="Q195" s="1"/>
-      <c r="R195" s="1"/>
-      <c r="S195" s="1"/>
-      <c r="T195" s="1"/>
-      <c r="U195" s="1"/>
-      <c r="V195" s="1"/>
-      <c r="W195" s="1"/>
-      <c r="X195" s="1"/>
-      <c r="Y195" s="1"/>
-      <c r="Z195" s="1"/>
-      <c r="AA195" s="1"/>
-      <c r="AB195" s="1"/>
-      <c r="AC195" s="1"/>
-      <c r="AD195" s="1"/>
-    </row>
-    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1" t="s">
-        <v>7987</v>
-      </c>
+      <c r="C195" s="28" t="s">
+        <v>7988</v>
+      </c>
+      <c r="D195" s="43" t="s">
+        <v>7989</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>7990</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>7991</v>
+      </c>
+    </row>
+    <row r="196" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
+      <c r="E196" s="1"/>
+      <c r="F196" s="1"/>
       <c r="G196" s="1"/>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
@@ -86783,199 +86801,248 @@
       <c r="AC196" s="1"/>
       <c r="AD196" s="1"/>
     </row>
-    <row r="197" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="57" t="n">
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1" t="s">
+        <v>7992</v>
+      </c>
+      <c r="G197" s="1"/>
+      <c r="H197" s="1"/>
+      <c r="I197" s="1"/>
+      <c r="J197" s="1"/>
+      <c r="K197" s="1"/>
+      <c r="L197" s="1"/>
+      <c r="M197" s="1"/>
+      <c r="N197" s="1"/>
+      <c r="O197" s="1"/>
+      <c r="P197" s="1"/>
+      <c r="Q197" s="1"/>
+      <c r="R197" s="1"/>
+      <c r="S197" s="1"/>
+      <c r="T197" s="1"/>
+      <c r="U197" s="1"/>
+      <c r="V197" s="1"/>
+      <c r="W197" s="1"/>
+      <c r="X197" s="1"/>
+      <c r="Y197" s="1"/>
+      <c r="Z197" s="1"/>
+      <c r="AA197" s="1"/>
+      <c r="AB197" s="1"/>
+      <c r="AC197" s="1"/>
+      <c r="AD197" s="1"/>
+    </row>
+    <row r="198" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="58" t="n">
         <v>39252</v>
       </c>
-      <c r="B197" s="41"/>
-      <c r="C197" s="41" t="s">
-        <v>7988</v>
-      </c>
-      <c r="D197" s="59" t="s">
-        <v>7989</v>
-      </c>
-      <c r="E197" s="41" t="s">
-        <v>7990</v>
-      </c>
-      <c r="F197" s="41" t="s">
-        <v>7991</v>
-      </c>
-      <c r="G197" s="41" t="s">
-        <v>7992</v>
-      </c>
-      <c r="H197" s="41"/>
-      <c r="I197" s="41"/>
-      <c r="J197" s="41"/>
-      <c r="K197" s="41"/>
-      <c r="L197" s="41"/>
-      <c r="M197" s="41"/>
-      <c r="N197" s="41"/>
-      <c r="O197" s="41"/>
-      <c r="P197" s="41"/>
-      <c r="Q197" s="41"/>
-      <c r="R197" s="41"/>
-      <c r="S197" s="41"/>
-      <c r="T197" s="41"/>
-      <c r="U197" s="41"/>
-      <c r="V197" s="41"/>
-      <c r="W197" s="41"/>
-      <c r="X197" s="41"/>
-      <c r="Y197" s="41"/>
-      <c r="Z197" s="41"/>
-      <c r="AA197" s="41"/>
-      <c r="AB197" s="41"/>
-      <c r="AC197" s="41"/>
-      <c r="AD197" s="41"/>
-    </row>
-    <row r="198" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="47" t="n">
+      <c r="B198" s="41"/>
+      <c r="C198" s="41" t="s">
+        <v>7993</v>
+      </c>
+      <c r="D198" s="60" t="s">
+        <v>7994</v>
+      </c>
+      <c r="E198" s="41" t="s">
+        <v>7995</v>
+      </c>
+      <c r="F198" s="41" t="s">
+        <v>7996</v>
+      </c>
+      <c r="G198" s="41" t="s">
+        <v>7997</v>
+      </c>
+      <c r="H198" s="41"/>
+      <c r="I198" s="41"/>
+      <c r="J198" s="41"/>
+      <c r="K198" s="41"/>
+      <c r="L198" s="41"/>
+      <c r="M198" s="41"/>
+      <c r="N198" s="41"/>
+      <c r="O198" s="41"/>
+      <c r="P198" s="41"/>
+      <c r="Q198" s="41"/>
+      <c r="R198" s="41"/>
+      <c r="S198" s="41"/>
+      <c r="T198" s="41"/>
+      <c r="U198" s="41"/>
+      <c r="V198" s="41"/>
+      <c r="W198" s="41"/>
+      <c r="X198" s="41"/>
+      <c r="Y198" s="41"/>
+      <c r="Z198" s="41"/>
+      <c r="AA198" s="41"/>
+      <c r="AB198" s="41"/>
+      <c r="AC198" s="41"/>
+      <c r="AD198" s="41"/>
+    </row>
+    <row r="199" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="47" t="n">
         <v>46241</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>7993</v>
-      </c>
-      <c r="C198" s="28" t="s">
-        <v>7994</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>7995</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>7996</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="47" t="s">
-        <v>7997</v>
-      </c>
-      <c r="B199" s="28" t="s">
+      <c r="B199" s="1" t="s">
         <v>7998</v>
       </c>
-      <c r="C199" s="1" t="s">
+      <c r="C199" s="28" t="s">
         <v>7999</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="F199" s="1" t="s">
         <v>8000</v>
       </c>
-      <c r="F199" s="28" t="s">
+      <c r="G199" s="1" t="s">
         <v>8001</v>
       </c>
-      <c r="G199" s="2" t="s">
+    </row>
+    <row r="200" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="47" t="s">
         <v>8002</v>
       </c>
-    </row>
-    <row r="200" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="54" t="n">
-        <v>42866</v>
-      </c>
-      <c r="B200" s="1" t="s">
+      <c r="B200" s="28" t="s">
         <v>8003</v>
       </c>
-      <c r="C200" s="28" t="s">
+      <c r="C200" s="1" t="s">
         <v>8004</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>8005</v>
       </c>
-      <c r="E200" s="1" t="s">
+      <c r="F200" s="28" t="s">
         <v>8006</v>
-      </c>
-      <c r="F200" s="28" t="s">
-        <v>7835</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>8007</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B204" s="63" t="s">
+    <row r="201" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="55" t="n">
+        <v>42866</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>8008</v>
       </c>
-      <c r="C204" s="1" t="s">
+      <c r="C201" s="28" t="s">
         <v>8009</v>
       </c>
-    </row>
-    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B205" s="1" t="s">
+      <c r="D201" s="1" t="s">
         <v>8010</v>
       </c>
+      <c r="E201" s="1" t="s">
+        <v>8011</v>
+      </c>
+      <c r="F201" s="28" t="s">
+        <v>7836</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>8012</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="47" t="n">
+        <v>41531</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>7747</v>
+      </c>
+      <c r="D202" s="0" t="s">
+        <v>8013</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>8014</v>
+      </c>
+      <c r="G202" s="0" t="s">
+        <v>8015</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D203" s="44"/>
+    </row>
+    <row r="205" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B205" s="54" t="s">
+        <v>8016</v>
+      </c>
       <c r="C205" s="1" t="s">
-        <v>8011</v>
+        <v>8017</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B206" s="0" t="s">
-        <v>8012</v>
+      <c r="B206" s="1" t="s">
+        <v>8018</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>8013</v>
-      </c>
-    </row>
-    <row r="207" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B207" s="63" t="s">
-        <v>8014</v>
-      </c>
-      <c r="C207" s="50" t="s">
-        <v>8015</v>
-      </c>
-      <c r="F207" s="48" t="s">
-        <v>8016</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B209" s="71" t="s">
-        <v>8017</v>
-      </c>
-      <c r="C209" s="72" t="s">
-        <v>8018</v>
+        <v>8019</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B207" s="0" t="s">
+        <v>8020</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>8021</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B208" s="54" t="s">
+        <v>8022</v>
+      </c>
+      <c r="C208" s="50" t="s">
+        <v>8023</v>
+      </c>
+      <c r="F208" s="48" t="s">
+        <v>8024</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B210" s="1" t="s">
-        <v>8019</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>8020</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B212" s="1" t="s">
-        <v>8021</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>8022</v>
+      <c r="B210" s="71" t="s">
+        <v>8025</v>
+      </c>
+      <c r="C210" s="72" t="s">
+        <v>8026</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B211" s="1" t="s">
+        <v>8027</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>8028</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B213" s="48" t="s">
-        <v>8023</v>
+      <c r="B213" s="1" t="s">
+        <v>8029</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>8024</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B214" s="56" t="s">
-        <v>8025</v>
+        <v>8030</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B214" s="48" t="s">
+        <v>8031</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>8026</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B216" s="63" t="s">
-        <v>8027</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>8028</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B217" s="0" t="s">
-        <v>8029</v>
+        <v>8032</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B215" s="57" t="s">
+        <v>8033</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>8034</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B217" s="54" t="s">
+        <v>8035</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>8030</v>
+        <v>8036</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B218" s="0" t="s">
+        <v>8037</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>8038</v>
       </c>
     </row>
   </sheetData>
@@ -87071,16 +87138,16 @@
     <hyperlink ref="G176" r:id="rId89" display="https://whly.gd.gov.cn/service_newwwbwg/content/post_4738424.html"/>
     <hyperlink ref="G177" r:id="rId90" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
     <hyperlink ref="G179" r:id="rId91" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G180" r:id="rId92" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G183" r:id="rId93" display="https://edu.sina.com.cn/wander/2000-09-25/12790.shtml"/>
-    <hyperlink ref="G189" r:id="rId94" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
-    <hyperlink ref="F191" r:id="rId95" display="中新网北京3月21日电 (记者 应妮) "/>
-    <hyperlink ref="G191" r:id="rId96" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
-    <hyperlink ref="G193" r:id="rId97" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
-    <hyperlink ref="G197" r:id="rId98" display="https://discovery.cctv.com/20070619/107154.shtml"/>
-    <hyperlink ref="G200" r:id="rId99" display="https://book.kongfz.com/102740/682706591"/>
-    <hyperlink ref="C207" r:id="rId100" location="4" display="https://opac.ryukoku.ac.jp/iwjs0005opc/bdyview.do?bodyid=BD00000117&amp;elmid=Body&amp;fname=r-rn_471_006.pdf&amp;loginflg=on&amp;once=true#4"/>
-    <hyperlink ref="B214" r:id="rId101" display="《清藏》研究"/>
+    <hyperlink ref="G181" r:id="rId92" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G184" r:id="rId93" display="https://edu.sina.com.cn/wander/2000-09-25/12790.shtml"/>
+    <hyperlink ref="G190" r:id="rId94" display="https://fo.ifeng.com/c/8OJFatCTn2p"/>
+    <hyperlink ref="F192" r:id="rId95" display="中新网北京3月21日电 (记者 应妮) "/>
+    <hyperlink ref="G192" r:id="rId96" display="https://www.chinanews.com/cul/2023/03-21/9975999.shtml"/>
+    <hyperlink ref="G194" r:id="rId97" display="http://www.gxwkzx.gxnu.edu.cn/2023/0610/c12765a301664/page.htm"/>
+    <hyperlink ref="G198" r:id="rId98" display="https://discovery.cctv.com/20070619/107154.shtml"/>
+    <hyperlink ref="G201" r:id="rId99" display="https://book.kongfz.com/102740/682706591"/>
+    <hyperlink ref="C208" r:id="rId100" location="4" display="https://opac.ryukoku.ac.jp/iwjs0005opc/bdyview.do?bodyid=BD00000117&amp;elmid=Body&amp;fname=r-rn_471_006.pdf&amp;loginflg=on&amp;once=true#4"/>
+    <hyperlink ref="B215" r:id="rId101" display="《清藏》研究"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -87110,7 +87177,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8031</v>
+        <v>8039</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -87121,7 +87188,7 @@
         <v>6766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8032</v>
+        <v>8040</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -87132,7 +87199,7 @@
         <v>7140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8033</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -87143,7 +87210,7 @@
         <v>7442</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8034</v>
+        <v>8042</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -87154,7 +87221,7 @@
         <v>7181</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8035</v>
+        <v>8043</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -87165,55 +87232,55 @@
         <v>7329</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8036</v>
+        <v>8044</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>8037</v>
+        <v>8045</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8038</v>
+        <v>8046</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>8039</v>
+        <v>8047</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8040</v>
+        <v>8048</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>8041</v>
+        <v>8049</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8042</v>
+        <v>8050</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>8043</v>
+        <v>8051</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8044</v>
+        <v>8052</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>8045</v>
+        <v>8053</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8046</v>
+        <v>8054</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>8047</v>
+        <v>8055</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>8048</v>
+        <v>8056</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -87228,45 +87295,45 @@
     <row r="22" customFormat="false" ht="12.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>7975</v>
+        <v>7980</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>8049</v>
+        <v>8057</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>8050</v>
+        <v>8058</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>8051</v>
+        <v>8059</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>8052</v>
+        <v>8060</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>8053</v>
+        <v>8061</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>8054</v>
+        <v>8062</v>
       </c>
       <c r="E23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>8055</v>
+        <v>8063</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>8056</v>
+        <v>8064</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="28" t="s">
         <v>7616</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>8057</v>
+        <v>8065</v>
       </c>
     </row>
   </sheetData>
@@ -87299,83 +87366,83 @@
   <sheetData>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="72" t="s">
-        <v>8058</v>
+        <v>8066</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="72" t="s">
-        <v>8059</v>
+        <v>8067</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="72" t="s">
-        <v>8060</v>
+        <v>8068</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="72" t="s">
-        <v>8061</v>
+        <v>8069</v>
       </c>
       <c r="B12" s="75" t="n">
         <v>45735</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8062</v>
+        <v>8070</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8063</v>
+        <v>8071</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="72" t="s">
-        <v>8064</v>
+        <v>8072</v>
       </c>
       <c r="B13" s="75" t="n">
         <v>45970</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8065</v>
+        <v>8073</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8066</v>
+        <v>8074</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="72" t="s">
-        <v>8067</v>
+        <v>8075</v>
       </c>
       <c r="B14" s="75" t="n">
         <v>45995</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8068</v>
+        <v>8076</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8069</v>
+        <v>8077</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="72" t="s">
-        <v>8070</v>
+        <v>8078</v>
       </c>
       <c r="B15" s="75" t="n">
         <v>46036</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8071</v>
+        <v>8079</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8072</v>
+        <v>8080</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>8073</v>
+        <v>8081</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>8074</v>
+        <v>8082</v>
       </c>
     </row>
   </sheetData>
